--- a/data.xlsx
+++ b/data.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView windowWidth="19200" windowHeight="6910"/>
   </bookViews>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1704" uniqueCount="861">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1704" uniqueCount="860">
   <si>
     <t>SHOP_CODE</t>
   </si>
@@ -2315,9 +2315,6 @@
   </si>
   <si>
     <t>SGSAFA4S25C000885</t>
-  </si>
-  <si>
-    <t>CR RECEIVED TO SLMO</t>
   </si>
   <si>
     <t>BCT-H18802</t>
@@ -2607,10 +2604,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -2630,6 +2627,14 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="18"/>
       <color theme="3"/>
       <name val="Calibri"/>
@@ -2638,7 +2643,38 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2651,6 +2687,30 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -2659,15 +2719,7 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -2697,62 +2749,8 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2765,9 +2763,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2788,7 +2785,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2800,19 +2809,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2824,13 +2887,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2842,55 +2935,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2902,67 +2953,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2997,11 +2994,70 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3035,77 +3091,18 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3117,130 +3114,130 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="26" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -4061,7 +4058,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:Z129"/>
   <sheetFormatPr defaultColWidth="8.89090909090909" defaultRowHeight="14.5"/>
   <cols>
@@ -5736,7 +5733,7 @@
         <v>36</v>
       </c>
       <c r="Y29" s="3" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="Z29" s="9"/>
     </row>
@@ -6250,7 +6247,7 @@
         <v>36</v>
       </c>
       <c r="Y38" s="3" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="Z38" s="9"/>
     </row>
@@ -6696,7 +6693,7 @@
         <v>36</v>
       </c>
       <c r="Y46" s="3" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="Z46" s="9"/>
     </row>
@@ -6748,7 +6745,7 @@
         <v>36</v>
       </c>
       <c r="Y47" s="3" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="Z47" s="9"/>
     </row>
@@ -10430,7 +10427,7 @@
         <v>36</v>
       </c>
       <c r="Y113" s="9" t="s">
-        <v>766</v>
+        <v>47</v>
       </c>
       <c r="Z113" s="9"/>
     </row>
@@ -10445,19 +10442,19 @@
         <v>550</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="F114" s="8">
         <v>46265</v>
       </c>
       <c r="G114" s="3" t="s">
+        <v>767</v>
+      </c>
+      <c r="H114" s="3" t="s">
         <v>768</v>
-      </c>
-      <c r="H114" s="3" t="s">
-        <v>769</v>
       </c>
       <c r="I114" s="3" t="s">
         <v>32</v>
@@ -10467,7 +10464,7 @@
       <c r="L114" s="9"/>
       <c r="M114" s="3"/>
       <c r="N114" s="3" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="O114" s="3"/>
       <c r="P114" s="3"/>
@@ -10484,7 +10481,7 @@
         <v>36</v>
       </c>
       <c r="Y114" s="9" t="s">
-        <v>211</v>
+        <v>47</v>
       </c>
       <c r="Z114" s="9"/>
     </row>
@@ -10499,19 +10496,19 @@
         <v>189</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="F115" s="8">
         <v>46249</v>
       </c>
       <c r="G115" s="3" t="s">
+        <v>771</v>
+      </c>
+      <c r="H115" s="3" t="s">
         <v>772</v>
-      </c>
-      <c r="H115" s="3" t="s">
-        <v>773</v>
       </c>
       <c r="I115" s="3" t="s">
         <v>32</v>
@@ -10521,7 +10518,7 @@
       <c r="L115" s="9"/>
       <c r="M115" s="3"/>
       <c r="N115" s="3" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="O115" s="3"/>
       <c r="P115" s="3"/>
@@ -10553,19 +10550,19 @@
         <v>142</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="F116" s="8">
         <v>46252</v>
       </c>
       <c r="G116" s="3" t="s">
+        <v>775</v>
+      </c>
+      <c r="H116" s="3" t="s">
         <v>776</v>
-      </c>
-      <c r="H116" s="3" t="s">
-        <v>777</v>
       </c>
       <c r="I116" s="3" t="s">
         <v>540</v>
@@ -10575,7 +10572,7 @@
       <c r="L116" s="9"/>
       <c r="M116" s="3"/>
       <c r="N116" s="3" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="O116" s="3"/>
       <c r="P116" s="3"/>
@@ -10607,19 +10604,19 @@
         <v>722</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="F117" s="8">
         <v>46263</v>
       </c>
       <c r="G117" s="3" t="s">
+        <v>779</v>
+      </c>
+      <c r="H117" s="3" t="s">
         <v>780</v>
-      </c>
-      <c r="H117" s="3" t="s">
-        <v>781</v>
       </c>
       <c r="I117" s="3" t="s">
         <v>32</v>
@@ -10629,7 +10626,7 @@
       <c r="L117" s="9"/>
       <c r="M117" s="3"/>
       <c r="N117" s="3" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="O117" s="3"/>
       <c r="P117" s="3"/>
@@ -10652,28 +10649,28 @@
     </row>
     <row r="118" spans="1:26">
       <c r="A118" s="3" t="s">
+        <v>782</v>
+      </c>
+      <c r="B118" s="3" t="s">
         <v>783</v>
       </c>
-      <c r="B118" s="3" t="s">
+      <c r="C118" s="3" t="s">
         <v>784</v>
       </c>
-      <c r="C118" s="3" t="s">
+      <c r="D118" s="3" t="s">
         <v>785</v>
       </c>
-      <c r="D118" s="3" t="s">
-        <v>786</v>
-      </c>
       <c r="E118" s="3" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="F118" s="8">
         <v>46265</v>
       </c>
       <c r="G118" s="3" t="s">
+        <v>786</v>
+      </c>
+      <c r="H118" s="3" t="s">
         <v>787</v>
-      </c>
-      <c r="H118" s="3" t="s">
-        <v>788</v>
       </c>
       <c r="I118" s="3" t="s">
         <v>32</v>
@@ -10683,7 +10680,7 @@
       <c r="L118" s="9"/>
       <c r="M118" s="3"/>
       <c r="N118" s="3" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="O118" s="3"/>
       <c r="P118" s="3"/>
@@ -10706,28 +10703,28 @@
     </row>
     <row r="119" spans="1:26">
       <c r="A119" s="3" t="s">
+        <v>789</v>
+      </c>
+      <c r="B119" s="3" t="s">
         <v>790</v>
       </c>
-      <c r="B119" s="3" t="s">
+      <c r="C119" s="3" t="s">
         <v>791</v>
       </c>
-      <c r="C119" s="3" t="s">
+      <c r="D119" s="3" t="s">
         <v>792</v>
       </c>
-      <c r="D119" s="3" t="s">
-        <v>793</v>
-      </c>
       <c r="E119" s="3" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="F119" s="8">
         <v>46265</v>
       </c>
       <c r="G119" s="3" t="s">
+        <v>793</v>
+      </c>
+      <c r="H119" s="3" t="s">
         <v>794</v>
-      </c>
-      <c r="H119" s="3" t="s">
-        <v>795</v>
       </c>
       <c r="I119" s="3" t="s">
         <v>540</v>
@@ -10737,7 +10734,7 @@
       <c r="L119" s="9"/>
       <c r="M119" s="3"/>
       <c r="N119" s="3" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="O119" s="3"/>
       <c r="P119" s="3"/>
@@ -10754,34 +10751,34 @@
         <v>36</v>
       </c>
       <c r="Y119" s="9" t="s">
-        <v>243</v>
+        <v>211</v>
       </c>
       <c r="Z119" s="9"/>
     </row>
     <row r="120" spans="1:26">
       <c r="A120" s="3" t="s">
+        <v>796</v>
+      </c>
+      <c r="B120" s="3" t="s">
         <v>797</v>
       </c>
-      <c r="B120" s="3" t="s">
+      <c r="C120" s="3" t="s">
         <v>798</v>
       </c>
-      <c r="C120" s="3" t="s">
+      <c r="D120" s="3" t="s">
         <v>799</v>
       </c>
-      <c r="D120" s="3" t="s">
-        <v>800</v>
-      </c>
       <c r="E120" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="F120" s="8">
         <v>46251</v>
       </c>
       <c r="G120" s="3" t="s">
+        <v>800</v>
+      </c>
+      <c r="H120" s="3" t="s">
         <v>801</v>
-      </c>
-      <c r="H120" s="3" t="s">
-        <v>802</v>
       </c>
       <c r="I120" s="3" t="s">
         <v>32</v>
@@ -10791,7 +10788,7 @@
       <c r="L120" s="9"/>
       <c r="M120" s="3"/>
       <c r="N120" s="3" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="O120" s="3"/>
       <c r="P120" s="3"/>
@@ -10814,28 +10811,28 @@
     </row>
     <row r="121" spans="1:26">
       <c r="A121" s="3" t="s">
+        <v>803</v>
+      </c>
+      <c r="B121" s="3" t="s">
         <v>804</v>
       </c>
-      <c r="B121" s="3" t="s">
+      <c r="C121" s="3" t="s">
         <v>805</v>
       </c>
-      <c r="C121" s="3" t="s">
+      <c r="D121" s="3" t="s">
         <v>806</v>
       </c>
-      <c r="D121" s="3" t="s">
-        <v>807</v>
-      </c>
       <c r="E121" s="3" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="F121" s="8">
         <v>46258</v>
       </c>
       <c r="G121" s="3" t="s">
+        <v>807</v>
+      </c>
+      <c r="H121" s="3" t="s">
         <v>808</v>
-      </c>
-      <c r="H121" s="3" t="s">
-        <v>809</v>
       </c>
       <c r="I121" s="3" t="s">
         <v>32</v>
@@ -10845,7 +10842,7 @@
       <c r="L121" s="9"/>
       <c r="M121" s="3"/>
       <c r="N121" s="3" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="O121" s="3"/>
       <c r="P121" s="3"/>
@@ -10862,34 +10859,34 @@
         <v>36</v>
       </c>
       <c r="Y121" s="9" t="s">
-        <v>243</v>
+        <v>211</v>
       </c>
       <c r="Z121" s="9"/>
     </row>
     <row r="122" spans="1:26">
       <c r="A122" s="3" t="s">
+        <v>810</v>
+      </c>
+      <c r="B122" s="3" t="s">
         <v>811</v>
       </c>
-      <c r="B122" s="3" t="s">
+      <c r="C122" s="3" t="s">
         <v>812</v>
       </c>
-      <c r="C122" s="3" t="s">
+      <c r="D122" s="3" t="s">
         <v>813</v>
       </c>
-      <c r="D122" s="3" t="s">
-        <v>814</v>
-      </c>
       <c r="E122" s="3" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="F122" s="8">
         <v>46265</v>
       </c>
       <c r="G122" s="3" t="s">
+        <v>814</v>
+      </c>
+      <c r="H122" s="3" t="s">
         <v>815</v>
-      </c>
-      <c r="H122" s="3" t="s">
-        <v>816</v>
       </c>
       <c r="I122" s="3" t="s">
         <v>32</v>
@@ -10899,7 +10896,7 @@
       <c r="L122" s="9"/>
       <c r="M122" s="3"/>
       <c r="N122" s="3" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="O122" s="3"/>
       <c r="P122" s="3"/>
@@ -10922,28 +10919,28 @@
     </row>
     <row r="123" spans="1:26">
       <c r="A123" s="3" t="s">
+        <v>817</v>
+      </c>
+      <c r="B123" s="3" t="s">
         <v>818</v>
       </c>
-      <c r="B123" s="3" t="s">
+      <c r="C123" s="3" t="s">
         <v>819</v>
       </c>
-      <c r="C123" s="3" t="s">
+      <c r="D123" s="3" t="s">
         <v>820</v>
       </c>
-      <c r="D123" s="3" t="s">
-        <v>821</v>
-      </c>
       <c r="E123" s="3" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="F123" s="8">
         <v>46259</v>
       </c>
       <c r="G123" s="3" t="s">
+        <v>821</v>
+      </c>
+      <c r="H123" s="3" t="s">
         <v>822</v>
-      </c>
-      <c r="H123" s="3" t="s">
-        <v>823</v>
       </c>
       <c r="I123" s="3" t="s">
         <v>32</v>
@@ -10953,7 +10950,7 @@
       <c r="L123" s="9"/>
       <c r="M123" s="3"/>
       <c r="N123" s="3" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="O123" s="3"/>
       <c r="P123" s="3"/>
@@ -10976,28 +10973,28 @@
     </row>
     <row r="124" spans="1:26">
       <c r="A124" s="3" t="s">
+        <v>824</v>
+      </c>
+      <c r="B124" s="3" t="s">
         <v>825</v>
       </c>
-      <c r="B124" s="3" t="s">
+      <c r="C124" s="3" t="s">
         <v>826</v>
       </c>
-      <c r="C124" s="3" t="s">
+      <c r="D124" s="3" t="s">
         <v>827</v>
       </c>
-      <c r="D124" s="3" t="s">
-        <v>828</v>
-      </c>
       <c r="E124" s="3" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="F124" s="8">
         <v>46265</v>
       </c>
       <c r="G124" s="3" t="s">
+        <v>828</v>
+      </c>
+      <c r="H124" s="3" t="s">
         <v>829</v>
-      </c>
-      <c r="H124" s="3" t="s">
-        <v>830</v>
       </c>
       <c r="I124" s="3" t="s">
         <v>32</v>
@@ -11007,7 +11004,7 @@
       <c r="L124" s="9"/>
       <c r="M124" s="3"/>
       <c r="N124" s="3" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="O124" s="3"/>
       <c r="P124" s="3"/>
@@ -11039,19 +11036,19 @@
         <v>40</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F125" s="8">
         <v>46255</v>
       </c>
       <c r="G125" s="3" t="s">
+        <v>832</v>
+      </c>
+      <c r="H125" s="3" t="s">
         <v>833</v>
-      </c>
-      <c r="H125" s="3" t="s">
-        <v>834</v>
       </c>
       <c r="I125" s="3" t="s">
         <v>32</v>
@@ -11061,7 +11058,7 @@
       <c r="L125" s="9"/>
       <c r="M125" s="3"/>
       <c r="N125" s="3" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="O125" s="3"/>
       <c r="P125" s="3"/>
@@ -11078,7 +11075,7 @@
         <v>36</v>
       </c>
       <c r="Y125" s="9" t="s">
-        <v>243</v>
+        <v>211</v>
       </c>
       <c r="Z125" s="9"/>
     </row>
@@ -11093,19 +11090,19 @@
         <v>215</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="F126" s="8">
         <v>46251</v>
       </c>
       <c r="G126" s="3" t="s">
+        <v>836</v>
+      </c>
+      <c r="H126" s="3" t="s">
         <v>837</v>
-      </c>
-      <c r="H126" s="3" t="s">
-        <v>838</v>
       </c>
       <c r="I126" s="3" t="s">
         <v>32</v>
@@ -11115,7 +11112,7 @@
       <c r="L126" s="9"/>
       <c r="M126" s="3"/>
       <c r="N126" s="3" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="O126" s="3"/>
       <c r="P126" s="3"/>
@@ -11138,28 +11135,28 @@
     </row>
     <row r="127" spans="1:26">
       <c r="A127" s="3" t="s">
+        <v>839</v>
+      </c>
+      <c r="B127" s="3" t="s">
         <v>840</v>
       </c>
-      <c r="B127" s="3" t="s">
+      <c r="C127" s="3" t="s">
         <v>841</v>
       </c>
-      <c r="C127" s="3" t="s">
+      <c r="D127" s="3" t="s">
         <v>842</v>
       </c>
-      <c r="D127" s="3" t="s">
-        <v>843</v>
-      </c>
       <c r="E127" s="3" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="F127" s="8">
         <v>46265</v>
       </c>
       <c r="G127" s="3" t="s">
+        <v>843</v>
+      </c>
+      <c r="H127" s="3" t="s">
         <v>844</v>
-      </c>
-      <c r="H127" s="3" t="s">
-        <v>845</v>
       </c>
       <c r="I127" s="3" t="s">
         <v>32</v>
@@ -11169,7 +11166,7 @@
       <c r="L127" s="9"/>
       <c r="M127" s="3"/>
       <c r="N127" s="3" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="O127" s="3"/>
       <c r="P127" s="3"/>
@@ -11192,28 +11189,28 @@
     </row>
     <row r="128" spans="1:26">
       <c r="A128" s="3" t="s">
+        <v>846</v>
+      </c>
+      <c r="B128" s="3" t="s">
         <v>847</v>
       </c>
-      <c r="B128" s="3" t="s">
+      <c r="C128" s="3" t="s">
         <v>848</v>
       </c>
-      <c r="C128" s="3" t="s">
+      <c r="D128" s="3" t="s">
         <v>849</v>
       </c>
-      <c r="D128" s="3" t="s">
-        <v>850</v>
-      </c>
       <c r="E128" s="3" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="F128" s="8">
         <v>46262</v>
       </c>
       <c r="G128" s="3" t="s">
+        <v>850</v>
+      </c>
+      <c r="H128" s="3" t="s">
         <v>851</v>
-      </c>
-      <c r="H128" s="3" t="s">
-        <v>852</v>
       </c>
       <c r="I128" s="3" t="s">
         <v>32</v>
@@ -11223,7 +11220,7 @@
       <c r="L128" s="9"/>
       <c r="M128" s="3"/>
       <c r="N128" s="3" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="O128" s="3"/>
       <c r="P128" s="3"/>
@@ -11240,34 +11237,34 @@
         <v>36</v>
       </c>
       <c r="Y128" s="9" t="s">
-        <v>211</v>
+        <v>47</v>
       </c>
       <c r="Z128" s="9"/>
     </row>
     <row r="129" spans="1:26">
       <c r="A129" s="3" t="s">
+        <v>853</v>
+      </c>
+      <c r="B129" s="3" t="s">
         <v>854</v>
       </c>
-      <c r="B129" s="3" t="s">
+      <c r="C129" s="3" t="s">
         <v>855</v>
       </c>
-      <c r="C129" s="3" t="s">
+      <c r="D129" s="3" t="s">
         <v>856</v>
       </c>
-      <c r="D129" s="3" t="s">
-        <v>857</v>
-      </c>
       <c r="E129" s="3" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="F129" s="8">
         <v>46259</v>
       </c>
       <c r="G129" s="3" t="s">
+        <v>857</v>
+      </c>
+      <c r="H129" s="3" t="s">
         <v>858</v>
-      </c>
-      <c r="H129" s="3" t="s">
-        <v>859</v>
       </c>
       <c r="I129" s="3" t="s">
         <v>32</v>
@@ -11277,7 +11274,7 @@
       <c r="L129" s="9"/>
       <c r="M129" s="3"/>
       <c r="N129" s="3" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="O129" s="3"/>
       <c r="P129" s="3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1704" uniqueCount="860">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1718" uniqueCount="860">
   <si>
     <t>SHOP_CODE</t>
   </si>
@@ -130,7 +130,7 @@
     <t>Active</t>
   </si>
   <si>
-    <t>RETURNED FOR CORRECTIONS</t>
+    <t>CR RETURNED TO RMV FOR CORRECTIONS</t>
   </si>
   <si>
     <t>BGY01</t>
@@ -235,6 +235,9 @@
     <t>SALE RETURN</t>
   </si>
   <si>
+    <t>ACCOUNT CLOSED</t>
+  </si>
+  <si>
     <t>BGX-H23026</t>
   </si>
   <si>
@@ -652,10 +655,7 @@
     <t>Close</t>
   </si>
   <si>
-    <t>CR NOT RECEIVED</t>
-  </si>
-  <si>
-    <t>ACCOUNT CLOSED</t>
+    <t>CR NOT RECEIVE FROM RMV</t>
   </si>
   <si>
     <t>BLE01</t>
@@ -748,7 +748,7 @@
     <t>Document sent but book not received</t>
   </si>
   <si>
-    <t>PENDING DOCUMENTS</t>
+    <t>DOCUMENTS TO BE RECEIVE</t>
   </si>
   <si>
     <t>BOC01</t>
@@ -1618,7 +1618,7 @@
     <t>SGSAFA4S25A000043</t>
   </si>
   <si>
-    <t>PENDING DOCUMENTS FROM CUSTOMER END</t>
+    <t>DOCUMENTS TO BE RECEIVE FROM CUSTOMER END</t>
   </si>
   <si>
     <t>BDX01</t>
@@ -4443,7 +4443,9 @@
       <c r="Y6" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="Z6" s="9"/>
+      <c r="Z6" s="9" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="7" spans="1:26">
       <c r="A7" s="3" t="s">
@@ -4456,19 +4458,19 @@
         <v>59</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>66</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>69</v>
@@ -4478,7 +4480,7 @@
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
       <c r="N7" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="O7" s="3"/>
       <c r="P7" s="3"/>
@@ -4495,7 +4497,9 @@
       <c r="Y7" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="Z7" s="9"/>
+      <c r="Z7" s="9" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="8" spans="1:26">
       <c r="A8" s="3" t="s">
@@ -4508,19 +4512,19 @@
         <v>59</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>66</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>69</v>
@@ -4530,7 +4534,7 @@
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
       <c r="N8" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O8" s="3"/>
       <c r="P8" s="3"/>
@@ -4547,7 +4551,9 @@
       <c r="Y8" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="Z8" s="9"/>
+      <c r="Z8" s="9" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="9" spans="1:26">
       <c r="A9" s="3" t="s">
@@ -4560,19 +4566,19 @@
         <v>59</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>66</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>32</v>
@@ -4582,7 +4588,7 @@
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
       <c r="N9" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O9" s="3"/>
       <c r="P9" s="3"/>
@@ -4599,32 +4605,34 @@
       <c r="Y9" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="Z9" s="9"/>
+      <c r="Z9" s="9" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="10" spans="1:26">
       <c r="A10" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F10" s="4">
         <v>46112</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>32</v>
@@ -4634,7 +4642,7 @@
       <c r="L10" s="7"/>
       <c r="M10" s="3"/>
       <c r="N10" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="O10" s="3"/>
       <c r="P10" s="3"/>
@@ -4642,14 +4650,14 @@
       <c r="R10" s="3"/>
       <c r="S10" s="3"/>
       <c r="T10" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="U10" s="3"/>
       <c r="V10" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="W10" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="X10" s="3" t="s">
         <v>36</v>
@@ -4657,46 +4665,48 @@
       <c r="Y10" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="Z10" s="3"/>
+      <c r="Z10" s="3" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="11" spans="1:26">
       <c r="A11" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F11" s="4">
         <v>46106</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>32</v>
       </c>
       <c r="J11" s="5"/>
       <c r="K11" s="7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L11" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M11" s="3"/>
       <c r="N11" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
@@ -4706,43 +4716,43 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="W11" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="X11" s="3" t="s">
         <v>36</v>
       </c>
       <c r="Y11" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Z11" s="9"/>
     </row>
     <row r="12" spans="1:26">
       <c r="A12" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F12" s="4">
         <v>46097</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>69</v>
@@ -4752,7 +4762,7 @@
       <c r="L12" s="7"/>
       <c r="M12" s="3"/>
       <c r="N12" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
@@ -4760,57 +4770,57 @@
       <c r="R12" s="3"/>
       <c r="S12" s="3"/>
       <c r="T12" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="U12" s="3"/>
       <c r="V12" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="W12" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="X12" s="3" t="s">
         <v>36</v>
       </c>
       <c r="Y12" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Z12" s="9"/>
     </row>
     <row r="13" spans="1:26">
       <c r="A13" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F13" s="4">
         <v>46173</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J13" s="5"/>
       <c r="K13" s="7"/>
       <c r="L13" s="7"/>
       <c r="M13" s="3"/>
       <c r="N13" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O13" s="3"/>
       <c r="P13" s="3"/>
@@ -4818,14 +4828,14 @@
       <c r="R13" s="3"/>
       <c r="S13" s="3"/>
       <c r="T13" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="U13" s="3"/>
       <c r="V13" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="W13" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="X13" s="3" t="s">
         <v>36</v>
@@ -4837,28 +4847,28 @@
     </row>
     <row r="14" spans="1:26">
       <c r="A14" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F14" s="4">
         <v>46173</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>32</v>
@@ -4868,7 +4878,7 @@
       <c r="L14" s="7"/>
       <c r="M14" s="3"/>
       <c r="N14" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O14" s="3"/>
       <c r="P14" s="3"/>
@@ -4876,57 +4886,57 @@
       <c r="R14" s="3"/>
       <c r="S14" s="3"/>
       <c r="T14" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="U14" s="3"/>
       <c r="V14" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="W14" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>36</v>
       </c>
       <c r="Y14" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Z14" s="9"/>
     </row>
     <row r="15" spans="1:26">
       <c r="A15" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F15" s="4">
         <v>46173</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J15" s="5"/>
       <c r="K15" s="7"/>
       <c r="L15" s="7"/>
       <c r="M15" s="3"/>
       <c r="N15" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O15" s="3"/>
       <c r="P15" s="3"/>
@@ -4934,14 +4944,14 @@
       <c r="R15" s="3"/>
       <c r="S15" s="3"/>
       <c r="T15" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="U15" s="3"/>
       <c r="V15" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="W15" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="X15" s="3" t="s">
         <v>36</v>
@@ -4953,28 +4963,28 @@
     </row>
     <row r="16" spans="1:26">
       <c r="A16" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F16" s="4">
         <v>46177</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>32</v>
@@ -4984,7 +4994,7 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
@@ -4994,10 +5004,10 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="W16" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="X16" s="3" t="s">
         <v>36</v>
@@ -5009,28 +5019,28 @@
     </row>
     <row r="17" spans="1:26">
       <c r="A17" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>61</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>32</v>
@@ -5040,7 +5050,7 @@
       <c r="L17" s="3"/>
       <c r="M17" s="3"/>
       <c r="N17" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O17" s="3"/>
       <c r="P17" s="3"/>
@@ -5061,28 +5071,28 @@
     </row>
     <row r="18" spans="1:26">
       <c r="A18" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F18" s="6">
         <v>46149</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>32</v>
@@ -5092,7 +5102,7 @@
       <c r="L18" s="3"/>
       <c r="M18" s="3"/>
       <c r="N18" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O18" s="3"/>
       <c r="P18" s="3"/>
@@ -5113,40 +5123,40 @@
     </row>
     <row r="19" spans="1:26">
       <c r="A19" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F19" s="4">
         <v>46101</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J19" s="5"/>
       <c r="K19" s="7" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L19" s="7"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
@@ -5156,10 +5166,10 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="W19" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="X19" s="3" t="s">
         <v>36</v>
@@ -5171,28 +5181,28 @@
     </row>
     <row r="20" spans="1:26">
       <c r="A20" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F20" s="4">
         <v>46110</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>32</v>
@@ -5202,7 +5212,7 @@
       <c r="L20" s="7"/>
       <c r="M20" s="3"/>
       <c r="N20" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O20" s="3"/>
       <c r="P20" s="3"/>
@@ -5210,14 +5220,14 @@
       <c r="R20" s="3"/>
       <c r="S20" s="3"/>
       <c r="T20" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="U20" s="3"/>
       <c r="V20" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="W20" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="X20" s="3" t="s">
         <v>36</v>
@@ -5229,42 +5239,42 @@
     </row>
     <row r="21" spans="1:26">
       <c r="A21" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F21" s="4">
         <v>46095</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>32</v>
       </c>
       <c r="J21" s="5"/>
       <c r="K21" s="7" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L21" s="7" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M21" s="3"/>
       <c r="N21" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O21" s="3"/>
       <c r="P21" s="3"/>
@@ -5274,10 +5284,10 @@
       <c r="T21" s="3"/>
       <c r="U21" s="3"/>
       <c r="V21" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="W21" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="X21" s="3" t="s">
         <v>36</v>
@@ -5289,28 +5299,28 @@
     </row>
     <row r="22" spans="1:26">
       <c r="A22" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F22" s="4">
         <v>46190</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>69</v>
@@ -5320,7 +5330,7 @@
       <c r="L22" s="3"/>
       <c r="M22" s="3"/>
       <c r="N22" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O22" s="3"/>
       <c r="P22" s="3"/>
@@ -5330,10 +5340,10 @@
       <c r="T22" s="3"/>
       <c r="U22" s="3"/>
       <c r="V22" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="W22" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="X22" s="3" t="s">
         <v>36</v>
@@ -5345,40 +5355,40 @@
     </row>
     <row r="23" spans="1:26">
       <c r="A23" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F23" s="4">
         <v>46099</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I23" s="3" t="s">
         <v>32</v>
       </c>
       <c r="J23" s="5"/>
       <c r="K23" s="7" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L23" s="7"/>
       <c r="M23" s="3"/>
       <c r="N23" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="O23" s="3"/>
       <c r="P23" s="3"/>
@@ -5388,10 +5398,10 @@
       <c r="T23" s="3"/>
       <c r="U23" s="3"/>
       <c r="V23" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="W23" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="X23" s="3" t="s">
         <v>36</v>
@@ -5403,28 +5413,28 @@
     </row>
     <row r="24" spans="1:26">
       <c r="A24" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F24" s="5" t="s">
         <v>66</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>32</v>
@@ -5434,7 +5444,7 @@
       <c r="L24" s="3"/>
       <c r="M24" s="3"/>
       <c r="N24" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O24" s="3"/>
       <c r="P24" s="3"/>
@@ -5455,28 +5465,28 @@
     </row>
     <row r="25" spans="1:26">
       <c r="A25" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>32</v>
@@ -5486,7 +5496,7 @@
       <c r="L25" s="3"/>
       <c r="M25" s="3"/>
       <c r="N25" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O25" s="3"/>
       <c r="P25" s="3"/>
@@ -5507,28 +5517,28 @@
     </row>
     <row r="26" spans="1:26">
       <c r="A26" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F26" s="4">
         <v>46203</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>32</v>
@@ -5538,7 +5548,7 @@
       <c r="L26" s="3"/>
       <c r="M26" s="3"/>
       <c r="N26" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="O26" s="3"/>
       <c r="P26" s="3"/>
@@ -5548,10 +5558,10 @@
       <c r="T26" s="3"/>
       <c r="U26" s="3"/>
       <c r="V26" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="W26" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="X26" s="3" t="s">
         <v>36</v>
@@ -5563,40 +5573,40 @@
     </row>
     <row r="27" spans="1:26">
       <c r="A27" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F27" s="4">
         <v>46107</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>32</v>
       </c>
       <c r="J27" s="5"/>
       <c r="K27" s="7" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L27" s="7"/>
       <c r="M27" s="3"/>
       <c r="N27" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="O27" s="3"/>
       <c r="P27" s="3"/>
@@ -5606,19 +5616,19 @@
       <c r="T27" s="3"/>
       <c r="U27" s="3"/>
       <c r="V27" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="W27" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="X27" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Y27" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Z27" s="9" t="s">
-        <v>212</v>
+        <v>72</v>
       </c>
     </row>
     <row r="28" spans="1:26">
@@ -5669,13 +5679,13 @@
         <v>219</v>
       </c>
       <c r="W28" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="X28" s="3" t="s">
         <v>36</v>
       </c>
       <c r="Y28" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Z28" s="9"/>
     </row>
@@ -5783,7 +5793,7 @@
         <v>232</v>
       </c>
       <c r="W30" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="X30" s="3" t="s">
         <v>36</v>
@@ -5845,7 +5855,7 @@
         <v>240</v>
       </c>
       <c r="W31" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="X31" s="3" t="s">
         <v>36</v>
@@ -5965,7 +5975,7 @@
         <v>256</v>
       </c>
       <c r="W33" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="X33" s="3" t="s">
         <v>36</v>
@@ -6020,13 +6030,13 @@
       <c r="V34" s="3"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Y34" s="3" t="s">
         <v>243</v>
       </c>
       <c r="Z34" s="9" t="s">
-        <v>212</v>
+        <v>72</v>
       </c>
     </row>
     <row r="35" spans="1:26">
@@ -6079,7 +6089,7 @@
         <v>273</v>
       </c>
       <c r="W35" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="X35" s="3" t="s">
         <v>36</v>
@@ -6299,7 +6309,7 @@
         <v>298</v>
       </c>
       <c r="W39" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="X39" s="3" t="s">
         <v>36</v>
@@ -6357,16 +6367,16 @@
         <v>303</v>
       </c>
       <c r="W40" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="X40" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Y40" s="3" t="s">
         <v>243</v>
       </c>
       <c r="Z40" s="9" t="s">
-        <v>212</v>
+        <v>72</v>
       </c>
     </row>
     <row r="41" spans="1:26">
@@ -6518,13 +6528,13 @@
       <c r="V43" s="3"/>
       <c r="W43" s="3"/>
       <c r="X43" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Y43" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Z43" s="9" t="s">
-        <v>212</v>
+        <v>72</v>
       </c>
     </row>
     <row r="44" spans="1:26">
@@ -6631,13 +6641,13 @@
         <v>338</v>
       </c>
       <c r="W45" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="X45" s="3" t="s">
         <v>36</v>
       </c>
       <c r="Y45" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Z45" s="9"/>
     </row>
@@ -6799,7 +6809,7 @@
         <v>36</v>
       </c>
       <c r="Y48" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Z48" s="9"/>
     </row>
@@ -6961,7 +6971,7 @@
         <v>383</v>
       </c>
       <c r="W51" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="X51" s="3" t="s">
         <v>36</v>
@@ -7077,7 +7087,7 @@
         <v>36</v>
       </c>
       <c r="Y53" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Z53" s="9"/>
     </row>
@@ -7429,7 +7439,7 @@
         <v>433</v>
       </c>
       <c r="W59" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="X59" s="3" t="s">
         <v>36</v>
@@ -7609,7 +7619,7 @@
         <v>447</v>
       </c>
       <c r="W62" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="X62" s="3" t="s">
         <v>36</v>
@@ -7771,7 +7781,7 @@
         <v>465</v>
       </c>
       <c r="W65" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="X65" s="3" t="s">
         <v>36</v>
@@ -7829,7 +7839,7 @@
         <v>470</v>
       </c>
       <c r="W66" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="X66" s="3" t="s">
         <v>36</v>
@@ -7941,16 +7951,16 @@
         <v>481</v>
       </c>
       <c r="W68" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="X68" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Y68" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Z68" s="9" t="s">
-        <v>212</v>
+        <v>72</v>
       </c>
     </row>
     <row r="69" spans="1:26">
@@ -8001,7 +8011,7 @@
         <v>490</v>
       </c>
       <c r="W69" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="X69" s="3" t="s">
         <v>36</v>
@@ -8061,7 +8071,7 @@
         <v>498</v>
       </c>
       <c r="W70" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="X70" s="3" t="s">
         <v>36</v>
@@ -8181,13 +8191,13 @@
         <v>511</v>
       </c>
       <c r="W72" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="X72" s="3" t="s">
         <v>36</v>
       </c>
       <c r="Y72" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Z72" s="9"/>
     </row>
@@ -8297,13 +8307,13 @@
         <v>525</v>
       </c>
       <c r="W74" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="X74" s="3" t="s">
         <v>36</v>
       </c>
       <c r="Y74" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Z74" s="9"/>
     </row>
@@ -8411,7 +8421,9 @@
       <c r="Y76" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="Z76" s="9"/>
+      <c r="Z76" s="9" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="77" spans="1:26">
       <c r="A77" s="3" t="s">
@@ -8463,7 +8475,9 @@
       <c r="Y77" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="Z77" s="9"/>
+      <c r="Z77" s="9" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="78" spans="1:26">
       <c r="A78" s="3" t="s">
@@ -8515,7 +8529,9 @@
       <c r="Y78" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="Z78" s="9"/>
+      <c r="Z78" s="9" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="79" spans="1:26">
       <c r="A79" s="3" t="s">
@@ -8633,7 +8649,7 @@
         <v>562</v>
       </c>
       <c r="W80" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="X80" s="3" t="s">
         <v>36</v>
@@ -8693,7 +8709,7 @@
         <v>571</v>
       </c>
       <c r="W81" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="X81" s="3" t="s">
         <v>36</v>
@@ -8805,7 +8821,9 @@
       <c r="Y83" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="Z83" s="9"/>
+      <c r="Z83" s="9" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="84" spans="1:26">
       <c r="A84" s="3" t="s">
@@ -8857,7 +8875,9 @@
       <c r="Y84" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="Z84" s="9"/>
+      <c r="Z84" s="9" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="85" spans="1:26">
       <c r="A85" s="3" t="s">
@@ -8909,7 +8929,9 @@
       <c r="Y85" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="Z85" s="9"/>
+      <c r="Z85" s="9" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="86" spans="1:26">
       <c r="A86" s="3" t="s">
@@ -8961,7 +8983,9 @@
       <c r="Y86" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="Z86" s="9"/>
+      <c r="Z86" s="9" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="87" spans="1:26">
       <c r="A87" s="3" t="s">
@@ -9013,7 +9037,9 @@
       <c r="Y87" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="Z87" s="9"/>
+      <c r="Z87" s="9" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="88" spans="1:26">
       <c r="A88" s="3" t="s">
@@ -9225,7 +9251,7 @@
         <v>36</v>
       </c>
       <c r="Y91" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Z91" s="9"/>
     </row>
@@ -9277,7 +9303,7 @@
         <v>634</v>
       </c>
       <c r="W92" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="X92" s="3" t="s">
         <v>36</v>
@@ -9451,7 +9477,7 @@
         <v>36</v>
       </c>
       <c r="Y95" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Z95" s="9"/>
     </row>
@@ -9615,7 +9641,7 @@
         <v>677</v>
       </c>
       <c r="W98" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="X98" s="3" t="s">
         <v>36</v>
@@ -9785,13 +9811,13 @@
     </row>
     <row r="102" spans="1:26">
       <c r="A102" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D102" s="3" t="s">
         <v>694</v>
@@ -10487,13 +10513,13 @@
     </row>
     <row r="115" spans="1:26">
       <c r="A115" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D115" s="3" t="s">
         <v>770</v>
@@ -10541,13 +10567,13 @@
     </row>
     <row r="116" spans="1:26">
       <c r="A116" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D116" s="3" t="s">
         <v>774</v>
@@ -10751,7 +10777,7 @@
         <v>36</v>
       </c>
       <c r="Y119" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Z119" s="9"/>
     </row>
@@ -10859,7 +10885,7 @@
         <v>36</v>
       </c>
       <c r="Y121" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Z121" s="9"/>
     </row>
@@ -10913,9 +10939,11 @@
         <v>36</v>
       </c>
       <c r="Y122" s="9" t="s">
-        <v>211</v>
-      </c>
-      <c r="Z122" s="9"/>
+        <v>98</v>
+      </c>
+      <c r="Z122" s="9" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="123" spans="1:26">
       <c r="A123" s="3" t="s">
@@ -11075,7 +11103,7 @@
         <v>36</v>
       </c>
       <c r="Y125" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Z125" s="9"/>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -232,6 +232,9 @@
     <t>LGMMVU1K0T0002510</t>
   </si>
   <si>
+    <t>Close</t>
+  </si>
+  <si>
     <t>SALE RETURN</t>
   </si>
   <si>
@@ -650,9 +653,6 @@
   </si>
   <si>
     <t>SGSAFA4S25A000016</t>
-  </si>
-  <si>
-    <t>Close</t>
   </si>
   <si>
     <t>CR NOT RECEIVE FROM RMV</t>
@@ -4438,13 +4438,13 @@
       <c r="V6" s="3"/>
       <c r="W6" s="3"/>
       <c r="X6" s="3" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="Y6" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z6" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:26">
@@ -4458,19 +4458,19 @@
         <v>59</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>66</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>69</v>
@@ -4480,7 +4480,7 @@
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
       <c r="N7" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="O7" s="3"/>
       <c r="P7" s="3"/>
@@ -4492,13 +4492,13 @@
       <c r="V7" s="3"/>
       <c r="W7" s="3"/>
       <c r="X7" s="3" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="Y7" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z7" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8" spans="1:26">
@@ -4512,19 +4512,19 @@
         <v>59</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>66</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>69</v>
@@ -4534,7 +4534,7 @@
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
       <c r="N8" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O8" s="3"/>
       <c r="P8" s="3"/>
@@ -4546,13 +4546,13 @@
       <c r="V8" s="3"/>
       <c r="W8" s="3"/>
       <c r="X8" s="3" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="Y8" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z8" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:26">
@@ -4566,19 +4566,19 @@
         <v>59</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>66</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>32</v>
@@ -4588,7 +4588,7 @@
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
       <c r="N9" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="O9" s="3"/>
       <c r="P9" s="3"/>
@@ -4600,39 +4600,39 @@
       <c r="V9" s="3"/>
       <c r="W9" s="3"/>
       <c r="X9" s="3" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="Y9" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z9" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="10" spans="1:26">
       <c r="A10" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F10" s="4">
         <v>46112</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>32</v>
@@ -4642,7 +4642,7 @@
       <c r="L10" s="7"/>
       <c r="M10" s="3"/>
       <c r="N10" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O10" s="3"/>
       <c r="P10" s="3"/>
@@ -4650,63 +4650,63 @@
       <c r="R10" s="3"/>
       <c r="S10" s="3"/>
       <c r="T10" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="U10" s="3"/>
       <c r="V10" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="W10" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="X10" s="3" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="Y10" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z10" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11" spans="1:26">
       <c r="A11" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F11" s="4">
         <v>46106</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>32</v>
       </c>
       <c r="J11" s="5"/>
       <c r="K11" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L11" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M11" s="3"/>
       <c r="N11" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
@@ -4716,43 +4716,43 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="W11" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="X11" s="3" t="s">
         <v>36</v>
       </c>
       <c r="Y11" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Z11" s="9"/>
     </row>
     <row r="12" spans="1:26">
       <c r="A12" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F12" s="4">
         <v>46097</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>69</v>
@@ -4762,7 +4762,7 @@
       <c r="L12" s="7"/>
       <c r="M12" s="3"/>
       <c r="N12" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
@@ -4770,57 +4770,57 @@
       <c r="R12" s="3"/>
       <c r="S12" s="3"/>
       <c r="T12" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="U12" s="3"/>
       <c r="V12" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="W12" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="X12" s="3" t="s">
         <v>36</v>
       </c>
       <c r="Y12" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Z12" s="9"/>
     </row>
     <row r="13" spans="1:26">
       <c r="A13" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F13" s="4">
         <v>46173</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J13" s="5"/>
       <c r="K13" s="7"/>
       <c r="L13" s="7"/>
       <c r="M13" s="3"/>
       <c r="N13" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O13" s="3"/>
       <c r="P13" s="3"/>
@@ -4828,14 +4828,14 @@
       <c r="R13" s="3"/>
       <c r="S13" s="3"/>
       <c r="T13" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="U13" s="3"/>
       <c r="V13" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="W13" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="X13" s="3" t="s">
         <v>36</v>
@@ -4847,28 +4847,28 @@
     </row>
     <row r="14" spans="1:26">
       <c r="A14" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F14" s="4">
         <v>46173</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>32</v>
@@ -4878,7 +4878,7 @@
       <c r="L14" s="7"/>
       <c r="M14" s="3"/>
       <c r="N14" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O14" s="3"/>
       <c r="P14" s="3"/>
@@ -4886,57 +4886,57 @@
       <c r="R14" s="3"/>
       <c r="S14" s="3"/>
       <c r="T14" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="U14" s="3"/>
       <c r="V14" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="W14" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>36</v>
       </c>
       <c r="Y14" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Z14" s="9"/>
     </row>
     <row r="15" spans="1:26">
       <c r="A15" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F15" s="4">
         <v>46173</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J15" s="5"/>
       <c r="K15" s="7"/>
       <c r="L15" s="7"/>
       <c r="M15" s="3"/>
       <c r="N15" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="O15" s="3"/>
       <c r="P15" s="3"/>
@@ -4944,14 +4944,14 @@
       <c r="R15" s="3"/>
       <c r="S15" s="3"/>
       <c r="T15" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="U15" s="3"/>
       <c r="V15" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="W15" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="X15" s="3" t="s">
         <v>36</v>
@@ -4963,28 +4963,28 @@
     </row>
     <row r="16" spans="1:26">
       <c r="A16" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F16" s="4">
         <v>46177</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>32</v>
@@ -4994,7 +4994,7 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
@@ -5004,10 +5004,10 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="W16" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="X16" s="3" t="s">
         <v>36</v>
@@ -5019,28 +5019,28 @@
     </row>
     <row r="17" spans="1:26">
       <c r="A17" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>61</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>32</v>
@@ -5050,7 +5050,7 @@
       <c r="L17" s="3"/>
       <c r="M17" s="3"/>
       <c r="N17" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="O17" s="3"/>
       <c r="P17" s="3"/>
@@ -5071,28 +5071,28 @@
     </row>
     <row r="18" spans="1:26">
       <c r="A18" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F18" s="6">
         <v>46149</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>32</v>
@@ -5102,7 +5102,7 @@
       <c r="L18" s="3"/>
       <c r="M18" s="3"/>
       <c r="N18" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O18" s="3"/>
       <c r="P18" s="3"/>
@@ -5123,40 +5123,40 @@
     </row>
     <row r="19" spans="1:26">
       <c r="A19" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F19" s="4">
         <v>46101</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="J19" s="5"/>
       <c r="K19" s="7" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L19" s="7"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
@@ -5166,10 +5166,10 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="W19" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="X19" s="3" t="s">
         <v>36</v>
@@ -5181,28 +5181,28 @@
     </row>
     <row r="20" spans="1:26">
       <c r="A20" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F20" s="4">
         <v>46110</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>32</v>
@@ -5212,7 +5212,7 @@
       <c r="L20" s="7"/>
       <c r="M20" s="3"/>
       <c r="N20" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O20" s="3"/>
       <c r="P20" s="3"/>
@@ -5220,14 +5220,14 @@
       <c r="R20" s="3"/>
       <c r="S20" s="3"/>
       <c r="T20" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="U20" s="3"/>
       <c r="V20" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="W20" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="X20" s="3" t="s">
         <v>36</v>
@@ -5239,42 +5239,42 @@
     </row>
     <row r="21" spans="1:26">
       <c r="A21" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F21" s="4">
         <v>46095</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>32</v>
       </c>
       <c r="J21" s="5"/>
       <c r="K21" s="7" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L21" s="7" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M21" s="3"/>
       <c r="N21" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O21" s="3"/>
       <c r="P21" s="3"/>
@@ -5284,10 +5284,10 @@
       <c r="T21" s="3"/>
       <c r="U21" s="3"/>
       <c r="V21" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="W21" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="X21" s="3" t="s">
         <v>36</v>
@@ -5299,28 +5299,28 @@
     </row>
     <row r="22" spans="1:26">
       <c r="A22" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F22" s="4">
         <v>46190</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>69</v>
@@ -5330,7 +5330,7 @@
       <c r="L22" s="3"/>
       <c r="M22" s="3"/>
       <c r="N22" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O22" s="3"/>
       <c r="P22" s="3"/>
@@ -5340,10 +5340,10 @@
       <c r="T22" s="3"/>
       <c r="U22" s="3"/>
       <c r="V22" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="W22" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="X22" s="3" t="s">
         <v>36</v>
@@ -5355,40 +5355,40 @@
     </row>
     <row r="23" spans="1:26">
       <c r="A23" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F23" s="4">
         <v>46099</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I23" s="3" t="s">
         <v>32</v>
       </c>
       <c r="J23" s="5"/>
       <c r="K23" s="7" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="L23" s="7"/>
       <c r="M23" s="3"/>
       <c r="N23" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="O23" s="3"/>
       <c r="P23" s="3"/>
@@ -5398,10 +5398,10 @@
       <c r="T23" s="3"/>
       <c r="U23" s="3"/>
       <c r="V23" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="W23" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="X23" s="3" t="s">
         <v>36</v>
@@ -5413,28 +5413,28 @@
     </row>
     <row r="24" spans="1:26">
       <c r="A24" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F24" s="5" t="s">
         <v>66</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>32</v>
@@ -5444,7 +5444,7 @@
       <c r="L24" s="3"/>
       <c r="M24" s="3"/>
       <c r="N24" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O24" s="3"/>
       <c r="P24" s="3"/>
@@ -5465,28 +5465,28 @@
     </row>
     <row r="25" spans="1:26">
       <c r="A25" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>32</v>
@@ -5496,7 +5496,7 @@
       <c r="L25" s="3"/>
       <c r="M25" s="3"/>
       <c r="N25" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O25" s="3"/>
       <c r="P25" s="3"/>
@@ -5517,28 +5517,28 @@
     </row>
     <row r="26" spans="1:26">
       <c r="A26" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F26" s="4">
         <v>46203</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>32</v>
@@ -5548,7 +5548,7 @@
       <c r="L26" s="3"/>
       <c r="M26" s="3"/>
       <c r="N26" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="O26" s="3"/>
       <c r="P26" s="3"/>
@@ -5558,10 +5558,10 @@
       <c r="T26" s="3"/>
       <c r="U26" s="3"/>
       <c r="V26" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="W26" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="X26" s="3" t="s">
         <v>36</v>
@@ -5573,40 +5573,40 @@
     </row>
     <row r="27" spans="1:26">
       <c r="A27" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F27" s="4">
         <v>46107</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>32</v>
       </c>
       <c r="J27" s="5"/>
       <c r="K27" s="7" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L27" s="7"/>
       <c r="M27" s="3"/>
       <c r="N27" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="O27" s="3"/>
       <c r="P27" s="3"/>
@@ -5616,19 +5616,19 @@
       <c r="T27" s="3"/>
       <c r="U27" s="3"/>
       <c r="V27" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="W27" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="X27" s="3" t="s">
-        <v>211</v>
+        <v>71</v>
       </c>
       <c r="Y27" s="3" t="s">
         <v>212</v>
       </c>
       <c r="Z27" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="28" spans="1:26">
@@ -5679,7 +5679,7 @@
         <v>219</v>
       </c>
       <c r="W28" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="X28" s="3" t="s">
         <v>36</v>
@@ -5793,7 +5793,7 @@
         <v>232</v>
       </c>
       <c r="W30" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="X30" s="3" t="s">
         <v>36</v>
@@ -5855,7 +5855,7 @@
         <v>240</v>
       </c>
       <c r="W31" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="X31" s="3" t="s">
         <v>36</v>
@@ -5975,7 +5975,7 @@
         <v>256</v>
       </c>
       <c r="W33" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="X33" s="3" t="s">
         <v>36</v>
@@ -6030,13 +6030,13 @@
       <c r="V34" s="3"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3" t="s">
-        <v>211</v>
+        <v>71</v>
       </c>
       <c r="Y34" s="3" t="s">
         <v>243</v>
       </c>
       <c r="Z34" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="35" spans="1:26">
@@ -6089,7 +6089,7 @@
         <v>273</v>
       </c>
       <c r="W35" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="X35" s="3" t="s">
         <v>36</v>
@@ -6309,7 +6309,7 @@
         <v>298</v>
       </c>
       <c r="W39" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="X39" s="3" t="s">
         <v>36</v>
@@ -6367,16 +6367,16 @@
         <v>303</v>
       </c>
       <c r="W40" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="X40" s="3" t="s">
-        <v>211</v>
+        <v>71</v>
       </c>
       <c r="Y40" s="3" t="s">
         <v>243</v>
       </c>
       <c r="Z40" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="41" spans="1:26">
@@ -6528,13 +6528,13 @@
       <c r="V43" s="3"/>
       <c r="W43" s="3"/>
       <c r="X43" s="3" t="s">
-        <v>211</v>
+        <v>71</v>
       </c>
       <c r="Y43" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Z43" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="44" spans="1:26">
@@ -6641,13 +6641,13 @@
         <v>338</v>
       </c>
       <c r="W45" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="X45" s="3" t="s">
         <v>36</v>
       </c>
       <c r="Y45" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Z45" s="9"/>
     </row>
@@ -6809,7 +6809,7 @@
         <v>36</v>
       </c>
       <c r="Y48" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Z48" s="9"/>
     </row>
@@ -6971,7 +6971,7 @@
         <v>383</v>
       </c>
       <c r="W51" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="X51" s="3" t="s">
         <v>36</v>
@@ -7087,7 +7087,7 @@
         <v>36</v>
       </c>
       <c r="Y53" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Z53" s="9"/>
     </row>
@@ -7439,7 +7439,7 @@
         <v>433</v>
       </c>
       <c r="W59" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="X59" s="3" t="s">
         <v>36</v>
@@ -7619,7 +7619,7 @@
         <v>447</v>
       </c>
       <c r="W62" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="X62" s="3" t="s">
         <v>36</v>
@@ -7781,7 +7781,7 @@
         <v>465</v>
       </c>
       <c r="W65" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="X65" s="3" t="s">
         <v>36</v>
@@ -7839,7 +7839,7 @@
         <v>470</v>
       </c>
       <c r="W66" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="X66" s="3" t="s">
         <v>36</v>
@@ -7951,16 +7951,16 @@
         <v>481</v>
       </c>
       <c r="W68" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="X68" s="3" t="s">
-        <v>211</v>
+        <v>71</v>
       </c>
       <c r="Y68" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Z68" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="69" spans="1:26">
@@ -8011,7 +8011,7 @@
         <v>490</v>
       </c>
       <c r="W69" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="X69" s="3" t="s">
         <v>36</v>
@@ -8071,7 +8071,7 @@
         <v>498</v>
       </c>
       <c r="W70" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="X70" s="3" t="s">
         <v>36</v>
@@ -8191,7 +8191,7 @@
         <v>511</v>
       </c>
       <c r="W72" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="X72" s="3" t="s">
         <v>36</v>
@@ -8307,7 +8307,7 @@
         <v>525</v>
       </c>
       <c r="W74" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="X74" s="3" t="s">
         <v>36</v>
@@ -8416,13 +8416,13 @@
       <c r="V76" s="3"/>
       <c r="W76" s="3"/>
       <c r="X76" s="3" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="Y76" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z76" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="77" spans="1:26">
@@ -8470,13 +8470,13 @@
       <c r="V77" s="3"/>
       <c r="W77" s="3"/>
       <c r="X77" s="3" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="Y77" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z77" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="78" spans="1:26">
@@ -8524,13 +8524,13 @@
       <c r="V78" s="3"/>
       <c r="W78" s="3"/>
       <c r="X78" s="3" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="Y78" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z78" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="79" spans="1:26">
@@ -8649,7 +8649,7 @@
         <v>562</v>
       </c>
       <c r="W80" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="X80" s="3" t="s">
         <v>36</v>
@@ -8709,7 +8709,7 @@
         <v>571</v>
       </c>
       <c r="W81" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="X81" s="3" t="s">
         <v>36</v>
@@ -8816,13 +8816,13 @@
       <c r="V83" s="3"/>
       <c r="W83" s="3"/>
       <c r="X83" s="3" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="Y83" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z83" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="84" spans="1:26">
@@ -8870,13 +8870,13 @@
       <c r="V84" s="3"/>
       <c r="W84" s="3"/>
       <c r="X84" s="3" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="Y84" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z84" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="85" spans="1:26">
@@ -8924,13 +8924,13 @@
       <c r="V85" s="3"/>
       <c r="W85" s="3"/>
       <c r="X85" s="3" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="Y85" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z85" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="86" spans="1:26">
@@ -8978,13 +8978,13 @@
       <c r="V86" s="3"/>
       <c r="W86" s="3"/>
       <c r="X86" s="3" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="Y86" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z86" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="87" spans="1:26">
@@ -9032,13 +9032,13 @@
       <c r="V87" s="3"/>
       <c r="W87" s="3"/>
       <c r="X87" s="3" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="Y87" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z87" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="88" spans="1:26">
@@ -9303,7 +9303,7 @@
         <v>634</v>
       </c>
       <c r="W92" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="X92" s="3" t="s">
         <v>36</v>
@@ -9477,7 +9477,7 @@
         <v>36</v>
       </c>
       <c r="Y95" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Z95" s="9"/>
     </row>
@@ -9641,7 +9641,7 @@
         <v>677</v>
       </c>
       <c r="W98" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="X98" s="3" t="s">
         <v>36</v>
@@ -9811,13 +9811,13 @@
     </row>
     <row r="102" spans="1:26">
       <c r="A102" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D102" s="3" t="s">
         <v>694</v>
@@ -10513,13 +10513,13 @@
     </row>
     <row r="115" spans="1:26">
       <c r="A115" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D115" s="3" t="s">
         <v>770</v>
@@ -10567,13 +10567,13 @@
     </row>
     <row r="116" spans="1:26">
       <c r="A116" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D116" s="3" t="s">
         <v>774</v>
@@ -10936,13 +10936,13 @@
       </c>
       <c r="W122" s="9"/>
       <c r="X122" s="3" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="Y122" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Z122" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="123" spans="1:26">

--- a/data.xlsx
+++ b/data.xlsx
@@ -2604,10 +2604,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -2626,22 +2626,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -2650,22 +2634,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -2681,9 +2657,17 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="0"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2696,7 +2680,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF3F3F76"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2718,8 +2702,15 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="15"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -2727,16 +2718,17 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="Calibri"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2756,15 +2748,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF3F3F3F"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2785,13 +2785,127 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2803,7 +2917,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2815,115 +2947,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2942,30 +2966,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2994,69 +2994,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -3091,18 +3032,77 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3114,130 +3114,130 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="19" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -5293,7 +5293,7 @@
         <v>36</v>
       </c>
       <c r="Y21" s="3" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="Z21" s="9"/>
     </row>
@@ -10885,7 +10885,7 @@
         <v>36</v>
       </c>
       <c r="Y121" s="9" t="s">
-        <v>212</v>
+        <v>47</v>
       </c>
       <c r="Z121" s="9"/>
     </row>
@@ -11103,7 +11103,7 @@
         <v>36</v>
       </c>
       <c r="Y125" s="9" t="s">
-        <v>212</v>
+        <v>47</v>
       </c>
       <c r="Z125" s="9"/>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1718" uniqueCount="860">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1719" uniqueCount="861">
   <si>
     <t>SHOP_CODE</t>
   </si>
@@ -2383,7 +2383,7 @@
     <t>Mrs. UPEKSHA WANNI ARACHCHI W.A.D.</t>
   </si>
   <si>
-    <t>MB-SAFARI4S-RED</t>
+    <t>SGSAFA4S25C001071</t>
   </si>
   <si>
     <t>BBI01</t>
@@ -2405,6 +2405,9 @@
   </si>
   <si>
     <t>SGSAFA4S25A000064</t>
+  </si>
+  <si>
+    <t>CR RECEIVED TO SLMO</t>
   </si>
   <si>
     <t>BMV01</t>
@@ -2605,11 +2608,11 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2626,72 +2629,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="9"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -2702,8 +2643,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2718,7 +2668,30 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2732,9 +2705,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2742,17 +2723,31 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="Calibri"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2764,7 +2759,21 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2785,13 +2794,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2803,31 +2812,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2845,13 +2848,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2863,7 +2878,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2875,49 +2896,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2935,13 +2956,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2953,19 +2968,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2996,6 +3005,32 @@
     <border>
       <left/>
       <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
       <bottom style="medium">
         <color theme="4"/>
@@ -3019,16 +3054,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3050,11 +3085,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3067,42 +3100,18 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3117,131 +3126,131 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3264,6 +3273,9 @@
     </xf>
     <xf numFmtId="58" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -4337,7 +4349,7 @@
         <v>36</v>
       </c>
       <c r="Y4" s="3" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="Z4" s="9"/>
     </row>
@@ -6977,7 +6989,7 @@
         <v>36</v>
       </c>
       <c r="Y51" s="3" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="Z51" s="3"/>
     </row>
@@ -10705,7 +10717,7 @@
       <c r="K118" s="3"/>
       <c r="L118" s="9"/>
       <c r="M118" s="3"/>
-      <c r="N118" s="3" t="s">
+      <c r="N118" s="10" t="s">
         <v>788</v>
       </c>
       <c r="O118" s="3"/>
@@ -10723,7 +10735,7 @@
         <v>36</v>
       </c>
       <c r="Y118" s="9" t="s">
-        <v>243</v>
+        <v>47</v>
       </c>
       <c r="Z118" s="9"/>
     </row>
@@ -10777,34 +10789,34 @@
         <v>36</v>
       </c>
       <c r="Y119" s="9" t="s">
-        <v>212</v>
+        <v>796</v>
       </c>
       <c r="Z119" s="9"/>
     </row>
     <row r="120" spans="1:26">
       <c r="A120" s="3" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="F120" s="8">
         <v>46251</v>
       </c>
       <c r="G120" s="3" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H120" s="3" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="I120" s="3" t="s">
         <v>32</v>
@@ -10814,7 +10826,7 @@
       <c r="L120" s="9"/>
       <c r="M120" s="3"/>
       <c r="N120" s="3" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="O120" s="3"/>
       <c r="P120" s="3"/>
@@ -10837,28 +10849,28 @@
     </row>
     <row r="121" spans="1:26">
       <c r="A121" s="3" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="F121" s="8">
         <v>46258</v>
       </c>
       <c r="G121" s="3" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H121" s="3" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="I121" s="3" t="s">
         <v>32</v>
@@ -10868,7 +10880,7 @@
       <c r="L121" s="9"/>
       <c r="M121" s="3"/>
       <c r="N121" s="3" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="O121" s="3"/>
       <c r="P121" s="3"/>
@@ -10891,28 +10903,28 @@
     </row>
     <row r="122" spans="1:26">
       <c r="A122" s="3" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="F122" s="8">
         <v>46265</v>
       </c>
       <c r="G122" s="3" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H122" s="3" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="I122" s="3" t="s">
         <v>32</v>
@@ -10922,7 +10934,7 @@
       <c r="L122" s="9"/>
       <c r="M122" s="3"/>
       <c r="N122" s="3" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="O122" s="3"/>
       <c r="P122" s="3"/>
@@ -10947,28 +10959,28 @@
     </row>
     <row r="123" spans="1:26">
       <c r="A123" s="3" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="F123" s="8">
         <v>46259</v>
       </c>
       <c r="G123" s="3" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="H123" s="3" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="I123" s="3" t="s">
         <v>32</v>
@@ -10978,7 +10990,7 @@
       <c r="L123" s="9"/>
       <c r="M123" s="3"/>
       <c r="N123" s="3" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="O123" s="3"/>
       <c r="P123" s="3"/>
@@ -10995,34 +11007,34 @@
         <v>36</v>
       </c>
       <c r="Y123" s="9" t="s">
-        <v>243</v>
+        <v>796</v>
       </c>
       <c r="Z123" s="9"/>
     </row>
     <row r="124" spans="1:26">
       <c r="A124" s="3" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="F124" s="8">
         <v>46265</v>
       </c>
       <c r="G124" s="3" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="H124" s="3" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="I124" s="3" t="s">
         <v>32</v>
@@ -11032,7 +11044,7 @@
       <c r="L124" s="9"/>
       <c r="M124" s="3"/>
       <c r="N124" s="3" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="O124" s="3"/>
       <c r="P124" s="3"/>
@@ -11049,9 +11061,11 @@
         <v>36</v>
       </c>
       <c r="Y124" s="9" t="s">
-        <v>243</v>
-      </c>
-      <c r="Z124" s="9"/>
+        <v>99</v>
+      </c>
+      <c r="Z124" s="9" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="125" spans="1:26">
       <c r="A125" s="3" t="s">
@@ -11064,19 +11078,19 @@
         <v>40</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="F125" s="8">
         <v>46255</v>
       </c>
       <c r="G125" s="3" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="H125" s="3" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="I125" s="3" t="s">
         <v>32</v>
@@ -11086,7 +11100,7 @@
       <c r="L125" s="9"/>
       <c r="M125" s="3"/>
       <c r="N125" s="3" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="O125" s="3"/>
       <c r="P125" s="3"/>
@@ -11118,19 +11132,19 @@
         <v>215</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="F126" s="8">
         <v>46251</v>
       </c>
       <c r="G126" s="3" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="H126" s="3" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="I126" s="3" t="s">
         <v>32</v>
@@ -11140,7 +11154,7 @@
       <c r="L126" s="9"/>
       <c r="M126" s="3"/>
       <c r="N126" s="3" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="O126" s="3"/>
       <c r="P126" s="3"/>
@@ -11163,28 +11177,28 @@
     </row>
     <row r="127" spans="1:26">
       <c r="A127" s="3" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="F127" s="8">
         <v>46265</v>
       </c>
       <c r="G127" s="3" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="H127" s="3" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="I127" s="3" t="s">
         <v>32</v>
@@ -11194,7 +11208,7 @@
       <c r="L127" s="9"/>
       <c r="M127" s="3"/>
       <c r="N127" s="3" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="O127" s="3"/>
       <c r="P127" s="3"/>
@@ -11217,28 +11231,28 @@
     </row>
     <row r="128" spans="1:26">
       <c r="A128" s="3" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="F128" s="8">
         <v>46262</v>
       </c>
       <c r="G128" s="3" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="H128" s="3" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="I128" s="3" t="s">
         <v>32</v>
@@ -11248,7 +11262,7 @@
       <c r="L128" s="9"/>
       <c r="M128" s="3"/>
       <c r="N128" s="3" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="O128" s="3"/>
       <c r="P128" s="3"/>
@@ -11271,28 +11285,28 @@
     </row>
     <row r="129" spans="1:26">
       <c r="A129" s="3" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="F129" s="8">
         <v>46259</v>
       </c>
       <c r="G129" s="3" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="H129" s="3" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="I129" s="3" t="s">
         <v>32</v>
@@ -11302,7 +11316,7 @@
       <c r="L129" s="9"/>
       <c r="M129" s="3"/>
       <c r="N129" s="3" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="O129" s="3"/>
       <c r="P129" s="3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://singerlk-my.sharepoint.com/personal/dihank_singersl_com/Documents/Desktop/DIHAN/cr dashboard/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="41" documentId="11_5847038500C079F1E35F4C8C432471BF012A7624" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{703ABECC-CA5A-4373-A058-3F3AE68F5F0A}"/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="6910"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DETAILS" sheetId="3" r:id="rId1"/>
@@ -17,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1719" uniqueCount="861">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1722" uniqueCount="860">
   <si>
     <t>SHOP_CODE</t>
   </si>
@@ -1304,9 +1310,6 @@
   </si>
   <si>
     <t>L1Z1LL514SA569146</t>
-  </si>
-  <si>
-    <t>DOCUMENTS COMPLETED ON 31-AUG</t>
   </si>
   <si>
     <t>BNK-H25972</t>
@@ -2605,14 +2608,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-  </numFmts>
-  <fonts count="22">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2634,152 +2631,8 @@
       <name val="Calibri"/>
       <charset val="134"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="34">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2792,194 +2645,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -3002,251 +2669,9 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -3254,24 +2679,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="58" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="58" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="58" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -3279,58 +2704,40 @@
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="40% - Accent1" xfId="1" builtinId="31"/>
-    <cellStyle name="Comma" xfId="2" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="3" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
-    <cellStyle name="Currency" xfId="5" builtinId="4"/>
-    <cellStyle name="Percent" xfId="6" builtinId="5"/>
-    <cellStyle name="Hyperlink" xfId="7" builtinId="8"/>
-    <cellStyle name="60% - Accent4" xfId="8" builtinId="44"/>
-    <cellStyle name="Followed Hyperlink" xfId="9" builtinId="9"/>
-    <cellStyle name="Check Cell" xfId="10" builtinId="23"/>
-    <cellStyle name="Heading 2" xfId="11" builtinId="17"/>
-    <cellStyle name="Note" xfId="12" builtinId="10"/>
-    <cellStyle name="40% - Accent3" xfId="13" builtinId="39"/>
-    <cellStyle name="Warning Text" xfId="14" builtinId="11"/>
-    <cellStyle name="40% - Accent2" xfId="15" builtinId="35"/>
-    <cellStyle name="Title" xfId="16" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="17" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="18" builtinId="16"/>
-    <cellStyle name="Heading 3" xfId="19" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="20" builtinId="19"/>
-    <cellStyle name="Input" xfId="21" builtinId="20"/>
-    <cellStyle name="60% - Accent3" xfId="22" builtinId="40"/>
-    <cellStyle name="Good" xfId="23" builtinId="26"/>
-    <cellStyle name="Output" xfId="24" builtinId="21"/>
-    <cellStyle name="20% - Accent1" xfId="25" builtinId="30"/>
-    <cellStyle name="Calculation" xfId="26" builtinId="22"/>
-    <cellStyle name="Linked Cell" xfId="27" builtinId="24"/>
-    <cellStyle name="Total" xfId="28" builtinId="25"/>
-    <cellStyle name="Bad" xfId="29" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="30" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="31" builtinId="29"/>
-    <cellStyle name="20% - Accent5" xfId="32" builtinId="46"/>
-    <cellStyle name="60% - Accent1" xfId="33" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="34" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="35" builtinId="34"/>
-    <cellStyle name="20% - Accent6" xfId="36" builtinId="50"/>
-    <cellStyle name="60% - Accent2" xfId="37" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="38" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="39" builtinId="38"/>
-    <cellStyle name="Accent4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="42" builtinId="43"/>
-    <cellStyle name="Accent5" xfId="43" builtinId="45"/>
-    <cellStyle name="40% - Accent5" xfId="44" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="45" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="46" builtinId="49"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="38">
+  <dxfs count="41">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3344,34 +2751,385 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
         <color theme="1"/>
       </font>
       <border>
@@ -3382,7 +3140,7 @@
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="0"/>
       </font>
       <fill>
@@ -3410,412 +3168,64 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.399975585192419"/>
+          <color theme="4" tint="0.39994506668294322"/>
         </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
       </border>
     </dxf>
   </dxfs>
   <tableStyles count="4" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
-      <tableStyleElement type="wholeTable" dxfId="7"/>
-      <tableStyleElement type="headerRow" dxfId="6"/>
-      <tableStyleElement type="totalRow" dxfId="5"/>
-      <tableStyleElement type="firstColumn" dxfId="4"/>
-      <tableStyleElement type="lastColumn" dxfId="3"/>
-      <tableStyleElement type="firstRowStripe" dxfId="2"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="1"/>
-    </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1 2" pivot="0" table="0" count="10">
-      <tableStyleElement type="headerRow" dxfId="17"/>
-      <tableStyleElement type="totalRow" dxfId="16"/>
-      <tableStyleElement type="firstRowStripe" dxfId="15"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="14"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="13"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="11"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="10"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="9"/>
-      <tableStyleElement type="pageFieldValues" dxfId="8"/>
-    </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1 3" pivot="0" table="0" count="10">
-      <tableStyleElement type="headerRow" dxfId="27"/>
-      <tableStyleElement type="totalRow" dxfId="26"/>
-      <tableStyleElement type="firstRowStripe" dxfId="25"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="24"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="23"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="22"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="21"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="20"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="19"/>
-      <tableStyleElement type="pageFieldValues" dxfId="18"/>
-    </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10">
-      <tableStyleElement type="headerRow" dxfId="37"/>
-      <tableStyleElement type="totalRow" dxfId="36"/>
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
+      <tableStyleElement type="wholeTable" dxfId="40"/>
+      <tableStyleElement type="headerRow" dxfId="39"/>
+      <tableStyleElement type="totalRow" dxfId="38"/>
+      <tableStyleElement type="firstColumn" dxfId="37"/>
+      <tableStyleElement type="lastColumn" dxfId="36"/>
       <tableStyleElement type="firstRowStripe" dxfId="35"/>
       <tableStyleElement type="firstColumnStripe" dxfId="34"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="33"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="32"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="31"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="30"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="29"/>
-      <tableStyleElement type="pageFieldValues" dxfId="28"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1 2" pivot="0" table="0" count="10" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
+      <tableStyleElement type="headerRow" dxfId="33"/>
+      <tableStyleElement type="totalRow" dxfId="32"/>
+      <tableStyleElement type="firstRowStripe" dxfId="31"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="30"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="29"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="28"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="27"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="26"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="25"/>
+      <tableStyleElement type="pageFieldValues" dxfId="24"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1 3" pivot="0" table="0" count="10" xr9:uid="{00000000-0011-0000-FFFF-FFFF02000000}">
+      <tableStyleElement type="headerRow" dxfId="23"/>
+      <tableStyleElement type="totalRow" dxfId="22"/>
+      <tableStyleElement type="firstRowStripe" dxfId="21"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="20"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="19"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="18"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="17"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="16"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="15"/>
+      <tableStyleElement type="pageFieldValues" dxfId="14"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{00000000-0011-0000-FFFF-FFFF03000000}">
+      <tableStyleElement type="headerRow" dxfId="13"/>
+      <tableStyleElement type="totalRow" dxfId="12"/>
+      <tableStyleElement type="firstRowStripe" dxfId="11"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="9"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="8"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="7"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="6"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="5"/>
+      <tableStyleElement type="pageFieldValues" dxfId="4"/>
     </tableStyle>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -4065,40 +3475,41 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:Z129"/>
-  <sheetFormatPr defaultColWidth="8.89090909090909" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="34.7090909090909" customWidth="1"/>
-    <col min="2" max="2" width="24.2181818181818" customWidth="1"/>
-    <col min="3" max="3" width="15.4272727272727" customWidth="1"/>
-    <col min="4" max="4" width="20.1090909090909" customWidth="1"/>
+    <col min="1" max="1" width="34.7265625" customWidth="1"/>
+    <col min="2" max="2" width="24.1796875" customWidth="1"/>
+    <col min="3" max="3" width="15.453125" customWidth="1"/>
+    <col min="4" max="4" width="20.08984375" customWidth="1"/>
     <col min="5" max="5" width="13" customWidth="1"/>
-    <col min="6" max="6" width="21.2181818181818" customWidth="1"/>
-    <col min="7" max="7" width="15.2181818181818" customWidth="1"/>
-    <col min="8" max="8" width="74.8909090909091" customWidth="1"/>
-    <col min="9" max="9" width="8.33636363636364" customWidth="1"/>
-    <col min="10" max="10" width="6.78181818181818" customWidth="1"/>
+    <col min="6" max="6" width="21.1796875" customWidth="1"/>
+    <col min="7" max="7" width="15.1796875" customWidth="1"/>
+    <col min="8" max="8" width="74.90625" customWidth="1"/>
+    <col min="9" max="9" width="8.36328125" customWidth="1"/>
+    <col min="10" max="10" width="6.81640625" customWidth="1"/>
     <col min="11" max="11" width="22" customWidth="1"/>
-    <col min="12" max="12" width="33.6363636363636" customWidth="1"/>
-    <col min="13" max="13" width="11.7818181818182" customWidth="1"/>
-    <col min="14" max="14" width="22.1090909090909" customWidth="1"/>
+    <col min="12" max="12" width="33.6328125" customWidth="1"/>
+    <col min="13" max="13" width="11.81640625" customWidth="1"/>
+    <col min="14" max="14" width="22.08984375" customWidth="1"/>
     <col min="15" max="15" width="15" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="24.4454545454545" hidden="1" customWidth="1"/>
-    <col min="17" max="17" width="28.1090909090909" hidden="1" customWidth="1"/>
-    <col min="18" max="18" width="10.2181818181818" hidden="1" customWidth="1"/>
-    <col min="19" max="19" width="25.6636363636364" hidden="1" customWidth="1"/>
-    <col min="20" max="20" width="239.218181818182" hidden="1" customWidth="1"/>
-    <col min="21" max="21" width="99.8909090909091" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="24.453125" hidden="1" customWidth="1"/>
+    <col min="17" max="17" width="28.08984375" hidden="1" customWidth="1"/>
+    <col min="18" max="18" width="10.1796875" hidden="1" customWidth="1"/>
+    <col min="19" max="19" width="25.6328125" hidden="1" customWidth="1"/>
+    <col min="20" max="20" width="239.1796875" hidden="1" customWidth="1"/>
+    <col min="21" max="21" width="99.90625" hidden="1" customWidth="1"/>
     <col min="22" max="22" width="22" hidden="1" customWidth="1"/>
-    <col min="23" max="23" width="70.7818181818182" customWidth="1"/>
-    <col min="24" max="24" width="8.21818181818182" customWidth="1"/>
-    <col min="25" max="26" width="49.4454545454545" customWidth="1"/>
+    <col min="23" max="23" width="70.81640625" customWidth="1"/>
+    <col min="24" max="24" width="8.1796875" customWidth="1"/>
+    <col min="25" max="26" width="49.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26">
@@ -4737,7 +4148,7 @@
         <v>36</v>
       </c>
       <c r="Y11" s="3" t="s">
-        <v>99</v>
+        <v>47</v>
       </c>
       <c r="Z11" s="9"/>
     </row>
@@ -4792,12 +4203,14 @@
         <v>108</v>
       </c>
       <c r="X12" s="3" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="Y12" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="Z12" s="9"/>
+      <c r="Z12" s="9" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="13" spans="1:26">
       <c r="A13" s="3" t="s">
@@ -4911,7 +4324,7 @@
         <v>36</v>
       </c>
       <c r="Y14" s="3" t="s">
-        <v>99</v>
+        <v>47</v>
       </c>
       <c r="Z14" s="9"/>
     </row>
@@ -6818,12 +6231,14 @@
         <v>360</v>
       </c>
       <c r="X48" s="3" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="Y48" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="Z48" s="9"/>
+      <c r="Z48" s="9" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="49" spans="1:26">
       <c r="A49" s="3" t="s">
@@ -7099,7 +6514,7 @@
         <v>36</v>
       </c>
       <c r="Y53" s="3" t="s">
-        <v>99</v>
+        <v>47</v>
       </c>
       <c r="Z53" s="9"/>
     </row>
@@ -7397,11 +6812,9 @@
         <v>36</v>
       </c>
       <c r="Y58" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="Z58" s="3" t="s">
-        <v>429</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="Z58" s="3"/>
     </row>
     <row r="59" spans="1:26">
       <c r="A59" s="3" t="s">
@@ -7414,31 +6827,31 @@
         <v>403</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="F59" s="4">
         <v>46107</v>
       </c>
       <c r="G59" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="H59" s="3" t="s">
         <v>431</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>432</v>
       </c>
       <c r="I59" s="3" t="s">
         <v>32</v>
       </c>
       <c r="J59" s="5"/>
       <c r="K59" s="7" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="L59" s="7"/>
       <c r="M59" s="3"/>
       <c r="N59" s="3" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="O59" s="3"/>
       <c r="P59" s="3"/>
@@ -7448,7 +6861,7 @@
       <c r="T59" s="3"/>
       <c r="U59" s="3"/>
       <c r="V59" s="3" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="W59" s="3" t="s">
         <v>181</v>
@@ -7472,19 +6885,19 @@
         <v>403</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="F60" s="4">
         <v>46135</v>
       </c>
       <c r="G60" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="H60" s="3" t="s">
         <v>435</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>436</v>
       </c>
       <c r="I60" s="3" t="s">
         <v>32</v>
@@ -7494,7 +6907,7 @@
       <c r="L60" s="7"/>
       <c r="M60" s="3"/>
       <c r="N60" s="3" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="O60" s="3"/>
       <c r="P60" s="3"/>
@@ -7508,10 +6921,10 @@
         <v>409</v>
       </c>
       <c r="V60" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="W60" s="3" t="s">
         <v>437</v>
-      </c>
-      <c r="W60" s="3" t="s">
-        <v>438</v>
       </c>
       <c r="X60" s="3" t="s">
         <v>36</v>
@@ -7532,19 +6945,19 @@
         <v>403</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="F61" s="4">
         <v>46139</v>
       </c>
       <c r="G61" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="H61" s="3" t="s">
         <v>440</v>
-      </c>
-      <c r="H61" s="3" t="s">
-        <v>441</v>
       </c>
       <c r="I61" s="3" t="s">
         <v>32</v>
@@ -7554,7 +6967,7 @@
       <c r="L61" s="7"/>
       <c r="M61" s="3"/>
       <c r="N61" s="3" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="O61" s="3"/>
       <c r="P61" s="3"/>
@@ -7568,10 +6981,10 @@
         <v>409</v>
       </c>
       <c r="V61" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="W61" s="3" t="s">
         <v>442</v>
-      </c>
-      <c r="W61" s="3" t="s">
-        <v>443</v>
       </c>
       <c r="X61" s="3" t="s">
         <v>36</v>
@@ -7592,19 +7005,19 @@
         <v>403</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F62" s="4">
         <v>46173</v>
       </c>
       <c r="G62" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="H62" s="3" t="s">
         <v>445</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>446</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>32</v>
@@ -7614,7 +7027,7 @@
       <c r="L62" s="7"/>
       <c r="M62" s="3"/>
       <c r="N62" s="3" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="O62" s="3"/>
       <c r="P62" s="3"/>
@@ -7622,13 +7035,13 @@
       <c r="R62" s="3"/>
       <c r="S62" s="3"/>
       <c r="T62" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="U62" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>449</v>
-      </c>
       <c r="V62" s="3" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="W62" s="3" t="s">
         <v>181</v>
@@ -7652,19 +7065,19 @@
         <v>403</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F63" s="6">
         <v>46180</v>
       </c>
       <c r="G63" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="H63" s="3" t="s">
         <v>451</v>
-      </c>
-      <c r="H63" s="3" t="s">
-        <v>452</v>
       </c>
       <c r="I63" s="3" t="s">
         <v>32</v>
@@ -7674,7 +7087,7 @@
       <c r="L63" s="3"/>
       <c r="M63" s="3"/>
       <c r="N63" s="3" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="O63" s="3"/>
       <c r="P63" s="3"/>
@@ -7704,19 +7117,19 @@
         <v>403</v>
       </c>
       <c r="D64" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="F64" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="E64" s="3" t="s">
-        <v>454</v>
-      </c>
-      <c r="F64" s="5" t="s">
+      <c r="G64" s="3" t="s">
         <v>455</v>
       </c>
-      <c r="G64" s="3" t="s">
+      <c r="H64" s="3" t="s">
         <v>456</v>
-      </c>
-      <c r="H64" s="3" t="s">
-        <v>457</v>
       </c>
       <c r="I64" s="3" t="s">
         <v>32</v>
@@ -7726,7 +7139,7 @@
       <c r="L64" s="3"/>
       <c r="M64" s="3"/>
       <c r="N64" s="3" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="O64" s="3"/>
       <c r="P64" s="3"/>
@@ -7747,28 +7160,28 @@
     </row>
     <row r="65" spans="1:26">
       <c r="A65" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="B65" s="3" t="s">
         <v>459</v>
       </c>
-      <c r="B65" s="3" t="s">
+      <c r="C65" s="3" t="s">
         <v>460</v>
       </c>
-      <c r="C65" s="3" t="s">
+      <c r="D65" s="3" t="s">
         <v>461</v>
       </c>
-      <c r="D65" s="3" t="s">
-        <v>462</v>
-      </c>
       <c r="E65" s="3" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="F65" s="4">
         <v>46109</v>
       </c>
       <c r="G65" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="H65" s="3" t="s">
         <v>463</v>
-      </c>
-      <c r="H65" s="3" t="s">
-        <v>464</v>
       </c>
       <c r="I65" s="3" t="s">
         <v>32</v>
@@ -7778,7 +7191,7 @@
       <c r="L65" s="7"/>
       <c r="M65" s="3"/>
       <c r="N65" s="3" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="O65" s="3"/>
       <c r="P65" s="3"/>
@@ -7786,11 +7199,11 @@
       <c r="R65" s="3"/>
       <c r="S65" s="3"/>
       <c r="T65" s="3" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="U65" s="3"/>
       <c r="V65" s="3" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="W65" s="3" t="s">
         <v>92</v>
@@ -7805,28 +7218,28 @@
     </row>
     <row r="66" spans="1:26">
       <c r="A66" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="B66" s="3" t="s">
         <v>459</v>
       </c>
-      <c r="B66" s="3" t="s">
+      <c r="C66" s="3" t="s">
         <v>460</v>
       </c>
-      <c r="C66" s="3" t="s">
-        <v>461</v>
-      </c>
       <c r="D66" s="3" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="F66" s="4">
         <v>46156</v>
       </c>
       <c r="G66" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="H66" s="3" t="s">
         <v>468</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>469</v>
       </c>
       <c r="I66" s="3" t="s">
         <v>45</v>
@@ -7836,7 +7249,7 @@
       <c r="L66" s="7"/>
       <c r="M66" s="3"/>
       <c r="N66" s="3" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="O66" s="3"/>
       <c r="P66" s="3"/>
@@ -7844,11 +7257,11 @@
       <c r="R66" s="3"/>
       <c r="S66" s="3"/>
       <c r="T66" s="3" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="U66" s="3"/>
       <c r="V66" s="3" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="W66" s="3" t="s">
         <v>92</v>
@@ -7863,28 +7276,28 @@
     </row>
     <row r="67" spans="1:26">
       <c r="A67" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="B67" s="3" t="s">
         <v>459</v>
       </c>
-      <c r="B67" s="3" t="s">
+      <c r="C67" s="3" t="s">
         <v>460</v>
       </c>
-      <c r="C67" s="3" t="s">
-        <v>461</v>
-      </c>
       <c r="D67" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F67" s="5" t="s">
         <v>309</v>
       </c>
       <c r="G67" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="H67" s="3" t="s">
         <v>472</v>
-      </c>
-      <c r="H67" s="3" t="s">
-        <v>473</v>
       </c>
       <c r="I67" s="3" t="s">
         <v>45</v>
@@ -7894,7 +7307,7 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
@@ -7915,28 +7328,28 @@
     </row>
     <row r="68" spans="1:26">
       <c r="A68" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="B68" s="3" t="s">
         <v>475</v>
       </c>
-      <c r="B68" s="3" t="s">
+      <c r="C68" s="3" t="s">
         <v>476</v>
       </c>
-      <c r="C68" s="3" t="s">
+      <c r="D68" s="3" t="s">
         <v>477</v>
       </c>
-      <c r="D68" s="3" t="s">
-        <v>478</v>
-      </c>
       <c r="E68" s="3" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="F68" s="4">
         <v>46137</v>
       </c>
       <c r="G68" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="H68" s="3" t="s">
         <v>479</v>
-      </c>
-      <c r="H68" s="3" t="s">
-        <v>480</v>
       </c>
       <c r="I68" s="3" t="s">
         <v>32</v>
@@ -7946,7 +7359,7 @@
       <c r="L68" s="7"/>
       <c r="M68" s="3"/>
       <c r="N68" s="3" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="O68" s="3"/>
       <c r="P68" s="3"/>
@@ -7954,13 +7367,13 @@
       <c r="R68" s="3"/>
       <c r="S68" s="3"/>
       <c r="T68" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="U68" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="U68" s="3" t="s">
-        <v>483</v>
-      </c>
       <c r="V68" s="3" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="W68" s="3" t="s">
         <v>181</v>
@@ -7977,28 +7390,28 @@
     </row>
     <row r="69" spans="1:26">
       <c r="A69" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="B69" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="B69" s="3" t="s">
+      <c r="C69" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="C69" s="3" t="s">
+      <c r="D69" s="3" t="s">
         <v>486</v>
       </c>
-      <c r="D69" s="3" t="s">
-        <v>487</v>
-      </c>
       <c r="E69" s="3" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="F69" s="4">
         <v>46100</v>
       </c>
       <c r="G69" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="H69" s="3" t="s">
         <v>488</v>
-      </c>
-      <c r="H69" s="3" t="s">
-        <v>489</v>
       </c>
       <c r="I69" s="3" t="s">
         <v>32</v>
@@ -8008,7 +7421,7 @@
       <c r="L69" s="7"/>
       <c r="M69" s="3"/>
       <c r="N69" s="3" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="O69" s="3"/>
       <c r="P69" s="3"/>
@@ -8016,11 +7429,11 @@
       <c r="R69" s="3"/>
       <c r="S69" s="3"/>
       <c r="T69" s="3" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="U69" s="3"/>
       <c r="V69" s="3" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="W69" s="3" t="s">
         <v>92</v>
@@ -8035,28 +7448,28 @@
     </row>
     <row r="70" spans="1:26">
       <c r="A70" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="B70" s="3" t="s">
         <v>492</v>
       </c>
-      <c r="B70" s="3" t="s">
+      <c r="C70" s="3" t="s">
         <v>493</v>
       </c>
-      <c r="C70" s="3" t="s">
+      <c r="D70" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="D70" s="3" t="s">
-        <v>495</v>
-      </c>
       <c r="E70" s="3" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="F70" s="4">
         <v>46106</v>
       </c>
       <c r="G70" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="H70" s="3" t="s">
         <v>496</v>
-      </c>
-      <c r="H70" s="3" t="s">
-        <v>497</v>
       </c>
       <c r="I70" s="3" t="s">
         <v>32</v>
@@ -8066,7 +7479,7 @@
       <c r="L70" s="7"/>
       <c r="M70" s="3"/>
       <c r="N70" s="3" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="O70" s="3"/>
       <c r="P70" s="3"/>
@@ -8074,13 +7487,13 @@
       <c r="R70" s="3"/>
       <c r="S70" s="3"/>
       <c r="T70" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="U70" s="3" t="s">
         <v>499</v>
       </c>
-      <c r="U70" s="3" t="s">
-        <v>500</v>
-      </c>
       <c r="V70" s="3" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="W70" s="3" t="s">
         <v>92</v>
@@ -8095,28 +7508,28 @@
     </row>
     <row r="71" spans="1:26">
       <c r="A71" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="B71" s="3" t="s">
         <v>492</v>
       </c>
-      <c r="B71" s="3" t="s">
+      <c r="C71" s="3" t="s">
         <v>493</v>
       </c>
-      <c r="C71" s="3" t="s">
-        <v>494</v>
-      </c>
       <c r="D71" s="3" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="F71" s="4">
         <v>46107</v>
       </c>
       <c r="G71" s="3" t="s">
+        <v>501</v>
+      </c>
+      <c r="H71" s="3" t="s">
         <v>502</v>
-      </c>
-      <c r="H71" s="3" t="s">
-        <v>503</v>
       </c>
       <c r="I71" s="3" t="s">
         <v>32</v>
@@ -8126,7 +7539,7 @@
       <c r="L71" s="7"/>
       <c r="M71" s="3"/>
       <c r="N71" s="3" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="O71" s="3"/>
       <c r="P71" s="3"/>
@@ -8134,16 +7547,16 @@
       <c r="R71" s="3"/>
       <c r="S71" s="3"/>
       <c r="T71" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="U71" s="3" t="s">
         <v>505</v>
       </c>
-      <c r="U71" s="3" t="s">
+      <c r="V71" s="3" t="s">
+        <v>503</v>
+      </c>
+      <c r="W71" s="3" t="s">
         <v>506</v>
-      </c>
-      <c r="V71" s="3" t="s">
-        <v>504</v>
-      </c>
-      <c r="W71" s="3" t="s">
-        <v>507</v>
       </c>
       <c r="X71" s="3" t="s">
         <v>36</v>
@@ -8155,28 +7568,28 @@
     </row>
     <row r="72" spans="1:26">
       <c r="A72" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="B72" s="3" t="s">
         <v>492</v>
       </c>
-      <c r="B72" s="3" t="s">
+      <c r="C72" s="3" t="s">
         <v>493</v>
       </c>
-      <c r="C72" s="3" t="s">
-        <v>494</v>
-      </c>
       <c r="D72" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="F72" s="4">
         <v>46111</v>
       </c>
       <c r="G72" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="H72" s="3" t="s">
         <v>509</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>510</v>
       </c>
       <c r="I72" s="3" t="s">
         <v>32</v>
@@ -8186,7 +7599,7 @@
       <c r="L72" s="7"/>
       <c r="M72" s="3"/>
       <c r="N72" s="3" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="O72" s="3"/>
       <c r="P72" s="3"/>
@@ -8194,13 +7607,13 @@
       <c r="R72" s="3"/>
       <c r="S72" s="3"/>
       <c r="T72" s="3" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="U72" s="3" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="V72" s="3" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="W72" s="3" t="s">
         <v>92</v>
@@ -8215,42 +7628,42 @@
     </row>
     <row r="73" spans="1:26">
       <c r="A73" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="B73" s="3" t="s">
         <v>492</v>
       </c>
-      <c r="B73" s="3" t="s">
+      <c r="C73" s="3" t="s">
         <v>493</v>
       </c>
-      <c r="C73" s="3" t="s">
-        <v>494</v>
-      </c>
       <c r="D73" s="3" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="F73" s="4">
         <v>46111</v>
       </c>
       <c r="G73" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="H73" s="3" t="s">
         <v>514</v>
-      </c>
-      <c r="H73" s="3" t="s">
-        <v>515</v>
       </c>
       <c r="I73" s="3" t="s">
         <v>32</v>
       </c>
       <c r="J73" s="5"/>
       <c r="K73" s="7" t="s">
+        <v>515</v>
+      </c>
+      <c r="L73" s="7" t="s">
         <v>516</v>
-      </c>
-      <c r="L73" s="7" t="s">
-        <v>517</v>
       </c>
       <c r="M73" s="3"/>
       <c r="N73" s="3" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="O73" s="3"/>
       <c r="P73" s="3"/>
@@ -8260,10 +7673,10 @@
       <c r="T73" s="3"/>
       <c r="U73" s="3"/>
       <c r="V73" s="3" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="W73" s="3" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="X73" s="3" t="s">
         <v>36</v>
@@ -8275,28 +7688,28 @@
     </row>
     <row r="74" spans="1:26">
       <c r="A74" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="B74" s="3" t="s">
         <v>519</v>
       </c>
-      <c r="B74" s="3" t="s">
+      <c r="C74" s="3" t="s">
         <v>520</v>
       </c>
-      <c r="C74" s="3" t="s">
+      <c r="D74" s="3" t="s">
         <v>521</v>
       </c>
-      <c r="D74" s="3" t="s">
-        <v>522</v>
-      </c>
       <c r="E74" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F74" s="4">
         <v>46203</v>
       </c>
       <c r="G74" s="3" t="s">
+        <v>522</v>
+      </c>
+      <c r="H74" s="3" t="s">
         <v>523</v>
-      </c>
-      <c r="H74" s="3" t="s">
-        <v>524</v>
       </c>
       <c r="I74" s="3" t="s">
         <v>32</v>
@@ -8306,7 +7719,7 @@
       <c r="L74" s="3"/>
       <c r="M74" s="3"/>
       <c r="N74" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="O74" s="3"/>
       <c r="P74" s="3"/>
@@ -8316,7 +7729,7 @@
       <c r="T74" s="3"/>
       <c r="U74" s="3"/>
       <c r="V74" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="W74" s="3" t="s">
         <v>92</v>
@@ -8331,28 +7744,28 @@
     </row>
     <row r="75" spans="1:26">
       <c r="A75" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="B75" s="3" t="s">
         <v>526</v>
       </c>
-      <c r="B75" s="3" t="s">
+      <c r="C75" s="3" t="s">
         <v>527</v>
       </c>
-      <c r="C75" s="3" t="s">
+      <c r="D75" s="3" t="s">
         <v>528</v>
       </c>
-      <c r="D75" s="3" t="s">
-        <v>529</v>
-      </c>
       <c r="E75" s="3" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="F75" s="5" t="s">
         <v>66</v>
       </c>
       <c r="G75" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="H75" s="3" t="s">
         <v>530</v>
-      </c>
-      <c r="H75" s="3" t="s">
-        <v>531</v>
       </c>
       <c r="I75" s="3" t="s">
         <v>32</v>
@@ -8362,7 +7775,7 @@
       <c r="L75" s="3"/>
       <c r="M75" s="3"/>
       <c r="N75" s="3" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="O75" s="3"/>
       <c r="P75" s="3"/>
@@ -8380,43 +7793,43 @@
         <v>243</v>
       </c>
       <c r="Z75" s="9" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="76" spans="1:26">
       <c r="A76" s="3" t="s">
+        <v>533</v>
+      </c>
+      <c r="B76" s="3" t="s">
         <v>534</v>
       </c>
-      <c r="B76" s="3" t="s">
+      <c r="C76" s="3" t="s">
         <v>535</v>
       </c>
-      <c r="C76" s="3" t="s">
+      <c r="D76" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="D76" s="3" t="s">
-        <v>537</v>
-      </c>
       <c r="E76" s="3" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="F76" s="5" t="s">
         <v>66</v>
       </c>
       <c r="G76" s="3" t="s">
+        <v>537</v>
+      </c>
+      <c r="H76" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="H76" s="3" t="s">
+      <c r="I76" s="3" t="s">
         <v>539</v>
-      </c>
-      <c r="I76" s="3" t="s">
-        <v>540</v>
       </c>
       <c r="J76" s="3"/>
       <c r="K76" s="3"/>
       <c r="L76" s="3"/>
       <c r="M76" s="3"/>
       <c r="N76" s="3" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="O76" s="3"/>
       <c r="P76" s="3"/>
@@ -8439,38 +7852,38 @@
     </row>
     <row r="77" spans="1:26">
       <c r="A77" s="3" t="s">
+        <v>533</v>
+      </c>
+      <c r="B77" s="3" t="s">
         <v>534</v>
       </c>
-      <c r="B77" s="3" t="s">
+      <c r="C77" s="3" t="s">
         <v>535</v>
       </c>
-      <c r="C77" s="3" t="s">
-        <v>536</v>
-      </c>
       <c r="D77" s="3" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="F77" s="5" t="s">
         <v>66</v>
       </c>
       <c r="G77" s="3" t="s">
+        <v>542</v>
+      </c>
+      <c r="H77" s="3" t="s">
         <v>543</v>
       </c>
-      <c r="H77" s="3" t="s">
-        <v>544</v>
-      </c>
       <c r="I77" s="3" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="J77" s="3"/>
       <c r="K77" s="3"/>
       <c r="L77" s="3"/>
       <c r="M77" s="3"/>
       <c r="N77" s="3" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="O77" s="3"/>
       <c r="P77" s="3"/>
@@ -8493,38 +7906,38 @@
     </row>
     <row r="78" spans="1:26">
       <c r="A78" s="3" t="s">
+        <v>533</v>
+      </c>
+      <c r="B78" s="3" t="s">
         <v>534</v>
       </c>
-      <c r="B78" s="3" t="s">
+      <c r="C78" s="3" t="s">
         <v>535</v>
       </c>
-      <c r="C78" s="3" t="s">
-        <v>536</v>
-      </c>
       <c r="D78" s="3" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="F78" s="5" t="s">
         <v>66</v>
       </c>
       <c r="G78" s="3" t="s">
+        <v>542</v>
+      </c>
+      <c r="H78" s="3" t="s">
         <v>543</v>
       </c>
-      <c r="H78" s="3" t="s">
-        <v>544</v>
-      </c>
       <c r="I78" s="3" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="J78" s="3"/>
       <c r="K78" s="3"/>
       <c r="L78" s="3"/>
       <c r="M78" s="3"/>
       <c r="N78" s="3" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="O78" s="3"/>
       <c r="P78" s="3"/>
@@ -8547,49 +7960,49 @@
     </row>
     <row r="79" spans="1:26">
       <c r="A79" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="B79" s="3" t="s">
         <v>548</v>
       </c>
-      <c r="B79" s="3" t="s">
+      <c r="C79" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="C79" s="3" t="s">
+      <c r="D79" s="3" t="s">
         <v>550</v>
       </c>
-      <c r="D79" s="3" t="s">
-        <v>551</v>
-      </c>
       <c r="E79" s="3" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="F79" s="4">
         <v>46110</v>
       </c>
       <c r="G79" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="H79" s="3" t="s">
         <v>552</v>
-      </c>
-      <c r="H79" s="3" t="s">
-        <v>553</v>
       </c>
       <c r="I79" s="3" t="s">
         <v>32</v>
       </c>
       <c r="J79" s="5"/>
       <c r="K79" s="7" t="s">
+        <v>553</v>
+      </c>
+      <c r="L79" s="7" t="s">
         <v>554</v>
-      </c>
-      <c r="L79" s="7" t="s">
-        <v>555</v>
       </c>
       <c r="M79" s="3"/>
       <c r="N79" s="3" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="O79" s="3"/>
       <c r="P79" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="Q79" s="3" t="s">
         <v>556</v>
-      </c>
-      <c r="Q79" s="3" t="s">
-        <v>557</v>
       </c>
       <c r="R79" s="8">
         <v>46217</v>
@@ -8598,10 +8011,10 @@
       <c r="T79" s="3"/>
       <c r="U79" s="3"/>
       <c r="V79" s="3" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="W79" s="3" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="X79" s="3" t="s">
         <v>36</v>
@@ -8613,28 +8026,28 @@
     </row>
     <row r="80" spans="1:26">
       <c r="A80" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="B80" s="3" t="s">
         <v>548</v>
       </c>
-      <c r="B80" s="3" t="s">
+      <c r="C80" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="C80" s="3" t="s">
-        <v>550</v>
-      </c>
       <c r="D80" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="F80" s="4">
         <v>46173</v>
       </c>
       <c r="G80" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="H80" s="3" t="s">
         <v>560</v>
-      </c>
-      <c r="H80" s="3" t="s">
-        <v>561</v>
       </c>
       <c r="I80" s="3" t="s">
         <v>32</v>
@@ -8644,7 +8057,7 @@
       <c r="L80" s="7"/>
       <c r="M80" s="3"/>
       <c r="N80" s="3" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="O80" s="3"/>
       <c r="P80" s="3"/>
@@ -8652,13 +8065,13 @@
       <c r="R80" s="3"/>
       <c r="S80" s="3"/>
       <c r="T80" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="U80" s="3" t="s">
         <v>563</v>
       </c>
-      <c r="U80" s="3" t="s">
-        <v>564</v>
-      </c>
       <c r="V80" s="3" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="W80" s="3" t="s">
         <v>92</v>
@@ -8673,28 +8086,28 @@
     </row>
     <row r="81" spans="1:26">
       <c r="A81" s="3" t="s">
+        <v>564</v>
+      </c>
+      <c r="B81" s="3" t="s">
         <v>565</v>
       </c>
-      <c r="B81" s="3" t="s">
+      <c r="C81" s="3" t="s">
         <v>566</v>
       </c>
-      <c r="C81" s="3" t="s">
+      <c r="D81" s="3" t="s">
         <v>567</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>568</v>
-      </c>
       <c r="E81" s="3" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F81" s="4">
         <v>46073</v>
       </c>
       <c r="G81" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="H81" s="3" t="s">
         <v>569</v>
-      </c>
-      <c r="H81" s="3" t="s">
-        <v>570</v>
       </c>
       <c r="I81" s="3" t="s">
         <v>32</v>
@@ -8704,7 +8117,7 @@
       <c r="L81" s="7"/>
       <c r="M81" s="3"/>
       <c r="N81" s="3" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="O81" s="3"/>
       <c r="P81" s="3"/>
@@ -8712,13 +8125,13 @@
       <c r="R81" s="8"/>
       <c r="S81" s="8"/>
       <c r="T81" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="U81" s="3" t="s">
         <v>572</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>573</v>
-      </c>
       <c r="V81" s="3" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="W81" s="3" t="s">
         <v>92</v>
@@ -8733,28 +8146,28 @@
     </row>
     <row r="82" spans="1:26">
       <c r="A82" s="3" t="s">
+        <v>564</v>
+      </c>
+      <c r="B82" s="3" t="s">
         <v>565</v>
       </c>
-      <c r="B82" s="3" t="s">
+      <c r="C82" s="3" t="s">
         <v>566</v>
       </c>
-      <c r="C82" s="3" t="s">
-        <v>567</v>
-      </c>
       <c r="D82" s="3" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="F82" s="6">
         <v>46272</v>
       </c>
       <c r="G82" s="3" t="s">
+        <v>574</v>
+      </c>
+      <c r="H82" s="3" t="s">
         <v>575</v>
-      </c>
-      <c r="H82" s="3" t="s">
-        <v>576</v>
       </c>
       <c r="I82" s="3" t="s">
         <v>32</v>
@@ -8764,7 +8177,7 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
@@ -8785,28 +8198,28 @@
     </row>
     <row r="83" spans="1:26">
       <c r="A83" s="3" t="s">
+        <v>577</v>
+      </c>
+      <c r="B83" s="3" t="s">
         <v>578</v>
       </c>
-      <c r="B83" s="3" t="s">
+      <c r="C83" s="3" t="s">
         <v>579</v>
       </c>
-      <c r="C83" s="3" t="s">
+      <c r="D83" s="3" t="s">
         <v>580</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>581</v>
-      </c>
       <c r="E83" s="3" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="F83" s="5" t="s">
         <v>66</v>
       </c>
       <c r="G83" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="H83" s="3" t="s">
         <v>582</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>583</v>
       </c>
       <c r="I83" s="3" t="s">
         <v>32</v>
@@ -8816,7 +8229,7 @@
       <c r="L83" s="3"/>
       <c r="M83" s="3"/>
       <c r="N83" s="3" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="O83" s="3"/>
       <c r="P83" s="3"/>
@@ -8839,28 +8252,28 @@
     </row>
     <row r="84" spans="1:26">
       <c r="A84" s="3" t="s">
+        <v>584</v>
+      </c>
+      <c r="B84" s="3" t="s">
         <v>585</v>
       </c>
-      <c r="B84" s="3" t="s">
+      <c r="C84" s="3" t="s">
         <v>586</v>
       </c>
-      <c r="C84" s="3" t="s">
+      <c r="D84" s="3" t="s">
         <v>587</v>
       </c>
-      <c r="D84" s="3" t="s">
-        <v>588</v>
-      </c>
       <c r="E84" s="3" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="F84" s="5" t="s">
         <v>66</v>
       </c>
       <c r="G84" s="3" t="s">
+        <v>588</v>
+      </c>
+      <c r="H84" s="3" t="s">
         <v>589</v>
-      </c>
-      <c r="H84" s="3" t="s">
-        <v>590</v>
       </c>
       <c r="I84" s="3" t="s">
         <v>69</v>
@@ -8870,7 +8283,7 @@
       <c r="L84" s="3"/>
       <c r="M84" s="3"/>
       <c r="N84" s="3" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="O84" s="3"/>
       <c r="P84" s="3"/>
@@ -8893,28 +8306,28 @@
     </row>
     <row r="85" spans="1:26">
       <c r="A85" s="3" t="s">
+        <v>584</v>
+      </c>
+      <c r="B85" s="3" t="s">
         <v>585</v>
       </c>
-      <c r="B85" s="3" t="s">
+      <c r="C85" s="3" t="s">
         <v>586</v>
       </c>
-      <c r="C85" s="3" t="s">
-        <v>587</v>
-      </c>
       <c r="D85" s="3" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="F85" s="5" t="s">
         <v>66</v>
       </c>
       <c r="G85" s="3" t="s">
+        <v>592</v>
+      </c>
+      <c r="H85" s="3" t="s">
         <v>593</v>
-      </c>
-      <c r="H85" s="3" t="s">
-        <v>594</v>
       </c>
       <c r="I85" s="3" t="s">
         <v>69</v>
@@ -8924,7 +8337,7 @@
       <c r="L85" s="3"/>
       <c r="M85" s="3"/>
       <c r="N85" s="3" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="O85" s="3"/>
       <c r="P85" s="3"/>
@@ -8947,28 +8360,28 @@
     </row>
     <row r="86" spans="1:26">
       <c r="A86" s="3" t="s">
+        <v>584</v>
+      </c>
+      <c r="B86" s="3" t="s">
         <v>585</v>
       </c>
-      <c r="B86" s="3" t="s">
+      <c r="C86" s="3" t="s">
         <v>586</v>
       </c>
-      <c r="C86" s="3" t="s">
-        <v>587</v>
-      </c>
       <c r="D86" s="3" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="F86" s="5" t="s">
         <v>66</v>
       </c>
       <c r="G86" s="3" t="s">
+        <v>596</v>
+      </c>
+      <c r="H86" s="3" t="s">
         <v>597</v>
-      </c>
-      <c r="H86" s="3" t="s">
-        <v>598</v>
       </c>
       <c r="I86" s="3" t="s">
         <v>69</v>
@@ -8978,7 +8391,7 @@
       <c r="L86" s="3"/>
       <c r="M86" s="3"/>
       <c r="N86" s="3" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="O86" s="3"/>
       <c r="P86" s="3"/>
@@ -9001,28 +8414,28 @@
     </row>
     <row r="87" spans="1:26">
       <c r="A87" s="3" t="s">
+        <v>584</v>
+      </c>
+      <c r="B87" s="3" t="s">
         <v>585</v>
       </c>
-      <c r="B87" s="3" t="s">
+      <c r="C87" s="3" t="s">
         <v>586</v>
       </c>
-      <c r="C87" s="3" t="s">
-        <v>587</v>
-      </c>
       <c r="D87" s="3" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="F87" s="5" t="s">
         <v>66</v>
       </c>
       <c r="G87" s="3" t="s">
+        <v>600</v>
+      </c>
+      <c r="H87" s="3" t="s">
         <v>601</v>
-      </c>
-      <c r="H87" s="3" t="s">
-        <v>602</v>
       </c>
       <c r="I87" s="3" t="s">
         <v>69</v>
@@ -9032,7 +8445,7 @@
       <c r="L87" s="3"/>
       <c r="M87" s="3"/>
       <c r="N87" s="3" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="O87" s="3"/>
       <c r="P87" s="3"/>
@@ -9055,28 +8468,28 @@
     </row>
     <row r="88" spans="1:26">
       <c r="A88" s="3" t="s">
+        <v>603</v>
+      </c>
+      <c r="B88" s="3" t="s">
         <v>604</v>
       </c>
-      <c r="B88" s="3" t="s">
+      <c r="C88" s="3" t="s">
         <v>605</v>
       </c>
-      <c r="C88" s="3" t="s">
+      <c r="D88" s="3" t="s">
         <v>606</v>
       </c>
-      <c r="D88" s="3" t="s">
+      <c r="E88" s="3" t="s">
+        <v>606</v>
+      </c>
+      <c r="F88" s="5" t="s">
         <v>607</v>
       </c>
-      <c r="E88" s="3" t="s">
-        <v>607</v>
-      </c>
-      <c r="F88" s="5" t="s">
+      <c r="G88" s="3" t="s">
         <v>608</v>
       </c>
-      <c r="G88" s="3" t="s">
+      <c r="H88" s="3" t="s">
         <v>609</v>
-      </c>
-      <c r="H88" s="3" t="s">
-        <v>610</v>
       </c>
       <c r="I88" s="3" t="s">
         <v>32</v>
@@ -9086,7 +8499,7 @@
       <c r="L88" s="3"/>
       <c r="M88" s="3"/>
       <c r="N88" s="3" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="O88" s="3"/>
       <c r="P88" s="3"/>
@@ -9107,28 +8520,28 @@
     </row>
     <row r="89" spans="1:26">
       <c r="A89" s="3" t="s">
+        <v>603</v>
+      </c>
+      <c r="B89" s="3" t="s">
         <v>604</v>
       </c>
-      <c r="B89" s="3" t="s">
+      <c r="C89" s="3" t="s">
         <v>605</v>
       </c>
-      <c r="C89" s="3" t="s">
-        <v>606</v>
-      </c>
       <c r="D89" s="3" t="s">
+        <v>611</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>611</v>
+      </c>
+      <c r="F89" s="5" t="s">
+        <v>607</v>
+      </c>
+      <c r="G89" s="3" t="s">
         <v>612</v>
       </c>
-      <c r="E89" s="3" t="s">
-        <v>612</v>
-      </c>
-      <c r="F89" s="5" t="s">
-        <v>608</v>
-      </c>
-      <c r="G89" s="3" t="s">
+      <c r="H89" s="3" t="s">
         <v>613</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>614</v>
       </c>
       <c r="I89" s="3" t="s">
         <v>32</v>
@@ -9138,7 +8551,7 @@
       <c r="L89" s="3"/>
       <c r="M89" s="3"/>
       <c r="N89" s="3" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="O89" s="3"/>
       <c r="P89" s="3"/>
@@ -9159,40 +8572,40 @@
     </row>
     <row r="90" spans="1:26">
       <c r="A90" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="B90" s="3" t="s">
         <v>616</v>
       </c>
-      <c r="B90" s="3" t="s">
+      <c r="C90" s="3" t="s">
         <v>617</v>
       </c>
-      <c r="C90" s="3" t="s">
+      <c r="D90" s="3" t="s">
         <v>618</v>
       </c>
-      <c r="D90" s="3" t="s">
-        <v>619</v>
-      </c>
       <c r="E90" s="3" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="F90" s="4">
         <v>46170</v>
       </c>
       <c r="G90" s="3" t="s">
+        <v>619</v>
+      </c>
+      <c r="H90" s="3" t="s">
         <v>620</v>
-      </c>
-      <c r="H90" s="3" t="s">
-        <v>621</v>
       </c>
       <c r="I90" s="3" t="s">
         <v>32</v>
       </c>
       <c r="J90" s="5"/>
       <c r="K90" s="7" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="L90" s="7"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
@@ -9202,10 +8615,10 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3" t="s">
+        <v>621</v>
+      </c>
+      <c r="W90" s="3" t="s">
         <v>622</v>
-      </c>
-      <c r="W90" s="3" t="s">
-        <v>623</v>
       </c>
       <c r="X90" s="3" t="s">
         <v>36</v>
@@ -9217,28 +8630,28 @@
     </row>
     <row r="91" spans="1:26">
       <c r="A91" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="B91" s="3" t="s">
         <v>616</v>
       </c>
-      <c r="B91" s="3" t="s">
+      <c r="C91" s="3" t="s">
         <v>617</v>
       </c>
-      <c r="C91" s="3" t="s">
-        <v>618</v>
-      </c>
       <c r="D91" s="3" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="F91" s="5" t="s">
         <v>66</v>
       </c>
       <c r="G91" s="3" t="s">
+        <v>624</v>
+      </c>
+      <c r="H91" s="3" t="s">
         <v>625</v>
-      </c>
-      <c r="H91" s="3" t="s">
-        <v>626</v>
       </c>
       <c r="I91" s="3" t="s">
         <v>32</v>
@@ -9248,7 +8661,7 @@
       <c r="L91" s="3"/>
       <c r="M91" s="3"/>
       <c r="N91" s="3" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="O91" s="3"/>
       <c r="P91" s="3"/>
@@ -9269,28 +8682,28 @@
     </row>
     <row r="92" spans="1:26">
       <c r="A92" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="B92" s="3" t="s">
         <v>628</v>
       </c>
-      <c r="B92" s="3" t="s">
+      <c r="C92" s="3" t="s">
         <v>629</v>
       </c>
-      <c r="C92" s="3" t="s">
+      <c r="D92" s="3" t="s">
         <v>630</v>
       </c>
-      <c r="D92" s="3" t="s">
-        <v>631</v>
-      </c>
       <c r="E92" s="3" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="F92" s="4">
         <v>46101</v>
       </c>
       <c r="G92" s="3" t="s">
+        <v>631</v>
+      </c>
+      <c r="H92" s="3" t="s">
         <v>632</v>
-      </c>
-      <c r="H92" s="3" t="s">
-        <v>633</v>
       </c>
       <c r="I92" s="3" t="s">
         <v>32</v>
@@ -9300,7 +8713,7 @@
       <c r="L92" s="7"/>
       <c r="M92" s="3"/>
       <c r="N92" s="3" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="O92" s="3"/>
       <c r="P92" s="3"/>
@@ -9308,11 +8721,11 @@
       <c r="R92" s="3"/>
       <c r="S92" s="3"/>
       <c r="T92" s="3" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="U92" s="3"/>
       <c r="V92" s="3" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="W92" s="3" t="s">
         <v>92</v>
@@ -9327,28 +8740,28 @@
     </row>
     <row r="93" spans="1:26">
       <c r="A93" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="B93" s="3" t="s">
         <v>628</v>
       </c>
-      <c r="B93" s="3" t="s">
+      <c r="C93" s="3" t="s">
         <v>629</v>
       </c>
-      <c r="C93" s="3" t="s">
-        <v>630</v>
-      </c>
       <c r="D93" s="3" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="F93" s="4">
         <v>46112</v>
       </c>
       <c r="G93" s="3" t="s">
+        <v>636</v>
+      </c>
+      <c r="H93" s="3" t="s">
         <v>637</v>
-      </c>
-      <c r="H93" s="3" t="s">
-        <v>638</v>
       </c>
       <c r="I93" s="3" t="s">
         <v>32</v>
@@ -9358,7 +8771,7 @@
       <c r="L93" s="7"/>
       <c r="M93" s="3"/>
       <c r="N93" s="3" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="O93" s="3"/>
       <c r="P93" s="3"/>
@@ -9366,14 +8779,14 @@
       <c r="R93" s="3"/>
       <c r="S93" s="3"/>
       <c r="T93" s="3" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="U93" s="3"/>
       <c r="V93" s="3" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="W93" s="3" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="X93" s="3" t="s">
         <v>36</v>
@@ -9385,28 +8798,28 @@
     </row>
     <row r="94" spans="1:26">
       <c r="A94" s="3" t="s">
+        <v>641</v>
+      </c>
+      <c r="B94" s="3" t="s">
         <v>642</v>
       </c>
-      <c r="B94" s="3" t="s">
+      <c r="C94" s="3" t="s">
         <v>643</v>
       </c>
-      <c r="C94" s="3" t="s">
+      <c r="D94" s="3" t="s">
         <v>644</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>645</v>
-      </c>
       <c r="E94" s="3" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="F94" s="5" t="s">
         <v>66</v>
       </c>
       <c r="G94" s="3" t="s">
+        <v>645</v>
+      </c>
+      <c r="H94" s="3" t="s">
         <v>646</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>647</v>
       </c>
       <c r="I94" s="3" t="s">
         <v>32</v>
@@ -9416,7 +8829,7 @@
       <c r="L94" s="3"/>
       <c r="M94" s="3"/>
       <c r="N94" s="3" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="O94" s="3"/>
       <c r="P94" s="3"/>
@@ -9437,28 +8850,28 @@
     </row>
     <row r="95" spans="1:26">
       <c r="A95" s="3" t="s">
+        <v>648</v>
+      </c>
+      <c r="B95" s="3" t="s">
         <v>649</v>
       </c>
-      <c r="B95" s="3" t="s">
+      <c r="C95" s="3" t="s">
         <v>650</v>
       </c>
-      <c r="C95" s="3" t="s">
+      <c r="D95" s="3" t="s">
         <v>651</v>
       </c>
-      <c r="D95" s="3" t="s">
-        <v>652</v>
-      </c>
       <c r="E95" s="3" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="F95" s="4">
         <v>46101</v>
       </c>
       <c r="G95" s="3" t="s">
+        <v>652</v>
+      </c>
+      <c r="H95" s="3" t="s">
         <v>653</v>
-      </c>
-      <c r="H95" s="3" t="s">
-        <v>654</v>
       </c>
       <c r="I95" s="3" t="s">
         <v>32</v>
@@ -9468,7 +8881,7 @@
       <c r="L95" s="7"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
@@ -9476,14 +8889,14 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="U95" s="3"/>
       <c r="V95" s="3" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="W95" s="3" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="X95" s="3" t="s">
         <v>36</v>
@@ -9495,28 +8908,28 @@
     </row>
     <row r="96" spans="1:26">
       <c r="A96" s="3" t="s">
+        <v>648</v>
+      </c>
+      <c r="B96" s="3" t="s">
         <v>649</v>
       </c>
-      <c r="B96" s="3" t="s">
+      <c r="C96" s="3" t="s">
         <v>650</v>
       </c>
-      <c r="C96" s="3" t="s">
-        <v>651</v>
-      </c>
       <c r="D96" s="3" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="F96" s="5" t="s">
         <v>66</v>
       </c>
       <c r="G96" s="3" t="s">
+        <v>658</v>
+      </c>
+      <c r="H96" s="3" t="s">
         <v>659</v>
-      </c>
-      <c r="H96" s="3" t="s">
-        <v>660</v>
       </c>
       <c r="I96" s="3" t="s">
         <v>32</v>
@@ -9526,7 +8939,7 @@
       <c r="L96" s="3"/>
       <c r="M96" s="3"/>
       <c r="N96" s="3" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="O96" s="3"/>
       <c r="P96" s="3"/>
@@ -9547,42 +8960,42 @@
     </row>
     <row r="97" spans="1:26">
       <c r="A97" s="3" t="s">
+        <v>661</v>
+      </c>
+      <c r="B97" s="3" t="s">
         <v>662</v>
       </c>
-      <c r="B97" s="3" t="s">
+      <c r="C97" s="3" t="s">
         <v>663</v>
       </c>
-      <c r="C97" s="3" t="s">
+      <c r="D97" s="3" t="s">
         <v>664</v>
       </c>
-      <c r="D97" s="3" t="s">
-        <v>665</v>
-      </c>
       <c r="E97" s="3" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="F97" s="4">
         <v>46101</v>
       </c>
       <c r="G97" s="3" t="s">
+        <v>665</v>
+      </c>
+      <c r="H97" s="3" t="s">
         <v>666</v>
-      </c>
-      <c r="H97" s="3" t="s">
-        <v>667</v>
       </c>
       <c r="I97" s="3" t="s">
         <v>32</v>
       </c>
       <c r="J97" s="5"/>
       <c r="K97" s="7" t="s">
+        <v>667</v>
+      </c>
+      <c r="L97" s="7" t="s">
         <v>668</v>
-      </c>
-      <c r="L97" s="7" t="s">
-        <v>669</v>
       </c>
       <c r="M97" s="3"/>
       <c r="N97" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="O97" s="3"/>
       <c r="P97" s="3"/>
@@ -9592,10 +9005,10 @@
       <c r="T97" s="3"/>
       <c r="U97" s="3"/>
       <c r="V97" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="W97" s="3" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="X97" s="3" t="s">
         <v>36</v>
@@ -9607,40 +9020,40 @@
     </row>
     <row r="98" spans="1:26">
       <c r="A98" s="3" t="s">
+        <v>670</v>
+      </c>
+      <c r="B98" s="3" t="s">
         <v>671</v>
       </c>
-      <c r="B98" s="3" t="s">
+      <c r="C98" s="3" t="s">
         <v>672</v>
       </c>
-      <c r="C98" s="3" t="s">
+      <c r="D98" s="3" t="s">
         <v>673</v>
       </c>
-      <c r="D98" s="3" t="s">
-        <v>674</v>
-      </c>
       <c r="E98" s="3" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="F98" s="4">
         <v>46102</v>
       </c>
       <c r="G98" s="3" t="s">
+        <v>674</v>
+      </c>
+      <c r="H98" s="3" t="s">
         <v>675</v>
-      </c>
-      <c r="H98" s="3" t="s">
-        <v>676</v>
       </c>
       <c r="I98" s="3" t="s">
         <v>32</v>
       </c>
       <c r="J98" s="5"/>
       <c r="K98" s="7" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="L98" s="7"/>
       <c r="M98" s="3"/>
       <c r="N98" s="3" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="O98" s="3"/>
       <c r="P98" s="3"/>
@@ -9650,43 +9063,45 @@
       <c r="T98" s="3"/>
       <c r="U98" s="3"/>
       <c r="V98" s="3" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="W98" s="3" t="s">
         <v>181</v>
       </c>
       <c r="X98" s="3" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="Y98" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="Z98" s="9"/>
+        <v>47</v>
+      </c>
+      <c r="Z98" s="9" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="99" spans="1:26">
       <c r="A99" s="3" t="s">
+        <v>670</v>
+      </c>
+      <c r="B99" s="3" t="s">
         <v>671</v>
       </c>
-      <c r="B99" s="3" t="s">
+      <c r="C99" s="3" t="s">
         <v>672</v>
       </c>
-      <c r="C99" s="3" t="s">
-        <v>673</v>
-      </c>
       <c r="D99" s="3" t="s">
+        <v>677</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>677</v>
+      </c>
+      <c r="F99" s="5" t="s">
         <v>678</v>
       </c>
-      <c r="E99" s="3" t="s">
-        <v>678</v>
-      </c>
-      <c r="F99" s="5" t="s">
+      <c r="G99" s="3" t="s">
         <v>679</v>
       </c>
-      <c r="G99" s="3" t="s">
+      <c r="H99" s="3" t="s">
         <v>680</v>
-      </c>
-      <c r="H99" s="3" t="s">
-        <v>681</v>
       </c>
       <c r="I99" s="3" t="s">
         <v>32</v>
@@ -9696,7 +9111,7 @@
       <c r="L99" s="3"/>
       <c r="M99" s="3"/>
       <c r="N99" s="3" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="O99" s="3"/>
       <c r="P99" s="3"/>
@@ -9717,28 +9132,28 @@
     </row>
     <row r="100" spans="1:26">
       <c r="A100" s="3" t="s">
+        <v>670</v>
+      </c>
+      <c r="B100" s="3" t="s">
         <v>671</v>
       </c>
-      <c r="B100" s="3" t="s">
+      <c r="C100" s="3" t="s">
         <v>672</v>
       </c>
-      <c r="C100" s="3" t="s">
-        <v>673</v>
-      </c>
       <c r="D100" s="3" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="F100" s="5" t="s">
         <v>42</v>
       </c>
       <c r="G100" s="3" t="s">
+        <v>683</v>
+      </c>
+      <c r="H100" s="3" t="s">
         <v>684</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>685</v>
       </c>
       <c r="I100" s="3" t="s">
         <v>32</v>
@@ -9748,7 +9163,7 @@
       <c r="L100" s="3"/>
       <c r="M100" s="3"/>
       <c r="N100" s="3" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="O100" s="3"/>
       <c r="P100" s="3"/>
@@ -9769,28 +9184,28 @@
     </row>
     <row r="101" spans="1:26">
       <c r="A101" s="3" t="s">
+        <v>686</v>
+      </c>
+      <c r="B101" s="3" t="s">
         <v>687</v>
       </c>
-      <c r="B101" s="3" t="s">
+      <c r="C101" s="3" t="s">
         <v>688</v>
       </c>
-      <c r="C101" s="3" t="s">
+      <c r="D101" s="3" t="s">
         <v>689</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>690</v>
-      </c>
       <c r="E101" s="3" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="F101" s="8">
         <v>46246</v>
       </c>
       <c r="G101" s="3" t="s">
+        <v>690</v>
+      </c>
+      <c r="H101" s="3" t="s">
         <v>691</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>692</v>
       </c>
       <c r="I101" s="3" t="s">
         <v>32</v>
@@ -9800,7 +9215,7 @@
       <c r="L101" s="9"/>
       <c r="M101" s="3"/>
       <c r="N101" s="3" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="O101" s="3"/>
       <c r="P101" s="3"/>
@@ -9832,19 +9247,19 @@
         <v>184</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="F102" s="8">
         <v>46265</v>
       </c>
       <c r="G102" s="3" t="s">
+        <v>694</v>
+      </c>
+      <c r="H102" s="3" t="s">
         <v>695</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>696</v>
       </c>
       <c r="I102" s="3" t="s">
         <v>32</v>
@@ -9854,7 +9269,7 @@
       <c r="L102" s="9"/>
       <c r="M102" s="3"/>
       <c r="N102" s="3" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="O102" s="3"/>
       <c r="P102" s="3"/>
@@ -9877,28 +9292,28 @@
     </row>
     <row r="103" spans="1:26">
       <c r="A103" s="3" t="s">
+        <v>697</v>
+      </c>
+      <c r="B103" s="3" t="s">
         <v>698</v>
       </c>
-      <c r="B103" s="3" t="s">
+      <c r="C103" s="3" t="s">
         <v>699</v>
       </c>
-      <c r="C103" s="3" t="s">
+      <c r="D103" s="3" t="s">
         <v>700</v>
       </c>
-      <c r="D103" s="3" t="s">
-        <v>701</v>
-      </c>
       <c r="E103" s="3" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="F103" s="8">
         <v>46265</v>
       </c>
       <c r="G103" s="3" t="s">
+        <v>701</v>
+      </c>
+      <c r="H103" s="3" t="s">
         <v>702</v>
-      </c>
-      <c r="H103" s="3" t="s">
-        <v>703</v>
       </c>
       <c r="I103" s="3" t="s">
         <v>32</v>
@@ -9908,7 +9323,7 @@
       <c r="L103" s="9"/>
       <c r="M103" s="3"/>
       <c r="N103" s="3" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="O103" s="3"/>
       <c r="P103" s="3"/>
@@ -9940,19 +9355,19 @@
         <v>215</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="F104" s="8">
         <v>46265</v>
       </c>
       <c r="G104" s="3" t="s">
+        <v>705</v>
+      </c>
+      <c r="H104" s="3" t="s">
         <v>706</v>
-      </c>
-      <c r="H104" s="3" t="s">
-        <v>707</v>
       </c>
       <c r="I104" s="3" t="s">
         <v>32</v>
@@ -9962,7 +9377,7 @@
       <c r="L104" s="9"/>
       <c r="M104" s="3"/>
       <c r="N104" s="3" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="O104" s="3"/>
       <c r="P104" s="3"/>
@@ -9985,28 +9400,28 @@
     </row>
     <row r="105" spans="1:26">
       <c r="A105" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="B105" s="3" t="s">
         <v>709</v>
       </c>
-      <c r="B105" s="3" t="s">
+      <c r="C105" s="3" t="s">
         <v>710</v>
       </c>
-      <c r="C105" s="3" t="s">
+      <c r="D105" s="3" t="s">
         <v>711</v>
       </c>
-      <c r="D105" s="3" t="s">
-        <v>712</v>
-      </c>
       <c r="E105" s="3" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="F105" s="8">
         <v>46265</v>
       </c>
       <c r="G105" s="3" t="s">
+        <v>712</v>
+      </c>
+      <c r="H105" s="3" t="s">
         <v>713</v>
-      </c>
-      <c r="H105" s="3" t="s">
-        <v>714</v>
       </c>
       <c r="I105" s="3" t="s">
         <v>32</v>
@@ -10016,7 +9431,7 @@
       <c r="L105" s="9"/>
       <c r="M105" s="3"/>
       <c r="N105" s="3" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="O105" s="3"/>
       <c r="P105" s="3"/>
@@ -10048,19 +9463,19 @@
         <v>28</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="F106" s="8">
         <v>46265</v>
       </c>
       <c r="G106" s="3" t="s">
+        <v>716</v>
+      </c>
+      <c r="H106" s="3" t="s">
         <v>717</v>
-      </c>
-      <c r="H106" s="3" t="s">
-        <v>718</v>
       </c>
       <c r="I106" s="3" t="s">
         <v>32</v>
@@ -10070,7 +9485,7 @@
       <c r="L106" s="9"/>
       <c r="M106" s="3"/>
       <c r="N106" s="3" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="O106" s="3"/>
       <c r="P106" s="3"/>
@@ -10093,28 +9508,28 @@
     </row>
     <row r="107" spans="1:26">
       <c r="A107" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="B107" s="3" t="s">
         <v>720</v>
       </c>
-      <c r="B107" s="3" t="s">
+      <c r="C107" s="3" t="s">
         <v>721</v>
       </c>
-      <c r="C107" s="3" t="s">
+      <c r="D107" s="3" t="s">
         <v>722</v>
       </c>
-      <c r="D107" s="3" t="s">
-        <v>723</v>
-      </c>
       <c r="E107" s="3" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="F107" s="8">
         <v>46263</v>
       </c>
       <c r="G107" s="3" t="s">
+        <v>723</v>
+      </c>
+      <c r="H107" s="3" t="s">
         <v>724</v>
-      </c>
-      <c r="H107" s="3" t="s">
-        <v>725</v>
       </c>
       <c r="I107" s="3" t="s">
         <v>32</v>
@@ -10124,7 +9539,7 @@
       <c r="L107" s="9"/>
       <c r="M107" s="3"/>
       <c r="N107" s="3" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="O107" s="3"/>
       <c r="P107" s="3"/>
@@ -10147,28 +9562,28 @@
     </row>
     <row r="108" spans="1:26">
       <c r="A108" s="3" t="s">
+        <v>726</v>
+      </c>
+      <c r="B108" s="3" t="s">
         <v>727</v>
       </c>
-      <c r="B108" s="3" t="s">
+      <c r="C108" s="3" t="s">
         <v>728</v>
       </c>
-      <c r="C108" s="3" t="s">
+      <c r="D108" s="3" t="s">
         <v>729</v>
       </c>
-      <c r="D108" s="3" t="s">
-        <v>730</v>
-      </c>
       <c r="E108" s="3" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="F108" s="8">
         <v>46265</v>
       </c>
       <c r="G108" s="3" t="s">
+        <v>730</v>
+      </c>
+      <c r="H108" s="3" t="s">
         <v>731</v>
-      </c>
-      <c r="H108" s="3" t="s">
-        <v>732</v>
       </c>
       <c r="I108" s="3" t="s">
         <v>32</v>
@@ -10178,7 +9593,7 @@
       <c r="L108" s="9"/>
       <c r="M108" s="3"/>
       <c r="N108" s="3" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="O108" s="3"/>
       <c r="P108" s="3"/>
@@ -10195,34 +9610,34 @@
         <v>36</v>
       </c>
       <c r="Y108" s="9" t="s">
-        <v>243</v>
+        <v>795</v>
       </c>
       <c r="Z108" s="9"/>
     </row>
     <row r="109" spans="1:26">
       <c r="A109" s="3" t="s">
+        <v>733</v>
+      </c>
+      <c r="B109" s="3" t="s">
         <v>734</v>
       </c>
-      <c r="B109" s="3" t="s">
+      <c r="C109" s="3" t="s">
         <v>735</v>
       </c>
-      <c r="C109" s="3" t="s">
+      <c r="D109" s="3" t="s">
         <v>736</v>
       </c>
-      <c r="D109" s="3" t="s">
-        <v>737</v>
-      </c>
       <c r="E109" s="3" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="F109" s="8">
         <v>46260</v>
       </c>
       <c r="G109" s="3" t="s">
+        <v>737</v>
+      </c>
+      <c r="H109" s="3" t="s">
         <v>738</v>
-      </c>
-      <c r="H109" s="3" t="s">
-        <v>739</v>
       </c>
       <c r="I109" s="3" t="s">
         <v>32</v>
@@ -10232,7 +9647,7 @@
       <c r="L109" s="9"/>
       <c r="M109" s="3"/>
       <c r="N109" s="3" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O109" s="3"/>
       <c r="P109" s="3"/>
@@ -10255,28 +9670,28 @@
     </row>
     <row r="110" spans="1:26">
       <c r="A110" s="3" t="s">
+        <v>740</v>
+      </c>
+      <c r="B110" s="3" t="s">
         <v>741</v>
       </c>
-      <c r="B110" s="3" t="s">
+      <c r="C110" s="3" t="s">
         <v>742</v>
       </c>
-      <c r="C110" s="3" t="s">
+      <c r="D110" s="3" t="s">
         <v>743</v>
       </c>
-      <c r="D110" s="3" t="s">
-        <v>744</v>
-      </c>
       <c r="E110" s="3" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="F110" s="8">
         <v>46257</v>
       </c>
       <c r="G110" s="3" t="s">
+        <v>744</v>
+      </c>
+      <c r="H110" s="3" t="s">
         <v>745</v>
-      </c>
-      <c r="H110" s="3" t="s">
-        <v>746</v>
       </c>
       <c r="I110" s="3" t="s">
         <v>32</v>
@@ -10286,7 +9701,7 @@
       <c r="L110" s="9"/>
       <c r="M110" s="3"/>
       <c r="N110" s="3" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="O110" s="3"/>
       <c r="P110" s="3"/>
@@ -10318,19 +9733,19 @@
         <v>403</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="F111" s="8">
         <v>46247</v>
       </c>
       <c r="G111" s="3" t="s">
+        <v>748</v>
+      </c>
+      <c r="H111" s="3" t="s">
         <v>749</v>
-      </c>
-      <c r="H111" s="3" t="s">
-        <v>750</v>
       </c>
       <c r="I111" s="3" t="s">
         <v>32</v>
@@ -10340,7 +9755,7 @@
       <c r="L111" s="9"/>
       <c r="M111" s="3"/>
       <c r="N111" s="3" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="O111" s="3"/>
       <c r="P111" s="3"/>
@@ -10363,28 +9778,28 @@
     </row>
     <row r="112" spans="1:26">
       <c r="A112" s="3" t="s">
+        <v>751</v>
+      </c>
+      <c r="B112" s="3" t="s">
         <v>752</v>
       </c>
-      <c r="B112" s="3" t="s">
+      <c r="C112" s="3" t="s">
         <v>753</v>
       </c>
-      <c r="C112" s="3" t="s">
+      <c r="D112" s="3" t="s">
         <v>754</v>
       </c>
-      <c r="D112" s="3" t="s">
-        <v>755</v>
-      </c>
       <c r="E112" s="3" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="F112" s="8">
         <v>46265</v>
       </c>
       <c r="G112" s="3" t="s">
+        <v>755</v>
+      </c>
+      <c r="H112" s="3" t="s">
         <v>756</v>
-      </c>
-      <c r="H112" s="3" t="s">
-        <v>757</v>
       </c>
       <c r="I112" s="3" t="s">
         <v>32</v>
@@ -10394,7 +9809,7 @@
       <c r="L112" s="9"/>
       <c r="M112" s="3"/>
       <c r="N112" s="3" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="O112" s="3"/>
       <c r="P112" s="3"/>
@@ -10417,28 +9832,28 @@
     </row>
     <row r="113" spans="1:26">
       <c r="A113" s="3" t="s">
+        <v>758</v>
+      </c>
+      <c r="B113" s="3" t="s">
         <v>759</v>
       </c>
-      <c r="B113" s="3" t="s">
+      <c r="C113" s="3" t="s">
         <v>760</v>
       </c>
-      <c r="C113" s="3" t="s">
+      <c r="D113" s="3" t="s">
         <v>761</v>
       </c>
-      <c r="D113" s="3" t="s">
-        <v>762</v>
-      </c>
       <c r="E113" s="3" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="F113" s="8">
         <v>46265</v>
       </c>
       <c r="G113" s="3" t="s">
+        <v>762</v>
+      </c>
+      <c r="H113" s="3" t="s">
         <v>763</v>
-      </c>
-      <c r="H113" s="3" t="s">
-        <v>764</v>
       </c>
       <c r="I113" s="3" t="s">
         <v>69</v>
@@ -10448,7 +9863,7 @@
       <c r="L113" s="9"/>
       <c r="M113" s="3"/>
       <c r="N113" s="3" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="O113" s="3"/>
       <c r="P113" s="3"/>
@@ -10471,28 +9886,28 @@
     </row>
     <row r="114" spans="1:26">
       <c r="A114" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="B114" s="3" t="s">
         <v>548</v>
       </c>
-      <c r="B114" s="3" t="s">
+      <c r="C114" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="C114" s="3" t="s">
-        <v>550</v>
-      </c>
       <c r="D114" s="3" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F114" s="8">
         <v>46265</v>
       </c>
       <c r="G114" s="3" t="s">
+        <v>766</v>
+      </c>
+      <c r="H114" s="3" t="s">
         <v>767</v>
-      </c>
-      <c r="H114" s="3" t="s">
-        <v>768</v>
       </c>
       <c r="I114" s="3" t="s">
         <v>32</v>
@@ -10502,7 +9917,7 @@
       <c r="L114" s="9"/>
       <c r="M114" s="3"/>
       <c r="N114" s="3" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="O114" s="3"/>
       <c r="P114" s="3"/>
@@ -10534,19 +9949,19 @@
         <v>191</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="F115" s="8">
         <v>46249</v>
       </c>
       <c r="G115" s="3" t="s">
+        <v>770</v>
+      </c>
+      <c r="H115" s="3" t="s">
         <v>771</v>
-      </c>
-      <c r="H115" s="3" t="s">
-        <v>772</v>
       </c>
       <c r="I115" s="3" t="s">
         <v>32</v>
@@ -10556,7 +9971,7 @@
       <c r="L115" s="9"/>
       <c r="M115" s="3"/>
       <c r="N115" s="3" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="O115" s="3"/>
       <c r="P115" s="3"/>
@@ -10588,29 +10003,29 @@
         <v>144</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="F116" s="8">
         <v>46252</v>
       </c>
       <c r="G116" s="3" t="s">
+        <v>774</v>
+      </c>
+      <c r="H116" s="3" t="s">
         <v>775</v>
       </c>
-      <c r="H116" s="3" t="s">
-        <v>776</v>
-      </c>
       <c r="I116" s="3" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="J116" s="3"/>
       <c r="K116" s="3"/>
       <c r="L116" s="9"/>
       <c r="M116" s="3"/>
       <c r="N116" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="O116" s="3"/>
       <c r="P116" s="3"/>
@@ -10633,28 +10048,28 @@
     </row>
     <row r="117" spans="1:26">
       <c r="A117" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="B117" s="3" t="s">
         <v>720</v>
       </c>
-      <c r="B117" s="3" t="s">
+      <c r="C117" s="3" t="s">
         <v>721</v>
       </c>
-      <c r="C117" s="3" t="s">
-        <v>722</v>
-      </c>
       <c r="D117" s="3" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="F117" s="8">
         <v>46263</v>
       </c>
       <c r="G117" s="3" t="s">
+        <v>778</v>
+      </c>
+      <c r="H117" s="3" t="s">
         <v>779</v>
-      </c>
-      <c r="H117" s="3" t="s">
-        <v>780</v>
       </c>
       <c r="I117" s="3" t="s">
         <v>32</v>
@@ -10664,7 +10079,7 @@
       <c r="L117" s="9"/>
       <c r="M117" s="3"/>
       <c r="N117" s="3" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="O117" s="3"/>
       <c r="P117" s="3"/>
@@ -10687,28 +10102,28 @@
     </row>
     <row r="118" spans="1:26">
       <c r="A118" s="3" t="s">
+        <v>781</v>
+      </c>
+      <c r="B118" s="3" t="s">
         <v>782</v>
       </c>
-      <c r="B118" s="3" t="s">
+      <c r="C118" s="3" t="s">
         <v>783</v>
       </c>
-      <c r="C118" s="3" t="s">
+      <c r="D118" s="3" t="s">
         <v>784</v>
       </c>
-      <c r="D118" s="3" t="s">
-        <v>785</v>
-      </c>
       <c r="E118" s="3" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="F118" s="8">
         <v>46265</v>
       </c>
       <c r="G118" s="3" t="s">
+        <v>785</v>
+      </c>
+      <c r="H118" s="3" t="s">
         <v>786</v>
-      </c>
-      <c r="H118" s="3" t="s">
-        <v>787</v>
       </c>
       <c r="I118" s="3" t="s">
         <v>32</v>
@@ -10718,7 +10133,7 @@
       <c r="L118" s="9"/>
       <c r="M118" s="3"/>
       <c r="N118" s="10" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="O118" s="3"/>
       <c r="P118" s="3"/>
@@ -10741,38 +10156,38 @@
     </row>
     <row r="119" spans="1:26">
       <c r="A119" s="3" t="s">
+        <v>788</v>
+      </c>
+      <c r="B119" s="3" t="s">
         <v>789</v>
       </c>
-      <c r="B119" s="3" t="s">
+      <c r="C119" s="3" t="s">
         <v>790</v>
       </c>
-      <c r="C119" s="3" t="s">
+      <c r="D119" s="3" t="s">
         <v>791</v>
       </c>
-      <c r="D119" s="3" t="s">
-        <v>792</v>
-      </c>
       <c r="E119" s="3" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="F119" s="8">
         <v>46265</v>
       </c>
       <c r="G119" s="3" t="s">
+        <v>792</v>
+      </c>
+      <c r="H119" s="3" t="s">
         <v>793</v>
       </c>
-      <c r="H119" s="3" t="s">
-        <v>794</v>
-      </c>
       <c r="I119" s="3" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="J119" s="3"/>
       <c r="K119" s="3"/>
       <c r="L119" s="9"/>
       <c r="M119" s="3"/>
       <c r="N119" s="3" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="O119" s="3"/>
       <c r="P119" s="3"/>
@@ -10786,37 +10201,39 @@
       </c>
       <c r="W119" s="9"/>
       <c r="X119" s="3" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="Y119" s="9" t="s">
-        <v>796</v>
-      </c>
-      <c r="Z119" s="9"/>
+        <v>47</v>
+      </c>
+      <c r="Z119" s="9" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="120" spans="1:26">
       <c r="A120" s="3" t="s">
+        <v>796</v>
+      </c>
+      <c r="B120" s="3" t="s">
         <v>797</v>
       </c>
-      <c r="B120" s="3" t="s">
+      <c r="C120" s="3" t="s">
         <v>798</v>
       </c>
-      <c r="C120" s="3" t="s">
+      <c r="D120" s="3" t="s">
         <v>799</v>
       </c>
-      <c r="D120" s="3" t="s">
-        <v>800</v>
-      </c>
       <c r="E120" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="F120" s="8">
         <v>46251</v>
       </c>
       <c r="G120" s="3" t="s">
+        <v>800</v>
+      </c>
+      <c r="H120" s="3" t="s">
         <v>801</v>
-      </c>
-      <c r="H120" s="3" t="s">
-        <v>802</v>
       </c>
       <c r="I120" s="3" t="s">
         <v>32</v>
@@ -10826,7 +10243,7 @@
       <c r="L120" s="9"/>
       <c r="M120" s="3"/>
       <c r="N120" s="3" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="O120" s="3"/>
       <c r="P120" s="3"/>
@@ -10849,28 +10266,28 @@
     </row>
     <row r="121" spans="1:26">
       <c r="A121" s="3" t="s">
+        <v>803</v>
+      </c>
+      <c r="B121" s="3" t="s">
         <v>804</v>
       </c>
-      <c r="B121" s="3" t="s">
+      <c r="C121" s="3" t="s">
         <v>805</v>
       </c>
-      <c r="C121" s="3" t="s">
+      <c r="D121" s="3" t="s">
         <v>806</v>
       </c>
-      <c r="D121" s="3" t="s">
-        <v>807</v>
-      </c>
       <c r="E121" s="3" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="F121" s="8">
         <v>46258</v>
       </c>
       <c r="G121" s="3" t="s">
+        <v>807</v>
+      </c>
+      <c r="H121" s="3" t="s">
         <v>808</v>
-      </c>
-      <c r="H121" s="3" t="s">
-        <v>809</v>
       </c>
       <c r="I121" s="3" t="s">
         <v>32</v>
@@ -10880,7 +10297,7 @@
       <c r="L121" s="9"/>
       <c r="M121" s="3"/>
       <c r="N121" s="3" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="O121" s="3"/>
       <c r="P121" s="3"/>
@@ -10903,28 +10320,28 @@
     </row>
     <row r="122" spans="1:26">
       <c r="A122" s="3" t="s">
+        <v>810</v>
+      </c>
+      <c r="B122" s="3" t="s">
         <v>811</v>
       </c>
-      <c r="B122" s="3" t="s">
+      <c r="C122" s="3" t="s">
         <v>812</v>
       </c>
-      <c r="C122" s="3" t="s">
+      <c r="D122" s="3" t="s">
         <v>813</v>
       </c>
-      <c r="D122" s="3" t="s">
-        <v>814</v>
-      </c>
       <c r="E122" s="3" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="F122" s="8">
         <v>46265</v>
       </c>
       <c r="G122" s="3" t="s">
+        <v>814</v>
+      </c>
+      <c r="H122" s="3" t="s">
         <v>815</v>
-      </c>
-      <c r="H122" s="3" t="s">
-        <v>816</v>
       </c>
       <c r="I122" s="3" t="s">
         <v>32</v>
@@ -10934,7 +10351,7 @@
       <c r="L122" s="9"/>
       <c r="M122" s="3"/>
       <c r="N122" s="3" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="O122" s="3"/>
       <c r="P122" s="3"/>
@@ -10959,28 +10376,28 @@
     </row>
     <row r="123" spans="1:26">
       <c r="A123" s="3" t="s">
+        <v>817</v>
+      </c>
+      <c r="B123" s="3" t="s">
         <v>818</v>
       </c>
-      <c r="B123" s="3" t="s">
+      <c r="C123" s="3" t="s">
         <v>819</v>
       </c>
-      <c r="C123" s="3" t="s">
+      <c r="D123" s="3" t="s">
         <v>820</v>
       </c>
-      <c r="D123" s="3" t="s">
-        <v>821</v>
-      </c>
       <c r="E123" s="3" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="F123" s="8">
         <v>46259</v>
       </c>
       <c r="G123" s="3" t="s">
+        <v>821</v>
+      </c>
+      <c r="H123" s="3" t="s">
         <v>822</v>
-      </c>
-      <c r="H123" s="3" t="s">
-        <v>823</v>
       </c>
       <c r="I123" s="3" t="s">
         <v>32</v>
@@ -10990,7 +10407,7 @@
       <c r="L123" s="9"/>
       <c r="M123" s="3"/>
       <c r="N123" s="3" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="O123" s="3"/>
       <c r="P123" s="3"/>
@@ -11007,34 +10424,34 @@
         <v>36</v>
       </c>
       <c r="Y123" s="9" t="s">
-        <v>796</v>
+        <v>37</v>
       </c>
       <c r="Z123" s="9"/>
     </row>
     <row r="124" spans="1:26">
       <c r="A124" s="3" t="s">
+        <v>824</v>
+      </c>
+      <c r="B124" s="3" t="s">
         <v>825</v>
       </c>
-      <c r="B124" s="3" t="s">
+      <c r="C124" s="3" t="s">
         <v>826</v>
       </c>
-      <c r="C124" s="3" t="s">
+      <c r="D124" s="3" t="s">
         <v>827</v>
       </c>
-      <c r="D124" s="3" t="s">
-        <v>828</v>
-      </c>
       <c r="E124" s="3" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="F124" s="8">
         <v>46265</v>
       </c>
       <c r="G124" s="3" t="s">
+        <v>828</v>
+      </c>
+      <c r="H124" s="3" t="s">
         <v>829</v>
-      </c>
-      <c r="H124" s="3" t="s">
-        <v>830</v>
       </c>
       <c r="I124" s="3" t="s">
         <v>32</v>
@@ -11044,7 +10461,7 @@
       <c r="L124" s="9"/>
       <c r="M124" s="3"/>
       <c r="N124" s="3" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="O124" s="3"/>
       <c r="P124" s="3"/>
@@ -11058,7 +10475,7 @@
       </c>
       <c r="W124" s="9"/>
       <c r="X124" s="3" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="Y124" s="9" t="s">
         <v>99</v>
@@ -11078,19 +10495,19 @@
         <v>40</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F125" s="8">
         <v>46255</v>
       </c>
       <c r="G125" s="3" t="s">
+        <v>832</v>
+      </c>
+      <c r="H125" s="3" t="s">
         <v>833</v>
-      </c>
-      <c r="H125" s="3" t="s">
-        <v>834</v>
       </c>
       <c r="I125" s="3" t="s">
         <v>32</v>
@@ -11100,7 +10517,7 @@
       <c r="L125" s="9"/>
       <c r="M125" s="3"/>
       <c r="N125" s="3" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="O125" s="3"/>
       <c r="P125" s="3"/>
@@ -11132,19 +10549,19 @@
         <v>215</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="F126" s="8">
         <v>46251</v>
       </c>
       <c r="G126" s="3" t="s">
+        <v>836</v>
+      </c>
+      <c r="H126" s="3" t="s">
         <v>837</v>
-      </c>
-      <c r="H126" s="3" t="s">
-        <v>838</v>
       </c>
       <c r="I126" s="3" t="s">
         <v>32</v>
@@ -11154,7 +10571,7 @@
       <c r="L126" s="9"/>
       <c r="M126" s="3"/>
       <c r="N126" s="3" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="O126" s="3"/>
       <c r="P126" s="3"/>
@@ -11177,28 +10594,28 @@
     </row>
     <row r="127" spans="1:26">
       <c r="A127" s="3" t="s">
+        <v>839</v>
+      </c>
+      <c r="B127" s="3" t="s">
         <v>840</v>
       </c>
-      <c r="B127" s="3" t="s">
+      <c r="C127" s="3" t="s">
         <v>841</v>
       </c>
-      <c r="C127" s="3" t="s">
+      <c r="D127" s="3" t="s">
         <v>842</v>
       </c>
-      <c r="D127" s="3" t="s">
-        <v>843</v>
-      </c>
       <c r="E127" s="3" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="F127" s="8">
         <v>46265</v>
       </c>
       <c r="G127" s="3" t="s">
+        <v>843</v>
+      </c>
+      <c r="H127" s="3" t="s">
         <v>844</v>
-      </c>
-      <c r="H127" s="3" t="s">
-        <v>845</v>
       </c>
       <c r="I127" s="3" t="s">
         <v>32</v>
@@ -11208,7 +10625,7 @@
       <c r="L127" s="9"/>
       <c r="M127" s="3"/>
       <c r="N127" s="3" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="O127" s="3"/>
       <c r="P127" s="3"/>
@@ -11231,28 +10648,28 @@
     </row>
     <row r="128" spans="1:26">
       <c r="A128" s="3" t="s">
+        <v>846</v>
+      </c>
+      <c r="B128" s="3" t="s">
         <v>847</v>
       </c>
-      <c r="B128" s="3" t="s">
+      <c r="C128" s="3" t="s">
         <v>848</v>
       </c>
-      <c r="C128" s="3" t="s">
+      <c r="D128" s="3" t="s">
         <v>849</v>
       </c>
-      <c r="D128" s="3" t="s">
-        <v>850</v>
-      </c>
       <c r="E128" s="3" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="F128" s="8">
         <v>46262</v>
       </c>
       <c r="G128" s="3" t="s">
+        <v>850</v>
+      </c>
+      <c r="H128" s="3" t="s">
         <v>851</v>
-      </c>
-      <c r="H128" s="3" t="s">
-        <v>852</v>
       </c>
       <c r="I128" s="3" t="s">
         <v>32</v>
@@ -11262,7 +10679,7 @@
       <c r="L128" s="9"/>
       <c r="M128" s="3"/>
       <c r="N128" s="3" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="O128" s="3"/>
       <c r="P128" s="3"/>
@@ -11285,28 +10702,28 @@
     </row>
     <row r="129" spans="1:26">
       <c r="A129" s="3" t="s">
+        <v>853</v>
+      </c>
+      <c r="B129" s="3" t="s">
         <v>854</v>
       </c>
-      <c r="B129" s="3" t="s">
+      <c r="C129" s="3" t="s">
         <v>855</v>
       </c>
-      <c r="C129" s="3" t="s">
+      <c r="D129" s="3" t="s">
         <v>856</v>
       </c>
-      <c r="D129" s="3" t="s">
-        <v>857</v>
-      </c>
       <c r="E129" s="3" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="F129" s="8">
         <v>46259</v>
       </c>
       <c r="G129" s="3" t="s">
+        <v>857</v>
+      </c>
+      <c r="H129" s="3" t="s">
         <v>858</v>
-      </c>
-      <c r="H129" s="3" t="s">
-        <v>859</v>
       </c>
       <c r="I129" s="3" t="s">
         <v>32</v>
@@ -11316,7 +10733,7 @@
       <c r="L129" s="9"/>
       <c r="M129" s="3"/>
       <c r="N129" s="3" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="O129" s="3"/>
       <c r="P129" s="3"/>
@@ -11338,22 +10755,21 @@
       <c r="Z129" s="9"/>
     </row>
   </sheetData>
-  <sortState ref="A4:Z102">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:Z102">
     <sortCondition ref="B4"/>
   </sortState>
   <conditionalFormatting sqref="J2:J60">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:M60">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N2:N60 J61:J100">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N2:N100">
     <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N60 J61:J100">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
-  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://singerlk-my.sharepoint.com/personal/dihank_singersl_com/Documents/Desktop/DIHAN/cr dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="41" documentId="11_5847038500C079F1E35F4C8C432471BF012A7624" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{703ABECC-CA5A-4373-A058-3F3AE68F5F0A}"/>
+  <xr:revisionPtr revIDLastSave="61" documentId="11_5847038500C079F1E35F4C8C432471BF012A7624" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C9BFF1F-93B6-4E39-9F04-BB6EF36C09AB}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1722" uniqueCount="860">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1723" uniqueCount="860">
   <si>
     <t>SHOP_CODE</t>
   </si>
@@ -3697,7 +3697,7 @@
       <c r="V3" s="3"/>
       <c r="W3" s="3"/>
       <c r="X3" s="3" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="Y3" s="3" t="s">
         <v>47</v>
@@ -4487,7 +4487,7 @@
       <c r="V17" s="3"/>
       <c r="W17" s="3"/>
       <c r="X17" s="3" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="Y17" s="3" t="s">
         <v>47</v>
@@ -4881,7 +4881,7 @@
       <c r="V24" s="3"/>
       <c r="W24" s="3"/>
       <c r="X24" s="3" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="Y24" s="3" t="s">
         <v>47</v>
@@ -6291,7 +6291,7 @@
         <v>369</v>
       </c>
       <c r="X49" s="3" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="Y49" s="3" t="s">
         <v>47</v>
@@ -6453,7 +6453,7 @@
       <c r="V52" s="3"/>
       <c r="W52" s="3"/>
       <c r="X52" s="3" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="Y52" s="3" t="s">
         <v>47</v>
@@ -6809,7 +6809,7 @@
       </c>
       <c r="W58" s="3"/>
       <c r="X58" s="3" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="Y58" s="3" t="s">
         <v>47</v>
@@ -7209,7 +7209,7 @@
         <v>92</v>
       </c>
       <c r="X65" s="3" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="Y65" s="3" t="s">
         <v>243</v>
@@ -7319,7 +7319,7 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="Y67" s="3" t="s">
         <v>47</v>
@@ -8621,7 +8621,7 @@
         <v>622</v>
       </c>
       <c r="X90" s="3" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="Y90" s="3" t="s">
         <v>47</v>
@@ -8899,12 +8899,14 @@
         <v>656</v>
       </c>
       <c r="X95" s="3" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="Y95" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="Z95" s="9"/>
+      <c r="Z95" s="9" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="96" spans="1:26">
       <c r="A96" s="3" t="s">
@@ -8951,7 +8953,7 @@
       <c r="V96" s="3"/>
       <c r="W96" s="3"/>
       <c r="X96" s="3" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="Y96" s="3" t="s">
         <v>47</v>
@@ -9175,7 +9177,7 @@
       <c r="V100" s="3"/>
       <c r="W100" s="3"/>
       <c r="X100" s="3" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="Y100" s="3" t="s">
         <v>47</v>
@@ -9607,7 +9609,7 @@
       </c>
       <c r="W108" s="9"/>
       <c r="X108" s="3" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="Y108" s="9" t="s">
         <v>795</v>
@@ -9769,7 +9771,7 @@
       </c>
       <c r="W111" s="9"/>
       <c r="X111" s="3" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="Y111" s="9" t="s">
         <v>243</v>
@@ -9877,7 +9879,7 @@
       </c>
       <c r="W113" s="9"/>
       <c r="X113" s="3" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="Y113" s="9" t="s">
         <v>47</v>
@@ -10639,7 +10641,7 @@
       </c>
       <c r="W127" s="9"/>
       <c r="X127" s="3" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="Y127" s="9" t="s">
         <v>243</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://singerlk-my.sharepoint.com/personal/dihank_singersl_com/Documents/Desktop/DIHAN/cr dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="61" documentId="11_5847038500C079F1E35F4C8C432471BF012A7624" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C9BFF1F-93B6-4E39-9F04-BB6EF36C09AB}"/>
+  <xr:revisionPtr revIDLastSave="180" documentId="11_5847038500C079F1E35F4C8C432471BF012A7624" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{428960B8-A592-4179-90C1-4B7EEE0AE02F}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,76 @@
     <sheet name="DETAILS" sheetId="3" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">DETAILS!$A$1:$Z$129</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">DETAILS!$A$1:$Z$221</definedName>
   </definedNames>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Dinithi Rohana</author>
+  </authors>
+  <commentList>
+    <comment ref="K147" authorId="0" shapeId="0" xr:uid="{E6299EC1-74CB-4056-B2CB-9AF89BEE99DC}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Dinithi Rohana:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+sent to shop</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K157" authorId="0" shapeId="0" xr:uid="{61B2352E-9157-4159-9A68-42A4D4B2E4ED}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Dinithi Rohana:
+to shop</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1723" uniqueCount="860">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2711" uniqueCount="1104">
   <si>
     <t>SHOP_CODE</t>
   </si>
@@ -2603,18 +2665,757 @@
   </si>
   <si>
     <t>SGSAFA4S25A000056</t>
+  </si>
+  <si>
+    <t>BBM-H73826</t>
+  </si>
+  <si>
+    <t>BHM01</t>
+  </si>
+  <si>
+    <t>HABARANA</t>
+  </si>
+  <si>
+    <t>RAJEEWAW</t>
+  </si>
+  <si>
+    <t>BHM-H35960</t>
+  </si>
+  <si>
+    <t>*553611849V</t>
+  </si>
+  <si>
+    <t>Mr. S.SAMARASIRI.</t>
+  </si>
+  <si>
+    <t>SGSAFA4S25D001155</t>
+  </si>
+  <si>
+    <t>BMH-H37781</t>
+  </si>
+  <si>
+    <t>*200750800110</t>
+  </si>
+  <si>
+    <t>Miss. JEEVAKARAN ARUNTHIKA</t>
+  </si>
+  <si>
+    <t>BDK01</t>
+  </si>
+  <si>
+    <t>KATTANKUDY</t>
+  </si>
+  <si>
+    <t>GURUTHAR</t>
+  </si>
+  <si>
+    <t>BDK-H17319</t>
+  </si>
+  <si>
+    <t>*946884170V</t>
+  </si>
+  <si>
+    <t>YOGARASA VISHNAVENI</t>
+  </si>
+  <si>
+    <t>SGSAFA4S25C001127</t>
+  </si>
+  <si>
+    <t>BGP01</t>
+  </si>
+  <si>
+    <t>MANNAR</t>
+  </si>
+  <si>
+    <t>ARUMUGAMY</t>
+  </si>
+  <si>
+    <t>BGP-H22329</t>
+  </si>
+  <si>
+    <t>*891640862V</t>
+  </si>
+  <si>
+    <t>Mr. AMROSE JENIS ALBAN CROOS</t>
+  </si>
+  <si>
+    <t>SGSAFA4S25C001049</t>
+  </si>
+  <si>
+    <t>BJF01</t>
+  </si>
+  <si>
+    <t>SURIYAWEWA</t>
+  </si>
+  <si>
+    <t>MAHESHIW</t>
+  </si>
+  <si>
+    <t>BJF-H25598</t>
+  </si>
+  <si>
+    <t>*672260671V</t>
+  </si>
+  <si>
+    <t>Mr. K A JAYARATHNA</t>
+  </si>
+  <si>
+    <t>SGSAFA4S25C001122</t>
+  </si>
+  <si>
+    <t>BCU01</t>
+  </si>
+  <si>
+    <t>KIRINDIWELA</t>
+  </si>
+  <si>
+    <t>SISIKELUM</t>
+  </si>
+  <si>
+    <t>BCU-H49623</t>
+  </si>
+  <si>
+    <t>*901114668V</t>
+  </si>
+  <si>
+    <t>BANDARAGE HISHANTHA MADUSHANKA</t>
+  </si>
+  <si>
+    <t>LGMMVU1K7T0002407</t>
+  </si>
+  <si>
+    <t>SDC01</t>
+  </si>
+  <si>
+    <t>GALEWELA</t>
+  </si>
+  <si>
+    <t>SURENA</t>
+  </si>
+  <si>
+    <t>SDC-H11232</t>
+  </si>
+  <si>
+    <t>*802923589V</t>
+  </si>
+  <si>
+    <t>Mr. R.S.RAJAPAKSHA</t>
+  </si>
+  <si>
+    <t>SGSAFA4S25A000001</t>
+  </si>
+  <si>
+    <t>BHH-H23550</t>
+  </si>
+  <si>
+    <t>*736240564V</t>
+  </si>
+  <si>
+    <t>Mrs. J A PRIYANTHA JAYAMANNA</t>
+  </si>
+  <si>
+    <t>L1Z1LL519SA569496</t>
+  </si>
+  <si>
+    <t>BEU01</t>
+  </si>
+  <si>
+    <t>ATHURUGIRIYA</t>
+  </si>
+  <si>
+    <t>MATARAGEC</t>
+  </si>
+  <si>
+    <t>BEU-H41355</t>
+  </si>
+  <si>
+    <t>*866362939V</t>
+  </si>
+  <si>
+    <t>Ms. E A S UDAYAKUMARI</t>
+  </si>
+  <si>
+    <t>SGSAFA4S25A000048</t>
+  </si>
+  <si>
+    <t>BNF-H26460</t>
+  </si>
+  <si>
+    <t>*199561103318</t>
+  </si>
+  <si>
+    <t>Mrs. SUNTHARALINGAM BANUJA</t>
+  </si>
+  <si>
+    <t>BNT01</t>
+  </si>
+  <si>
+    <t>POTHUHARA</t>
+  </si>
+  <si>
+    <t>NIRANJANS</t>
+  </si>
+  <si>
+    <t>BNT-H15225</t>
+  </si>
+  <si>
+    <t>*968343963V</t>
+  </si>
+  <si>
+    <t>Mrs. T M SHILPA SADAMALI</t>
+  </si>
+  <si>
+    <t>SGSAFA4S25B000653</t>
+  </si>
+  <si>
+    <t>BLE-H47913</t>
+  </si>
+  <si>
+    <t>*196912604335</t>
+  </si>
+  <si>
+    <t>Mr. D SUMATHIPALA</t>
+  </si>
+  <si>
+    <t>SGSAFA4S25C001028</t>
+  </si>
+  <si>
+    <t>MBC-H4023</t>
+  </si>
+  <si>
+    <t>*200724603507</t>
+  </si>
+  <si>
+    <t>Mr. H.M.PAVAN SANDEEPA HEARTH</t>
+  </si>
+  <si>
+    <t>BHD-H24987</t>
+  </si>
+  <si>
+    <t>BBP01</t>
+  </si>
+  <si>
+    <t>MIRIGAMA</t>
+  </si>
+  <si>
+    <t>JANAKAN</t>
+  </si>
+  <si>
+    <t>BBP-H50709</t>
+  </si>
+  <si>
+    <t>*621254421V</t>
+  </si>
+  <si>
+    <t>M.P.ABERATHNA</t>
+  </si>
+  <si>
+    <t>SGSAFA4S25D001281</t>
+  </si>
+  <si>
+    <t>SAI01</t>
+  </si>
+  <si>
+    <t>KATUGASTOTA - B</t>
+  </si>
+  <si>
+    <t>ANURUDDAJ</t>
+  </si>
+  <si>
+    <t>SAI-H16938</t>
+  </si>
+  <si>
+    <t>*885062130V</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. A.W.M.K.CHATHUMALA KUMARI WIJEKOON </t>
+  </si>
+  <si>
+    <t>BOD01</t>
+  </si>
+  <si>
+    <t>MATTAKKULIYA</t>
+  </si>
+  <si>
+    <t>ASANKAF</t>
+  </si>
+  <si>
+    <t>BOD-H10200</t>
+  </si>
+  <si>
+    <t>*772645007V</t>
+  </si>
+  <si>
+    <t>Mr. WEERAMALE SAGADEVAN</t>
+  </si>
+  <si>
+    <t>BDL-H35313</t>
+  </si>
+  <si>
+    <t>*195006405709</t>
+  </si>
+  <si>
+    <t>Mr. ELAIYATHAMBY KATHIRKAMATHTHAMBY</t>
+  </si>
+  <si>
+    <t>SGSAFA4S25D001418</t>
+  </si>
+  <si>
+    <t>BDT01</t>
+  </si>
+  <si>
+    <t>BUTTALA</t>
+  </si>
+  <si>
+    <t>LAHIRUG</t>
+  </si>
+  <si>
+    <t>BDT-H51176</t>
+  </si>
+  <si>
+    <t>*790912373V</t>
+  </si>
+  <si>
+    <t>Mr. N B INDUNIL PRIYANTHI</t>
+  </si>
+  <si>
+    <t>BPH-H806</t>
+  </si>
+  <si>
+    <t>*762093413V</t>
+  </si>
+  <si>
+    <t>Mr. W CHAMINDA ANURASIRI SILVA</t>
+  </si>
+  <si>
+    <t>SGSAFA4S25D001412</t>
+  </si>
+  <si>
+    <t>BGM-H44500</t>
+  </si>
+  <si>
+    <t>*200422301164</t>
+  </si>
+  <si>
+    <t>Mr. K A N K  LEELARATHNA</t>
+  </si>
+  <si>
+    <t>SGSAFA4S25B000492</t>
+  </si>
+  <si>
+    <t>BHM-H35910</t>
+  </si>
+  <si>
+    <t>*632633998V</t>
+  </si>
+  <si>
+    <t>M.R.SUNIL SHANTHA</t>
+  </si>
+  <si>
+    <t>SGSAFA4S25B000511</t>
+  </si>
+  <si>
+    <t>BGJ01</t>
+  </si>
+  <si>
+    <t>THAMBUTTEGAMA</t>
+  </si>
+  <si>
+    <t>PESHALAR</t>
+  </si>
+  <si>
+    <t>BGJ-H33766</t>
+  </si>
+  <si>
+    <t>*956192480V</t>
+  </si>
+  <si>
+    <t>M A S RASANGANI</t>
+  </si>
+  <si>
+    <t>LGMMVU1K0T0002409</t>
+  </si>
+  <si>
+    <t>BED01</t>
+  </si>
+  <si>
+    <t>WILGAMUWA</t>
+  </si>
+  <si>
+    <t>RANJITHD</t>
+  </si>
+  <si>
+    <t>BED-H29675</t>
+  </si>
+  <si>
+    <t>*885016294V</t>
+  </si>
+  <si>
+    <t>Ms. R.D.HASANJALI</t>
+  </si>
+  <si>
+    <t>BHM-H35751</t>
+  </si>
+  <si>
+    <t>*685984660V</t>
+  </si>
+  <si>
+    <t>Mrs. R.M.BANADARA MENIKE</t>
+  </si>
+  <si>
+    <t>SGSAFA4S25B000710</t>
+  </si>
+  <si>
+    <t>BMK-H18513</t>
+  </si>
+  <si>
+    <t>*640101890V</t>
+  </si>
+  <si>
+    <t>VARKISH MANIVEL</t>
+  </si>
+  <si>
+    <t>SGSAFA4S25A000358</t>
+  </si>
+  <si>
+    <t>BNF-H26419</t>
+  </si>
+  <si>
+    <t>*978471048V</t>
+  </si>
+  <si>
+    <t>Ms. T. ALAKSHIYA</t>
+  </si>
+  <si>
+    <t>SGSAFA4S25C000798</t>
+  </si>
+  <si>
+    <t>BGH-H42295</t>
+  </si>
+  <si>
+    <t>*757490439V</t>
+  </si>
+  <si>
+    <t>Mr. P A SUNTHTHRA</t>
+  </si>
+  <si>
+    <t>SGSAFA4S25C001097</t>
+  </si>
+  <si>
+    <t>BCD-H65169</t>
+  </si>
+  <si>
+    <t>*923102523V</t>
+  </si>
+  <si>
+    <t>W.M SURESH DINESHA WANNINAYAKE</t>
+  </si>
+  <si>
+    <t>SGSAFA4S25C000974</t>
+  </si>
+  <si>
+    <t>BOJ-H9465</t>
+  </si>
+  <si>
+    <t>*198463804138</t>
+  </si>
+  <si>
+    <t>Mrs. THAVANESHWARAN KIRIYA</t>
+  </si>
+  <si>
+    <t>SGSAFA4S25C001072</t>
+  </si>
+  <si>
+    <t>BCX01</t>
+  </si>
+  <si>
+    <t>MAWARAMANDIYA</t>
+  </si>
+  <si>
+    <t>JANAKACHA</t>
+  </si>
+  <si>
+    <t>BCX-H17403</t>
+  </si>
+  <si>
+    <t>*200635603981</t>
+  </si>
+  <si>
+    <t>Mr. DESHA VIMUKTHI  BANDARANAYAKE</t>
+  </si>
+  <si>
+    <t>BMK-H18552</t>
+  </si>
+  <si>
+    <t>*746314477V</t>
+  </si>
+  <si>
+    <t>Miss. MEGI APPAN MARI AMMA</t>
+  </si>
+  <si>
+    <t>SGSAFA4S25C000944</t>
+  </si>
+  <si>
+    <t>BBI-H27631</t>
+  </si>
+  <si>
+    <t>BJE-H26939</t>
+  </si>
+  <si>
+    <t>*197627601823</t>
+  </si>
+  <si>
+    <t>Mr. D CHAMINDA RANJITH KUMARA</t>
+  </si>
+  <si>
+    <t>SGSAFA4S25B000672</t>
+  </si>
+  <si>
+    <t>BGH-H42191</t>
+  </si>
+  <si>
+    <t>*971091851V</t>
+  </si>
+  <si>
+    <t>Mr. A S DARSHANA MADUSHANKA</t>
+  </si>
+  <si>
+    <t>SGSAFA4S25C001033</t>
+  </si>
+  <si>
+    <t>BGY-H7766</t>
+  </si>
+  <si>
+    <t>BGH-H42375</t>
+  </si>
+  <si>
+    <t>*921211767V</t>
+  </si>
+  <si>
+    <t>Mr. J.A.S.P.S.JAYAKODI.</t>
+  </si>
+  <si>
+    <t>SGSAFA4S25D001308</t>
+  </si>
+  <si>
+    <t>BKY-H25879</t>
+  </si>
+  <si>
+    <t>BJD-H53431</t>
+  </si>
+  <si>
+    <t>*200605002051</t>
+  </si>
+  <si>
+    <t>Mr. A N RASHMIKA</t>
+  </si>
+  <si>
+    <t>L1Z1LL518SA569621</t>
+  </si>
+  <si>
+    <t>SCN-H13415</t>
+  </si>
+  <si>
+    <t>*845054231V</t>
+  </si>
+  <si>
+    <t>Mrs. Yogawathy Krishnakumar</t>
+  </si>
+  <si>
+    <t>SGSAFA4S25D001224</t>
+  </si>
+  <si>
+    <t>BBP-H50710</t>
+  </si>
+  <si>
+    <t>*838201504V</t>
+  </si>
+  <si>
+    <t>Miss. AMALPA MADUSHANI</t>
+  </si>
+  <si>
+    <t>SGSAFA4S25A000187</t>
+  </si>
+  <si>
+    <t>FBA01</t>
+  </si>
+  <si>
+    <t>SHOMES-KADAWATHA</t>
+  </si>
+  <si>
+    <t>PALITHAC</t>
+  </si>
+  <si>
+    <t>FBA-H13201</t>
+  </si>
+  <si>
+    <t>*840942201V</t>
+  </si>
+  <si>
+    <t>Mr. K.A.CHILAN AKALANKA</t>
+  </si>
+  <si>
+    <t>BEA01</t>
+  </si>
+  <si>
+    <t>DEHIATTAKANDIYA</t>
+  </si>
+  <si>
+    <t>GAMINIT</t>
+  </si>
+  <si>
+    <t>BEA-H56754</t>
+  </si>
+  <si>
+    <t>*561500096V</t>
+  </si>
+  <si>
+    <t>Mr. D.S ARIYAPALA</t>
+  </si>
+  <si>
+    <t>SGSAFA4S25D001225</t>
+  </si>
+  <si>
+    <t>SBU01</t>
+  </si>
+  <si>
+    <t>KAHAWATTA - B</t>
+  </si>
+  <si>
+    <t>MANJULAT</t>
+  </si>
+  <si>
+    <t>SBU-H25800</t>
+  </si>
+  <si>
+    <t>*200804401075</t>
+  </si>
+  <si>
+    <t>Mr. WARUSHA NIMALKA L.A.</t>
+  </si>
+  <si>
+    <t>BJE-H26775</t>
+  </si>
+  <si>
+    <t>*712223740V</t>
+  </si>
+  <si>
+    <t>Mr. W D JAYASEKARA</t>
+  </si>
+  <si>
+    <t>SGSAFA4S25B000734</t>
+  </si>
+  <si>
+    <t>BHH-H23602</t>
+  </si>
+  <si>
+    <t>*817580556V</t>
+  </si>
+  <si>
+    <t>Mrs. B W DEEPIKA</t>
+  </si>
+  <si>
+    <t>LGMMVU1K1T0002306.</t>
+  </si>
+  <si>
+    <t>BMF01</t>
+  </si>
+  <si>
+    <t>MANIPAY</t>
+  </si>
+  <si>
+    <t>THANUJANT</t>
+  </si>
+  <si>
+    <t>BMF-H15673</t>
+  </si>
+  <si>
+    <t>*198108702136</t>
+  </si>
+  <si>
+    <t>Mr. KANTHAYA JEYAKUMAR</t>
+  </si>
+  <si>
+    <t>SGSAFA4S25B000415</t>
+  </si>
+  <si>
+    <t>BJP01</t>
+  </si>
+  <si>
+    <t>HAKMANA</t>
+  </si>
+  <si>
+    <t>SARATHD</t>
+  </si>
+  <si>
+    <t>BJP-H43416</t>
+  </si>
+  <si>
+    <t>*840333191V</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. S. A. JANAKA  PRIYADARSHANA </t>
+  </si>
+  <si>
+    <t>BNK-H27222</t>
+  </si>
+  <si>
+    <t>*630902916V</t>
+  </si>
+  <si>
+    <t>Mr. K. GNASEKARAM</t>
+  </si>
+  <si>
+    <t>LGMMVU1KXT0002112</t>
+  </si>
+  <si>
+    <t>LGMMVU1H0T0000115</t>
+  </si>
+  <si>
+    <t>LGMMVU1H6T0000233</t>
+  </si>
+  <si>
+    <t>LGMMVU1K0T0002006</t>
+  </si>
+  <si>
+    <t>LGMMVU1K3T0001965</t>
+  </si>
+  <si>
+    <t>LGMMVU1K4T0003000</t>
+  </si>
+  <si>
+    <t>LGMMVU1K6T0002494</t>
+  </si>
+  <si>
+    <t>LGMMVU1H1T0000401</t>
+  </si>
+  <si>
+    <t>LGMMVU1HXT0000395</t>
+  </si>
+  <si>
+    <t>LGMMVU1K1T0002287</t>
+  </si>
+  <si>
+    <t>LGMMVU1K1T0002208</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="3">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2631,8 +3432,27 @@
       <name val="Calibri"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2642,6 +3462,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2675,12 +3501,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
@@ -2700,14 +3526,77 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="41">
+  <dxfs count="46">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3175,49 +4064,49 @@
   </dxfs>
   <tableStyles count="4" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" dxfId="40"/>
-      <tableStyleElement type="headerRow" dxfId="39"/>
-      <tableStyleElement type="totalRow" dxfId="38"/>
-      <tableStyleElement type="firstColumn" dxfId="37"/>
-      <tableStyleElement type="lastColumn" dxfId="36"/>
-      <tableStyleElement type="firstRowStripe" dxfId="35"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="34"/>
+      <tableStyleElement type="wholeTable" dxfId="45"/>
+      <tableStyleElement type="headerRow" dxfId="44"/>
+      <tableStyleElement type="totalRow" dxfId="43"/>
+      <tableStyleElement type="firstColumn" dxfId="42"/>
+      <tableStyleElement type="lastColumn" dxfId="41"/>
+      <tableStyleElement type="firstRowStripe" dxfId="40"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="39"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1 2" pivot="0" table="0" count="10" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
-      <tableStyleElement type="headerRow" dxfId="33"/>
-      <tableStyleElement type="totalRow" dxfId="32"/>
-      <tableStyleElement type="firstRowStripe" dxfId="31"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="30"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="29"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="28"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="27"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="26"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="25"/>
-      <tableStyleElement type="pageFieldValues" dxfId="24"/>
+      <tableStyleElement type="headerRow" dxfId="38"/>
+      <tableStyleElement type="totalRow" dxfId="37"/>
+      <tableStyleElement type="firstRowStripe" dxfId="36"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="35"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="34"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="33"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="32"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="31"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="30"/>
+      <tableStyleElement type="pageFieldValues" dxfId="29"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1 3" pivot="0" table="0" count="10" xr9:uid="{00000000-0011-0000-FFFF-FFFF02000000}">
-      <tableStyleElement type="headerRow" dxfId="23"/>
-      <tableStyleElement type="totalRow" dxfId="22"/>
-      <tableStyleElement type="firstRowStripe" dxfId="21"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="20"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="19"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="18"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="17"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="16"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="15"/>
-      <tableStyleElement type="pageFieldValues" dxfId="14"/>
+      <tableStyleElement type="headerRow" dxfId="28"/>
+      <tableStyleElement type="totalRow" dxfId="27"/>
+      <tableStyleElement type="firstRowStripe" dxfId="26"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="25"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="24"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="23"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="22"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="21"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="20"/>
+      <tableStyleElement type="pageFieldValues" dxfId="19"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{00000000-0011-0000-FFFF-FFFF03000000}">
-      <tableStyleElement type="headerRow" dxfId="13"/>
-      <tableStyleElement type="totalRow" dxfId="12"/>
-      <tableStyleElement type="firstRowStripe" dxfId="11"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="9"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="8"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="7"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="6"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="5"/>
-      <tableStyleElement type="pageFieldValues" dxfId="4"/>
+      <tableStyleElement type="headerRow" dxfId="18"/>
+      <tableStyleElement type="totalRow" dxfId="17"/>
+      <tableStyleElement type="firstRowStripe" dxfId="16"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="15"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="14"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="13"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="12"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="11"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="10"/>
+      <tableStyleElement type="pageFieldValues" dxfId="9"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -3229,6 +4118,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3480,14 +4373,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:Z129"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr codeName="Sheet1" filterMode="1"/>
+  <dimension ref="A1:Z221"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="34.7265625" customWidth="1"/>
-    <col min="2" max="2" width="24.1796875" customWidth="1"/>
-    <col min="3" max="3" width="15.453125" customWidth="1"/>
+    <col min="1" max="1" width="34.7265625" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="24.1796875" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="15.453125" hidden="1" customWidth="1"/>
     <col min="4" max="4" width="20.08984375" customWidth="1"/>
     <col min="5" max="5" width="13" customWidth="1"/>
     <col min="6" max="6" width="21.1796875" customWidth="1"/>
@@ -3499,14 +4392,14 @@
     <col min="12" max="12" width="33.6328125" customWidth="1"/>
     <col min="13" max="13" width="11.81640625" customWidth="1"/>
     <col min="14" max="14" width="22.08984375" customWidth="1"/>
-    <col min="15" max="15" width="15" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="24.453125" hidden="1" customWidth="1"/>
-    <col min="17" max="17" width="28.08984375" hidden="1" customWidth="1"/>
-    <col min="18" max="18" width="10.1796875" hidden="1" customWidth="1"/>
-    <col min="19" max="19" width="25.6328125" hidden="1" customWidth="1"/>
-    <col min="20" max="20" width="239.1796875" hidden="1" customWidth="1"/>
-    <col min="21" max="21" width="99.90625" hidden="1" customWidth="1"/>
-    <col min="22" max="22" width="22" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="15" customWidth="1"/>
+    <col min="16" max="16" width="24.453125" customWidth="1"/>
+    <col min="17" max="17" width="28.08984375" customWidth="1"/>
+    <col min="18" max="18" width="10.1796875" customWidth="1"/>
+    <col min="19" max="19" width="25.6328125" customWidth="1"/>
+    <col min="20" max="20" width="239.1796875" customWidth="1"/>
+    <col min="21" max="21" width="99.90625" customWidth="1"/>
+    <col min="22" max="22" width="22" customWidth="1"/>
     <col min="23" max="23" width="70.81640625" customWidth="1"/>
     <col min="24" max="24" width="8.1796875" customWidth="1"/>
     <col min="25" max="26" width="49.453125" customWidth="1"/>
@@ -3592,7 +4485,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:26">
+    <row r="2" spans="1:26" hidden="1">
       <c r="A2" s="3" t="s">
         <v>26</v>
       </c>
@@ -3652,7 +4545,7 @@
       </c>
       <c r="Z2" s="9"/>
     </row>
-    <row r="3" spans="1:26">
+    <row r="3" spans="1:26" hidden="1">
       <c r="A3" s="3" t="s">
         <v>38</v>
       </c>
@@ -3704,7 +4597,7 @@
       </c>
       <c r="Z3" s="9"/>
     </row>
-    <row r="4" spans="1:26">
+    <row r="4" spans="1:26" hidden="1">
       <c r="A4" s="3" t="s">
         <v>48</v>
       </c>
@@ -3764,7 +4657,7 @@
       </c>
       <c r="Z4" s="9"/>
     </row>
-    <row r="5" spans="1:26">
+    <row r="5" spans="1:26" hidden="1">
       <c r="A5" s="3" t="s">
         <v>57</v>
       </c>
@@ -3816,7 +4709,7 @@
       </c>
       <c r="Z5" s="9"/>
     </row>
-    <row r="6" spans="1:26">
+    <row r="6" spans="1:26" hidden="1">
       <c r="A6" s="3" t="s">
         <v>57</v>
       </c>
@@ -3870,7 +4763,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="7" spans="1:26">
+    <row r="7" spans="1:26" hidden="1">
       <c r="A7" s="3" t="s">
         <v>57</v>
       </c>
@@ -3924,7 +4817,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="8" spans="1:26">
+    <row r="8" spans="1:26" hidden="1">
       <c r="A8" s="3" t="s">
         <v>57</v>
       </c>
@@ -3978,7 +4871,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="9" spans="1:26">
+    <row r="9" spans="1:26" hidden="1">
       <c r="A9" s="3" t="s">
         <v>57</v>
       </c>
@@ -4032,7 +4925,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="10" spans="1:26">
+    <row r="10" spans="1:26" hidden="1">
       <c r="A10" s="3" t="s">
         <v>84</v>
       </c>
@@ -4092,7 +4985,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="11" spans="1:26">
+    <row r="11" spans="1:26" hidden="1">
       <c r="A11" s="3" t="s">
         <v>84</v>
       </c>
@@ -4152,7 +5045,7 @@
       </c>
       <c r="Z11" s="9"/>
     </row>
-    <row r="12" spans="1:26">
+    <row r="12" spans="1:26" hidden="1">
       <c r="A12" s="3" t="s">
         <v>100</v>
       </c>
@@ -4212,7 +5105,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="13" spans="1:26">
+    <row r="13" spans="1:26" hidden="1">
       <c r="A13" s="3" t="s">
         <v>100</v>
       </c>
@@ -4270,7 +5163,7 @@
       </c>
       <c r="Z13" s="9"/>
     </row>
-    <row r="14" spans="1:26">
+    <row r="14" spans="1:26" hidden="1">
       <c r="A14" s="3" t="s">
         <v>100</v>
       </c>
@@ -4328,7 +5221,7 @@
       </c>
       <c r="Z14" s="9"/>
     </row>
-    <row r="15" spans="1:26">
+    <row r="15" spans="1:26" hidden="1">
       <c r="A15" s="3" t="s">
         <v>100</v>
       </c>
@@ -4386,7 +5279,7 @@
       </c>
       <c r="Z15" s="9"/>
     </row>
-    <row r="16" spans="1:26">
+    <row r="16" spans="1:26" hidden="1">
       <c r="A16" s="3" t="s">
         <v>100</v>
       </c>
@@ -4442,7 +5335,7 @@
       </c>
       <c r="Z16" s="9"/>
     </row>
-    <row r="17" spans="1:26">
+    <row r="17" spans="1:26" hidden="1">
       <c r="A17" s="3" t="s">
         <v>100</v>
       </c>
@@ -4494,7 +5387,7 @@
       </c>
       <c r="Z17" s="9"/>
     </row>
-    <row r="18" spans="1:26">
+    <row r="18" spans="1:26" hidden="1">
       <c r="A18" s="3" t="s">
         <v>135</v>
       </c>
@@ -4546,7 +5439,7 @@
       </c>
       <c r="Z18" s="9"/>
     </row>
-    <row r="19" spans="1:26">
+    <row r="19" spans="1:26" hidden="1">
       <c r="A19" s="3" t="s">
         <v>142</v>
       </c>
@@ -4604,7 +5497,7 @@
       </c>
       <c r="Z19" s="9"/>
     </row>
-    <row r="20" spans="1:26">
+    <row r="20" spans="1:26" hidden="1">
       <c r="A20" s="3" t="s">
         <v>151</v>
       </c>
@@ -4662,7 +5555,7 @@
       </c>
       <c r="Z20" s="9"/>
     </row>
-    <row r="21" spans="1:26">
+    <row r="21" spans="1:26" hidden="1">
       <c r="A21" s="3" t="s">
         <v>159</v>
       </c>
@@ -4722,7 +5615,7 @@
       </c>
       <c r="Z21" s="9"/>
     </row>
-    <row r="22" spans="1:26">
+    <row r="22" spans="1:26" hidden="1">
       <c r="A22" s="3" t="s">
         <v>159</v>
       </c>
@@ -4778,7 +5671,7 @@
       </c>
       <c r="Z22" s="3"/>
     </row>
-    <row r="23" spans="1:26">
+    <row r="23" spans="1:26" hidden="1">
       <c r="A23" s="3" t="s">
         <v>174</v>
       </c>
@@ -4836,7 +5729,7 @@
       </c>
       <c r="Z23" s="9"/>
     </row>
-    <row r="24" spans="1:26">
+    <row r="24" spans="1:26" hidden="1">
       <c r="A24" s="3" t="s">
         <v>182</v>
       </c>
@@ -4888,7 +5781,7 @@
       </c>
       <c r="Z24" s="3"/>
     </row>
-    <row r="25" spans="1:26">
+    <row r="25" spans="1:26" hidden="1">
       <c r="A25" s="3" t="s">
         <v>189</v>
       </c>
@@ -4940,7 +5833,7 @@
       </c>
       <c r="Z25" s="9"/>
     </row>
-    <row r="26" spans="1:26">
+    <row r="26" spans="1:26" hidden="1">
       <c r="A26" s="3" t="s">
         <v>197</v>
       </c>
@@ -4996,7 +5889,7 @@
       </c>
       <c r="Z26" s="9"/>
     </row>
-    <row r="27" spans="1:26">
+    <row r="27" spans="1:26" hidden="1">
       <c r="A27" s="3" t="s">
         <v>205</v>
       </c>
@@ -5056,7 +5949,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="28" spans="1:26">
+    <row r="28" spans="1:26" hidden="1">
       <c r="A28" s="3" t="s">
         <v>213</v>
       </c>
@@ -5114,7 +6007,7 @@
       </c>
       <c r="Z28" s="9"/>
     </row>
-    <row r="29" spans="1:26">
+    <row r="29" spans="1:26" hidden="1">
       <c r="A29" s="3" t="s">
         <v>220</v>
       </c>
@@ -5172,7 +6065,7 @@
       </c>
       <c r="Z29" s="9"/>
     </row>
-    <row r="30" spans="1:26">
+    <row r="30" spans="1:26" hidden="1">
       <c r="A30" s="3" t="s">
         <v>220</v>
       </c>
@@ -5230,7 +6123,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="31" spans="1:26">
+    <row r="31" spans="1:26" hidden="1">
       <c r="A31" s="3" t="s">
         <v>234</v>
       </c>
@@ -5290,7 +6183,7 @@
       </c>
       <c r="Z31" s="9"/>
     </row>
-    <row r="32" spans="1:26">
+    <row r="32" spans="1:26" hidden="1">
       <c r="A32" s="3" t="s">
         <v>244</v>
       </c>
@@ -5350,7 +6243,7 @@
       </c>
       <c r="Z32" s="9"/>
     </row>
-    <row r="33" spans="1:26">
+    <row r="33" spans="1:26" hidden="1">
       <c r="A33" s="3" t="s">
         <v>244</v>
       </c>
@@ -5410,7 +6303,7 @@
       </c>
       <c r="Z33" s="9"/>
     </row>
-    <row r="34" spans="1:26">
+    <row r="34" spans="1:26" hidden="1">
       <c r="A34" s="3" t="s">
         <v>259</v>
       </c>
@@ -5464,7 +6357,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="35" spans="1:26">
+    <row r="35" spans="1:26" hidden="1">
       <c r="A35" s="3" t="s">
         <v>267</v>
       </c>
@@ -5524,7 +6417,7 @@
       </c>
       <c r="Z35" s="9"/>
     </row>
-    <row r="36" spans="1:26">
+    <row r="36" spans="1:26" hidden="1">
       <c r="A36" s="3" t="s">
         <v>275</v>
       </c>
@@ -5576,7 +6469,7 @@
       </c>
       <c r="Z36" s="9"/>
     </row>
-    <row r="37" spans="1:26">
+    <row r="37" spans="1:26" hidden="1">
       <c r="A37" s="3" t="s">
         <v>275</v>
       </c>
@@ -5628,7 +6521,7 @@
       </c>
       <c r="Z37" s="9"/>
     </row>
-    <row r="38" spans="1:26">
+    <row r="38" spans="1:26" hidden="1">
       <c r="A38" s="3" t="s">
         <v>287</v>
       </c>
@@ -5686,7 +6579,7 @@
       </c>
       <c r="Z38" s="9"/>
     </row>
-    <row r="39" spans="1:26">
+    <row r="39" spans="1:26" hidden="1">
       <c r="A39" s="3" t="s">
         <v>287</v>
       </c>
@@ -5744,7 +6637,7 @@
       </c>
       <c r="Z39" s="9"/>
     </row>
-    <row r="40" spans="1:26">
+    <row r="40" spans="1:26" hidden="1">
       <c r="A40" s="3" t="s">
         <v>287</v>
       </c>
@@ -5804,7 +6697,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="41" spans="1:26">
+    <row r="41" spans="1:26" hidden="1">
       <c r="A41" s="3" t="s">
         <v>305</v>
       </c>
@@ -5856,7 +6749,7 @@
       </c>
       <c r="Z41" s="9"/>
     </row>
-    <row r="42" spans="1:26">
+    <row r="42" spans="1:26" hidden="1">
       <c r="A42" s="3" t="s">
         <v>305</v>
       </c>
@@ -5908,7 +6801,7 @@
       </c>
       <c r="Z42" s="9"/>
     </row>
-    <row r="43" spans="1:26">
+    <row r="43" spans="1:26" hidden="1">
       <c r="A43" s="3" t="s">
         <v>317</v>
       </c>
@@ -5962,7 +6855,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="44" spans="1:26">
+    <row r="44" spans="1:26" hidden="1">
       <c r="A44" s="3" t="s">
         <v>324</v>
       </c>
@@ -6018,7 +6911,7 @@
       </c>
       <c r="Z44" s="9"/>
     </row>
-    <row r="45" spans="1:26">
+    <row r="45" spans="1:26" hidden="1">
       <c r="A45" s="3" t="s">
         <v>332</v>
       </c>
@@ -6076,7 +6969,7 @@
       </c>
       <c r="Z45" s="9"/>
     </row>
-    <row r="46" spans="1:26">
+    <row r="46" spans="1:26" hidden="1">
       <c r="A46" s="3" t="s">
         <v>332</v>
       </c>
@@ -6132,7 +7025,7 @@
       </c>
       <c r="Z46" s="9"/>
     </row>
-    <row r="47" spans="1:26">
+    <row r="47" spans="1:26" hidden="1">
       <c r="A47" s="3" t="s">
         <v>345</v>
       </c>
@@ -6184,7 +7077,7 @@
       </c>
       <c r="Z47" s="9"/>
     </row>
-    <row r="48" spans="1:26">
+    <row r="48" spans="1:26" hidden="1">
       <c r="A48" s="3" t="s">
         <v>353</v>
       </c>
@@ -6240,7 +7133,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="49" spans="1:26">
+    <row r="49" spans="1:26" hidden="1">
       <c r="A49" s="3" t="s">
         <v>361</v>
       </c>
@@ -6298,7 +7191,7 @@
       </c>
       <c r="Z49" s="9"/>
     </row>
-    <row r="50" spans="1:26">
+    <row r="50" spans="1:26" hidden="1">
       <c r="A50" s="3" t="s">
         <v>370</v>
       </c>
@@ -6350,7 +7243,7 @@
       </c>
       <c r="Z50" s="3"/>
     </row>
-    <row r="51" spans="1:26">
+    <row r="51" spans="1:26" hidden="1">
       <c r="A51" s="3" t="s">
         <v>377</v>
       </c>
@@ -6408,7 +7301,7 @@
       </c>
       <c r="Z51" s="3"/>
     </row>
-    <row r="52" spans="1:26">
+    <row r="52" spans="1:26" hidden="1">
       <c r="A52" s="3" t="s">
         <v>385</v>
       </c>
@@ -6460,7 +7353,7 @@
       </c>
       <c r="Z52" s="9"/>
     </row>
-    <row r="53" spans="1:26">
+    <row r="53" spans="1:26" hidden="1">
       <c r="A53" s="3" t="s">
         <v>392</v>
       </c>
@@ -6518,7 +7411,7 @@
       </c>
       <c r="Z53" s="9"/>
     </row>
-    <row r="54" spans="1:26">
+    <row r="54" spans="1:26" hidden="1">
       <c r="A54" s="3" t="s">
         <v>401</v>
       </c>
@@ -6578,7 +7471,7 @@
       </c>
       <c r="Z54" s="9"/>
     </row>
-    <row r="55" spans="1:26">
+    <row r="55" spans="1:26" hidden="1">
       <c r="A55" s="3" t="s">
         <v>401</v>
       </c>
@@ -6638,7 +7531,7 @@
       </c>
       <c r="Z55" s="9"/>
     </row>
-    <row r="56" spans="1:26">
+    <row r="56" spans="1:26" hidden="1">
       <c r="A56" s="3" t="s">
         <v>401</v>
       </c>
@@ -6698,7 +7591,7 @@
       </c>
       <c r="Z56" s="9"/>
     </row>
-    <row r="57" spans="1:26">
+    <row r="57" spans="1:26" hidden="1">
       <c r="A57" s="3" t="s">
         <v>401</v>
       </c>
@@ -6758,7 +7651,7 @@
       </c>
       <c r="Z57" s="9"/>
     </row>
-    <row r="58" spans="1:26">
+    <row r="58" spans="1:26" hidden="1">
       <c r="A58" s="3" t="s">
         <v>401</v>
       </c>
@@ -6816,7 +7709,7 @@
       </c>
       <c r="Z58" s="3"/>
     </row>
-    <row r="59" spans="1:26">
+    <row r="59" spans="1:26" hidden="1">
       <c r="A59" s="3" t="s">
         <v>401</v>
       </c>
@@ -6874,7 +7767,7 @@
       </c>
       <c r="Z59" s="9"/>
     </row>
-    <row r="60" spans="1:26">
+    <row r="60" spans="1:26" hidden="1">
       <c r="A60" s="3" t="s">
         <v>401</v>
       </c>
@@ -6934,7 +7827,7 @@
       </c>
       <c r="Z60" s="9"/>
     </row>
-    <row r="61" spans="1:26">
+    <row r="61" spans="1:26" hidden="1">
       <c r="A61" s="3" t="s">
         <v>401</v>
       </c>
@@ -6994,7 +7887,7 @@
       </c>
       <c r="Z61" s="9"/>
     </row>
-    <row r="62" spans="1:26">
+    <row r="62" spans="1:26" hidden="1">
       <c r="A62" s="3" t="s">
         <v>401</v>
       </c>
@@ -7054,7 +7947,7 @@
       </c>
       <c r="Z62" s="9"/>
     </row>
-    <row r="63" spans="1:26">
+    <row r="63" spans="1:26" hidden="1">
       <c r="A63" s="3" t="s">
         <v>401</v>
       </c>
@@ -7106,7 +7999,7 @@
       </c>
       <c r="Z63" s="9"/>
     </row>
-    <row r="64" spans="1:26">
+    <row r="64" spans="1:26" hidden="1">
       <c r="A64" s="3" t="s">
         <v>401</v>
       </c>
@@ -7158,7 +8051,7 @@
       </c>
       <c r="Z64" s="9"/>
     </row>
-    <row r="65" spans="1:26">
+    <row r="65" spans="1:26" hidden="1">
       <c r="A65" s="3" t="s">
         <v>458</v>
       </c>
@@ -7216,7 +8109,7 @@
       </c>
       <c r="Z65" s="9"/>
     </row>
-    <row r="66" spans="1:26">
+    <row r="66" spans="1:26" hidden="1">
       <c r="A66" s="3" t="s">
         <v>458</v>
       </c>
@@ -7274,7 +8167,7 @@
       </c>
       <c r="Z66" s="9"/>
     </row>
-    <row r="67" spans="1:26">
+    <row r="67" spans="1:26" hidden="1">
       <c r="A67" s="3" t="s">
         <v>458</v>
       </c>
@@ -7326,7 +8219,7 @@
       </c>
       <c r="Z67" s="3"/>
     </row>
-    <row r="68" spans="1:26">
+    <row r="68" spans="1:26" hidden="1">
       <c r="A68" s="3" t="s">
         <v>474</v>
       </c>
@@ -7388,7 +8281,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="69" spans="1:26">
+    <row r="69" spans="1:26" hidden="1">
       <c r="A69" s="3" t="s">
         <v>483</v>
       </c>
@@ -7446,7 +8339,7 @@
       </c>
       <c r="Z69" s="9"/>
     </row>
-    <row r="70" spans="1:26">
+    <row r="70" spans="1:26" hidden="1">
       <c r="A70" s="3" t="s">
         <v>491</v>
       </c>
@@ -7506,7 +8399,7 @@
       </c>
       <c r="Z70" s="9"/>
     </row>
-    <row r="71" spans="1:26">
+    <row r="71" spans="1:26" hidden="1">
       <c r="A71" s="3" t="s">
         <v>491</v>
       </c>
@@ -7566,7 +8459,7 @@
       </c>
       <c r="Z71" s="9"/>
     </row>
-    <row r="72" spans="1:26">
+    <row r="72" spans="1:26" hidden="1">
       <c r="A72" s="3" t="s">
         <v>491</v>
       </c>
@@ -7626,7 +8519,7 @@
       </c>
       <c r="Z72" s="9"/>
     </row>
-    <row r="73" spans="1:26">
+    <row r="73" spans="1:26" hidden="1">
       <c r="A73" s="3" t="s">
         <v>491</v>
       </c>
@@ -7686,7 +8579,7 @@
       </c>
       <c r="Z73" s="9"/>
     </row>
-    <row r="74" spans="1:26">
+    <row r="74" spans="1:26" hidden="1">
       <c r="A74" s="3" t="s">
         <v>518</v>
       </c>
@@ -7742,7 +8635,7 @@
       </c>
       <c r="Z74" s="9"/>
     </row>
-    <row r="75" spans="1:26">
+    <row r="75" spans="1:26" hidden="1">
       <c r="A75" s="3" t="s">
         <v>525</v>
       </c>
@@ -7796,7 +8689,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="76" spans="1:26">
+    <row r="76" spans="1:26" hidden="1">
       <c r="A76" s="3" t="s">
         <v>533</v>
       </c>
@@ -7850,7 +8743,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="77" spans="1:26">
+    <row r="77" spans="1:26" hidden="1">
       <c r="A77" s="3" t="s">
         <v>533</v>
       </c>
@@ -7904,7 +8797,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="78" spans="1:26">
+    <row r="78" spans="1:26" hidden="1">
       <c r="A78" s="3" t="s">
         <v>533</v>
       </c>
@@ -7958,7 +8851,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="79" spans="1:26">
+    <row r="79" spans="1:26" hidden="1">
       <c r="A79" s="3" t="s">
         <v>547</v>
       </c>
@@ -8024,7 +8917,7 @@
       </c>
       <c r="Z79" s="9"/>
     </row>
-    <row r="80" spans="1:26">
+    <row r="80" spans="1:26" hidden="1">
       <c r="A80" s="3" t="s">
         <v>547</v>
       </c>
@@ -8084,7 +8977,7 @@
       </c>
       <c r="Z80" s="9"/>
     </row>
-    <row r="81" spans="1:26">
+    <row r="81" spans="1:26" hidden="1">
       <c r="A81" s="3" t="s">
         <v>564</v>
       </c>
@@ -8144,7 +9037,7 @@
       </c>
       <c r="Z81" s="9"/>
     </row>
-    <row r="82" spans="1:26">
+    <row r="82" spans="1:26" hidden="1">
       <c r="A82" s="3" t="s">
         <v>564</v>
       </c>
@@ -8196,7 +9089,7 @@
       </c>
       <c r="Z82" s="9"/>
     </row>
-    <row r="83" spans="1:26">
+    <row r="83" spans="1:26" hidden="1">
       <c r="A83" s="3" t="s">
         <v>577</v>
       </c>
@@ -8250,7 +9143,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="84" spans="1:26">
+    <row r="84" spans="1:26" hidden="1">
       <c r="A84" s="3" t="s">
         <v>584</v>
       </c>
@@ -8304,7 +9197,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="85" spans="1:26">
+    <row r="85" spans="1:26" hidden="1">
       <c r="A85" s="3" t="s">
         <v>584</v>
       </c>
@@ -8358,7 +9251,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="86" spans="1:26">
+    <row r="86" spans="1:26" hidden="1">
       <c r="A86" s="3" t="s">
         <v>584</v>
       </c>
@@ -8412,7 +9305,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="87" spans="1:26">
+    <row r="87" spans="1:26" hidden="1">
       <c r="A87" s="3" t="s">
         <v>584</v>
       </c>
@@ -8466,7 +9359,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="88" spans="1:26">
+    <row r="88" spans="1:26" hidden="1">
       <c r="A88" s="3" t="s">
         <v>603</v>
       </c>
@@ -8518,7 +9411,7 @@
       </c>
       <c r="Z88" s="9"/>
     </row>
-    <row r="89" spans="1:26">
+    <row r="89" spans="1:26" hidden="1">
       <c r="A89" s="3" t="s">
         <v>603</v>
       </c>
@@ -8570,7 +9463,7 @@
       </c>
       <c r="Z89" s="9"/>
     </row>
-    <row r="90" spans="1:26">
+    <row r="90" spans="1:26" hidden="1">
       <c r="A90" s="3" t="s">
         <v>615</v>
       </c>
@@ -8628,7 +9521,7 @@
       </c>
       <c r="Z90" s="9"/>
     </row>
-    <row r="91" spans="1:26">
+    <row r="91" spans="1:26" hidden="1">
       <c r="A91" s="3" t="s">
         <v>615</v>
       </c>
@@ -8680,7 +9573,7 @@
       </c>
       <c r="Z91" s="9"/>
     </row>
-    <row r="92" spans="1:26">
+    <row r="92" spans="1:26" hidden="1">
       <c r="A92" s="3" t="s">
         <v>627</v>
       </c>
@@ -8738,7 +9631,7 @@
       </c>
       <c r="Z92" s="9"/>
     </row>
-    <row r="93" spans="1:26">
+    <row r="93" spans="1:26" hidden="1">
       <c r="A93" s="3" t="s">
         <v>627</v>
       </c>
@@ -8796,7 +9689,7 @@
       </c>
       <c r="Z93" s="9"/>
     </row>
-    <row r="94" spans="1:26">
+    <row r="94" spans="1:26" hidden="1">
       <c r="A94" s="3" t="s">
         <v>641</v>
       </c>
@@ -8848,7 +9741,7 @@
       </c>
       <c r="Z94" s="9"/>
     </row>
-    <row r="95" spans="1:26">
+    <row r="95" spans="1:26" hidden="1">
       <c r="A95" s="3" t="s">
         <v>648</v>
       </c>
@@ -8908,7 +9801,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="96" spans="1:26">
+    <row r="96" spans="1:26" hidden="1">
       <c r="A96" s="3" t="s">
         <v>648</v>
       </c>
@@ -8960,7 +9853,7 @@
       </c>
       <c r="Z96" s="9"/>
     </row>
-    <row r="97" spans="1:26">
+    <row r="97" spans="1:26" hidden="1">
       <c r="A97" s="3" t="s">
         <v>661</v>
       </c>
@@ -9020,7 +9913,7 @@
       </c>
       <c r="Z97" s="9"/>
     </row>
-    <row r="98" spans="1:26">
+    <row r="98" spans="1:26" hidden="1">
       <c r="A98" s="3" t="s">
         <v>670</v>
       </c>
@@ -9080,7 +9973,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="99" spans="1:26">
+    <row r="99" spans="1:26" hidden="1">
       <c r="A99" s="3" t="s">
         <v>670</v>
       </c>
@@ -9132,7 +10025,7 @@
       </c>
       <c r="Z99" s="9"/>
     </row>
-    <row r="100" spans="1:26">
+    <row r="100" spans="1:26" hidden="1">
       <c r="A100" s="3" t="s">
         <v>670</v>
       </c>
@@ -9184,7 +10077,7 @@
       </c>
       <c r="Z100" s="9"/>
     </row>
-    <row r="101" spans="1:26">
+    <row r="101" spans="1:26" hidden="1">
       <c r="A101" s="3" t="s">
         <v>686</v>
       </c>
@@ -9226,9 +10119,7 @@
       <c r="S101" s="3"/>
       <c r="T101" s="3"/>
       <c r="U101" s="3"/>
-      <c r="V101" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="V101" s="3"/>
       <c r="W101" s="9"/>
       <c r="X101" s="3" t="s">
         <v>36</v>
@@ -9238,7 +10129,7 @@
       </c>
       <c r="Z101" s="9"/>
     </row>
-    <row r="102" spans="1:26">
+    <row r="102" spans="1:26" hidden="1">
       <c r="A102" s="3" t="s">
         <v>182</v>
       </c>
@@ -9280,9 +10171,7 @@
       <c r="S102" s="3"/>
       <c r="T102" s="3"/>
       <c r="U102" s="3"/>
-      <c r="V102" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="V102" s="3"/>
       <c r="W102" s="9"/>
       <c r="X102" s="3" t="s">
         <v>36</v>
@@ -9292,7 +10181,7 @@
       </c>
       <c r="Z102" s="9"/>
     </row>
-    <row r="103" spans="1:26">
+    <row r="103" spans="1:26" hidden="1">
       <c r="A103" s="3" t="s">
         <v>697</v>
       </c>
@@ -9334,9 +10223,7 @@
       <c r="S103" s="3"/>
       <c r="T103" s="3"/>
       <c r="U103" s="3"/>
-      <c r="V103" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="V103" s="3"/>
       <c r="W103" s="9"/>
       <c r="X103" s="3" t="s">
         <v>36</v>
@@ -9346,7 +10233,7 @@
       </c>
       <c r="Z103" s="9"/>
     </row>
-    <row r="104" spans="1:26">
+    <row r="104" spans="1:26" hidden="1">
       <c r="A104" s="3" t="s">
         <v>213</v>
       </c>
@@ -9388,9 +10275,7 @@
       <c r="S104" s="3"/>
       <c r="T104" s="3"/>
       <c r="U104" s="3"/>
-      <c r="V104" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="V104" s="3"/>
       <c r="W104" s="9"/>
       <c r="X104" s="3" t="s">
         <v>36</v>
@@ -9400,7 +10285,7 @@
       </c>
       <c r="Z104" s="9"/>
     </row>
-    <row r="105" spans="1:26">
+    <row r="105" spans="1:26" hidden="1">
       <c r="A105" s="3" t="s">
         <v>708</v>
       </c>
@@ -9442,9 +10327,7 @@
       <c r="S105" s="3"/>
       <c r="T105" s="3"/>
       <c r="U105" s="3"/>
-      <c r="V105" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="V105" s="3"/>
       <c r="W105" s="9"/>
       <c r="X105" s="3" t="s">
         <v>36</v>
@@ -9454,7 +10337,7 @@
       </c>
       <c r="Z105" s="9"/>
     </row>
-    <row r="106" spans="1:26">
+    <row r="106" spans="1:26" hidden="1">
       <c r="A106" s="3" t="s">
         <v>26</v>
       </c>
@@ -9496,9 +10379,7 @@
       <c r="S106" s="3"/>
       <c r="T106" s="3"/>
       <c r="U106" s="3"/>
-      <c r="V106" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="V106" s="3"/>
       <c r="W106" s="9"/>
       <c r="X106" s="3" t="s">
         <v>36</v>
@@ -9508,7 +10389,7 @@
       </c>
       <c r="Z106" s="9"/>
     </row>
-    <row r="107" spans="1:26">
+    <row r="107" spans="1:26" hidden="1">
       <c r="A107" s="3" t="s">
         <v>719</v>
       </c>
@@ -9550,9 +10431,7 @@
       <c r="S107" s="3"/>
       <c r="T107" s="3"/>
       <c r="U107" s="3"/>
-      <c r="V107" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="V107" s="3"/>
       <c r="W107" s="9"/>
       <c r="X107" s="3" t="s">
         <v>36</v>
@@ -9562,7 +10441,7 @@
       </c>
       <c r="Z107" s="9"/>
     </row>
-    <row r="108" spans="1:26">
+    <row r="108" spans="1:26" hidden="1">
       <c r="A108" s="3" t="s">
         <v>726</v>
       </c>
@@ -9604,9 +10483,7 @@
       <c r="S108" s="3"/>
       <c r="T108" s="3"/>
       <c r="U108" s="3"/>
-      <c r="V108" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="V108" s="3"/>
       <c r="W108" s="9"/>
       <c r="X108" s="3" t="s">
         <v>71</v>
@@ -9616,7 +10493,7 @@
       </c>
       <c r="Z108" s="9"/>
     </row>
-    <row r="109" spans="1:26">
+    <row r="109" spans="1:26" hidden="1">
       <c r="A109" s="3" t="s">
         <v>733</v>
       </c>
@@ -9658,9 +10535,7 @@
       <c r="S109" s="3"/>
       <c r="T109" s="3"/>
       <c r="U109" s="3"/>
-      <c r="V109" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="V109" s="3"/>
       <c r="W109" s="9"/>
       <c r="X109" s="3" t="s">
         <v>36</v>
@@ -9670,7 +10545,7 @@
       </c>
       <c r="Z109" s="9"/>
     </row>
-    <row r="110" spans="1:26">
+    <row r="110" spans="1:26" hidden="1">
       <c r="A110" s="3" t="s">
         <v>740</v>
       </c>
@@ -9712,9 +10587,7 @@
       <c r="S110" s="3"/>
       <c r="T110" s="3"/>
       <c r="U110" s="3"/>
-      <c r="V110" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="V110" s="3"/>
       <c r="W110" s="9"/>
       <c r="X110" s="3" t="s">
         <v>36</v>
@@ -9724,7 +10597,7 @@
       </c>
       <c r="Z110" s="9"/>
     </row>
-    <row r="111" spans="1:26">
+    <row r="111" spans="1:26" hidden="1">
       <c r="A111" s="3" t="s">
         <v>401</v>
       </c>
@@ -9766,9 +10639,7 @@
       <c r="S111" s="3"/>
       <c r="T111" s="3"/>
       <c r="U111" s="3"/>
-      <c r="V111" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="V111" s="3"/>
       <c r="W111" s="9"/>
       <c r="X111" s="3" t="s">
         <v>71</v>
@@ -9778,7 +10649,7 @@
       </c>
       <c r="Z111" s="9"/>
     </row>
-    <row r="112" spans="1:26">
+    <row r="112" spans="1:26" hidden="1">
       <c r="A112" s="3" t="s">
         <v>751</v>
       </c>
@@ -9820,9 +10691,7 @@
       <c r="S112" s="3"/>
       <c r="T112" s="3"/>
       <c r="U112" s="3"/>
-      <c r="V112" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="V112" s="3"/>
       <c r="W112" s="9"/>
       <c r="X112" s="3" t="s">
         <v>36</v>
@@ -9832,7 +10701,7 @@
       </c>
       <c r="Z112" s="9"/>
     </row>
-    <row r="113" spans="1:26">
+    <row r="113" spans="1:26" hidden="1">
       <c r="A113" s="3" t="s">
         <v>758</v>
       </c>
@@ -9874,9 +10743,7 @@
       <c r="S113" s="3"/>
       <c r="T113" s="3"/>
       <c r="U113" s="3"/>
-      <c r="V113" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="V113" s="3"/>
       <c r="W113" s="9"/>
       <c r="X113" s="3" t="s">
         <v>71</v>
@@ -9886,7 +10753,7 @@
       </c>
       <c r="Z113" s="9"/>
     </row>
-    <row r="114" spans="1:26">
+    <row r="114" spans="1:26" hidden="1">
       <c r="A114" s="3" t="s">
         <v>547</v>
       </c>
@@ -9928,9 +10795,7 @@
       <c r="S114" s="3"/>
       <c r="T114" s="3"/>
       <c r="U114" s="3"/>
-      <c r="V114" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="V114" s="3"/>
       <c r="W114" s="9"/>
       <c r="X114" s="3" t="s">
         <v>36</v>
@@ -9940,7 +10805,7 @@
       </c>
       <c r="Z114" s="9"/>
     </row>
-    <row r="115" spans="1:26">
+    <row r="115" spans="1:26" hidden="1">
       <c r="A115" s="3" t="s">
         <v>189</v>
       </c>
@@ -9982,9 +10847,7 @@
       <c r="S115" s="3"/>
       <c r="T115" s="3"/>
       <c r="U115" s="3"/>
-      <c r="V115" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="V115" s="3"/>
       <c r="W115" s="9"/>
       <c r="X115" s="3" t="s">
         <v>36</v>
@@ -9994,7 +10857,7 @@
       </c>
       <c r="Z115" s="9"/>
     </row>
-    <row r="116" spans="1:26">
+    <row r="116" spans="1:26" hidden="1">
       <c r="A116" s="3" t="s">
         <v>142</v>
       </c>
@@ -10036,9 +10899,7 @@
       <c r="S116" s="3"/>
       <c r="T116" s="3"/>
       <c r="U116" s="3"/>
-      <c r="V116" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="V116" s="3"/>
       <c r="W116" s="9"/>
       <c r="X116" s="3" t="s">
         <v>36</v>
@@ -10048,7 +10909,7 @@
       </c>
       <c r="Z116" s="9"/>
     </row>
-    <row r="117" spans="1:26">
+    <row r="117" spans="1:26" hidden="1">
       <c r="A117" s="3" t="s">
         <v>719</v>
       </c>
@@ -10090,9 +10951,7 @@
       <c r="S117" s="3"/>
       <c r="T117" s="3"/>
       <c r="U117" s="3"/>
-      <c r="V117" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="V117" s="3"/>
       <c r="W117" s="9"/>
       <c r="X117" s="3" t="s">
         <v>36</v>
@@ -10102,7 +10961,7 @@
       </c>
       <c r="Z117" s="9"/>
     </row>
-    <row r="118" spans="1:26">
+    <row r="118" spans="1:26" hidden="1">
       <c r="A118" s="3" t="s">
         <v>781</v>
       </c>
@@ -10134,7 +10993,7 @@
       <c r="K118" s="3"/>
       <c r="L118" s="9"/>
       <c r="M118" s="3"/>
-      <c r="N118" s="10" t="s">
+      <c r="N118" s="15" t="s">
         <v>787</v>
       </c>
       <c r="O118" s="3"/>
@@ -10144,9 +11003,7 @@
       <c r="S118" s="3"/>
       <c r="T118" s="3"/>
       <c r="U118" s="3"/>
-      <c r="V118" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="V118" s="3"/>
       <c r="W118" s="9"/>
       <c r="X118" s="3" t="s">
         <v>36</v>
@@ -10156,7 +11013,7 @@
       </c>
       <c r="Z118" s="9"/>
     </row>
-    <row r="119" spans="1:26">
+    <row r="119" spans="1:26" hidden="1">
       <c r="A119" s="3" t="s">
         <v>788</v>
       </c>
@@ -10198,9 +11055,7 @@
       <c r="S119" s="3"/>
       <c r="T119" s="3"/>
       <c r="U119" s="3"/>
-      <c r="V119" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="V119" s="3"/>
       <c r="W119" s="9"/>
       <c r="X119" s="3" t="s">
         <v>71</v>
@@ -10212,7 +11067,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="120" spans="1:26">
+    <row r="120" spans="1:26" hidden="1">
       <c r="A120" s="3" t="s">
         <v>796</v>
       </c>
@@ -10254,9 +11109,7 @@
       <c r="S120" s="3"/>
       <c r="T120" s="3"/>
       <c r="U120" s="3"/>
-      <c r="V120" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="V120" s="3"/>
       <c r="W120" s="9"/>
       <c r="X120" s="3" t="s">
         <v>36</v>
@@ -10266,7 +11119,7 @@
       </c>
       <c r="Z120" s="9"/>
     </row>
-    <row r="121" spans="1:26">
+    <row r="121" spans="1:26" hidden="1">
       <c r="A121" s="3" t="s">
         <v>803</v>
       </c>
@@ -10308,9 +11161,7 @@
       <c r="S121" s="3"/>
       <c r="T121" s="3"/>
       <c r="U121" s="3"/>
-      <c r="V121" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="V121" s="3"/>
       <c r="W121" s="9"/>
       <c r="X121" s="3" t="s">
         <v>36</v>
@@ -10320,7 +11171,7 @@
       </c>
       <c r="Z121" s="9"/>
     </row>
-    <row r="122" spans="1:26">
+    <row r="122" spans="1:26" hidden="1">
       <c r="A122" s="3" t="s">
         <v>810</v>
       </c>
@@ -10362,9 +11213,7 @@
       <c r="S122" s="3"/>
       <c r="T122" s="3"/>
       <c r="U122" s="3"/>
-      <c r="V122" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="V122" s="3"/>
       <c r="W122" s="9"/>
       <c r="X122" s="3" t="s">
         <v>71</v>
@@ -10376,7 +11225,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="123" spans="1:26">
+    <row r="123" spans="1:26" hidden="1">
       <c r="A123" s="3" t="s">
         <v>817</v>
       </c>
@@ -10418,9 +11267,7 @@
       <c r="S123" s="3"/>
       <c r="T123" s="3"/>
       <c r="U123" s="3"/>
-      <c r="V123" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="V123" s="3"/>
       <c r="W123" s="9"/>
       <c r="X123" s="3" t="s">
         <v>36</v>
@@ -10430,7 +11277,7 @@
       </c>
       <c r="Z123" s="9"/>
     </row>
-    <row r="124" spans="1:26">
+    <row r="124" spans="1:26" hidden="1">
       <c r="A124" s="3" t="s">
         <v>824</v>
       </c>
@@ -10472,9 +11319,7 @@
       <c r="S124" s="3"/>
       <c r="T124" s="3"/>
       <c r="U124" s="3"/>
-      <c r="V124" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="V124" s="3"/>
       <c r="W124" s="9"/>
       <c r="X124" s="3" t="s">
         <v>71</v>
@@ -10486,7 +11331,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="125" spans="1:26">
+    <row r="125" spans="1:26" hidden="1">
       <c r="A125" s="3" t="s">
         <v>38</v>
       </c>
@@ -10528,9 +11373,7 @@
       <c r="S125" s="3"/>
       <c r="T125" s="3"/>
       <c r="U125" s="3"/>
-      <c r="V125" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="V125" s="3"/>
       <c r="W125" s="9"/>
       <c r="X125" s="3" t="s">
         <v>36</v>
@@ -10540,7 +11383,7 @@
       </c>
       <c r="Z125" s="9"/>
     </row>
-    <row r="126" spans="1:26">
+    <row r="126" spans="1:26" hidden="1">
       <c r="A126" s="3" t="s">
         <v>213</v>
       </c>
@@ -10582,9 +11425,7 @@
       <c r="S126" s="3"/>
       <c r="T126" s="3"/>
       <c r="U126" s="3"/>
-      <c r="V126" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="V126" s="3"/>
       <c r="W126" s="9"/>
       <c r="X126" s="3" t="s">
         <v>36</v>
@@ -10594,7 +11435,7 @@
       </c>
       <c r="Z126" s="9"/>
     </row>
-    <row r="127" spans="1:26">
+    <row r="127" spans="1:26" hidden="1">
       <c r="A127" s="3" t="s">
         <v>839</v>
       </c>
@@ -10636,9 +11477,7 @@
       <c r="S127" s="3"/>
       <c r="T127" s="3"/>
       <c r="U127" s="3"/>
-      <c r="V127" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="V127" s="3"/>
       <c r="W127" s="9"/>
       <c r="X127" s="3" t="s">
         <v>71</v>
@@ -10648,7 +11487,7 @@
       </c>
       <c r="Z127" s="9"/>
     </row>
-    <row r="128" spans="1:26">
+    <row r="128" spans="1:26" hidden="1">
       <c r="A128" s="3" t="s">
         <v>846</v>
       </c>
@@ -10690,9 +11529,7 @@
       <c r="S128" s="3"/>
       <c r="T128" s="3"/>
       <c r="U128" s="3"/>
-      <c r="V128" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="V128" s="3"/>
       <c r="W128" s="9"/>
       <c r="X128" s="3" t="s">
         <v>36</v>
@@ -10702,7 +11539,7 @@
       </c>
       <c r="Z128" s="9"/>
     </row>
-    <row r="129" spans="1:26">
+    <row r="129" spans="1:26" hidden="1">
       <c r="A129" s="3" t="s">
         <v>853</v>
       </c>
@@ -10744,9 +11581,7 @@
       <c r="S129" s="3"/>
       <c r="T129" s="3"/>
       <c r="U129" s="3"/>
-      <c r="V129" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="V129" s="3"/>
       <c r="W129" s="9"/>
       <c r="X129" s="3" t="s">
         <v>36</v>
@@ -10756,22 +11591,4829 @@
       </c>
       <c r="Z129" s="9"/>
     </row>
+    <row r="130" spans="1:26" hidden="1">
+      <c r="A130" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="B130" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="C130" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="D130" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="E130" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="F130" s="11">
+        <v>46112</v>
+      </c>
+      <c r="G130" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="H130" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="I130" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J130" s="10"/>
+      <c r="K130" s="10"/>
+      <c r="L130" s="9"/>
+      <c r="M130" s="9"/>
+      <c r="N130" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="O130" s="9"/>
+      <c r="P130" s="9"/>
+      <c r="Q130" s="9"/>
+      <c r="R130" s="9"/>
+      <c r="S130" s="9"/>
+      <c r="T130" s="9"/>
+      <c r="U130" s="9"/>
+      <c r="V130" s="9"/>
+      <c r="W130" s="9"/>
+      <c r="X130" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y130" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z130" s="9"/>
+    </row>
+    <row r="131" spans="1:26" hidden="1">
+      <c r="A131" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="B131" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="C131" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="D131" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="E131" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="F131" s="11">
+        <v>46106</v>
+      </c>
+      <c r="G131" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="H131" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="I131" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J131" s="10"/>
+      <c r="K131" s="10"/>
+      <c r="L131" s="9"/>
+      <c r="M131" s="9"/>
+      <c r="N131" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="O131" s="9"/>
+      <c r="P131" s="9"/>
+      <c r="Q131" s="9"/>
+      <c r="R131" s="9"/>
+      <c r="S131" s="9"/>
+      <c r="T131" s="9"/>
+      <c r="U131" s="9"/>
+      <c r="V131" s="9"/>
+      <c r="W131" s="9"/>
+      <c r="X131" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y131" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z131" s="9"/>
+    </row>
+    <row r="132" spans="1:26" hidden="1">
+      <c r="A132" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="B132" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="C132" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="D132" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="E132" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="F132" s="11">
+        <v>46106</v>
+      </c>
+      <c r="G132" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="H132" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="I132" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J132" s="10"/>
+      <c r="K132" s="10"/>
+      <c r="L132" s="9"/>
+      <c r="M132" s="9"/>
+      <c r="N132" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="O132" s="9"/>
+      <c r="P132" s="9"/>
+      <c r="Q132" s="9"/>
+      <c r="R132" s="9"/>
+      <c r="S132" s="9"/>
+      <c r="T132" s="9"/>
+      <c r="U132" s="9"/>
+      <c r="V132" s="9"/>
+      <c r="W132" s="9"/>
+      <c r="X132" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y132" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z132" s="9"/>
+    </row>
+    <row r="133" spans="1:26" hidden="1">
+      <c r="A133" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="B133" s="10" t="s">
+        <v>245</v>
+      </c>
+      <c r="C133" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="D133" s="10" t="s">
+        <v>247</v>
+      </c>
+      <c r="E133" s="10" t="s">
+        <v>247</v>
+      </c>
+      <c r="F133" s="11">
+        <v>46090</v>
+      </c>
+      <c r="G133" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="H133" s="10" t="s">
+        <v>249</v>
+      </c>
+      <c r="I133" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J133" s="10"/>
+      <c r="K133" s="10"/>
+      <c r="L133" s="9"/>
+      <c r="M133" s="9"/>
+      <c r="N133" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="O133" s="9"/>
+      <c r="P133" s="9"/>
+      <c r="Q133" s="9"/>
+      <c r="R133" s="9"/>
+      <c r="S133" s="9"/>
+      <c r="T133" s="9"/>
+      <c r="U133" s="9"/>
+      <c r="V133" s="9"/>
+      <c r="W133" s="9"/>
+      <c r="X133" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y133" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z133" s="9"/>
+    </row>
+    <row r="134" spans="1:26" hidden="1">
+      <c r="A134" s="10" t="s">
+        <v>392</v>
+      </c>
+      <c r="B134" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C134" s="10" t="s">
+        <v>394</v>
+      </c>
+      <c r="D134" s="10" t="s">
+        <v>395</v>
+      </c>
+      <c r="E134" s="10" t="s">
+        <v>395</v>
+      </c>
+      <c r="F134" s="11">
+        <v>46100</v>
+      </c>
+      <c r="G134" s="10" t="s">
+        <v>396</v>
+      </c>
+      <c r="H134" s="10" t="s">
+        <v>397</v>
+      </c>
+      <c r="I134" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J134" s="10"/>
+      <c r="K134" s="10"/>
+      <c r="L134" s="9"/>
+      <c r="M134" s="9"/>
+      <c r="N134" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="O134" s="9"/>
+      <c r="P134" s="9"/>
+      <c r="Q134" s="9"/>
+      <c r="R134" s="9"/>
+      <c r="S134" s="9"/>
+      <c r="T134" s="9"/>
+      <c r="U134" s="9"/>
+      <c r="V134" s="9"/>
+      <c r="W134" s="9"/>
+      <c r="X134" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y134" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z134" s="9"/>
+    </row>
+    <row r="135" spans="1:26" hidden="1">
+      <c r="A135" s="10" t="s">
+        <v>401</v>
+      </c>
+      <c r="B135" s="10" t="s">
+        <v>402</v>
+      </c>
+      <c r="C135" s="10" t="s">
+        <v>403</v>
+      </c>
+      <c r="D135" s="10" t="s">
+        <v>419</v>
+      </c>
+      <c r="E135" s="10" t="s">
+        <v>419</v>
+      </c>
+      <c r="F135" s="11">
+        <v>46099</v>
+      </c>
+      <c r="G135" s="10" t="s">
+        <v>420</v>
+      </c>
+      <c r="H135" s="10" t="s">
+        <v>421</v>
+      </c>
+      <c r="I135" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J135" s="10"/>
+      <c r="K135" s="10"/>
+      <c r="L135" s="9"/>
+      <c r="M135" s="9"/>
+      <c r="N135" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="O135" s="9"/>
+      <c r="P135" s="9"/>
+      <c r="Q135" s="9"/>
+      <c r="R135" s="9"/>
+      <c r="S135" s="9"/>
+      <c r="T135" s="9"/>
+      <c r="U135" s="9"/>
+      <c r="V135" s="9"/>
+      <c r="W135" s="9"/>
+      <c r="X135" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y135" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z135" s="9"/>
+    </row>
+    <row r="136" spans="1:26" hidden="1">
+      <c r="A136" s="10" t="s">
+        <v>401</v>
+      </c>
+      <c r="B136" s="10" t="s">
+        <v>402</v>
+      </c>
+      <c r="C136" s="10" t="s">
+        <v>403</v>
+      </c>
+      <c r="D136" s="10" t="s">
+        <v>424</v>
+      </c>
+      <c r="E136" s="10" t="s">
+        <v>425</v>
+      </c>
+      <c r="F136" s="11">
+        <v>46105</v>
+      </c>
+      <c r="G136" s="10" t="s">
+        <v>426</v>
+      </c>
+      <c r="H136" s="10" t="s">
+        <v>427</v>
+      </c>
+      <c r="I136" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J136" s="10"/>
+      <c r="K136" s="10"/>
+      <c r="L136" s="9"/>
+      <c r="M136" s="9"/>
+      <c r="N136" s="10" t="s">
+        <v>428</v>
+      </c>
+      <c r="O136" s="9"/>
+      <c r="P136" s="9"/>
+      <c r="Q136" s="9"/>
+      <c r="R136" s="9"/>
+      <c r="S136" s="9"/>
+      <c r="T136" s="9"/>
+      <c r="U136" s="9"/>
+      <c r="V136" s="9"/>
+      <c r="W136" s="9"/>
+      <c r="X136" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y136" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z136" s="9"/>
+    </row>
+    <row r="137" spans="1:26" hidden="1">
+      <c r="A137" s="10" t="s">
+        <v>491</v>
+      </c>
+      <c r="B137" s="10" t="s">
+        <v>492</v>
+      </c>
+      <c r="C137" s="10" t="s">
+        <v>493</v>
+      </c>
+      <c r="D137" s="10" t="s">
+        <v>494</v>
+      </c>
+      <c r="E137" s="10" t="s">
+        <v>494</v>
+      </c>
+      <c r="F137" s="11">
+        <v>46106</v>
+      </c>
+      <c r="G137" s="10" t="s">
+        <v>495</v>
+      </c>
+      <c r="H137" s="12" t="s">
+        <v>496</v>
+      </c>
+      <c r="I137" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J137" s="10"/>
+      <c r="K137" s="10"/>
+      <c r="L137" s="9"/>
+      <c r="M137" s="9"/>
+      <c r="N137" s="10" t="s">
+        <v>497</v>
+      </c>
+      <c r="O137" s="9"/>
+      <c r="P137" s="9"/>
+      <c r="Q137" s="9"/>
+      <c r="R137" s="9"/>
+      <c r="S137" s="9"/>
+      <c r="T137" s="9"/>
+      <c r="U137" s="9"/>
+      <c r="V137" s="9"/>
+      <c r="W137" s="9"/>
+      <c r="X137" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y137" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z137" s="9"/>
+    </row>
+    <row r="138" spans="1:26" hidden="1">
+      <c r="A138" s="10" t="s">
+        <v>491</v>
+      </c>
+      <c r="B138" s="10" t="s">
+        <v>492</v>
+      </c>
+      <c r="C138" s="10" t="s">
+        <v>493</v>
+      </c>
+      <c r="D138" s="10" t="s">
+        <v>500</v>
+      </c>
+      <c r="E138" s="10" t="s">
+        <v>500</v>
+      </c>
+      <c r="F138" s="11">
+        <v>46107</v>
+      </c>
+      <c r="G138" s="10" t="s">
+        <v>501</v>
+      </c>
+      <c r="H138" s="12" t="s">
+        <v>502</v>
+      </c>
+      <c r="I138" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J138" s="10"/>
+      <c r="K138" s="10"/>
+      <c r="L138" s="9"/>
+      <c r="M138" s="9"/>
+      <c r="N138" s="10" t="s">
+        <v>503</v>
+      </c>
+      <c r="O138" s="9"/>
+      <c r="P138" s="9"/>
+      <c r="Q138" s="9"/>
+      <c r="R138" s="9"/>
+      <c r="S138" s="9"/>
+      <c r="T138" s="9"/>
+      <c r="U138" s="9"/>
+      <c r="V138" s="9"/>
+      <c r="W138" s="9"/>
+      <c r="X138" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y138" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z138" s="9"/>
+    </row>
+    <row r="139" spans="1:26" hidden="1">
+      <c r="A139" s="10" t="s">
+        <v>491</v>
+      </c>
+      <c r="B139" s="10" t="s">
+        <v>492</v>
+      </c>
+      <c r="C139" s="10" t="s">
+        <v>493</v>
+      </c>
+      <c r="D139" s="10" t="s">
+        <v>507</v>
+      </c>
+      <c r="E139" s="10" t="s">
+        <v>507</v>
+      </c>
+      <c r="F139" s="11">
+        <v>46111</v>
+      </c>
+      <c r="G139" s="10" t="s">
+        <v>508</v>
+      </c>
+      <c r="H139" s="12" t="s">
+        <v>509</v>
+      </c>
+      <c r="I139" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J139" s="10"/>
+      <c r="K139" s="10"/>
+      <c r="L139" s="9"/>
+      <c r="M139" s="9"/>
+      <c r="N139" s="10" t="s">
+        <v>510</v>
+      </c>
+      <c r="O139" s="9"/>
+      <c r="P139" s="9"/>
+      <c r="Q139" s="9"/>
+      <c r="R139" s="9"/>
+      <c r="S139" s="9"/>
+      <c r="T139" s="9"/>
+      <c r="U139" s="9"/>
+      <c r="V139" s="9"/>
+      <c r="W139" s="9"/>
+      <c r="X139" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y139" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z139" s="9"/>
+    </row>
+    <row r="140" spans="1:26" hidden="1">
+      <c r="A140" s="10" t="s">
+        <v>474</v>
+      </c>
+      <c r="B140" s="10" t="s">
+        <v>475</v>
+      </c>
+      <c r="C140" s="10" t="s">
+        <v>476</v>
+      </c>
+      <c r="D140" s="10" t="s">
+        <v>477</v>
+      </c>
+      <c r="E140" s="10" t="s">
+        <v>477</v>
+      </c>
+      <c r="F140" s="11">
+        <v>46137</v>
+      </c>
+      <c r="G140" s="10" t="s">
+        <v>478</v>
+      </c>
+      <c r="H140" s="10" t="s">
+        <v>479</v>
+      </c>
+      <c r="I140" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J140" s="10"/>
+      <c r="K140" s="10"/>
+      <c r="L140" s="9"/>
+      <c r="M140" s="9"/>
+      <c r="N140" s="10" t="s">
+        <v>480</v>
+      </c>
+      <c r="O140" s="9"/>
+      <c r="P140" s="9"/>
+      <c r="Q140" s="9"/>
+      <c r="R140" s="9"/>
+      <c r="S140" s="9"/>
+      <c r="T140" s="9"/>
+      <c r="U140" s="9"/>
+      <c r="V140" s="9"/>
+      <c r="W140" s="9"/>
+      <c r="X140" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="Y140" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="Z140" s="9" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="141" spans="1:26" hidden="1">
+      <c r="A141" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="B141" s="10" t="s">
+        <v>245</v>
+      </c>
+      <c r="C141" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="D141" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="E141" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="F141" s="11">
+        <v>46137</v>
+      </c>
+      <c r="G141" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="H141" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="I141" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="J141" s="10"/>
+      <c r="K141" s="10"/>
+      <c r="L141" s="9"/>
+      <c r="M141" s="9"/>
+      <c r="N141" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="O141" s="9"/>
+      <c r="P141" s="9"/>
+      <c r="Q141" s="9"/>
+      <c r="R141" s="9"/>
+      <c r="S141" s="9"/>
+      <c r="T141" s="9"/>
+      <c r="U141" s="9"/>
+      <c r="V141" s="9"/>
+      <c r="W141" s="9"/>
+      <c r="X141" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y141" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z141" s="9"/>
+    </row>
+    <row r="142" spans="1:26" hidden="1">
+      <c r="A142" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="B142" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="C142" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="D142" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="E142" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="F142" s="11">
+        <v>46134</v>
+      </c>
+      <c r="G142" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="H142" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="I142" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J142" s="10"/>
+      <c r="K142" s="10"/>
+      <c r="L142" s="9"/>
+      <c r="M142" s="9"/>
+      <c r="N142" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="O142" s="9"/>
+      <c r="P142" s="9"/>
+      <c r="Q142" s="9"/>
+      <c r="R142" s="9"/>
+      <c r="S142" s="9"/>
+      <c r="T142" s="9"/>
+      <c r="U142" s="9"/>
+      <c r="V142" s="9"/>
+      <c r="W142" s="9"/>
+      <c r="X142" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y142" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="Z142" s="9"/>
+    </row>
+    <row r="143" spans="1:26" hidden="1">
+      <c r="A143" s="10" t="s">
+        <v>401</v>
+      </c>
+      <c r="B143" s="10" t="s">
+        <v>402</v>
+      </c>
+      <c r="C143" s="10" t="s">
+        <v>403</v>
+      </c>
+      <c r="D143" s="10" t="s">
+        <v>433</v>
+      </c>
+      <c r="E143" s="10" t="s">
+        <v>433</v>
+      </c>
+      <c r="F143" s="11">
+        <v>46135</v>
+      </c>
+      <c r="G143" s="10" t="s">
+        <v>434</v>
+      </c>
+      <c r="H143" s="10" t="s">
+        <v>435</v>
+      </c>
+      <c r="I143" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J143" s="10"/>
+      <c r="K143" s="10"/>
+      <c r="L143" s="9"/>
+      <c r="M143" s="9"/>
+      <c r="N143" s="10" t="s">
+        <v>436</v>
+      </c>
+      <c r="O143" s="9"/>
+      <c r="P143" s="9"/>
+      <c r="Q143" s="9"/>
+      <c r="R143" s="9"/>
+      <c r="S143" s="9"/>
+      <c r="T143" s="9"/>
+      <c r="U143" s="9"/>
+      <c r="V143" s="9"/>
+      <c r="W143" s="9"/>
+      <c r="X143" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y143" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z143" s="9"/>
+    </row>
+    <row r="144" spans="1:26">
+      <c r="A144" s="10" t="s">
+        <v>401</v>
+      </c>
+      <c r="B144" s="10" t="s">
+        <v>402</v>
+      </c>
+      <c r="C144" s="10" t="s">
+        <v>403</v>
+      </c>
+      <c r="D144" s="10" t="s">
+        <v>438</v>
+      </c>
+      <c r="E144" s="10" t="s">
+        <v>438</v>
+      </c>
+      <c r="F144" s="11">
+        <v>46139</v>
+      </c>
+      <c r="G144" s="10" t="s">
+        <v>439</v>
+      </c>
+      <c r="H144" s="10" t="s">
+        <v>440</v>
+      </c>
+      <c r="I144" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J144" s="10"/>
+      <c r="K144" s="10"/>
+      <c r="L144" s="9"/>
+      <c r="M144" s="9"/>
+      <c r="N144" s="10" t="s">
+        <v>441</v>
+      </c>
+      <c r="O144" s="9"/>
+      <c r="P144" s="9"/>
+      <c r="Q144" s="9"/>
+      <c r="R144" s="9"/>
+      <c r="S144" s="9"/>
+      <c r="T144" s="9"/>
+      <c r="U144" s="9"/>
+      <c r="V144" s="9"/>
+      <c r="W144" s="9"/>
+      <c r="X144" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y144" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z144" s="9"/>
+    </row>
+    <row r="145" spans="1:26">
+      <c r="A145" s="10" t="s">
+        <v>332</v>
+      </c>
+      <c r="B145" s="10" t="s">
+        <v>333</v>
+      </c>
+      <c r="C145" s="10" t="s">
+        <v>334</v>
+      </c>
+      <c r="D145" s="10" t="s">
+        <v>335</v>
+      </c>
+      <c r="E145" s="10" t="s">
+        <v>335</v>
+      </c>
+      <c r="F145" s="11">
+        <v>46135</v>
+      </c>
+      <c r="G145" s="10" t="s">
+        <v>336</v>
+      </c>
+      <c r="H145" s="10" t="s">
+        <v>337</v>
+      </c>
+      <c r="I145" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J145" s="10"/>
+      <c r="K145" s="10"/>
+      <c r="L145" s="9"/>
+      <c r="M145" s="9"/>
+      <c r="N145" s="10" t="s">
+        <v>338</v>
+      </c>
+      <c r="O145" s="9"/>
+      <c r="P145" s="9"/>
+      <c r="Q145" s="9"/>
+      <c r="R145" s="9"/>
+      <c r="S145" s="9"/>
+      <c r="T145" s="9"/>
+      <c r="U145" s="9"/>
+      <c r="V145" s="9"/>
+      <c r="W145" s="9"/>
+      <c r="X145" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y145" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z145" s="9"/>
+    </row>
+    <row r="146" spans="1:26">
+      <c r="A146" s="10" t="s">
+        <v>547</v>
+      </c>
+      <c r="B146" s="10" t="s">
+        <v>548</v>
+      </c>
+      <c r="C146" s="10" t="s">
+        <v>549</v>
+      </c>
+      <c r="D146" s="10" t="s">
+        <v>558</v>
+      </c>
+      <c r="E146" s="10" t="s">
+        <v>558</v>
+      </c>
+      <c r="F146" s="11">
+        <v>46173</v>
+      </c>
+      <c r="G146" s="10" t="s">
+        <v>559</v>
+      </c>
+      <c r="H146" s="10" t="s">
+        <v>560</v>
+      </c>
+      <c r="I146" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J146" s="10"/>
+      <c r="K146" s="10"/>
+      <c r="L146" s="9"/>
+      <c r="M146" s="9"/>
+      <c r="N146" s="10" t="s">
+        <v>561</v>
+      </c>
+      <c r="O146" s="9"/>
+      <c r="P146" s="9"/>
+      <c r="Q146" s="9"/>
+      <c r="R146" s="9"/>
+      <c r="S146" s="9"/>
+      <c r="T146" s="9"/>
+      <c r="U146" s="9"/>
+      <c r="V146" s="9"/>
+      <c r="W146" s="9"/>
+      <c r="X146" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y146" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z146" s="9"/>
+    </row>
+    <row r="147" spans="1:26">
+      <c r="A147" s="10" t="s">
+        <v>401</v>
+      </c>
+      <c r="B147" s="10" t="s">
+        <v>402</v>
+      </c>
+      <c r="C147" s="10" t="s">
+        <v>403</v>
+      </c>
+      <c r="D147" s="10" t="s">
+        <v>443</v>
+      </c>
+      <c r="E147" s="10" t="s">
+        <v>443</v>
+      </c>
+      <c r="F147" s="11">
+        <v>46173</v>
+      </c>
+      <c r="G147" s="10" t="s">
+        <v>444</v>
+      </c>
+      <c r="H147" s="10" t="s">
+        <v>445</v>
+      </c>
+      <c r="I147" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J147" s="10"/>
+      <c r="K147" s="10"/>
+      <c r="L147" s="9"/>
+      <c r="M147" s="9"/>
+      <c r="N147" s="10" t="s">
+        <v>446</v>
+      </c>
+      <c r="O147" s="9"/>
+      <c r="P147" s="9"/>
+      <c r="Q147" s="9"/>
+      <c r="R147" s="9"/>
+      <c r="S147" s="9"/>
+      <c r="T147" s="9"/>
+      <c r="U147" s="9"/>
+      <c r="V147" s="9"/>
+      <c r="W147" s="9"/>
+      <c r="X147" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y147" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z147" s="9"/>
+    </row>
+    <row r="148" spans="1:26">
+      <c r="A148" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="B148" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="C148" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="D148" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="E148" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="F148" s="11">
+        <v>46173</v>
+      </c>
+      <c r="G148" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="H148" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="I148" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="J148" s="10"/>
+      <c r="K148" s="10"/>
+      <c r="L148" s="9"/>
+      <c r="M148" s="9"/>
+      <c r="N148" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="O148" s="9"/>
+      <c r="P148" s="9"/>
+      <c r="Q148" s="9"/>
+      <c r="R148" s="9"/>
+      <c r="S148" s="9"/>
+      <c r="T148" s="9"/>
+      <c r="U148" s="9"/>
+      <c r="V148" s="9"/>
+      <c r="W148" s="9"/>
+      <c r="X148" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y148" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z148" s="9"/>
+    </row>
+    <row r="149" spans="1:26">
+      <c r="A149" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="B149" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="C149" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="D149" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="E149" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="F149" s="11">
+        <v>46173</v>
+      </c>
+      <c r="G149" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="H149" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="I149" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J149" s="10"/>
+      <c r="K149" s="10"/>
+      <c r="L149" s="9"/>
+      <c r="M149" s="9"/>
+      <c r="N149" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="O149" s="9"/>
+      <c r="P149" s="9"/>
+      <c r="Q149" s="9"/>
+      <c r="R149" s="9"/>
+      <c r="S149" s="9"/>
+      <c r="T149" s="9"/>
+      <c r="U149" s="9"/>
+      <c r="V149" s="9"/>
+      <c r="W149" s="9"/>
+      <c r="X149" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y149" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z149" s="9"/>
+    </row>
+    <row r="150" spans="1:26">
+      <c r="A150" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="B150" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="C150" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="D150" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="E150" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="F150" s="11">
+        <v>46173</v>
+      </c>
+      <c r="G150" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="H150" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="I150" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="J150" s="10"/>
+      <c r="K150" s="10"/>
+      <c r="L150" s="9"/>
+      <c r="M150" s="9"/>
+      <c r="N150" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="O150" s="9"/>
+      <c r="P150" s="9"/>
+      <c r="Q150" s="9"/>
+      <c r="R150" s="9"/>
+      <c r="S150" s="9"/>
+      <c r="T150" s="9"/>
+      <c r="U150" s="9"/>
+      <c r="V150" s="9"/>
+      <c r="W150" s="9"/>
+      <c r="X150" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y150" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z150" s="9"/>
+    </row>
+    <row r="151" spans="1:26">
+      <c r="A151" s="10" t="s">
+        <v>458</v>
+      </c>
+      <c r="B151" s="10" t="s">
+        <v>459</v>
+      </c>
+      <c r="C151" s="10" t="s">
+        <v>460</v>
+      </c>
+      <c r="D151" s="10" t="s">
+        <v>466</v>
+      </c>
+      <c r="E151" s="10" t="s">
+        <v>466</v>
+      </c>
+      <c r="F151" s="11">
+        <v>46156</v>
+      </c>
+      <c r="G151" s="10" t="s">
+        <v>467</v>
+      </c>
+      <c r="H151" s="10" t="s">
+        <v>468</v>
+      </c>
+      <c r="I151" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="J151" s="10"/>
+      <c r="K151" s="10"/>
+      <c r="L151" s="9"/>
+      <c r="M151" s="9"/>
+      <c r="N151" s="10" t="s">
+        <v>469</v>
+      </c>
+      <c r="O151" s="9"/>
+      <c r="P151" s="9"/>
+      <c r="Q151" s="9"/>
+      <c r="R151" s="9"/>
+      <c r="S151" s="9"/>
+      <c r="T151" s="9"/>
+      <c r="U151" s="9"/>
+      <c r="V151" s="9"/>
+      <c r="W151" s="9"/>
+      <c r="X151" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y151" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z151" s="9"/>
+    </row>
+    <row r="152" spans="1:26">
+      <c r="A152" s="10" t="s">
+        <v>518</v>
+      </c>
+      <c r="B152" s="10" t="s">
+        <v>519</v>
+      </c>
+      <c r="C152" s="10" t="s">
+        <v>520</v>
+      </c>
+      <c r="D152" s="10" t="s">
+        <v>521</v>
+      </c>
+      <c r="E152" s="10" t="s">
+        <v>521</v>
+      </c>
+      <c r="F152" s="11">
+        <v>46203</v>
+      </c>
+      <c r="G152" s="10" t="s">
+        <v>522</v>
+      </c>
+      <c r="H152" s="10" t="s">
+        <v>523</v>
+      </c>
+      <c r="I152" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J152" s="10"/>
+      <c r="K152" s="10"/>
+      <c r="L152" s="9"/>
+      <c r="M152" s="9"/>
+      <c r="N152" s="10" t="s">
+        <v>524</v>
+      </c>
+      <c r="O152" s="9"/>
+      <c r="P152" s="9"/>
+      <c r="Q152" s="9"/>
+      <c r="R152" s="9"/>
+      <c r="S152" s="9"/>
+      <c r="T152" s="9"/>
+      <c r="U152" s="9"/>
+      <c r="V152" s="9"/>
+      <c r="W152" s="9"/>
+      <c r="X152" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y152" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z152" s="9"/>
+    </row>
+    <row r="153" spans="1:26">
+      <c r="A153" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="B153" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="C153" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="D153" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="E153" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="F153" s="13">
+        <v>46177</v>
+      </c>
+      <c r="G153" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="H153" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="I153" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="J153" s="12"/>
+      <c r="K153" s="12"/>
+      <c r="L153" s="9"/>
+      <c r="M153" s="9"/>
+      <c r="N153" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="O153" s="9"/>
+      <c r="P153" s="9"/>
+      <c r="Q153" s="9"/>
+      <c r="R153" s="9"/>
+      <c r="S153" s="9"/>
+      <c r="T153" s="9"/>
+      <c r="U153" s="9"/>
+      <c r="V153" s="9"/>
+      <c r="W153" s="9"/>
+      <c r="X153" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y153" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z153" s="9"/>
+    </row>
+    <row r="154" spans="1:26">
+      <c r="A154" s="10" t="s">
+        <v>525</v>
+      </c>
+      <c r="B154" s="10" t="s">
+        <v>526</v>
+      </c>
+      <c r="C154" s="10" t="s">
+        <v>527</v>
+      </c>
+      <c r="D154" s="10" t="s">
+        <v>528</v>
+      </c>
+      <c r="E154" s="10" t="s">
+        <v>528</v>
+      </c>
+      <c r="F154" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="G154" s="10" t="s">
+        <v>529</v>
+      </c>
+      <c r="H154" s="10" t="s">
+        <v>530</v>
+      </c>
+      <c r="I154" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J154" s="10"/>
+      <c r="K154" s="10"/>
+      <c r="L154" s="9"/>
+      <c r="M154" s="9"/>
+      <c r="N154" s="10" t="s">
+        <v>531</v>
+      </c>
+      <c r="O154" s="9"/>
+      <c r="P154" s="9"/>
+      <c r="Q154" s="9"/>
+      <c r="R154" s="9"/>
+      <c r="S154" s="9"/>
+      <c r="T154" s="9"/>
+      <c r="U154" s="9"/>
+      <c r="V154" s="9"/>
+      <c r="W154" s="9"/>
+      <c r="X154" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y154" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z154" s="9"/>
+    </row>
+    <row r="155" spans="1:26">
+      <c r="A155" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="B155" s="10" t="s">
+        <v>276</v>
+      </c>
+      <c r="C155" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="D155" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="E155" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="F155" s="10" t="s">
+        <v>279</v>
+      </c>
+      <c r="G155" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="H155" s="10" t="s">
+        <v>281</v>
+      </c>
+      <c r="I155" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J155" s="10"/>
+      <c r="K155" s="10"/>
+      <c r="L155" s="9"/>
+      <c r="M155" s="9"/>
+      <c r="N155" s="10" t="s">
+        <v>282</v>
+      </c>
+      <c r="O155" s="9"/>
+      <c r="P155" s="9"/>
+      <c r="Q155" s="9"/>
+      <c r="R155" s="9"/>
+      <c r="S155" s="9"/>
+      <c r="T155" s="9"/>
+      <c r="U155" s="9"/>
+      <c r="V155" s="9"/>
+      <c r="W155" s="9"/>
+      <c r="X155" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y155" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z155" s="9"/>
+    </row>
+    <row r="156" spans="1:26">
+      <c r="A156" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="B156" s="10" t="s">
+        <v>276</v>
+      </c>
+      <c r="C156" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="D156" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="E156" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="F156" s="10" t="s">
+        <v>279</v>
+      </c>
+      <c r="G156" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="H156" s="10" t="s">
+        <v>285</v>
+      </c>
+      <c r="I156" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J156" s="10"/>
+      <c r="K156" s="10"/>
+      <c r="L156" s="9"/>
+      <c r="M156" s="9"/>
+      <c r="N156" s="10" t="s">
+        <v>286</v>
+      </c>
+      <c r="O156" s="9"/>
+      <c r="P156" s="9"/>
+      <c r="Q156" s="9"/>
+      <c r="R156" s="9"/>
+      <c r="S156" s="9"/>
+      <c r="T156" s="9"/>
+      <c r="U156" s="9"/>
+      <c r="V156" s="9"/>
+      <c r="W156" s="9"/>
+      <c r="X156" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y156" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z156" s="9"/>
+    </row>
+    <row r="157" spans="1:26">
+      <c r="A157" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="B157" s="10" t="s">
+        <v>354</v>
+      </c>
+      <c r="C157" s="10" t="s">
+        <v>355</v>
+      </c>
+      <c r="D157" s="10" t="s">
+        <v>356</v>
+      </c>
+      <c r="E157" s="10" t="s">
+        <v>356</v>
+      </c>
+      <c r="F157" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="G157" s="10" t="s">
+        <v>357</v>
+      </c>
+      <c r="H157" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="I157" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J157" s="10"/>
+      <c r="K157" s="10"/>
+      <c r="L157" s="9"/>
+      <c r="M157" s="9"/>
+      <c r="N157" s="10" t="s">
+        <v>359</v>
+      </c>
+      <c r="O157" s="9"/>
+      <c r="P157" s="9"/>
+      <c r="Q157" s="9"/>
+      <c r="R157" s="9"/>
+      <c r="S157" s="9"/>
+      <c r="T157" s="9"/>
+      <c r="U157" s="9"/>
+      <c r="V157" s="9"/>
+      <c r="W157" s="9"/>
+      <c r="X157" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y157" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z157" s="9"/>
+    </row>
+    <row r="158" spans="1:26">
+      <c r="A158" s="10" t="s">
+        <v>686</v>
+      </c>
+      <c r="B158" s="10" t="s">
+        <v>687</v>
+      </c>
+      <c r="C158" s="10" t="s">
+        <v>688</v>
+      </c>
+      <c r="D158" s="10" t="s">
+        <v>689</v>
+      </c>
+      <c r="E158" s="10" t="s">
+        <v>689</v>
+      </c>
+      <c r="F158" s="14">
+        <v>46246</v>
+      </c>
+      <c r="G158" s="10" t="s">
+        <v>690</v>
+      </c>
+      <c r="H158" s="10" t="s">
+        <v>691</v>
+      </c>
+      <c r="I158" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J158" s="10"/>
+      <c r="K158" s="10"/>
+      <c r="L158" s="9"/>
+      <c r="M158" s="9"/>
+      <c r="N158" s="10" t="s">
+        <v>692</v>
+      </c>
+      <c r="O158" s="9"/>
+      <c r="P158" s="9"/>
+      <c r="Q158" s="9"/>
+      <c r="R158" s="9"/>
+      <c r="S158" s="9"/>
+      <c r="T158" s="9"/>
+      <c r="U158" s="9"/>
+      <c r="V158" s="9"/>
+      <c r="W158" s="9"/>
+      <c r="X158" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y158" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z158" s="9"/>
+    </row>
+    <row r="159" spans="1:26">
+      <c r="A159" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="B159" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="C159" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="D159" s="10" t="s">
+        <v>693</v>
+      </c>
+      <c r="E159" s="10" t="s">
+        <v>693</v>
+      </c>
+      <c r="F159" s="14">
+        <v>46265</v>
+      </c>
+      <c r="G159" s="10" t="s">
+        <v>694</v>
+      </c>
+      <c r="H159" s="10" t="s">
+        <v>695</v>
+      </c>
+      <c r="I159" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J159" s="10"/>
+      <c r="K159" s="10"/>
+      <c r="L159" s="9"/>
+      <c r="M159" s="9"/>
+      <c r="N159" s="10" t="s">
+        <v>696</v>
+      </c>
+      <c r="O159" s="9"/>
+      <c r="P159" s="9"/>
+      <c r="Q159" s="9"/>
+      <c r="R159" s="9"/>
+      <c r="S159" s="9"/>
+      <c r="T159" s="9"/>
+      <c r="U159" s="9"/>
+      <c r="V159" s="9"/>
+      <c r="W159" s="9"/>
+      <c r="X159" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y159" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z159" s="9"/>
+    </row>
+    <row r="160" spans="1:26">
+      <c r="A160" s="10" t="s">
+        <v>697</v>
+      </c>
+      <c r="B160" s="10" t="s">
+        <v>698</v>
+      </c>
+      <c r="C160" s="10" t="s">
+        <v>699</v>
+      </c>
+      <c r="D160" s="10" t="s">
+        <v>700</v>
+      </c>
+      <c r="E160" s="10" t="s">
+        <v>700</v>
+      </c>
+      <c r="F160" s="14">
+        <v>46265</v>
+      </c>
+      <c r="G160" s="10" t="s">
+        <v>701</v>
+      </c>
+      <c r="H160" s="10" t="s">
+        <v>702</v>
+      </c>
+      <c r="I160" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J160" s="10"/>
+      <c r="K160" s="10"/>
+      <c r="L160" s="9"/>
+      <c r="M160" s="9"/>
+      <c r="N160" s="10" t="s">
+        <v>703</v>
+      </c>
+      <c r="O160" s="9"/>
+      <c r="P160" s="9"/>
+      <c r="Q160" s="9"/>
+      <c r="R160" s="9"/>
+      <c r="S160" s="9"/>
+      <c r="T160" s="9"/>
+      <c r="U160" s="9"/>
+      <c r="V160" s="9"/>
+      <c r="W160" s="9"/>
+      <c r="X160" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y160" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z160" s="9"/>
+    </row>
+    <row r="161" spans="1:26">
+      <c r="A161" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="B161" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="C161" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="D161" s="10" t="s">
+        <v>704</v>
+      </c>
+      <c r="E161" s="10" t="s">
+        <v>704</v>
+      </c>
+      <c r="F161" s="14">
+        <v>46265</v>
+      </c>
+      <c r="G161" s="10" t="s">
+        <v>705</v>
+      </c>
+      <c r="H161" s="10" t="s">
+        <v>706</v>
+      </c>
+      <c r="I161" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J161" s="10"/>
+      <c r="K161" s="10"/>
+      <c r="L161" s="9"/>
+      <c r="M161" s="9"/>
+      <c r="N161" s="10" t="s">
+        <v>707</v>
+      </c>
+      <c r="O161" s="9"/>
+      <c r="P161" s="9"/>
+      <c r="Q161" s="9"/>
+      <c r="R161" s="9"/>
+      <c r="S161" s="9"/>
+      <c r="T161" s="9"/>
+      <c r="U161" s="9"/>
+      <c r="V161" s="9"/>
+      <c r="W161" s="9"/>
+      <c r="X161" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y161" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z161" s="9"/>
+    </row>
+    <row r="162" spans="1:26">
+      <c r="A162" s="10" t="s">
+        <v>708</v>
+      </c>
+      <c r="B162" s="10" t="s">
+        <v>709</v>
+      </c>
+      <c r="C162" s="10" t="s">
+        <v>710</v>
+      </c>
+      <c r="D162" s="10" t="s">
+        <v>711</v>
+      </c>
+      <c r="E162" s="10" t="s">
+        <v>711</v>
+      </c>
+      <c r="F162" s="14">
+        <v>46265</v>
+      </c>
+      <c r="G162" s="10" t="s">
+        <v>712</v>
+      </c>
+      <c r="H162" s="10" t="s">
+        <v>713</v>
+      </c>
+      <c r="I162" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J162" s="10"/>
+      <c r="K162" s="10"/>
+      <c r="L162" s="9"/>
+      <c r="M162" s="9"/>
+      <c r="N162" s="10" t="s">
+        <v>714</v>
+      </c>
+      <c r="O162" s="9"/>
+      <c r="P162" s="9"/>
+      <c r="Q162" s="9"/>
+      <c r="R162" s="9"/>
+      <c r="S162" s="9"/>
+      <c r="T162" s="9"/>
+      <c r="U162" s="9"/>
+      <c r="V162" s="9"/>
+      <c r="W162" s="9"/>
+      <c r="X162" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y162" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z162" s="9"/>
+    </row>
+    <row r="163" spans="1:26">
+      <c r="A163" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B163" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C163" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D163" s="10" t="s">
+        <v>715</v>
+      </c>
+      <c r="E163" s="10" t="s">
+        <v>715</v>
+      </c>
+      <c r="F163" s="14">
+        <v>46265</v>
+      </c>
+      <c r="G163" s="10" t="s">
+        <v>716</v>
+      </c>
+      <c r="H163" s="10" t="s">
+        <v>717</v>
+      </c>
+      <c r="I163" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J163" s="10"/>
+      <c r="K163" s="10"/>
+      <c r="L163" s="9"/>
+      <c r="M163" s="9"/>
+      <c r="N163" s="10" t="s">
+        <v>718</v>
+      </c>
+      <c r="O163" s="9"/>
+      <c r="P163" s="9"/>
+      <c r="Q163" s="9"/>
+      <c r="R163" s="9"/>
+      <c r="S163" s="9"/>
+      <c r="T163" s="9"/>
+      <c r="U163" s="9"/>
+      <c r="V163" s="9"/>
+      <c r="W163" s="9"/>
+      <c r="X163" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y163" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z163" s="9"/>
+    </row>
+    <row r="164" spans="1:26">
+      <c r="A164" s="10" t="s">
+        <v>733</v>
+      </c>
+      <c r="B164" s="10" t="s">
+        <v>734</v>
+      </c>
+      <c r="C164" s="10" t="s">
+        <v>735</v>
+      </c>
+      <c r="D164" s="10" t="s">
+        <v>736</v>
+      </c>
+      <c r="E164" s="10" t="s">
+        <v>736</v>
+      </c>
+      <c r="F164" s="14">
+        <v>46260</v>
+      </c>
+      <c r="G164" s="10" t="s">
+        <v>737</v>
+      </c>
+      <c r="H164" s="10" t="s">
+        <v>738</v>
+      </c>
+      <c r="I164" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J164" s="10"/>
+      <c r="K164" s="10"/>
+      <c r="L164" s="9"/>
+      <c r="M164" s="9"/>
+      <c r="N164" s="10" t="s">
+        <v>739</v>
+      </c>
+      <c r="O164" s="9"/>
+      <c r="P164" s="9"/>
+      <c r="Q164" s="9"/>
+      <c r="R164" s="9"/>
+      <c r="S164" s="9"/>
+      <c r="T164" s="9"/>
+      <c r="U164" s="9"/>
+      <c r="V164" s="9"/>
+      <c r="W164" s="9"/>
+      <c r="X164" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y164" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z164" s="9"/>
+    </row>
+    <row r="165" spans="1:26">
+      <c r="A165" s="10" t="s">
+        <v>740</v>
+      </c>
+      <c r="B165" s="10" t="s">
+        <v>741</v>
+      </c>
+      <c r="C165" s="10" t="s">
+        <v>742</v>
+      </c>
+      <c r="D165" s="10" t="s">
+        <v>743</v>
+      </c>
+      <c r="E165" s="10" t="s">
+        <v>743</v>
+      </c>
+      <c r="F165" s="14">
+        <v>46257</v>
+      </c>
+      <c r="G165" s="10" t="s">
+        <v>744</v>
+      </c>
+      <c r="H165" s="10" t="s">
+        <v>745</v>
+      </c>
+      <c r="I165" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J165" s="10"/>
+      <c r="K165" s="10"/>
+      <c r="L165" s="9"/>
+      <c r="M165" s="9"/>
+      <c r="N165" s="10" t="s">
+        <v>746</v>
+      </c>
+      <c r="O165" s="9"/>
+      <c r="P165" s="9"/>
+      <c r="Q165" s="9"/>
+      <c r="R165" s="9"/>
+      <c r="S165" s="9"/>
+      <c r="T165" s="9"/>
+      <c r="U165" s="9"/>
+      <c r="V165" s="9"/>
+      <c r="W165" s="9"/>
+      <c r="X165" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y165" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z165" s="9"/>
+    </row>
+    <row r="166" spans="1:26">
+      <c r="A166" s="10" t="s">
+        <v>751</v>
+      </c>
+      <c r="B166" s="10" t="s">
+        <v>752</v>
+      </c>
+      <c r="C166" s="10" t="s">
+        <v>753</v>
+      </c>
+      <c r="D166" s="10" t="s">
+        <v>754</v>
+      </c>
+      <c r="E166" s="10" t="s">
+        <v>754</v>
+      </c>
+      <c r="F166" s="14">
+        <v>46265</v>
+      </c>
+      <c r="G166" s="10" t="s">
+        <v>755</v>
+      </c>
+      <c r="H166" s="10" t="s">
+        <v>756</v>
+      </c>
+      <c r="I166" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J166" s="10"/>
+      <c r="K166" s="10"/>
+      <c r="L166" s="9"/>
+      <c r="M166" s="9"/>
+      <c r="N166" s="10" t="s">
+        <v>757</v>
+      </c>
+      <c r="O166" s="9"/>
+      <c r="P166" s="9"/>
+      <c r="Q166" s="9"/>
+      <c r="R166" s="9"/>
+      <c r="S166" s="9"/>
+      <c r="T166" s="9"/>
+      <c r="U166" s="9"/>
+      <c r="V166" s="9"/>
+      <c r="W166" s="9"/>
+      <c r="X166" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y166" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z166" s="9"/>
+    </row>
+    <row r="167" spans="1:26">
+      <c r="A167" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="B167" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="C167" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="D167" s="10" t="s">
+        <v>773</v>
+      </c>
+      <c r="E167" s="10" t="s">
+        <v>773</v>
+      </c>
+      <c r="F167" s="14">
+        <v>46252</v>
+      </c>
+      <c r="G167" s="10" t="s">
+        <v>774</v>
+      </c>
+      <c r="H167" s="10" t="s">
+        <v>775</v>
+      </c>
+      <c r="I167" s="10" t="s">
+        <v>539</v>
+      </c>
+      <c r="J167" s="10"/>
+      <c r="K167" s="10"/>
+      <c r="L167" s="9"/>
+      <c r="M167" s="9"/>
+      <c r="N167" s="10" t="s">
+        <v>776</v>
+      </c>
+      <c r="O167" s="9"/>
+      <c r="P167" s="9"/>
+      <c r="Q167" s="9"/>
+      <c r="R167" s="9"/>
+      <c r="S167" s="9"/>
+      <c r="T167" s="9"/>
+      <c r="U167" s="9"/>
+      <c r="V167" s="9"/>
+      <c r="W167" s="9"/>
+      <c r="X167" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y167" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z167" s="9"/>
+    </row>
+    <row r="168" spans="1:26">
+      <c r="A168" s="10" t="s">
+        <v>577</v>
+      </c>
+      <c r="B168" s="10" t="s">
+        <v>578</v>
+      </c>
+      <c r="C168" s="10" t="s">
+        <v>579</v>
+      </c>
+      <c r="D168" s="10" t="s">
+        <v>860</v>
+      </c>
+      <c r="E168" s="10" t="s">
+        <v>860</v>
+      </c>
+      <c r="F168" s="14">
+        <v>46265</v>
+      </c>
+      <c r="G168" s="10" t="s">
+        <v>581</v>
+      </c>
+      <c r="H168" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="I168" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J168" s="10"/>
+      <c r="K168" s="10"/>
+      <c r="L168" s="9"/>
+      <c r="M168" s="9"/>
+      <c r="N168" s="10" t="s">
+        <v>583</v>
+      </c>
+      <c r="O168" s="9"/>
+      <c r="P168" s="9"/>
+      <c r="Q168" s="9"/>
+      <c r="R168" s="9"/>
+      <c r="S168" s="9"/>
+      <c r="T168" s="9"/>
+      <c r="U168" s="9"/>
+      <c r="V168" s="9"/>
+      <c r="W168" s="9"/>
+      <c r="X168" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y168" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z168" s="9"/>
+    </row>
+    <row r="169" spans="1:26">
+      <c r="A169" s="10" t="s">
+        <v>796</v>
+      </c>
+      <c r="B169" s="10" t="s">
+        <v>797</v>
+      </c>
+      <c r="C169" s="10" t="s">
+        <v>798</v>
+      </c>
+      <c r="D169" s="10" t="s">
+        <v>799</v>
+      </c>
+      <c r="E169" s="10" t="s">
+        <v>799</v>
+      </c>
+      <c r="F169" s="14">
+        <v>46251</v>
+      </c>
+      <c r="G169" s="10" t="s">
+        <v>800</v>
+      </c>
+      <c r="H169" s="10" t="s">
+        <v>801</v>
+      </c>
+      <c r="I169" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J169" s="10"/>
+      <c r="K169" s="10"/>
+      <c r="L169" s="9"/>
+      <c r="M169" s="9"/>
+      <c r="N169" s="10" t="s">
+        <v>802</v>
+      </c>
+      <c r="O169" s="9"/>
+      <c r="P169" s="9"/>
+      <c r="Q169" s="9"/>
+      <c r="R169" s="9"/>
+      <c r="S169" s="9"/>
+      <c r="T169" s="9"/>
+      <c r="U169" s="9"/>
+      <c r="V169" s="9"/>
+      <c r="W169" s="9"/>
+      <c r="X169" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y169" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z169" s="9"/>
+    </row>
+    <row r="170" spans="1:26" hidden="1">
+      <c r="A170" s="10" t="s">
+        <v>817</v>
+      </c>
+      <c r="B170" s="10" t="s">
+        <v>818</v>
+      </c>
+      <c r="C170" s="10" t="s">
+        <v>819</v>
+      </c>
+      <c r="D170" s="10" t="s">
+        <v>820</v>
+      </c>
+      <c r="E170" s="10" t="s">
+        <v>820</v>
+      </c>
+      <c r="F170" s="14">
+        <v>46259</v>
+      </c>
+      <c r="G170" s="10" t="s">
+        <v>821</v>
+      </c>
+      <c r="H170" s="10" t="s">
+        <v>822</v>
+      </c>
+      <c r="I170" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J170" s="10"/>
+      <c r="K170" s="10"/>
+      <c r="L170" s="9"/>
+      <c r="M170" s="9"/>
+      <c r="N170" s="10" t="s">
+        <v>823</v>
+      </c>
+      <c r="O170" s="9"/>
+      <c r="P170" s="9"/>
+      <c r="Q170" s="9"/>
+      <c r="R170" s="9"/>
+      <c r="S170" s="9"/>
+      <c r="T170" s="9"/>
+      <c r="U170" s="9"/>
+      <c r="V170" s="9"/>
+      <c r="W170" s="9"/>
+      <c r="X170" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y170" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="Z170" s="9"/>
+    </row>
+    <row r="171" spans="1:26">
+      <c r="A171" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="B171" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="C171" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="D171" s="10" t="s">
+        <v>835</v>
+      </c>
+      <c r="E171" s="10" t="s">
+        <v>835</v>
+      </c>
+      <c r="F171" s="14">
+        <v>46251</v>
+      </c>
+      <c r="G171" s="10" t="s">
+        <v>836</v>
+      </c>
+      <c r="H171" s="10" t="s">
+        <v>837</v>
+      </c>
+      <c r="I171" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J171" s="10"/>
+      <c r="K171" s="10"/>
+      <c r="L171" s="9"/>
+      <c r="M171" s="9"/>
+      <c r="N171" s="10" t="s">
+        <v>838</v>
+      </c>
+      <c r="O171" s="9"/>
+      <c r="P171" s="9"/>
+      <c r="Q171" s="9"/>
+      <c r="R171" s="9"/>
+      <c r="S171" s="9"/>
+      <c r="T171" s="9"/>
+      <c r="U171" s="9"/>
+      <c r="V171" s="9"/>
+      <c r="W171" s="9"/>
+      <c r="X171" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y171" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z171" s="9"/>
+    </row>
+    <row r="172" spans="1:26" hidden="1">
+      <c r="A172" s="10" t="s">
+        <v>853</v>
+      </c>
+      <c r="B172" s="10" t="s">
+        <v>854</v>
+      </c>
+      <c r="C172" s="10" t="s">
+        <v>855</v>
+      </c>
+      <c r="D172" s="10" t="s">
+        <v>856</v>
+      </c>
+      <c r="E172" s="10" t="s">
+        <v>856</v>
+      </c>
+      <c r="F172" s="14">
+        <v>46259</v>
+      </c>
+      <c r="G172" s="10" t="s">
+        <v>857</v>
+      </c>
+      <c r="H172" s="10" t="s">
+        <v>858</v>
+      </c>
+      <c r="I172" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J172" s="10"/>
+      <c r="K172" s="10"/>
+      <c r="L172" s="9"/>
+      <c r="M172" s="9"/>
+      <c r="N172" s="10" t="s">
+        <v>859</v>
+      </c>
+      <c r="O172" s="9"/>
+      <c r="P172" s="9"/>
+      <c r="Q172" s="9"/>
+      <c r="R172" s="9"/>
+      <c r="S172" s="9"/>
+      <c r="T172" s="9"/>
+      <c r="U172" s="9"/>
+      <c r="V172" s="9"/>
+      <c r="W172" s="9"/>
+      <c r="X172" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y172" s="9" t="s">
+        <v>795</v>
+      </c>
+      <c r="Z172" s="9"/>
+    </row>
+    <row r="173" spans="1:26">
+      <c r="A173" s="10" t="s">
+        <v>861</v>
+      </c>
+      <c r="B173" s="10" t="s">
+        <v>862</v>
+      </c>
+      <c r="C173" s="10" t="s">
+        <v>863</v>
+      </c>
+      <c r="D173" s="10" t="s">
+        <v>864</v>
+      </c>
+      <c r="E173" s="10" t="s">
+        <v>864</v>
+      </c>
+      <c r="F173" s="14">
+        <v>46293</v>
+      </c>
+      <c r="G173" s="10" t="s">
+        <v>865</v>
+      </c>
+      <c r="H173" s="10" t="s">
+        <v>866</v>
+      </c>
+      <c r="I173" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J173" s="10"/>
+      <c r="K173" s="10"/>
+      <c r="L173" s="9"/>
+      <c r="M173" s="9"/>
+      <c r="N173" s="10" t="s">
+        <v>867</v>
+      </c>
+      <c r="O173" s="9"/>
+      <c r="P173" s="9"/>
+      <c r="Q173" s="9"/>
+      <c r="R173" s="9"/>
+      <c r="S173" s="9"/>
+      <c r="T173" s="9"/>
+      <c r="U173" s="9"/>
+      <c r="V173" s="9"/>
+      <c r="W173" s="9"/>
+      <c r="X173" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y173" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z173" s="9"/>
+    </row>
+    <row r="174" spans="1:26">
+      <c r="A174" s="10" t="s">
+        <v>810</v>
+      </c>
+      <c r="B174" s="10" t="s">
+        <v>811</v>
+      </c>
+      <c r="C174" s="10" t="s">
+        <v>812</v>
+      </c>
+      <c r="D174" s="10" t="s">
+        <v>868</v>
+      </c>
+      <c r="E174" s="10" t="s">
+        <v>868</v>
+      </c>
+      <c r="F174" s="14">
+        <v>46295</v>
+      </c>
+      <c r="G174" s="10" t="s">
+        <v>869</v>
+      </c>
+      <c r="H174" s="10" t="s">
+        <v>870</v>
+      </c>
+      <c r="I174" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J174" s="10"/>
+      <c r="K174" s="10"/>
+      <c r="L174" s="9"/>
+      <c r="M174" s="9"/>
+      <c r="N174" s="10" t="s">
+        <v>1094</v>
+      </c>
+      <c r="O174" s="9"/>
+      <c r="P174" s="9"/>
+      <c r="Q174" s="9"/>
+      <c r="R174" s="9"/>
+      <c r="S174" s="9"/>
+      <c r="T174" s="9"/>
+      <c r="U174" s="9"/>
+      <c r="V174" s="9"/>
+      <c r="W174" s="9"/>
+      <c r="X174" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y174" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z174" s="9"/>
+    </row>
+    <row r="175" spans="1:26">
+      <c r="A175" s="10" t="s">
+        <v>871</v>
+      </c>
+      <c r="B175" s="10" t="s">
+        <v>872</v>
+      </c>
+      <c r="C175" s="10" t="s">
+        <v>873</v>
+      </c>
+      <c r="D175" s="10" t="s">
+        <v>874</v>
+      </c>
+      <c r="E175" s="10" t="s">
+        <v>874</v>
+      </c>
+      <c r="F175" s="14">
+        <v>46282</v>
+      </c>
+      <c r="G175" s="10" t="s">
+        <v>875</v>
+      </c>
+      <c r="H175" s="10" t="s">
+        <v>876</v>
+      </c>
+      <c r="I175" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J175" s="10"/>
+      <c r="K175" s="10"/>
+      <c r="L175" s="9"/>
+      <c r="M175" s="9"/>
+      <c r="N175" s="10" t="s">
+        <v>877</v>
+      </c>
+      <c r="O175" s="9"/>
+      <c r="P175" s="9"/>
+      <c r="Q175" s="9"/>
+      <c r="R175" s="9"/>
+      <c r="S175" s="9"/>
+      <c r="T175" s="9"/>
+      <c r="U175" s="9"/>
+      <c r="V175" s="9"/>
+      <c r="W175" s="9"/>
+      <c r="X175" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y175" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z175" s="9"/>
+    </row>
+    <row r="176" spans="1:26" hidden="1">
+      <c r="A176" s="10" t="s">
+        <v>878</v>
+      </c>
+      <c r="B176" s="10" t="s">
+        <v>879</v>
+      </c>
+      <c r="C176" s="10" t="s">
+        <v>880</v>
+      </c>
+      <c r="D176" s="10" t="s">
+        <v>881</v>
+      </c>
+      <c r="E176" s="10" t="s">
+        <v>881</v>
+      </c>
+      <c r="F176" s="14">
+        <v>46287</v>
+      </c>
+      <c r="G176" s="10" t="s">
+        <v>882</v>
+      </c>
+      <c r="H176" s="10" t="s">
+        <v>883</v>
+      </c>
+      <c r="I176" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J176" s="10"/>
+      <c r="K176" s="10"/>
+      <c r="L176" s="9"/>
+      <c r="M176" s="9"/>
+      <c r="N176" s="10" t="s">
+        <v>884</v>
+      </c>
+      <c r="O176" s="9"/>
+      <c r="P176" s="9"/>
+      <c r="Q176" s="9"/>
+      <c r="R176" s="9"/>
+      <c r="S176" s="9"/>
+      <c r="T176" s="9"/>
+      <c r="U176" s="9"/>
+      <c r="V176" s="9"/>
+      <c r="W176" s="9"/>
+      <c r="X176" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y176" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z176" s="9"/>
+    </row>
+    <row r="177" spans="1:26">
+      <c r="A177" s="10" t="s">
+        <v>885</v>
+      </c>
+      <c r="B177" s="10" t="s">
+        <v>886</v>
+      </c>
+      <c r="C177" s="10" t="s">
+        <v>887</v>
+      </c>
+      <c r="D177" s="10" t="s">
+        <v>888</v>
+      </c>
+      <c r="E177" s="10" t="s">
+        <v>888</v>
+      </c>
+      <c r="F177" s="14">
+        <v>46295</v>
+      </c>
+      <c r="G177" s="10" t="s">
+        <v>889</v>
+      </c>
+      <c r="H177" s="10" t="s">
+        <v>890</v>
+      </c>
+      <c r="I177" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J177" s="10"/>
+      <c r="K177" s="10"/>
+      <c r="L177" s="9"/>
+      <c r="M177" s="9"/>
+      <c r="N177" s="10" t="s">
+        <v>891</v>
+      </c>
+      <c r="O177" s="9"/>
+      <c r="P177" s="9"/>
+      <c r="Q177" s="9"/>
+      <c r="R177" s="9"/>
+      <c r="S177" s="9"/>
+      <c r="T177" s="9"/>
+      <c r="U177" s="9"/>
+      <c r="V177" s="9"/>
+      <c r="W177" s="9"/>
+      <c r="X177" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y177" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z177" s="9"/>
+    </row>
+    <row r="178" spans="1:26" hidden="1">
+      <c r="A178" s="10" t="s">
+        <v>892</v>
+      </c>
+      <c r="B178" s="10" t="s">
+        <v>893</v>
+      </c>
+      <c r="C178" s="10" t="s">
+        <v>894</v>
+      </c>
+      <c r="D178" s="10" t="s">
+        <v>895</v>
+      </c>
+      <c r="E178" s="10" t="s">
+        <v>895</v>
+      </c>
+      <c r="F178" s="14">
+        <v>46293</v>
+      </c>
+      <c r="G178" s="10" t="s">
+        <v>896</v>
+      </c>
+      <c r="H178" s="10" t="s">
+        <v>897</v>
+      </c>
+      <c r="I178" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J178" s="10"/>
+      <c r="K178" s="10"/>
+      <c r="L178" s="9"/>
+      <c r="M178" s="9"/>
+      <c r="N178" s="10" t="s">
+        <v>898</v>
+      </c>
+      <c r="O178" s="9"/>
+      <c r="P178" s="9"/>
+      <c r="Q178" s="9"/>
+      <c r="R178" s="9"/>
+      <c r="S178" s="9"/>
+      <c r="T178" s="9"/>
+      <c r="U178" s="9"/>
+      <c r="V178" s="9"/>
+      <c r="W178" s="9"/>
+      <c r="X178" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y178" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z178" s="9"/>
+    </row>
+    <row r="179" spans="1:26">
+      <c r="A179" s="10" t="s">
+        <v>899</v>
+      </c>
+      <c r="B179" s="10" t="s">
+        <v>900</v>
+      </c>
+      <c r="C179" s="10" t="s">
+        <v>901</v>
+      </c>
+      <c r="D179" s="10" t="s">
+        <v>902</v>
+      </c>
+      <c r="E179" s="10" t="s">
+        <v>902</v>
+      </c>
+      <c r="F179" s="14">
+        <v>46295</v>
+      </c>
+      <c r="G179" s="10" t="s">
+        <v>903</v>
+      </c>
+      <c r="H179" s="10" t="s">
+        <v>904</v>
+      </c>
+      <c r="I179" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J179" s="10"/>
+      <c r="K179" s="10"/>
+      <c r="L179" s="9"/>
+      <c r="M179" s="9"/>
+      <c r="N179" s="10" t="s">
+        <v>905</v>
+      </c>
+      <c r="O179" s="9"/>
+      <c r="P179" s="9"/>
+      <c r="Q179" s="9"/>
+      <c r="R179" s="9"/>
+      <c r="S179" s="9"/>
+      <c r="T179" s="9"/>
+      <c r="U179" s="9"/>
+      <c r="V179" s="9"/>
+      <c r="W179" s="9"/>
+      <c r="X179" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y179" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z179" s="9"/>
+    </row>
+    <row r="180" spans="1:26" hidden="1">
+      <c r="A180" s="10" t="s">
+        <v>491</v>
+      </c>
+      <c r="B180" s="10" t="s">
+        <v>492</v>
+      </c>
+      <c r="C180" s="10" t="s">
+        <v>493</v>
+      </c>
+      <c r="D180" s="10" t="s">
+        <v>906</v>
+      </c>
+      <c r="E180" s="10" t="s">
+        <v>906</v>
+      </c>
+      <c r="F180" s="14">
+        <v>46293</v>
+      </c>
+      <c r="G180" s="10" t="s">
+        <v>907</v>
+      </c>
+      <c r="H180" s="12" t="s">
+        <v>908</v>
+      </c>
+      <c r="I180" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J180" s="10"/>
+      <c r="K180" s="10"/>
+      <c r="L180" s="9"/>
+      <c r="M180" s="9"/>
+      <c r="N180" s="10" t="s">
+        <v>909</v>
+      </c>
+      <c r="O180" s="9"/>
+      <c r="P180" s="9"/>
+      <c r="Q180" s="9"/>
+      <c r="R180" s="9"/>
+      <c r="S180" s="9"/>
+      <c r="T180" s="9"/>
+      <c r="U180" s="9"/>
+      <c r="V180" s="9"/>
+      <c r="W180" s="9"/>
+      <c r="X180" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y180" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z180" s="9"/>
+    </row>
+    <row r="181" spans="1:26" hidden="1">
+      <c r="A181" s="10" t="s">
+        <v>910</v>
+      </c>
+      <c r="B181" s="10" t="s">
+        <v>911</v>
+      </c>
+      <c r="C181" s="10" t="s">
+        <v>912</v>
+      </c>
+      <c r="D181" s="10" t="s">
+        <v>913</v>
+      </c>
+      <c r="E181" s="10" t="s">
+        <v>913</v>
+      </c>
+      <c r="F181" s="14">
+        <v>46276</v>
+      </c>
+      <c r="G181" s="10" t="s">
+        <v>914</v>
+      </c>
+      <c r="H181" s="10" t="s">
+        <v>915</v>
+      </c>
+      <c r="I181" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="J181" s="10"/>
+      <c r="K181" s="10"/>
+      <c r="L181" s="9"/>
+      <c r="M181" s="9"/>
+      <c r="N181" s="10" t="s">
+        <v>916</v>
+      </c>
+      <c r="O181" s="9"/>
+      <c r="P181" s="9"/>
+      <c r="Q181" s="9"/>
+      <c r="R181" s="9"/>
+      <c r="S181" s="9"/>
+      <c r="T181" s="9"/>
+      <c r="U181" s="9"/>
+      <c r="V181" s="9"/>
+      <c r="W181" s="9"/>
+      <c r="X181" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y181" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z181" s="9"/>
+    </row>
+    <row r="182" spans="1:26">
+      <c r="A182" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="B182" s="10" t="s">
+        <v>276</v>
+      </c>
+      <c r="C182" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="D182" s="10" t="s">
+        <v>917</v>
+      </c>
+      <c r="E182" s="10" t="s">
+        <v>917</v>
+      </c>
+      <c r="F182" s="14">
+        <v>46294</v>
+      </c>
+      <c r="G182" s="10" t="s">
+        <v>918</v>
+      </c>
+      <c r="H182" s="10" t="s">
+        <v>919</v>
+      </c>
+      <c r="I182" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J182" s="10"/>
+      <c r="K182" s="10"/>
+      <c r="L182" s="9"/>
+      <c r="M182" s="9"/>
+      <c r="N182" s="10" t="s">
+        <v>1095</v>
+      </c>
+      <c r="O182" s="9"/>
+      <c r="P182" s="9"/>
+      <c r="Q182" s="9"/>
+      <c r="R182" s="9"/>
+      <c r="S182" s="9"/>
+      <c r="T182" s="9"/>
+      <c r="U182" s="9"/>
+      <c r="V182" s="9"/>
+      <c r="W182" s="9"/>
+      <c r="X182" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y182" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z182" s="9"/>
+    </row>
+    <row r="183" spans="1:26">
+      <c r="A183" s="10" t="s">
+        <v>920</v>
+      </c>
+      <c r="B183" s="10" t="s">
+        <v>921</v>
+      </c>
+      <c r="C183" s="10" t="s">
+        <v>922</v>
+      </c>
+      <c r="D183" s="10" t="s">
+        <v>923</v>
+      </c>
+      <c r="E183" s="10" t="s">
+        <v>923</v>
+      </c>
+      <c r="F183" s="14">
+        <v>46295</v>
+      </c>
+      <c r="G183" s="10" t="s">
+        <v>924</v>
+      </c>
+      <c r="H183" s="10" t="s">
+        <v>925</v>
+      </c>
+      <c r="I183" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J183" s="10"/>
+      <c r="K183" s="10"/>
+      <c r="L183" s="9"/>
+      <c r="M183" s="9"/>
+      <c r="N183" s="10" t="s">
+        <v>926</v>
+      </c>
+      <c r="O183" s="9"/>
+      <c r="P183" s="9"/>
+      <c r="Q183" s="9"/>
+      <c r="R183" s="9"/>
+      <c r="S183" s="9"/>
+      <c r="T183" s="9"/>
+      <c r="U183" s="9"/>
+      <c r="V183" s="9"/>
+      <c r="W183" s="9"/>
+      <c r="X183" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y183" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z183" s="9"/>
+    </row>
+    <row r="184" spans="1:26">
+      <c r="A184" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="B184" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="C184" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="D184" s="10" t="s">
+        <v>927</v>
+      </c>
+      <c r="E184" s="10" t="s">
+        <v>927</v>
+      </c>
+      <c r="F184" s="14">
+        <v>46283</v>
+      </c>
+      <c r="G184" s="10" t="s">
+        <v>928</v>
+      </c>
+      <c r="H184" s="10" t="s">
+        <v>929</v>
+      </c>
+      <c r="I184" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J184" s="10"/>
+      <c r="K184" s="10"/>
+      <c r="L184" s="9"/>
+      <c r="M184" s="9"/>
+      <c r="N184" s="10" t="s">
+        <v>930</v>
+      </c>
+      <c r="O184" s="9"/>
+      <c r="P184" s="9"/>
+      <c r="Q184" s="9"/>
+      <c r="R184" s="9"/>
+      <c r="S184" s="9"/>
+      <c r="T184" s="9"/>
+      <c r="U184" s="9"/>
+      <c r="V184" s="9"/>
+      <c r="W184" s="9"/>
+      <c r="X184" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y184" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z184" s="9"/>
+    </row>
+    <row r="185" spans="1:26">
+      <c r="A185" s="10" t="s">
+        <v>385</v>
+      </c>
+      <c r="B185" s="10" t="s">
+        <v>386</v>
+      </c>
+      <c r="C185" s="10" t="s">
+        <v>387</v>
+      </c>
+      <c r="D185" s="10" t="s">
+        <v>931</v>
+      </c>
+      <c r="E185" s="10" t="s">
+        <v>931</v>
+      </c>
+      <c r="F185" s="14">
+        <v>46295</v>
+      </c>
+      <c r="G185" s="10" t="s">
+        <v>932</v>
+      </c>
+      <c r="H185" s="10" t="s">
+        <v>933</v>
+      </c>
+      <c r="I185" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="J185" s="10"/>
+      <c r="K185" s="10"/>
+      <c r="L185" s="9"/>
+      <c r="M185" s="9"/>
+      <c r="N185" s="10" t="s">
+        <v>1096</v>
+      </c>
+      <c r="O185" s="9"/>
+      <c r="P185" s="9"/>
+      <c r="Q185" s="9"/>
+      <c r="R185" s="9"/>
+      <c r="S185" s="9"/>
+      <c r="T185" s="9"/>
+      <c r="U185" s="9"/>
+      <c r="V185" s="9"/>
+      <c r="W185" s="9"/>
+      <c r="X185" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y185" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z185" s="9"/>
+    </row>
+    <row r="186" spans="1:26" hidden="1">
+      <c r="A186" s="10" t="s">
+        <v>458</v>
+      </c>
+      <c r="B186" s="10" t="s">
+        <v>459</v>
+      </c>
+      <c r="C186" s="10" t="s">
+        <v>460</v>
+      </c>
+      <c r="D186" s="10" t="s">
+        <v>934</v>
+      </c>
+      <c r="E186" s="10" t="s">
+        <v>934</v>
+      </c>
+      <c r="F186" s="14">
+        <v>46295</v>
+      </c>
+      <c r="G186" s="10" t="s">
+        <v>471</v>
+      </c>
+      <c r="H186" s="10" t="s">
+        <v>472</v>
+      </c>
+      <c r="I186" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J186" s="10"/>
+      <c r="K186" s="10"/>
+      <c r="L186" s="9"/>
+      <c r="M186" s="9"/>
+      <c r="N186" s="10" t="s">
+        <v>473</v>
+      </c>
+      <c r="O186" s="9"/>
+      <c r="P186" s="9"/>
+      <c r="Q186" s="9"/>
+      <c r="R186" s="9"/>
+      <c r="S186" s="9"/>
+      <c r="T186" s="9"/>
+      <c r="U186" s="9"/>
+      <c r="V186" s="9"/>
+      <c r="W186" s="9"/>
+      <c r="X186" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y186" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z186" s="9"/>
+    </row>
+    <row r="187" spans="1:26">
+      <c r="A187" s="10" t="s">
+        <v>935</v>
+      </c>
+      <c r="B187" s="10" t="s">
+        <v>936</v>
+      </c>
+      <c r="C187" s="10" t="s">
+        <v>937</v>
+      </c>
+      <c r="D187" s="10" t="s">
+        <v>938</v>
+      </c>
+      <c r="E187" s="10" t="s">
+        <v>938</v>
+      </c>
+      <c r="F187" s="14">
+        <v>46266</v>
+      </c>
+      <c r="G187" s="10" t="s">
+        <v>939</v>
+      </c>
+      <c r="H187" s="10" t="s">
+        <v>940</v>
+      </c>
+      <c r="I187" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J187" s="10"/>
+      <c r="K187" s="10"/>
+      <c r="L187" s="9"/>
+      <c r="M187" s="9"/>
+      <c r="N187" s="10" t="s">
+        <v>941</v>
+      </c>
+      <c r="O187" s="9"/>
+      <c r="P187" s="9"/>
+      <c r="Q187" s="9"/>
+      <c r="R187" s="9"/>
+      <c r="S187" s="9"/>
+      <c r="T187" s="9"/>
+      <c r="U187" s="9"/>
+      <c r="V187" s="9"/>
+      <c r="W187" s="9"/>
+      <c r="X187" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y187" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z187" s="9"/>
+    </row>
+    <row r="188" spans="1:26">
+      <c r="A188" s="10" t="s">
+        <v>942</v>
+      </c>
+      <c r="B188" s="10" t="s">
+        <v>943</v>
+      </c>
+      <c r="C188" s="10" t="s">
+        <v>944</v>
+      </c>
+      <c r="D188" s="10" t="s">
+        <v>945</v>
+      </c>
+      <c r="E188" s="10" t="s">
+        <v>945</v>
+      </c>
+      <c r="F188" s="14">
+        <v>46295</v>
+      </c>
+      <c r="G188" s="10" t="s">
+        <v>946</v>
+      </c>
+      <c r="H188" s="10" t="s">
+        <v>947</v>
+      </c>
+      <c r="I188" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J188" s="10"/>
+      <c r="K188" s="10"/>
+      <c r="L188" s="9"/>
+      <c r="M188" s="9"/>
+      <c r="N188" s="10" t="s">
+        <v>1097</v>
+      </c>
+      <c r="O188" s="9"/>
+      <c r="P188" s="9"/>
+      <c r="Q188" s="9"/>
+      <c r="R188" s="9"/>
+      <c r="S188" s="9"/>
+      <c r="T188" s="9"/>
+      <c r="U188" s="9"/>
+      <c r="V188" s="9"/>
+      <c r="W188" s="9"/>
+      <c r="X188" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y188" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z188" s="9"/>
+    </row>
+    <row r="189" spans="1:26">
+      <c r="A189" s="10" t="s">
+        <v>948</v>
+      </c>
+      <c r="B189" s="10" t="s">
+        <v>949</v>
+      </c>
+      <c r="C189" s="10" t="s">
+        <v>950</v>
+      </c>
+      <c r="D189" s="10" t="s">
+        <v>951</v>
+      </c>
+      <c r="E189" s="10" t="s">
+        <v>951</v>
+      </c>
+      <c r="F189" s="14">
+        <v>46295</v>
+      </c>
+      <c r="G189" s="10" t="s">
+        <v>952</v>
+      </c>
+      <c r="H189" s="10" t="s">
+        <v>953</v>
+      </c>
+      <c r="I189" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J189" s="10"/>
+      <c r="K189" s="10"/>
+      <c r="L189" s="9"/>
+      <c r="M189" s="9"/>
+      <c r="N189" s="10" t="s">
+        <v>1098</v>
+      </c>
+      <c r="O189" s="9"/>
+      <c r="P189" s="9"/>
+      <c r="Q189" s="9"/>
+      <c r="R189" s="9"/>
+      <c r="S189" s="9"/>
+      <c r="T189" s="9"/>
+      <c r="U189" s="9"/>
+      <c r="V189" s="9"/>
+      <c r="W189" s="9"/>
+      <c r="X189" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y189" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z189" s="9"/>
+    </row>
+    <row r="190" spans="1:26">
+      <c r="A190" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="B190" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="C190" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="D190" s="10" t="s">
+        <v>954</v>
+      </c>
+      <c r="E190" s="10" t="s">
+        <v>954</v>
+      </c>
+      <c r="F190" s="14">
+        <v>46277</v>
+      </c>
+      <c r="G190" s="10" t="s">
+        <v>955</v>
+      </c>
+      <c r="H190" s="10" t="s">
+        <v>956</v>
+      </c>
+      <c r="I190" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J190" s="10"/>
+      <c r="K190" s="10"/>
+      <c r="L190" s="9"/>
+      <c r="M190" s="9"/>
+      <c r="N190" s="10" t="s">
+        <v>957</v>
+      </c>
+      <c r="O190" s="9"/>
+      <c r="P190" s="9"/>
+      <c r="Q190" s="9"/>
+      <c r="R190" s="9"/>
+      <c r="S190" s="9"/>
+      <c r="T190" s="9"/>
+      <c r="U190" s="9"/>
+      <c r="V190" s="9"/>
+      <c r="W190" s="9"/>
+      <c r="X190" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y190" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z190" s="9"/>
+    </row>
+    <row r="191" spans="1:26" hidden="1">
+      <c r="A191" s="10" t="s">
+        <v>958</v>
+      </c>
+      <c r="B191" s="10" t="s">
+        <v>959</v>
+      </c>
+      <c r="C191" s="10" t="s">
+        <v>960</v>
+      </c>
+      <c r="D191" s="10" t="s">
+        <v>961</v>
+      </c>
+      <c r="E191" s="10" t="s">
+        <v>961</v>
+      </c>
+      <c r="F191" s="14">
+        <v>46295</v>
+      </c>
+      <c r="G191" s="10" t="s">
+        <v>962</v>
+      </c>
+      <c r="H191" s="10" t="s">
+        <v>963</v>
+      </c>
+      <c r="I191" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J191" s="10"/>
+      <c r="K191" s="10"/>
+      <c r="L191" s="9"/>
+      <c r="M191" s="9"/>
+      <c r="N191" s="10" t="s">
+        <v>1099</v>
+      </c>
+      <c r="O191" s="9"/>
+      <c r="P191" s="9"/>
+      <c r="Q191" s="9"/>
+      <c r="R191" s="9"/>
+      <c r="S191" s="9"/>
+      <c r="T191" s="9"/>
+      <c r="U191" s="9"/>
+      <c r="V191" s="9"/>
+      <c r="W191" s="9"/>
+      <c r="X191" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="Y191" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z191" s="9"/>
+    </row>
+    <row r="192" spans="1:26">
+      <c r="A192" s="10" t="s">
+        <v>686</v>
+      </c>
+      <c r="B192" s="10" t="s">
+        <v>687</v>
+      </c>
+      <c r="C192" s="10" t="s">
+        <v>688</v>
+      </c>
+      <c r="D192" s="10" t="s">
+        <v>964</v>
+      </c>
+      <c r="E192" s="10" t="s">
+        <v>964</v>
+      </c>
+      <c r="F192" s="14">
+        <v>46289</v>
+      </c>
+      <c r="G192" s="10" t="s">
+        <v>965</v>
+      </c>
+      <c r="H192" s="10" t="s">
+        <v>966</v>
+      </c>
+      <c r="I192" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J192" s="10"/>
+      <c r="K192" s="10"/>
+      <c r="L192" s="9"/>
+      <c r="M192" s="9"/>
+      <c r="N192" s="10" t="s">
+        <v>967</v>
+      </c>
+      <c r="O192" s="9"/>
+      <c r="P192" s="9"/>
+      <c r="Q192" s="9"/>
+      <c r="R192" s="9"/>
+      <c r="S192" s="9"/>
+      <c r="T192" s="9"/>
+      <c r="U192" s="9"/>
+      <c r="V192" s="9"/>
+      <c r="W192" s="9"/>
+      <c r="X192" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y192" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z192" s="9"/>
+    </row>
+    <row r="193" spans="1:26" hidden="1">
+      <c r="A193" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B193" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C193" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D193" s="10" t="s">
+        <v>968</v>
+      </c>
+      <c r="E193" s="10" t="s">
+        <v>968</v>
+      </c>
+      <c r="F193" s="14">
+        <v>46267</v>
+      </c>
+      <c r="G193" s="10" t="s">
+        <v>969</v>
+      </c>
+      <c r="H193" s="10" t="s">
+        <v>970</v>
+      </c>
+      <c r="I193" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J193" s="10"/>
+      <c r="K193" s="10"/>
+      <c r="L193" s="9"/>
+      <c r="M193" s="9"/>
+      <c r="N193" s="10" t="s">
+        <v>971</v>
+      </c>
+      <c r="O193" s="9"/>
+      <c r="P193" s="9"/>
+      <c r="Q193" s="9"/>
+      <c r="R193" s="9"/>
+      <c r="S193" s="9"/>
+      <c r="T193" s="9"/>
+      <c r="U193" s="9"/>
+      <c r="V193" s="9"/>
+      <c r="W193" s="9"/>
+      <c r="X193" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y193" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z193" s="9"/>
+    </row>
+    <row r="194" spans="1:26">
+      <c r="A194" s="10" t="s">
+        <v>861</v>
+      </c>
+      <c r="B194" s="10" t="s">
+        <v>862</v>
+      </c>
+      <c r="C194" s="10" t="s">
+        <v>863</v>
+      </c>
+      <c r="D194" s="10" t="s">
+        <v>972</v>
+      </c>
+      <c r="E194" s="10" t="s">
+        <v>972</v>
+      </c>
+      <c r="F194" s="14">
+        <v>46293</v>
+      </c>
+      <c r="G194" s="10" t="s">
+        <v>973</v>
+      </c>
+      <c r="H194" s="10" t="s">
+        <v>974</v>
+      </c>
+      <c r="I194" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J194" s="10"/>
+      <c r="K194" s="10"/>
+      <c r="L194" s="9"/>
+      <c r="M194" s="9"/>
+      <c r="N194" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="O194" s="9"/>
+      <c r="P194" s="9"/>
+      <c r="Q194" s="9"/>
+      <c r="R194" s="9"/>
+      <c r="S194" s="9"/>
+      <c r="T194" s="9"/>
+      <c r="U194" s="9"/>
+      <c r="V194" s="9"/>
+      <c r="W194" s="9"/>
+      <c r="X194" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y194" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z194" s="9"/>
+    </row>
+    <row r="195" spans="1:26">
+      <c r="A195" s="10" t="s">
+        <v>976</v>
+      </c>
+      <c r="B195" s="10" t="s">
+        <v>977</v>
+      </c>
+      <c r="C195" s="10" t="s">
+        <v>978</v>
+      </c>
+      <c r="D195" s="10" t="s">
+        <v>979</v>
+      </c>
+      <c r="E195" s="10" t="s">
+        <v>979</v>
+      </c>
+      <c r="F195" s="14">
+        <v>46295</v>
+      </c>
+      <c r="G195" s="10" t="s">
+        <v>980</v>
+      </c>
+      <c r="H195" s="10" t="s">
+        <v>981</v>
+      </c>
+      <c r="I195" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J195" s="10"/>
+      <c r="K195" s="10"/>
+      <c r="L195" s="9"/>
+      <c r="M195" s="9"/>
+      <c r="N195" s="10" t="s">
+        <v>982</v>
+      </c>
+      <c r="O195" s="9"/>
+      <c r="P195" s="9"/>
+      <c r="Q195" s="9"/>
+      <c r="R195" s="9"/>
+      <c r="S195" s="9"/>
+      <c r="T195" s="9"/>
+      <c r="U195" s="9"/>
+      <c r="V195" s="9"/>
+      <c r="W195" s="9"/>
+      <c r="X195" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y195" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z195" s="9"/>
+    </row>
+    <row r="196" spans="1:26">
+      <c r="A196" s="10" t="s">
+        <v>983</v>
+      </c>
+      <c r="B196" s="10" t="s">
+        <v>984</v>
+      </c>
+      <c r="C196" s="10" t="s">
+        <v>985</v>
+      </c>
+      <c r="D196" s="10" t="s">
+        <v>986</v>
+      </c>
+      <c r="E196" s="10" t="s">
+        <v>986</v>
+      </c>
+      <c r="F196" s="14">
+        <v>46286</v>
+      </c>
+      <c r="G196" s="10" t="s">
+        <v>987</v>
+      </c>
+      <c r="H196" s="10" t="s">
+        <v>988</v>
+      </c>
+      <c r="I196" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J196" s="10"/>
+      <c r="K196" s="10"/>
+      <c r="L196" s="9"/>
+      <c r="M196" s="9"/>
+      <c r="N196" s="10" t="s">
+        <v>1100</v>
+      </c>
+      <c r="O196" s="9"/>
+      <c r="P196" s="9"/>
+      <c r="Q196" s="9"/>
+      <c r="R196" s="9"/>
+      <c r="S196" s="9"/>
+      <c r="T196" s="9"/>
+      <c r="U196" s="9"/>
+      <c r="V196" s="9"/>
+      <c r="W196" s="9"/>
+      <c r="X196" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y196" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z196" s="9"/>
+    </row>
+    <row r="197" spans="1:26" hidden="1">
+      <c r="A197" s="10" t="s">
+        <v>861</v>
+      </c>
+      <c r="B197" s="10" t="s">
+        <v>862</v>
+      </c>
+      <c r="C197" s="10" t="s">
+        <v>863</v>
+      </c>
+      <c r="D197" s="10" t="s">
+        <v>989</v>
+      </c>
+      <c r="E197" s="10" t="s">
+        <v>989</v>
+      </c>
+      <c r="F197" s="14">
+        <v>46274</v>
+      </c>
+      <c r="G197" s="10" t="s">
+        <v>990</v>
+      </c>
+      <c r="H197" s="10" t="s">
+        <v>991</v>
+      </c>
+      <c r="I197" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J197" s="10"/>
+      <c r="K197" s="10"/>
+      <c r="L197" s="9"/>
+      <c r="M197" s="9"/>
+      <c r="N197" s="10" t="s">
+        <v>992</v>
+      </c>
+      <c r="O197" s="9"/>
+      <c r="P197" s="9"/>
+      <c r="Q197" s="9"/>
+      <c r="R197" s="9"/>
+      <c r="S197" s="9"/>
+      <c r="T197" s="9"/>
+      <c r="U197" s="9"/>
+      <c r="V197" s="9"/>
+      <c r="W197" s="9"/>
+      <c r="X197" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y197" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="Z197" s="9"/>
+    </row>
+    <row r="198" spans="1:26" hidden="1">
+      <c r="A198" s="10" t="s">
+        <v>345</v>
+      </c>
+      <c r="B198" s="10" t="s">
+        <v>346</v>
+      </c>
+      <c r="C198" s="10" t="s">
+        <v>347</v>
+      </c>
+      <c r="D198" s="10" t="s">
+        <v>993</v>
+      </c>
+      <c r="E198" s="10" t="s">
+        <v>993</v>
+      </c>
+      <c r="F198" s="14">
+        <v>46268</v>
+      </c>
+      <c r="G198" s="10" t="s">
+        <v>994</v>
+      </c>
+      <c r="H198" s="10" t="s">
+        <v>995</v>
+      </c>
+      <c r="I198" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J198" s="10"/>
+      <c r="K198" s="10"/>
+      <c r="L198" s="9"/>
+      <c r="M198" s="9"/>
+      <c r="N198" s="10" t="s">
+        <v>996</v>
+      </c>
+      <c r="O198" s="9"/>
+      <c r="P198" s="9"/>
+      <c r="Q198" s="9"/>
+      <c r="R198" s="9"/>
+      <c r="S198" s="9"/>
+      <c r="T198" s="9"/>
+      <c r="U198" s="9"/>
+      <c r="V198" s="9"/>
+      <c r="W198" s="9"/>
+      <c r="X198" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y198" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z198" s="9"/>
+    </row>
+    <row r="199" spans="1:26">
+      <c r="A199" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="B199" s="10" t="s">
+        <v>276</v>
+      </c>
+      <c r="C199" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="D199" s="10" t="s">
+        <v>997</v>
+      </c>
+      <c r="E199" s="10" t="s">
+        <v>997</v>
+      </c>
+      <c r="F199" s="14">
+        <v>46287</v>
+      </c>
+      <c r="G199" s="10" t="s">
+        <v>998</v>
+      </c>
+      <c r="H199" s="10" t="s">
+        <v>999</v>
+      </c>
+      <c r="I199" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J199" s="10"/>
+      <c r="K199" s="10"/>
+      <c r="L199" s="9"/>
+      <c r="M199" s="9"/>
+      <c r="N199" s="10" t="s">
+        <v>1000</v>
+      </c>
+      <c r="O199" s="9"/>
+      <c r="P199" s="9"/>
+      <c r="Q199" s="9"/>
+      <c r="R199" s="9"/>
+      <c r="S199" s="9"/>
+      <c r="T199" s="9"/>
+      <c r="U199" s="9"/>
+      <c r="V199" s="9"/>
+      <c r="W199" s="9"/>
+      <c r="X199" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y199" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z199" s="9"/>
+    </row>
+    <row r="200" spans="1:26" hidden="1">
+      <c r="A200" s="10" t="s">
+        <v>267</v>
+      </c>
+      <c r="B200" s="10" t="s">
+        <v>268</v>
+      </c>
+      <c r="C200" s="10" t="s">
+        <v>269</v>
+      </c>
+      <c r="D200" s="10" t="s">
+        <v>1001</v>
+      </c>
+      <c r="E200" s="10" t="s">
+        <v>1001</v>
+      </c>
+      <c r="F200" s="14">
+        <v>46282</v>
+      </c>
+      <c r="G200" s="10" t="s">
+        <v>1002</v>
+      </c>
+      <c r="H200" s="10" t="s">
+        <v>1003</v>
+      </c>
+      <c r="I200" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J200" s="10"/>
+      <c r="K200" s="10"/>
+      <c r="L200" s="9"/>
+      <c r="M200" s="9"/>
+      <c r="N200" s="10" t="s">
+        <v>1004</v>
+      </c>
+      <c r="O200" s="9"/>
+      <c r="P200" s="9"/>
+      <c r="Q200" s="9"/>
+      <c r="R200" s="9"/>
+      <c r="S200" s="9"/>
+      <c r="T200" s="9"/>
+      <c r="U200" s="9"/>
+      <c r="V200" s="9"/>
+      <c r="W200" s="9"/>
+      <c r="X200" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y200" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z200" s="9"/>
+    </row>
+    <row r="201" spans="1:26" hidden="1">
+      <c r="A201" s="10" t="s">
+        <v>719</v>
+      </c>
+      <c r="B201" s="10" t="s">
+        <v>720</v>
+      </c>
+      <c r="C201" s="10" t="s">
+        <v>721</v>
+      </c>
+      <c r="D201" s="10" t="s">
+        <v>1005</v>
+      </c>
+      <c r="E201" s="10" t="s">
+        <v>1005</v>
+      </c>
+      <c r="F201" s="14">
+        <v>46279</v>
+      </c>
+      <c r="G201" s="10" t="s">
+        <v>1006</v>
+      </c>
+      <c r="H201" s="10" t="s">
+        <v>1007</v>
+      </c>
+      <c r="I201" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J201" s="10"/>
+      <c r="K201" s="10"/>
+      <c r="L201" s="9"/>
+      <c r="M201" s="9"/>
+      <c r="N201" s="10" t="s">
+        <v>1008</v>
+      </c>
+      <c r="O201" s="9"/>
+      <c r="P201" s="9"/>
+      <c r="Q201" s="9"/>
+      <c r="R201" s="9"/>
+      <c r="S201" s="9"/>
+      <c r="T201" s="9"/>
+      <c r="U201" s="9"/>
+      <c r="V201" s="9"/>
+      <c r="W201" s="9"/>
+      <c r="X201" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y201" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="Z201" s="9"/>
+    </row>
+    <row r="202" spans="1:26" hidden="1">
+      <c r="A202" s="10" t="s">
+        <v>564</v>
+      </c>
+      <c r="B202" s="10" t="s">
+        <v>565</v>
+      </c>
+      <c r="C202" s="10" t="s">
+        <v>566</v>
+      </c>
+      <c r="D202" s="10" t="s">
+        <v>1009</v>
+      </c>
+      <c r="E202" s="10" t="s">
+        <v>1009</v>
+      </c>
+      <c r="F202" s="14">
+        <v>46289</v>
+      </c>
+      <c r="G202" s="10" t="s">
+        <v>1010</v>
+      </c>
+      <c r="H202" s="10" t="s">
+        <v>1011</v>
+      </c>
+      <c r="I202" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J202" s="10"/>
+      <c r="K202" s="10"/>
+      <c r="L202" s="9"/>
+      <c r="M202" s="9"/>
+      <c r="N202" s="10" t="s">
+        <v>1012</v>
+      </c>
+      <c r="O202" s="9"/>
+      <c r="P202" s="9"/>
+      <c r="Q202" s="9"/>
+      <c r="R202" s="9"/>
+      <c r="S202" s="9"/>
+      <c r="T202" s="9"/>
+      <c r="U202" s="9"/>
+      <c r="V202" s="9"/>
+      <c r="W202" s="9"/>
+      <c r="X202" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y202" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z202" s="9"/>
+    </row>
+    <row r="203" spans="1:26">
+      <c r="A203" s="10" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B203" s="10" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C203" s="10" t="s">
+        <v>1015</v>
+      </c>
+      <c r="D203" s="10" t="s">
+        <v>1016</v>
+      </c>
+      <c r="E203" s="10" t="s">
+        <v>1016</v>
+      </c>
+      <c r="F203" s="14">
+        <v>46289</v>
+      </c>
+      <c r="G203" s="10" t="s">
+        <v>1017</v>
+      </c>
+      <c r="H203" s="10" t="s">
+        <v>1018</v>
+      </c>
+      <c r="I203" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J203" s="10"/>
+      <c r="K203" s="10"/>
+      <c r="L203" s="9"/>
+      <c r="M203" s="9"/>
+      <c r="N203" s="10" t="s">
+        <v>1100</v>
+      </c>
+      <c r="O203" s="9"/>
+      <c r="P203" s="9"/>
+      <c r="Q203" s="9"/>
+      <c r="R203" s="9"/>
+      <c r="S203" s="9"/>
+      <c r="T203" s="9"/>
+      <c r="U203" s="9"/>
+      <c r="V203" s="9"/>
+      <c r="W203" s="9"/>
+      <c r="X203" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y203" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z203" s="9"/>
+    </row>
+    <row r="204" spans="1:26" hidden="1">
+      <c r="A204" s="10" t="s">
+        <v>345</v>
+      </c>
+      <c r="B204" s="10" t="s">
+        <v>346</v>
+      </c>
+      <c r="C204" s="10" t="s">
+        <v>347</v>
+      </c>
+      <c r="D204" s="10" t="s">
+        <v>1019</v>
+      </c>
+      <c r="E204" s="10" t="s">
+        <v>1019</v>
+      </c>
+      <c r="F204" s="14">
+        <v>46284</v>
+      </c>
+      <c r="G204" s="10" t="s">
+        <v>1020</v>
+      </c>
+      <c r="H204" s="10" t="s">
+        <v>1021</v>
+      </c>
+      <c r="I204" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J204" s="10"/>
+      <c r="K204" s="10"/>
+      <c r="L204" s="9"/>
+      <c r="M204" s="9"/>
+      <c r="N204" s="10" t="s">
+        <v>1022</v>
+      </c>
+      <c r="O204" s="9"/>
+      <c r="P204" s="9"/>
+      <c r="Q204" s="9"/>
+      <c r="R204" s="9"/>
+      <c r="S204" s="9"/>
+      <c r="T204" s="9"/>
+      <c r="U204" s="9"/>
+      <c r="V204" s="9"/>
+      <c r="W204" s="9"/>
+      <c r="X204" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y204" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z204" s="9"/>
+    </row>
+    <row r="205" spans="1:26" hidden="1">
+      <c r="A205" s="10" t="s">
+        <v>788</v>
+      </c>
+      <c r="B205" s="10" t="s">
+        <v>789</v>
+      </c>
+      <c r="C205" s="10" t="s">
+        <v>790</v>
+      </c>
+      <c r="D205" s="10" t="s">
+        <v>1023</v>
+      </c>
+      <c r="E205" s="10" t="s">
+        <v>1023</v>
+      </c>
+      <c r="F205" s="14">
+        <v>46272</v>
+      </c>
+      <c r="G205" s="10" t="s">
+        <v>792</v>
+      </c>
+      <c r="H205" s="10" t="s">
+        <v>793</v>
+      </c>
+      <c r="I205" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J205" s="10"/>
+      <c r="K205" s="10"/>
+      <c r="L205" s="9"/>
+      <c r="M205" s="9"/>
+      <c r="N205" s="10" t="s">
+        <v>794</v>
+      </c>
+      <c r="O205" s="9"/>
+      <c r="P205" s="9"/>
+      <c r="Q205" s="9"/>
+      <c r="R205" s="9"/>
+      <c r="S205" s="9"/>
+      <c r="T205" s="9"/>
+      <c r="U205" s="9"/>
+      <c r="V205" s="9"/>
+      <c r="W205" s="9"/>
+      <c r="X205" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y205" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z205" s="9"/>
+    </row>
+    <row r="206" spans="1:26" hidden="1">
+      <c r="A206" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="B206" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="C206" s="10" t="s">
+        <v>319</v>
+      </c>
+      <c r="D206" s="10" t="s">
+        <v>1024</v>
+      </c>
+      <c r="E206" s="10" t="s">
+        <v>1024</v>
+      </c>
+      <c r="F206" s="14">
+        <v>46294</v>
+      </c>
+      <c r="G206" s="10" t="s">
+        <v>1025</v>
+      </c>
+      <c r="H206" s="10" t="s">
+        <v>1026</v>
+      </c>
+      <c r="I206" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J206" s="10"/>
+      <c r="K206" s="10"/>
+      <c r="L206" s="9"/>
+      <c r="M206" s="9"/>
+      <c r="N206" s="10" t="s">
+        <v>1027</v>
+      </c>
+      <c r="O206" s="9"/>
+      <c r="P206" s="9"/>
+      <c r="Q206" s="9"/>
+      <c r="R206" s="9"/>
+      <c r="S206" s="9"/>
+      <c r="T206" s="9"/>
+      <c r="U206" s="9"/>
+      <c r="V206" s="9"/>
+      <c r="W206" s="9"/>
+      <c r="X206" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y206" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z206" s="9"/>
+    </row>
+    <row r="207" spans="1:26" hidden="1">
+      <c r="A207" s="10" t="s">
+        <v>267</v>
+      </c>
+      <c r="B207" s="10" t="s">
+        <v>268</v>
+      </c>
+      <c r="C207" s="10" t="s">
+        <v>269</v>
+      </c>
+      <c r="D207" s="10" t="s">
+        <v>1028</v>
+      </c>
+      <c r="E207" s="10" t="s">
+        <v>1028</v>
+      </c>
+      <c r="F207" s="14">
+        <v>46273</v>
+      </c>
+      <c r="G207" s="10" t="s">
+        <v>1029</v>
+      </c>
+      <c r="H207" s="10" t="s">
+        <v>1030</v>
+      </c>
+      <c r="I207" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J207" s="10"/>
+      <c r="K207" s="10"/>
+      <c r="L207" s="9"/>
+      <c r="M207" s="9"/>
+      <c r="N207" s="10" t="s">
+        <v>1031</v>
+      </c>
+      <c r="O207" s="9"/>
+      <c r="P207" s="9"/>
+      <c r="Q207" s="9"/>
+      <c r="R207" s="9"/>
+      <c r="S207" s="9"/>
+      <c r="T207" s="9"/>
+      <c r="U207" s="9"/>
+      <c r="V207" s="9"/>
+      <c r="W207" s="9"/>
+      <c r="X207" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y207" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z207" s="9"/>
+    </row>
+    <row r="208" spans="1:26" hidden="1">
+      <c r="A208" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B208" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C208" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D208" s="10" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E208" s="10" t="s">
+        <v>1032</v>
+      </c>
+      <c r="F208" s="14">
+        <v>46295</v>
+      </c>
+      <c r="G208" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="H208" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="I208" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J208" s="10"/>
+      <c r="K208" s="10"/>
+      <c r="L208" s="9"/>
+      <c r="M208" s="9"/>
+      <c r="N208" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="O208" s="9"/>
+      <c r="P208" s="9"/>
+      <c r="Q208" s="9"/>
+      <c r="R208" s="9"/>
+      <c r="S208" s="9"/>
+      <c r="T208" s="9"/>
+      <c r="U208" s="9"/>
+      <c r="V208" s="9"/>
+      <c r="W208" s="9"/>
+      <c r="X208" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y208" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z208" s="9"/>
+    </row>
+    <row r="209" spans="1:26">
+      <c r="A209" s="10" t="s">
+        <v>267</v>
+      </c>
+      <c r="B209" s="10" t="s">
+        <v>268</v>
+      </c>
+      <c r="C209" s="10" t="s">
+        <v>269</v>
+      </c>
+      <c r="D209" s="10" t="s">
+        <v>1033</v>
+      </c>
+      <c r="E209" s="10" t="s">
+        <v>1033</v>
+      </c>
+      <c r="F209" s="14">
+        <v>46294</v>
+      </c>
+      <c r="G209" s="10" t="s">
+        <v>1034</v>
+      </c>
+      <c r="H209" s="10" t="s">
+        <v>1035</v>
+      </c>
+      <c r="I209" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J209" s="10"/>
+      <c r="K209" s="10"/>
+      <c r="L209" s="9"/>
+      <c r="M209" s="9"/>
+      <c r="N209" s="10" t="s">
+        <v>1036</v>
+      </c>
+      <c r="O209" s="9"/>
+      <c r="P209" s="9"/>
+      <c r="Q209" s="9"/>
+      <c r="R209" s="9"/>
+      <c r="S209" s="9"/>
+      <c r="T209" s="9"/>
+      <c r="U209" s="9"/>
+      <c r="V209" s="9"/>
+      <c r="W209" s="9"/>
+      <c r="X209" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y209" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z209" s="9"/>
+    </row>
+    <row r="210" spans="1:26" hidden="1">
+      <c r="A210" s="10" t="s">
+        <v>758</v>
+      </c>
+      <c r="B210" s="10" t="s">
+        <v>759</v>
+      </c>
+      <c r="C210" s="10" t="s">
+        <v>760</v>
+      </c>
+      <c r="D210" s="10" t="s">
+        <v>1037</v>
+      </c>
+      <c r="E210" s="10" t="s">
+        <v>1037</v>
+      </c>
+      <c r="F210" s="14">
+        <v>46284</v>
+      </c>
+      <c r="G210" s="10" t="s">
+        <v>762</v>
+      </c>
+      <c r="H210" s="10" t="s">
+        <v>763</v>
+      </c>
+      <c r="I210" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J210" s="10"/>
+      <c r="K210" s="10"/>
+      <c r="L210" s="9"/>
+      <c r="M210" s="9"/>
+      <c r="N210" s="10" t="s">
+        <v>764</v>
+      </c>
+      <c r="O210" s="9"/>
+      <c r="P210" s="9"/>
+      <c r="Q210" s="9"/>
+      <c r="R210" s="9"/>
+      <c r="S210" s="9"/>
+      <c r="T210" s="9"/>
+      <c r="U210" s="9"/>
+      <c r="V210" s="9"/>
+      <c r="W210" s="9"/>
+      <c r="X210" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y210" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z210" s="9"/>
+    </row>
+    <row r="211" spans="1:26">
+      <c r="A211" s="10" t="s">
+        <v>648</v>
+      </c>
+      <c r="B211" s="10" t="s">
+        <v>649</v>
+      </c>
+      <c r="C211" s="10" t="s">
+        <v>650</v>
+      </c>
+      <c r="D211" s="10" t="s">
+        <v>1038</v>
+      </c>
+      <c r="E211" s="10" t="s">
+        <v>1038</v>
+      </c>
+      <c r="F211" s="14">
+        <v>46295</v>
+      </c>
+      <c r="G211" s="10" t="s">
+        <v>1039</v>
+      </c>
+      <c r="H211" s="10" t="s">
+        <v>1040</v>
+      </c>
+      <c r="I211" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J211" s="10"/>
+      <c r="K211" s="10"/>
+      <c r="L211" s="9"/>
+      <c r="M211" s="9"/>
+      <c r="N211" s="10" t="s">
+        <v>1041</v>
+      </c>
+      <c r="O211" s="9"/>
+      <c r="P211" s="9"/>
+      <c r="Q211" s="9"/>
+      <c r="R211" s="9"/>
+      <c r="S211" s="9"/>
+      <c r="T211" s="9"/>
+      <c r="U211" s="9"/>
+      <c r="V211" s="9"/>
+      <c r="W211" s="9"/>
+      <c r="X211" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y211" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z211" s="9"/>
+    </row>
+    <row r="212" spans="1:26">
+      <c r="A212" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="B212" s="10" t="s">
+        <v>354</v>
+      </c>
+      <c r="C212" s="10" t="s">
+        <v>355</v>
+      </c>
+      <c r="D212" s="10" t="s">
+        <v>1042</v>
+      </c>
+      <c r="E212" s="10" t="s">
+        <v>1042</v>
+      </c>
+      <c r="F212" s="14">
+        <v>46281</v>
+      </c>
+      <c r="G212" s="10" t="s">
+        <v>1043</v>
+      </c>
+      <c r="H212" s="10" t="s">
+        <v>1044</v>
+      </c>
+      <c r="I212" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J212" s="10"/>
+      <c r="K212" s="10"/>
+      <c r="L212" s="9"/>
+      <c r="M212" s="9"/>
+      <c r="N212" s="10" t="s">
+        <v>1045</v>
+      </c>
+      <c r="O212" s="9"/>
+      <c r="P212" s="9"/>
+      <c r="Q212" s="9"/>
+      <c r="R212" s="9"/>
+      <c r="S212" s="9"/>
+      <c r="T212" s="9"/>
+      <c r="U212" s="9"/>
+      <c r="V212" s="9"/>
+      <c r="W212" s="9"/>
+      <c r="X212" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y212" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z212" s="9"/>
+    </row>
+    <row r="213" spans="1:26">
+      <c r="A213" s="10" t="s">
+        <v>935</v>
+      </c>
+      <c r="B213" s="10" t="s">
+        <v>936</v>
+      </c>
+      <c r="C213" s="10" t="s">
+        <v>937</v>
+      </c>
+      <c r="D213" s="10" t="s">
+        <v>1046</v>
+      </c>
+      <c r="E213" s="10" t="s">
+        <v>1046</v>
+      </c>
+      <c r="F213" s="14">
+        <v>46266</v>
+      </c>
+      <c r="G213" s="10" t="s">
+        <v>1047</v>
+      </c>
+      <c r="H213" s="10" t="s">
+        <v>1048</v>
+      </c>
+      <c r="I213" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J213" s="10"/>
+      <c r="K213" s="10"/>
+      <c r="L213" s="9"/>
+      <c r="M213" s="9"/>
+      <c r="N213" s="10" t="s">
+        <v>1049</v>
+      </c>
+      <c r="O213" s="9"/>
+      <c r="P213" s="9"/>
+      <c r="Q213" s="9"/>
+      <c r="R213" s="9"/>
+      <c r="S213" s="9"/>
+      <c r="T213" s="9"/>
+      <c r="U213" s="9"/>
+      <c r="V213" s="9"/>
+      <c r="W213" s="9"/>
+      <c r="X213" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y213" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z213" s="9"/>
+    </row>
+    <row r="214" spans="1:26">
+      <c r="A214" s="10" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B214" s="10" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C214" s="10" t="s">
+        <v>1052</v>
+      </c>
+      <c r="D214" s="10" t="s">
+        <v>1053</v>
+      </c>
+      <c r="E214" s="10" t="s">
+        <v>1053</v>
+      </c>
+      <c r="F214" s="14">
+        <v>46295</v>
+      </c>
+      <c r="G214" s="10" t="s">
+        <v>1054</v>
+      </c>
+      <c r="H214" s="10" t="s">
+        <v>1055</v>
+      </c>
+      <c r="I214" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J214" s="10"/>
+      <c r="K214" s="10"/>
+      <c r="L214" s="9"/>
+      <c r="M214" s="9"/>
+      <c r="N214" s="10" t="s">
+        <v>1101</v>
+      </c>
+      <c r="O214" s="9"/>
+      <c r="P214" s="9"/>
+      <c r="Q214" s="9"/>
+      <c r="R214" s="9"/>
+      <c r="S214" s="9"/>
+      <c r="T214" s="9"/>
+      <c r="U214" s="9"/>
+      <c r="V214" s="9"/>
+      <c r="W214" s="9"/>
+      <c r="X214" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y214" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z214" s="9"/>
+    </row>
+    <row r="215" spans="1:26">
+      <c r="A215" s="10" t="s">
+        <v>1056</v>
+      </c>
+      <c r="B215" s="10" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C215" s="10" t="s">
+        <v>1058</v>
+      </c>
+      <c r="D215" s="10" t="s">
+        <v>1059</v>
+      </c>
+      <c r="E215" s="10" t="s">
+        <v>1059</v>
+      </c>
+      <c r="F215" s="14">
+        <v>46287</v>
+      </c>
+      <c r="G215" s="10" t="s">
+        <v>1060</v>
+      </c>
+      <c r="H215" s="10" t="s">
+        <v>1061</v>
+      </c>
+      <c r="I215" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J215" s="10"/>
+      <c r="K215" s="10"/>
+      <c r="L215" s="9"/>
+      <c r="M215" s="9"/>
+      <c r="N215" s="10" t="s">
+        <v>1062</v>
+      </c>
+      <c r="O215" s="9"/>
+      <c r="P215" s="9"/>
+      <c r="Q215" s="9"/>
+      <c r="R215" s="9"/>
+      <c r="S215" s="9"/>
+      <c r="T215" s="9"/>
+      <c r="U215" s="9"/>
+      <c r="V215" s="9"/>
+      <c r="W215" s="9"/>
+      <c r="X215" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y215" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z215" s="9"/>
+    </row>
+    <row r="216" spans="1:26">
+      <c r="A216" s="10" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B216" s="10" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C216" s="10" t="s">
+        <v>1065</v>
+      </c>
+      <c r="D216" s="10" t="s">
+        <v>1066</v>
+      </c>
+      <c r="E216" s="10" t="s">
+        <v>1066</v>
+      </c>
+      <c r="F216" s="14">
+        <v>46295</v>
+      </c>
+      <c r="G216" s="10" t="s">
+        <v>1067</v>
+      </c>
+      <c r="H216" s="10" t="s">
+        <v>1068</v>
+      </c>
+      <c r="I216" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J216" s="10"/>
+      <c r="K216" s="10"/>
+      <c r="L216" s="9"/>
+      <c r="M216" s="9"/>
+      <c r="N216" s="10" t="s">
+        <v>1102</v>
+      </c>
+      <c r="O216" s="9"/>
+      <c r="P216" s="9"/>
+      <c r="Q216" s="9"/>
+      <c r="R216" s="9"/>
+      <c r="S216" s="9"/>
+      <c r="T216" s="9"/>
+      <c r="U216" s="9"/>
+      <c r="V216" s="9"/>
+      <c r="W216" s="9"/>
+      <c r="X216" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y216" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z216" s="9"/>
+    </row>
+    <row r="217" spans="1:26" hidden="1">
+      <c r="A217" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="B217" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="C217" s="10" t="s">
+        <v>319</v>
+      </c>
+      <c r="D217" s="10" t="s">
+        <v>1069</v>
+      </c>
+      <c r="E217" s="10" t="s">
+        <v>1069</v>
+      </c>
+      <c r="F217" s="14">
+        <v>46273</v>
+      </c>
+      <c r="G217" s="10" t="s">
+        <v>1070</v>
+      </c>
+      <c r="H217" s="10" t="s">
+        <v>1071</v>
+      </c>
+      <c r="I217" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J217" s="10"/>
+      <c r="K217" s="10"/>
+      <c r="L217" s="9"/>
+      <c r="M217" s="9"/>
+      <c r="N217" s="10" t="s">
+        <v>1072</v>
+      </c>
+      <c r="O217" s="9"/>
+      <c r="P217" s="9"/>
+      <c r="Q217" s="9"/>
+      <c r="R217" s="9"/>
+      <c r="S217" s="9"/>
+      <c r="T217" s="9"/>
+      <c r="U217" s="9"/>
+      <c r="V217" s="9"/>
+      <c r="W217" s="9"/>
+      <c r="X217" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y217" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z217" s="9"/>
+    </row>
+    <row r="218" spans="1:26">
+      <c r="A218" s="10" t="s">
+        <v>491</v>
+      </c>
+      <c r="B218" s="10" t="s">
+        <v>492</v>
+      </c>
+      <c r="C218" s="10" t="s">
+        <v>493</v>
+      </c>
+      <c r="D218" s="10" t="s">
+        <v>1073</v>
+      </c>
+      <c r="E218" s="10" t="s">
+        <v>1073</v>
+      </c>
+      <c r="F218" s="14">
+        <v>46295</v>
+      </c>
+      <c r="G218" s="10" t="s">
+        <v>1074</v>
+      </c>
+      <c r="H218" s="12" t="s">
+        <v>1075</v>
+      </c>
+      <c r="I218" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J218" s="10"/>
+      <c r="K218" s="10"/>
+      <c r="L218" s="9"/>
+      <c r="M218" s="9"/>
+      <c r="N218" s="10" t="s">
+        <v>1076</v>
+      </c>
+      <c r="O218" s="9"/>
+      <c r="P218" s="9"/>
+      <c r="Q218" s="9"/>
+      <c r="R218" s="9"/>
+      <c r="S218" s="9"/>
+      <c r="T218" s="9"/>
+      <c r="U218" s="9"/>
+      <c r="V218" s="9"/>
+      <c r="W218" s="9"/>
+      <c r="X218" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y218" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z218" s="9"/>
+    </row>
+    <row r="219" spans="1:26">
+      <c r="A219" s="10" t="s">
+        <v>1077</v>
+      </c>
+      <c r="B219" s="10" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C219" s="10" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D219" s="10" t="s">
+        <v>1080</v>
+      </c>
+      <c r="E219" s="10" t="s">
+        <v>1080</v>
+      </c>
+      <c r="F219" s="14">
+        <v>46281</v>
+      </c>
+      <c r="G219" s="10" t="s">
+        <v>1081</v>
+      </c>
+      <c r="H219" s="10" t="s">
+        <v>1082</v>
+      </c>
+      <c r="I219" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J219" s="10"/>
+      <c r="K219" s="10"/>
+      <c r="L219" s="9"/>
+      <c r="M219" s="9"/>
+      <c r="N219" s="10" t="s">
+        <v>1083</v>
+      </c>
+      <c r="O219" s="9"/>
+      <c r="P219" s="9"/>
+      <c r="Q219" s="9"/>
+      <c r="R219" s="9"/>
+      <c r="S219" s="9"/>
+      <c r="T219" s="9"/>
+      <c r="U219" s="9"/>
+      <c r="V219" s="9"/>
+      <c r="W219" s="9"/>
+      <c r="X219" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y219" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z219" s="9"/>
+    </row>
+    <row r="220" spans="1:26">
+      <c r="A220" s="10" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B220" s="10" t="s">
+        <v>1085</v>
+      </c>
+      <c r="C220" s="10" t="s">
+        <v>1086</v>
+      </c>
+      <c r="D220" s="10" t="s">
+        <v>1087</v>
+      </c>
+      <c r="E220" s="10" t="s">
+        <v>1087</v>
+      </c>
+      <c r="F220" s="14">
+        <v>46294</v>
+      </c>
+      <c r="G220" s="10" t="s">
+        <v>1088</v>
+      </c>
+      <c r="H220" s="10" t="s">
+        <v>1089</v>
+      </c>
+      <c r="I220" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J220" s="10"/>
+      <c r="K220" s="10"/>
+      <c r="L220" s="9"/>
+      <c r="M220" s="9"/>
+      <c r="N220" s="10" t="s">
+        <v>1103</v>
+      </c>
+      <c r="O220" s="9"/>
+      <c r="P220" s="9"/>
+      <c r="Q220" s="9"/>
+      <c r="R220" s="9"/>
+      <c r="S220" s="9"/>
+      <c r="T220" s="9"/>
+      <c r="U220" s="9"/>
+      <c r="V220" s="9"/>
+      <c r="W220" s="9"/>
+      <c r="X220" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y220" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z220" s="9"/>
+    </row>
+    <row r="221" spans="1:26" hidden="1">
+      <c r="A221" s="10" t="s">
+        <v>401</v>
+      </c>
+      <c r="B221" s="10" t="s">
+        <v>402</v>
+      </c>
+      <c r="C221" s="10" t="s">
+        <v>403</v>
+      </c>
+      <c r="D221" s="10" t="s">
+        <v>1090</v>
+      </c>
+      <c r="E221" s="10" t="s">
+        <v>1090</v>
+      </c>
+      <c r="F221" s="14">
+        <v>46268</v>
+      </c>
+      <c r="G221" s="10" t="s">
+        <v>1091</v>
+      </c>
+      <c r="H221" s="10" t="s">
+        <v>1092</v>
+      </c>
+      <c r="I221" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J221" s="10"/>
+      <c r="K221" s="10"/>
+      <c r="L221" s="9"/>
+      <c r="M221" s="9"/>
+      <c r="N221" s="10" t="s">
+        <v>1093</v>
+      </c>
+      <c r="O221" s="9"/>
+      <c r="P221" s="9"/>
+      <c r="Q221" s="9"/>
+      <c r="R221" s="9"/>
+      <c r="S221" s="9"/>
+      <c r="T221" s="9"/>
+      <c r="U221" s="9"/>
+      <c r="V221" s="9"/>
+      <c r="W221" s="9"/>
+      <c r="X221" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y221" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z221" s="9"/>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:Z221" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="24">
+      <filters blank="1"/>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:Z102">
     <sortCondition ref="B4"/>
   </sortState>
   <conditionalFormatting sqref="J2:J60">
+    <cfRule type="duplicateValues" dxfId="8" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M2:M60">
+    <cfRule type="duplicateValues" dxfId="7" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N2:N60 J61:J100">
+    <cfRule type="duplicateValues" dxfId="6" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N2:N100">
+    <cfRule type="duplicateValues" dxfId="5" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K130:K153">
+    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N130:N153">
     <cfRule type="duplicateValues" dxfId="3" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M60">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+  <conditionalFormatting sqref="J130:J157">
+    <cfRule type="duplicateValues" dxfId="2" priority="12"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N60 J61:J100">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+  <conditionalFormatting sqref="N130:N157">
+    <cfRule type="duplicateValues" dxfId="1" priority="13"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N100">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+  <conditionalFormatting sqref="N130:N172">
+    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://singerlk-my.sharepoint.com/personal/dihank_singersl_com/Documents/Desktop/DIHAN/cr dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="180" documentId="11_5847038500C079F1E35F4C8C432471BF012A7624" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{428960B8-A592-4179-90C1-4B7EEE0AE02F}"/>
+  <xr:revisionPtr revIDLastSave="191" documentId="11_5847038500C079F1E35F4C8C432471BF012A7624" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F1E02A73-1C04-45F2-9171-D97F32E74B9B}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DETAILS" sheetId="3" r:id="rId1"/>
+    <sheet name="Emp Sales" sheetId="4" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">DETAILS!$A$1:$Z$221</definedName>
@@ -85,7 +86,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2711" uniqueCount="1104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2801" uniqueCount="1150">
   <si>
     <t>SHOP_CODE</t>
   </si>
@@ -3397,13 +3398,151 @@
   </si>
   <si>
     <t>LGMMVU1K1T0002208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SHOP CODE </t>
+  </si>
+  <si>
+    <t>SHOP</t>
+  </si>
+  <si>
+    <t>ORDER NUMBER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CUSTOMER NAME </t>
+  </si>
+  <si>
+    <t>MAKE</t>
+  </si>
+  <si>
+    <t>CHASSIS NUMBER</t>
+  </si>
+  <si>
+    <t>ENGINE NUMBER</t>
+  </si>
+  <si>
+    <t>CR STATUS</t>
+  </si>
+  <si>
+    <t>YEM01</t>
+  </si>
+  <si>
+    <t>EMPLOYEE SALES MILAG</t>
+  </si>
+  <si>
+    <t>YEM-H16418</t>
+  </si>
+  <si>
+    <t>D.M.A.ISHARA DISSANAYAKE</t>
+  </si>
+  <si>
+    <t>TAILG</t>
+  </si>
+  <si>
+    <t>LGMMVU1K2T0002430</t>
+  </si>
+  <si>
+    <t>TLLMEVTD5102153</t>
+  </si>
+  <si>
+    <t>YEM-H16415</t>
+  </si>
+  <si>
+    <t>H.H.S.HARISCHANDRA</t>
+  </si>
+  <si>
+    <t>LGMMVU1K5T0002051</t>
+  </si>
+  <si>
+    <t>TLLMEVTD5102055</t>
+  </si>
+  <si>
+    <t>K. GNANASEKARAM</t>
+  </si>
+  <si>
+    <t>TLLMEVTD5101682</t>
+  </si>
+  <si>
+    <t>YEM-H16421</t>
+  </si>
+  <si>
+    <t>P.A.H.RUKSHAN PIRISYALA</t>
+  </si>
+  <si>
+    <t>LGMMVU1K5T0002079</t>
+  </si>
+  <si>
+    <t>TLLMEVTD5102085</t>
+  </si>
+  <si>
+    <t>YEM-H16414</t>
+  </si>
+  <si>
+    <t>N.A.A.A.NARASINGHE</t>
+  </si>
+  <si>
+    <t>LGMMVU1K7T0002035</t>
+  </si>
+  <si>
+    <t>TLLMEVTD5101779</t>
+  </si>
+  <si>
+    <t>YEM-H16420</t>
+  </si>
+  <si>
+    <t>H.A.S.P.HAPUARACHCHI</t>
+  </si>
+  <si>
+    <t>LGMMVU1K0T0002393</t>
+  </si>
+  <si>
+    <t>TLLMEVTD5101875</t>
+  </si>
+  <si>
+    <t>YEM-H16416</t>
+  </si>
+  <si>
+    <t>M.S. PUSHPAKUMARA</t>
+  </si>
+  <si>
+    <t>LGMMVU1K9T0002490</t>
+  </si>
+  <si>
+    <t>TLLMEVTD5101949</t>
+  </si>
+  <si>
+    <t>YEM-H16184</t>
+  </si>
+  <si>
+    <t>H.M.K.KOKILA KARUNAARTHNE</t>
+  </si>
+  <si>
+    <t>LIMA</t>
+  </si>
+  <si>
+    <t>L1Z1LL516SA567673</t>
+  </si>
+  <si>
+    <t>10ZW7271320YA257010194</t>
+  </si>
+  <si>
+    <t>YEM-H16417</t>
+  </si>
+  <si>
+    <t>A.M.M.N. PRASAD ADIKARI</t>
+  </si>
+  <si>
+    <t>LGMMVU1K9T0001937</t>
+  </si>
+  <si>
+    <t>TLLMEVTD5101793</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3450,6 +3589,14 @@
       <color indexed="81"/>
       <name val="Tahoma"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -3501,7 +3648,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3542,31 +3689,14 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="46">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3623,6 +3753,26 @@
       </font>
       <fill>
         <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
@@ -16389,23 +16539,23 @@
   <conditionalFormatting sqref="J2:J60">
     <cfRule type="duplicateValues" dxfId="8" priority="9"/>
   </conditionalFormatting>
+  <conditionalFormatting sqref="J130:J157">
+    <cfRule type="duplicateValues" dxfId="7" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K130:K153">
+    <cfRule type="duplicateValues" dxfId="6" priority="1"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="M2:M60">
-    <cfRule type="duplicateValues" dxfId="7" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N2:N60 J61:J100">
-    <cfRule type="duplicateValues" dxfId="6" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N2:N100">
-    <cfRule type="duplicateValues" dxfId="5" priority="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K130:K153">
-    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N130:N153">
-    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J130:J157">
-    <cfRule type="duplicateValues" dxfId="2" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N130:N157">
     <cfRule type="duplicateValues" dxfId="1" priority="13"/>
@@ -16416,4 +16566,314 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6658DE2A-779D-4EE1-A99A-B2C2B8120413}">
+  <dimension ref="A1:I10"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="11.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.6328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.90625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.81640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="18" t="s">
+        <v>1104</v>
+      </c>
+      <c r="B1" s="18" t="s">
+        <v>1105</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>1106</v>
+      </c>
+      <c r="D1" s="18" t="s">
+        <v>1107</v>
+      </c>
+      <c r="E1" s="18" t="s">
+        <v>1108</v>
+      </c>
+      <c r="F1" s="18" t="s">
+        <v>1109</v>
+      </c>
+      <c r="G1" s="18" t="s">
+        <v>1110</v>
+      </c>
+      <c r="H1" s="18" t="s">
+        <v>1111</v>
+      </c>
+      <c r="I1" s="19" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="3" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>1114</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>1115</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>1116</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>1117</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>1118</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>795</v>
+      </c>
+      <c r="I2" s="20" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="3" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>1119</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>1120</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>1116</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>1121</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>1122</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>795</v>
+      </c>
+      <c r="I3" s="20" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>1090</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>1123</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>1116</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>1093</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>1124</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>795</v>
+      </c>
+      <c r="I4" s="20" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="3" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>1125</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>1126</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>1116</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>1127</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>1128</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>795</v>
+      </c>
+      <c r="I5" s="20" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="3" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>1129</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>1130</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>1116</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>1131</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>1132</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>795</v>
+      </c>
+      <c r="I6" s="20" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="3" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>1133</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>1134</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>1116</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>1135</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>1136</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>795</v>
+      </c>
+      <c r="I7" s="20" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="3" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>1137</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>1138</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>1116</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>1139</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>1140</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>795</v>
+      </c>
+      <c r="I8" s="20" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="3" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>1141</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>1142</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>1143</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>1144</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>1145</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>795</v>
+      </c>
+      <c r="I9" s="20" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="3" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>1146</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>1147</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>1116</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>1148</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>1149</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>795</v>
+      </c>
+      <c r="I10" s="20" t="s">
+        <v>36</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://singerlk-my.sharepoint.com/personal/dihank_singersl_com/Documents/Desktop/DIHAN/cr dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="191" documentId="11_5847038500C079F1E35F4C8C432471BF012A7624" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F1E02A73-1C04-45F2-9171-D97F32E74B9B}"/>
+  <xr:revisionPtr revIDLastSave="575" documentId="11_5847038500C079F1E35F4C8C432471BF012A7624" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{36F1E234-B60F-4C87-B78D-8290DF743906}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DETAILS" sheetId="3" r:id="rId1"/>
@@ -86,7 +86,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2801" uniqueCount="1150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3107" uniqueCount="1278">
   <si>
     <t>SHOP_CODE</t>
   </si>
@@ -3418,9 +3418,6 @@
     <t>CHASSIS NUMBER</t>
   </si>
   <si>
-    <t>ENGINE NUMBER</t>
-  </si>
-  <si>
     <t>CR STATUS</t>
   </si>
   <si>
@@ -3442,9 +3439,6 @@
     <t>LGMMVU1K2T0002430</t>
   </si>
   <si>
-    <t>TLLMEVTD5102153</t>
-  </si>
-  <si>
     <t>YEM-H16415</t>
   </si>
   <si>
@@ -3454,15 +3448,9 @@
     <t>LGMMVU1K5T0002051</t>
   </si>
   <si>
-    <t>TLLMEVTD5102055</t>
-  </si>
-  <si>
     <t>K. GNANASEKARAM</t>
   </si>
   <si>
-    <t>TLLMEVTD5101682</t>
-  </si>
-  <si>
     <t>YEM-H16421</t>
   </si>
   <si>
@@ -3472,9 +3460,6 @@
     <t>LGMMVU1K5T0002079</t>
   </si>
   <si>
-    <t>TLLMEVTD5102085</t>
-  </si>
-  <si>
     <t>YEM-H16414</t>
   </si>
   <si>
@@ -3484,9 +3469,6 @@
     <t>LGMMVU1K7T0002035</t>
   </si>
   <si>
-    <t>TLLMEVTD5101779</t>
-  </si>
-  <si>
     <t>YEM-H16420</t>
   </si>
   <si>
@@ -3496,9 +3478,6 @@
     <t>LGMMVU1K0T0002393</t>
   </si>
   <si>
-    <t>TLLMEVTD5101875</t>
-  </si>
-  <si>
     <t>YEM-H16416</t>
   </si>
   <si>
@@ -3508,9 +3487,6 @@
     <t>LGMMVU1K9T0002490</t>
   </si>
   <si>
-    <t>TLLMEVTD5101949</t>
-  </si>
-  <si>
     <t>YEM-H16184</t>
   </si>
   <si>
@@ -3523,9 +3499,6 @@
     <t>L1Z1LL516SA567673</t>
   </si>
   <si>
-    <t>10ZW7271320YA257010194</t>
-  </si>
-  <si>
     <t>YEM-H16417</t>
   </si>
   <si>
@@ -3535,14 +3508,425 @@
     <t>LGMMVU1K9T0001937</t>
   </si>
   <si>
-    <t>TLLMEVTD5101793</t>
+    <t>P.H.D. UDARA</t>
+  </si>
+  <si>
+    <t>L1Z1LL51XRA564186</t>
+  </si>
+  <si>
+    <t>S.B.PAKSHAPERUMA</t>
+  </si>
+  <si>
+    <t>L1Z1LL510RA564018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H.D.N.PRASANNA </t>
+  </si>
+  <si>
+    <t>L1Z1LL516SA569200</t>
+  </si>
+  <si>
+    <t>S.M.E.L. SENEVIRATHNA</t>
+  </si>
+  <si>
+    <t>L1Z1LL510SA566938</t>
+  </si>
+  <si>
+    <t>S.P.SOORIYABANDARA</t>
+  </si>
+  <si>
+    <t>L1Z1LL511SA567094</t>
+  </si>
+  <si>
+    <t>P.C.SILVA</t>
+  </si>
+  <si>
+    <t>L1Z1LL516SA567866</t>
+  </si>
+  <si>
+    <t>J.S.LIYANAGE</t>
+  </si>
+  <si>
+    <t>L1Z1LL510SA567085</t>
+  </si>
+  <si>
+    <t>H.M.S.K.WICKRAMANAYAKE</t>
+  </si>
+  <si>
+    <t>L1Z1LL514SA567719</t>
+  </si>
+  <si>
+    <t>W.P.T.L.CHANDRASIRI</t>
+  </si>
+  <si>
+    <t>LGMMVU1K6S0006382</t>
+  </si>
+  <si>
+    <t>W.N.A.KARUNATHILAKE</t>
+  </si>
+  <si>
+    <t>L1Z1LL510SA566809</t>
+  </si>
+  <si>
+    <t>K.D.S.NISHANTHA</t>
+  </si>
+  <si>
+    <t>LGMMVU1K3T0002470</t>
+  </si>
+  <si>
+    <t>M.A.M.FAIZAL</t>
+  </si>
+  <si>
+    <t>SAFARI</t>
+  </si>
+  <si>
+    <t>SGSAFA4S25B000674</t>
+  </si>
+  <si>
+    <t>P.K.A.N.CHAMIKARA</t>
+  </si>
+  <si>
+    <t>L1Z1LL515SA569138</t>
+  </si>
+  <si>
+    <t>T.S.PARANAGAMA</t>
+  </si>
+  <si>
+    <t>L1Z1LL315PA205036</t>
+  </si>
+  <si>
+    <t>W.A.S.KUMARATHUNGA</t>
+  </si>
+  <si>
+    <t>L1Z1LL12RA566255</t>
+  </si>
+  <si>
+    <t>R.M.W.G.C.M. RATHNAYAKE</t>
+  </si>
+  <si>
+    <t>L1Z1LL516RA566257</t>
+  </si>
+  <si>
+    <t>K.D.A.DEEPTHI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIMA </t>
+  </si>
+  <si>
+    <t>L1Z1LL513SA569140</t>
+  </si>
+  <si>
+    <t>K.H.R.KUMARATHUNGA</t>
+  </si>
+  <si>
+    <t>LGMMVU1K9S0006151</t>
+  </si>
+  <si>
+    <t>M.N.PERIS</t>
+  </si>
+  <si>
+    <t>LGMMVU1H3S0000964</t>
+  </si>
+  <si>
+    <t>G.S.P.HERATH</t>
+  </si>
+  <si>
+    <t>LGMMVU1H4S0000486</t>
+  </si>
+  <si>
+    <t>A.R.D.SILVA</t>
+  </si>
+  <si>
+    <t>L1Z1LL515SA569737</t>
+  </si>
+  <si>
+    <t>H.R.N.SENANAYAKE</t>
+  </si>
+  <si>
+    <t>LGMMVU1K7S0003474</t>
+  </si>
+  <si>
+    <t>T.A.PREMALAL</t>
+  </si>
+  <si>
+    <t>L1Z1LL511SA567791</t>
+  </si>
+  <si>
+    <t>H.G.S.LAKMAL</t>
+  </si>
+  <si>
+    <t>L1Z1LL510SA567782</t>
+  </si>
+  <si>
+    <t>M.A.J.H.FERNANDO</t>
+  </si>
+  <si>
+    <t>L1Z1LL513SA567940</t>
+  </si>
+  <si>
+    <t>B.THANURASAN</t>
+  </si>
+  <si>
+    <t>L1Z1LL514SA567879</t>
+  </si>
+  <si>
+    <t>A.R.N.D.SILVA</t>
+  </si>
+  <si>
+    <t>L1Z1LL519SA567845</t>
+  </si>
+  <si>
+    <t>H.I.VITHANAGE</t>
+  </si>
+  <si>
+    <t>L1Z1LL513SA569204</t>
+  </si>
+  <si>
+    <t>G.I.UPASHANTHA</t>
+  </si>
+  <si>
+    <t>L1Z1LL510RA566061</t>
+  </si>
+  <si>
+    <t>M.S.KUMAR</t>
+  </si>
+  <si>
+    <t>L1Z1LL516RA564153</t>
+  </si>
+  <si>
+    <t>A.P.KALUGALAGE</t>
+  </si>
+  <si>
+    <t>L1Z1LL510RA566173</t>
+  </si>
+  <si>
+    <t>D.R.JAYASOORIYA</t>
+  </si>
+  <si>
+    <t>L1Z1LL511SA567015</t>
+  </si>
+  <si>
+    <t>A.R.M.M.K.RAJAPAKSHA</t>
+  </si>
+  <si>
+    <t>L1Z1LL512SA567931</t>
+  </si>
+  <si>
+    <t>H.D.D.SAMPATH</t>
+  </si>
+  <si>
+    <t>L1Z1LL513RA566121</t>
+  </si>
+  <si>
+    <t>K.M.KAUSHALYA</t>
+  </si>
+  <si>
+    <t>L1Z1LL514RA565138</t>
+  </si>
+  <si>
+    <t>W.L.N.INDRAJEEWA</t>
+  </si>
+  <si>
+    <t>L1Z1LL517RA565120</t>
+  </si>
+  <si>
+    <t>I.M.J.L.BANDARA</t>
+  </si>
+  <si>
+    <t>L1Z1LL512RA564201</t>
+  </si>
+  <si>
+    <t>H.H.A.A.S.HETTIARACHCHI</t>
+  </si>
+  <si>
+    <t>L1Z1LL514RA564197</t>
+  </si>
+  <si>
+    <t>M.P.C.GUNATHILAKE</t>
+  </si>
+  <si>
+    <t>L1Z1LL311PA205051</t>
+  </si>
+  <si>
+    <t>R.M.T.L.BANDARA</t>
+  </si>
+  <si>
+    <t>L1Z1LL317PA205037</t>
+  </si>
+  <si>
+    <t>G.JEYANENTHIRAN</t>
+  </si>
+  <si>
+    <t>L1Z1LL518SA567898</t>
+  </si>
+  <si>
+    <t>BHC01</t>
+  </si>
+  <si>
+    <t>WENNAPPUWA</t>
+  </si>
+  <si>
+    <t>BHC-R75712</t>
+  </si>
+  <si>
+    <t>YAB01</t>
+  </si>
+  <si>
+    <t>EMPLOYEE SALE REGNIS</t>
+  </si>
+  <si>
+    <t>YAB-H5881</t>
+  </si>
+  <si>
+    <t>YEM-H15482</t>
+  </si>
+  <si>
+    <t>YAB-H5749</t>
+  </si>
+  <si>
+    <t>YAB-H5804</t>
+  </si>
+  <si>
+    <t>YAB-H5748</t>
+  </si>
+  <si>
+    <t>YEM-H15553</t>
+  </si>
+  <si>
+    <t>MEGA-MILAGIRIYA</t>
+  </si>
+  <si>
+    <t>MBJ-R7182</t>
+  </si>
+  <si>
+    <t>MBJ01</t>
+  </si>
+  <si>
+    <t>YEM-H15565</t>
+  </si>
+  <si>
+    <t>MEGA - PELIYAGODA</t>
+  </si>
+  <si>
+    <t>MBF-R22087</t>
+  </si>
+  <si>
+    <t>MBF01</t>
+  </si>
+  <si>
+    <t>MBJ-R5227</t>
+  </si>
+  <si>
+    <t>YAB-H5874</t>
+  </si>
+  <si>
+    <t>BAG01</t>
+  </si>
+  <si>
+    <t>BAG-R122225</t>
+  </si>
+  <si>
+    <t>MILAGIRIYA</t>
+  </si>
+  <si>
+    <t>YEM-H15900</t>
+  </si>
+  <si>
+    <t>YAB-H5933</t>
+  </si>
+  <si>
+    <t>YEM-H16009</t>
+  </si>
+  <si>
+    <t>BGM-R48709</t>
+  </si>
+  <si>
+    <t>YAB-H5922</t>
+  </si>
+  <si>
+    <t>YEM-H15869</t>
+  </si>
+  <si>
+    <t>YAB-H5759</t>
+  </si>
+  <si>
+    <t>YAB-H5803</t>
+  </si>
+  <si>
+    <t>YAB-H5789</t>
+  </si>
+  <si>
+    <t>YEM-H15588</t>
+  </si>
+  <si>
+    <t>YAB-H5817</t>
+  </si>
+  <si>
+    <t>MAO01</t>
+  </si>
+  <si>
+    <t>MEGA -MALABE</t>
+  </si>
+  <si>
+    <t>MAO-R83859</t>
+  </si>
+  <si>
+    <t>BAG-R122146</t>
+  </si>
+  <si>
+    <t>BAG-R122175</t>
+  </si>
+  <si>
+    <t>YEM-H15423</t>
+  </si>
+  <si>
+    <t>YAB-H5763</t>
+  </si>
+  <si>
+    <t>YEM-H15463</t>
+  </si>
+  <si>
+    <t>YEM-H14583</t>
+  </si>
+  <si>
+    <t>YEM-H15532</t>
+  </si>
+  <si>
+    <t>Closed</t>
+  </si>
+  <si>
+    <t>P.G.M.B.GUNAWARDANA</t>
+  </si>
+  <si>
+    <t>LGMMVU1K7T0002908</t>
+  </si>
+  <si>
+    <t>W.M.C.M.WANNINAYAKA</t>
+  </si>
+  <si>
+    <t>LGMMVU1KST0002979</t>
+  </si>
+  <si>
+    <t>G.S.R.FERNANDO</t>
+  </si>
+  <si>
+    <t>LGMMVU1H1T0000446</t>
+  </si>
+  <si>
+    <t>YEM-H16626</t>
+  </si>
+  <si>
+    <t>YEM-H16590</t>
+  </si>
+  <si>
+    <t>YEM-H16624</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3592,7 +3976,14 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -3648,7 +4039,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3690,8 +4081,11 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -16570,20 +16964,23 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6658DE2A-779D-4EE1-A99A-B2C2B8120413}">
-  <dimension ref="A1:I10"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H54"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="11.08984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.6328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="27" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.90625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="24" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.453125" customWidth="1"/>
+    <col min="2" max="2" width="30.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="39.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="29.1796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.26953125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:8" ht="21">
       <c r="A1" s="18" t="s">
         <v>1104</v>
       </c>
@@ -16606,274 +17003,1320 @@
         <v>1110</v>
       </c>
       <c r="H1" s="18" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="21">
+      <c r="A2" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>1250</v>
+      </c>
+      <c r="D2" s="20" t="s">
+        <v>1180</v>
+      </c>
+      <c r="E2" s="20" t="s">
+        <v>1115</v>
+      </c>
+      <c r="F2" s="20" t="s">
+        <v>1181</v>
+      </c>
+      <c r="G2" s="20" t="s">
+        <v>795</v>
+      </c>
+      <c r="H2" s="21" t="s">
+        <v>1268</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="21">
+      <c r="A3" s="19" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>1229</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>1144</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>1135</v>
+      </c>
+      <c r="F3" s="19" t="s">
+        <v>1145</v>
+      </c>
+      <c r="G3" s="19" t="s">
+        <v>795</v>
+      </c>
+      <c r="H3" s="21" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="21">
+      <c r="A4" s="19" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>1231</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>1148</v>
+      </c>
+      <c r="E4" s="19" t="s">
+        <v>1135</v>
+      </c>
+      <c r="F4" s="19" t="s">
+        <v>1149</v>
+      </c>
+      <c r="G4" s="19" t="s">
+        <v>795</v>
+      </c>
+      <c r="H4" s="21" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="21">
+      <c r="A5" s="19" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>1232</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>1150</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>1135</v>
+      </c>
+      <c r="F5" s="19" t="s">
+        <v>1151</v>
+      </c>
+      <c r="G5" s="19" t="s">
+        <v>795</v>
+      </c>
+      <c r="H5" s="21" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="21">
+      <c r="A6" s="19" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>1233</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>1152</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>1135</v>
+      </c>
+      <c r="F6" s="19" t="s">
+        <v>1153</v>
+      </c>
+      <c r="G6" s="19" t="s">
+        <v>795</v>
+      </c>
+      <c r="H6" s="21" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="21">
+      <c r="A7" s="19" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>1243</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>1165</v>
+      </c>
+      <c r="E7" s="20" t="s">
+        <v>1135</v>
+      </c>
+      <c r="F7" s="20" t="s">
+        <v>1166</v>
+      </c>
+      <c r="G7" s="20" t="s">
+        <v>795</v>
+      </c>
+      <c r="H7" s="21" t="s">
+        <v>1268</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="21">
+      <c r="A8" s="19" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>1248</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>1176</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>1115</v>
+      </c>
+      <c r="F8" s="20" t="s">
+        <v>1177</v>
+      </c>
+      <c r="G8" s="20" t="s">
+        <v>795</v>
+      </c>
+      <c r="H8" s="21" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="21">
+      <c r="A9" s="19" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>1251</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>1182</v>
+      </c>
+      <c r="E9" s="20" t="s">
+        <v>1135</v>
+      </c>
+      <c r="F9" s="20" t="s">
+        <v>1183</v>
+      </c>
+      <c r="G9" s="20" t="s">
+        <v>795</v>
+      </c>
+      <c r="H9" s="21" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="21">
+      <c r="A10" s="19" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>1253</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>1186</v>
+      </c>
+      <c r="E10" s="20" t="s">
+        <v>1135</v>
+      </c>
+      <c r="F10" s="20" t="s">
+        <v>1187</v>
+      </c>
+      <c r="G10" s="20" t="s">
+        <v>795</v>
+      </c>
+      <c r="H10" s="21" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="21">
+      <c r="A11" s="19" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>1188</v>
+      </c>
+      <c r="E11" s="20" t="s">
+        <v>1135</v>
+      </c>
+      <c r="F11" s="20" t="s">
+        <v>1189</v>
+      </c>
+      <c r="G11" s="20" t="s">
+        <v>795</v>
+      </c>
+      <c r="H11" s="21" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="21">
+      <c r="A12" s="19" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>1255</v>
+      </c>
+      <c r="D12" s="20" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E12" s="20" t="s">
+        <v>1135</v>
+      </c>
+      <c r="F12" s="20" t="s">
+        <v>1191</v>
+      </c>
+      <c r="G12" s="20" t="s">
+        <v>795</v>
+      </c>
+      <c r="H12" s="21" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="21">
+      <c r="A13" s="19" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>1257</v>
+      </c>
+      <c r="D13" s="20" t="s">
+        <v>1194</v>
+      </c>
+      <c r="E13" s="20" t="s">
+        <v>1135</v>
+      </c>
+      <c r="F13" s="20" t="s">
+        <v>1195</v>
+      </c>
+      <c r="G13" s="20" t="s">
+        <v>795</v>
+      </c>
+      <c r="H13" s="21" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="21">
+      <c r="A14" s="19" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>1264</v>
+      </c>
+      <c r="D14" s="20" t="s">
+        <v>1206</v>
+      </c>
+      <c r="E14" s="20" t="s">
+        <v>1135</v>
+      </c>
+      <c r="F14" s="20" t="s">
+        <v>1207</v>
+      </c>
+      <c r="G14" s="20" t="s">
+        <v>795</v>
+      </c>
+      <c r="H14" s="21" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="21">
+      <c r="A15" s="19" t="s">
         <v>1111</v>
       </c>
-      <c r="I1" s="19" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="3" t="s">
+      <c r="B15" s="19" t="s">
         <v>1112</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C15" s="19" t="s">
         <v>1113</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D15" s="19" t="s">
         <v>1114</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E15" s="19" t="s">
         <v>1115</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F15" s="19" t="s">
         <v>1116</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="G15" s="19" t="s">
+        <v>795</v>
+      </c>
+      <c r="H15" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="21">
+      <c r="A16" s="19" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C16" s="19" t="s">
         <v>1117</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="D16" s="19" t="s">
         <v>1118</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="E16" s="19" t="s">
+        <v>1115</v>
+      </c>
+      <c r="F16" s="19" t="s">
+        <v>1119</v>
+      </c>
+      <c r="G16" s="19" t="s">
         <v>795</v>
       </c>
-      <c r="I2" s="20" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" s="3" t="s">
+      <c r="H16" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="21">
+      <c r="A17" s="19" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B17" s="19" t="s">
         <v>1112</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>1113</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>1119</v>
-      </c>
-      <c r="D3" s="3" t="s">
+      <c r="C17" s="19" t="s">
+        <v>1121</v>
+      </c>
+      <c r="D17" s="19" t="s">
+        <v>1122</v>
+      </c>
+      <c r="E17" s="19" t="s">
+        <v>1115</v>
+      </c>
+      <c r="F17" s="19" t="s">
+        <v>1123</v>
+      </c>
+      <c r="G17" s="19" t="s">
+        <v>795</v>
+      </c>
+      <c r="H17" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="21">
+      <c r="A18" s="19" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B18" s="19" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C18" s="19" t="s">
+        <v>1124</v>
+      </c>
+      <c r="D18" s="19" t="s">
+        <v>1125</v>
+      </c>
+      <c r="E18" s="19" t="s">
+        <v>1115</v>
+      </c>
+      <c r="F18" s="19" t="s">
+        <v>1126</v>
+      </c>
+      <c r="G18" s="19" t="s">
+        <v>795</v>
+      </c>
+      <c r="H18" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="21">
+      <c r="A19" s="19" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B19" s="19" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C19" s="19" t="s">
+        <v>1127</v>
+      </c>
+      <c r="D19" s="19" t="s">
+        <v>1128</v>
+      </c>
+      <c r="E19" s="19" t="s">
+        <v>1115</v>
+      </c>
+      <c r="F19" s="19" t="s">
+        <v>1129</v>
+      </c>
+      <c r="G19" s="19" t="s">
+        <v>795</v>
+      </c>
+      <c r="H19" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="21">
+      <c r="A20" s="19" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B20" s="19" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C20" s="19" t="s">
+        <v>1130</v>
+      </c>
+      <c r="D20" s="19" t="s">
+        <v>1131</v>
+      </c>
+      <c r="E20" s="19" t="s">
+        <v>1115</v>
+      </c>
+      <c r="F20" s="19" t="s">
+        <v>1132</v>
+      </c>
+      <c r="G20" s="19" t="s">
+        <v>795</v>
+      </c>
+      <c r="H20" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="21">
+      <c r="A21" s="19" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B21" s="19" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C21" s="19" t="s">
+        <v>1133</v>
+      </c>
+      <c r="D21" s="19" t="s">
+        <v>1134</v>
+      </c>
+      <c r="E21" s="19" t="s">
+        <v>1135</v>
+      </c>
+      <c r="F21" s="19" t="s">
+        <v>1136</v>
+      </c>
+      <c r="G21" s="19" t="s">
+        <v>795</v>
+      </c>
+      <c r="H21" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="21">
+      <c r="A22" s="19" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B22" s="19" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C22" s="19" t="s">
+        <v>1137</v>
+      </c>
+      <c r="D22" s="19" t="s">
+        <v>1138</v>
+      </c>
+      <c r="E22" s="19" t="s">
+        <v>1115</v>
+      </c>
+      <c r="F22" s="19" t="s">
+        <v>1139</v>
+      </c>
+      <c r="G22" s="19" t="s">
+        <v>795</v>
+      </c>
+      <c r="H22" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="21">
+      <c r="A23" s="19" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B23" s="19" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C23" s="19" t="s">
+        <v>1230</v>
+      </c>
+      <c r="D23" s="19" t="s">
+        <v>1146</v>
+      </c>
+      <c r="E23" s="19" t="s">
+        <v>1135</v>
+      </c>
+      <c r="F23" s="19" t="s">
+        <v>1147</v>
+      </c>
+      <c r="G23" s="19" t="s">
+        <v>795</v>
+      </c>
+      <c r="H23" s="21" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="21">
+      <c r="A24" s="19" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B24" s="19" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C24" s="19" t="s">
+        <v>1234</v>
+      </c>
+      <c r="D24" s="19" t="s">
+        <v>1154</v>
+      </c>
+      <c r="E24" s="19" t="s">
+        <v>1135</v>
+      </c>
+      <c r="F24" s="19" t="s">
+        <v>1155</v>
+      </c>
+      <c r="G24" s="19" t="s">
+        <v>795</v>
+      </c>
+      <c r="H24" s="21" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="21">
+      <c r="A25" s="19" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B25" s="19" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C25" s="19" t="s">
+        <v>1238</v>
+      </c>
+      <c r="D25" s="20" t="s">
+        <v>1158</v>
+      </c>
+      <c r="E25" s="20" t="s">
+        <v>1135</v>
+      </c>
+      <c r="F25" s="20" t="s">
+        <v>1159</v>
+      </c>
+      <c r="G25" s="20" t="s">
+        <v>795</v>
+      </c>
+      <c r="H25" s="21" t="s">
+        <v>1268</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="21">
+      <c r="A26" s="19" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B26" s="19" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C26" s="19" t="s">
+        <v>1247</v>
+      </c>
+      <c r="D26" s="20" t="s">
+        <v>1173</v>
+      </c>
+      <c r="E26" s="20" t="s">
+        <v>1174</v>
+      </c>
+      <c r="F26" s="20" t="s">
+        <v>1175</v>
+      </c>
+      <c r="G26" s="20" t="s">
+        <v>795</v>
+      </c>
+      <c r="H26" s="21" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="21">
+      <c r="A27" s="19" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B27" s="19" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C27" s="19" t="s">
+        <v>1249</v>
+      </c>
+      <c r="D27" s="20" t="s">
+        <v>1178</v>
+      </c>
+      <c r="E27" s="20" t="s">
+        <v>1115</v>
+      </c>
+      <c r="F27" s="20" t="s">
+        <v>1179</v>
+      </c>
+      <c r="G27" s="20" t="s">
+        <v>795</v>
+      </c>
+      <c r="H27" s="21" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="21">
+      <c r="A28" s="19" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B28" s="19" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C28" s="19" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D28" s="20" t="s">
+        <v>1184</v>
+      </c>
+      <c r="E28" s="20" t="s">
+        <v>1115</v>
+      </c>
+      <c r="F28" s="20" t="s">
+        <v>1185</v>
+      </c>
+      <c r="G28" s="20" t="s">
+        <v>795</v>
+      </c>
+      <c r="H28" s="21" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="21">
+      <c r="A29" s="19" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B29" s="19" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C29" s="19" t="s">
+        <v>1256</v>
+      </c>
+      <c r="D29" s="20" t="s">
+        <v>1192</v>
+      </c>
+      <c r="E29" s="20" t="s">
+        <v>1135</v>
+      </c>
+      <c r="F29" s="20" t="s">
+        <v>1193</v>
+      </c>
+      <c r="G29" s="20" t="s">
+        <v>795</v>
+      </c>
+      <c r="H29" s="21" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="21">
+      <c r="A30" s="19" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B30" s="19" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C30" s="19" t="s">
+        <v>1263</v>
+      </c>
+      <c r="D30" s="20" t="s">
+        <v>1204</v>
+      </c>
+      <c r="E30" s="20" t="s">
+        <v>1135</v>
+      </c>
+      <c r="F30" s="20" t="s">
+        <v>1205</v>
+      </c>
+      <c r="G30" s="20" t="s">
+        <v>795</v>
+      </c>
+      <c r="H30" s="21" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="21">
+      <c r="A31" s="19" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B31" s="19" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C31" s="19" t="s">
+        <v>1265</v>
+      </c>
+      <c r="D31" s="20" t="s">
+        <v>1208</v>
+      </c>
+      <c r="E31" s="20" t="s">
+        <v>1135</v>
+      </c>
+      <c r="F31" s="20" t="s">
+        <v>1209</v>
+      </c>
+      <c r="G31" s="20" t="s">
+        <v>795</v>
+      </c>
+      <c r="H31" s="21" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="21">
+      <c r="A32" s="19" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B32" s="19" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C32" s="19" t="s">
+        <v>1266</v>
+      </c>
+      <c r="D32" s="20" t="s">
+        <v>1212</v>
+      </c>
+      <c r="E32" s="20" t="s">
+        <v>1135</v>
+      </c>
+      <c r="F32" s="20" t="s">
+        <v>1213</v>
+      </c>
+      <c r="G32" s="20" t="s">
+        <v>795</v>
+      </c>
+      <c r="H32" s="21" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="21">
+      <c r="A33" s="19" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B33" s="19" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C33" s="19" t="s">
+        <v>1267</v>
+      </c>
+      <c r="D33" s="20" t="s">
+        <v>1222</v>
+      </c>
+      <c r="E33" s="20" t="s">
+        <v>1135</v>
+      </c>
+      <c r="F33" s="20" t="s">
+        <v>1223</v>
+      </c>
+      <c r="G33" s="20" t="s">
+        <v>795</v>
+      </c>
+      <c r="H33" s="21" t="s">
+        <v>1268</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="21">
+      <c r="A34" s="19" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B34" s="19" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C34" s="19" t="s">
+        <v>1275</v>
+      </c>
+      <c r="D34" s="21" t="s">
+        <v>1269</v>
+      </c>
+      <c r="E34" s="21" t="s">
+        <v>1115</v>
+      </c>
+      <c r="F34" s="21" t="s">
+        <v>1270</v>
+      </c>
+      <c r="G34" s="21" t="s">
+        <v>795</v>
+      </c>
+      <c r="H34" s="21" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="21">
+      <c r="A35" s="19" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B35" s="19" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C35" s="19" t="s">
+        <v>1276</v>
+      </c>
+      <c r="D35" s="21" t="s">
+        <v>1271</v>
+      </c>
+      <c r="E35" s="21" t="s">
+        <v>1115</v>
+      </c>
+      <c r="F35" s="21" t="s">
+        <v>1272</v>
+      </c>
+      <c r="G35" s="21" t="s">
+        <v>795</v>
+      </c>
+      <c r="H35" s="21" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="21">
+      <c r="A36" s="19" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B36" s="19" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C36" s="19" t="s">
+        <v>1277</v>
+      </c>
+      <c r="D36" s="21" t="s">
+        <v>1273</v>
+      </c>
+      <c r="E36" s="21" t="s">
+        <v>1115</v>
+      </c>
+      <c r="F36" s="21" t="s">
+        <v>1274</v>
+      </c>
+      <c r="G36" s="21" t="s">
+        <v>795</v>
+      </c>
+      <c r="H36" s="21" t="s">
+        <v>1268</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="21">
+      <c r="A37" s="19" t="s">
+        <v>1241</v>
+      </c>
+      <c r="B37" s="19" t="s">
+        <v>1239</v>
+      </c>
+      <c r="C37" s="19" t="s">
+        <v>1240</v>
+      </c>
+      <c r="D37" s="20" t="s">
+        <v>1160</v>
+      </c>
+      <c r="E37" s="20" t="s">
+        <v>1115</v>
+      </c>
+      <c r="F37" s="20" t="s">
+        <v>1161</v>
+      </c>
+      <c r="G37" s="20" t="s">
+        <v>795</v>
+      </c>
+      <c r="H37" s="21" t="s">
+        <v>1268</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="21">
+      <c r="A38" s="19" t="s">
+        <v>1258</v>
+      </c>
+      <c r="B38" s="19" t="s">
+        <v>1259</v>
+      </c>
+      <c r="C38" s="19" t="s">
+        <v>1260</v>
+      </c>
+      <c r="D38" s="20" t="s">
+        <v>1196</v>
+      </c>
+      <c r="E38" s="20" t="s">
+        <v>1135</v>
+      </c>
+      <c r="F38" s="20" t="s">
+        <v>1197</v>
+      </c>
+      <c r="G38" s="20" t="s">
+        <v>795</v>
+      </c>
+      <c r="H38" s="21" t="s">
+        <v>1268</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="21">
+      <c r="A39" s="19" t="s">
+        <v>1237</v>
+      </c>
+      <c r="B39" s="19" t="s">
+        <v>1235</v>
+      </c>
+      <c r="C39" s="19" t="s">
+        <v>1236</v>
+      </c>
+      <c r="D39" s="19" t="s">
+        <v>1156</v>
+      </c>
+      <c r="E39" s="19" t="s">
+        <v>1115</v>
+      </c>
+      <c r="F39" s="19" t="s">
+        <v>1157</v>
+      </c>
+      <c r="G39" s="19" t="s">
+        <v>795</v>
+      </c>
+      <c r="H39" s="21" t="s">
+        <v>1268</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="21">
+      <c r="A40" s="19" t="s">
+        <v>1237</v>
+      </c>
+      <c r="B40" s="19" t="s">
+        <v>1235</v>
+      </c>
+      <c r="C40" s="19" t="s">
+        <v>1242</v>
+      </c>
+      <c r="D40" s="20" t="s">
+        <v>1162</v>
+      </c>
+      <c r="E40" s="20" t="s">
+        <v>1163</v>
+      </c>
+      <c r="F40" s="20" t="s">
+        <v>1164</v>
+      </c>
+      <c r="G40" s="20" t="s">
+        <v>795</v>
+      </c>
+      <c r="H40" s="21" t="s">
+        <v>1268</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="21">
+      <c r="A41" s="19" t="s">
+        <v>1244</v>
+      </c>
+      <c r="B41" s="19" t="s">
+        <v>1246</v>
+      </c>
+      <c r="C41" s="19" t="s">
+        <v>1245</v>
+      </c>
+      <c r="D41" s="20" t="s">
+        <v>1171</v>
+      </c>
+      <c r="E41" s="20" t="s">
+        <v>1135</v>
+      </c>
+      <c r="F41" s="20" t="s">
+        <v>1172</v>
+      </c>
+      <c r="G41" s="20" t="s">
+        <v>795</v>
+      </c>
+      <c r="H41" s="21" t="s">
+        <v>1268</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="21">
+      <c r="A42" s="19" t="s">
+        <v>1244</v>
+      </c>
+      <c r="B42" s="19" t="s">
+        <v>1246</v>
+      </c>
+      <c r="C42" s="19" t="s">
+        <v>1261</v>
+      </c>
+      <c r="D42" s="20" t="s">
+        <v>1198</v>
+      </c>
+      <c r="E42" s="20" t="s">
+        <v>1135</v>
+      </c>
+      <c r="F42" s="20" t="s">
+        <v>1199</v>
+      </c>
+      <c r="G42" s="20" t="s">
+        <v>795</v>
+      </c>
+      <c r="H42" s="21" t="s">
+        <v>1268</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="21">
+      <c r="A43" s="19" t="s">
+        <v>1244</v>
+      </c>
+      <c r="B43" s="19" t="s">
+        <v>1246</v>
+      </c>
+      <c r="C43" s="19" t="s">
+        <v>1262</v>
+      </c>
+      <c r="D43" s="20" t="s">
+        <v>1202</v>
+      </c>
+      <c r="E43" s="20" t="s">
+        <v>1135</v>
+      </c>
+      <c r="F43" s="20" t="s">
+        <v>1203</v>
+      </c>
+      <c r="G43" s="20" t="s">
+        <v>795</v>
+      </c>
+      <c r="H43" s="21" t="s">
+        <v>1268</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="21">
+      <c r="A44" s="19" t="s">
+        <v>401</v>
+      </c>
+      <c r="B44" s="19" t="s">
+        <v>402</v>
+      </c>
+      <c r="C44" s="19" t="s">
+        <v>1090</v>
+      </c>
+      <c r="D44" s="19" t="s">
         <v>1120</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>1116</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>1121</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>1122</v>
-      </c>
-      <c r="H3" s="3" t="s">
+      <c r="E44" s="19" t="s">
+        <v>1115</v>
+      </c>
+      <c r="F44" s="19" t="s">
+        <v>1093</v>
+      </c>
+      <c r="G44" s="19" t="s">
         <v>795</v>
       </c>
-      <c r="I3" s="20" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="3" t="s">
-        <v>401</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>402</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>1090</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>1123</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>1116</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>1093</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>1124</v>
-      </c>
-      <c r="H4" s="3" t="s">
+      <c r="H44" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="21">
+      <c r="A45" s="19" t="s">
+        <v>1224</v>
+      </c>
+      <c r="B45" s="19" t="s">
+        <v>1225</v>
+      </c>
+      <c r="C45" s="19" t="s">
+        <v>1226</v>
+      </c>
+      <c r="D45" s="19" t="s">
+        <v>1140</v>
+      </c>
+      <c r="E45" s="19" t="s">
+        <v>1135</v>
+      </c>
+      <c r="F45" s="19" t="s">
+        <v>1141</v>
+      </c>
+      <c r="G45" s="19" t="s">
         <v>795</v>
       </c>
-      <c r="I4" s="20" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" s="3" t="s">
-        <v>1112</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>1113</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>1125</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>1126</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>1116</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>1127</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>1128</v>
-      </c>
-      <c r="H5" s="3" t="s">
+      <c r="H45" s="21" t="s">
+        <v>1268</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="21">
+      <c r="A46" s="19"/>
+      <c r="B46" s="19"/>
+      <c r="C46" s="19"/>
+      <c r="D46" s="19" t="s">
+        <v>1142</v>
+      </c>
+      <c r="E46" s="19" t="s">
+        <v>1135</v>
+      </c>
+      <c r="F46" s="19" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G46" s="19" t="s">
         <v>795</v>
       </c>
-      <c r="I5" s="20" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" s="3" t="s">
-        <v>1112</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>1113</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>1129</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>1130</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>1116</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>1131</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>1132</v>
-      </c>
-      <c r="H6" s="3" t="s">
+      <c r="H46" s="21"/>
+    </row>
+    <row r="47" spans="1:8" ht="21">
+      <c r="A47" s="19"/>
+      <c r="B47" s="19"/>
+      <c r="C47" s="19"/>
+      <c r="D47" s="20" t="s">
+        <v>1167</v>
+      </c>
+      <c r="E47" s="20" t="s">
+        <v>1135</v>
+      </c>
+      <c r="F47" s="20" t="s">
+        <v>1168</v>
+      </c>
+      <c r="G47" s="20" t="s">
         <v>795</v>
       </c>
-      <c r="I6" s="20" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" s="3" t="s">
-        <v>1112</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>1113</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>1133</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>1134</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>1116</v>
-      </c>
-      <c r="F7" s="3" t="s">
+      <c r="H47" s="21"/>
+    </row>
+    <row r="48" spans="1:8" ht="21">
+      <c r="A48" s="19"/>
+      <c r="B48" s="19"/>
+      <c r="C48" s="19"/>
+      <c r="D48" s="20" t="s">
+        <v>1169</v>
+      </c>
+      <c r="E48" s="20" t="s">
         <v>1135</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>1136</v>
-      </c>
-      <c r="H7" s="3" t="s">
+      <c r="F48" s="20" t="s">
+        <v>1170</v>
+      </c>
+      <c r="G48" s="20" t="s">
         <v>795</v>
       </c>
-      <c r="I7" s="20" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" s="3" t="s">
-        <v>1112</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>1113</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>1137</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>1138</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>1116</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>1139</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>1140</v>
-      </c>
-      <c r="H8" s="3" t="s">
+      <c r="H48" s="21"/>
+    </row>
+    <row r="49" spans="1:8" ht="21">
+      <c r="A49" s="19"/>
+      <c r="B49" s="19"/>
+      <c r="C49" s="19"/>
+      <c r="D49" s="20" t="s">
+        <v>1200</v>
+      </c>
+      <c r="E49" s="20" t="s">
+        <v>1135</v>
+      </c>
+      <c r="F49" s="20" t="s">
+        <v>1201</v>
+      </c>
+      <c r="G49" s="20" t="s">
         <v>795</v>
       </c>
-      <c r="I8" s="20" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" s="3" t="s">
-        <v>1112</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>1113</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>1141</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>1142</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>1143</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>1144</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>1145</v>
-      </c>
-      <c r="H9" s="3" t="s">
+      <c r="H49" s="21"/>
+    </row>
+    <row r="50" spans="1:8" ht="21">
+      <c r="A50" s="19"/>
+      <c r="B50" s="19"/>
+      <c r="C50" s="19"/>
+      <c r="D50" s="20" t="s">
+        <v>1210</v>
+      </c>
+      <c r="E50" s="20" t="s">
+        <v>1135</v>
+      </c>
+      <c r="F50" s="20" t="s">
+        <v>1211</v>
+      </c>
+      <c r="G50" s="20" t="s">
         <v>795</v>
       </c>
-      <c r="I9" s="20" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" s="3" t="s">
-        <v>1112</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>1113</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>1146</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>1147</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>1116</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>1148</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>1149</v>
-      </c>
-      <c r="H10" s="3" t="s">
+      <c r="H50" s="21"/>
+    </row>
+    <row r="51" spans="1:8" ht="21">
+      <c r="A51" s="19"/>
+      <c r="B51" s="19"/>
+      <c r="C51" s="19"/>
+      <c r="D51" s="20" t="s">
+        <v>1214</v>
+      </c>
+      <c r="E51" s="20" t="s">
+        <v>1135</v>
+      </c>
+      <c r="F51" s="20" t="s">
+        <v>1215</v>
+      </c>
+      <c r="G51" s="20" t="s">
         <v>795</v>
       </c>
-      <c r="I10" s="20" t="s">
-        <v>36</v>
-      </c>
+      <c r="H51" s="21"/>
+    </row>
+    <row r="52" spans="1:8" ht="21">
+      <c r="A52" s="19"/>
+      <c r="B52" s="19"/>
+      <c r="C52" s="19"/>
+      <c r="D52" s="20" t="s">
+        <v>1216</v>
+      </c>
+      <c r="E52" s="20" t="s">
+        <v>1135</v>
+      </c>
+      <c r="F52" s="20" t="s">
+        <v>1217</v>
+      </c>
+      <c r="G52" s="20" t="s">
+        <v>795</v>
+      </c>
+      <c r="H52" s="21"/>
+    </row>
+    <row r="53" spans="1:8" ht="21">
+      <c r="A53" s="19"/>
+      <c r="B53" s="19"/>
+      <c r="C53" s="19"/>
+      <c r="D53" s="20" t="s">
+        <v>1218</v>
+      </c>
+      <c r="E53" s="20" t="s">
+        <v>1135</v>
+      </c>
+      <c r="F53" s="20" t="s">
+        <v>1219</v>
+      </c>
+      <c r="G53" s="20" t="s">
+        <v>795</v>
+      </c>
+      <c r="H53" s="21"/>
+    </row>
+    <row r="54" spans="1:8" ht="21">
+      <c r="A54" s="19"/>
+      <c r="B54" s="19"/>
+      <c r="C54" s="19"/>
+      <c r="D54" s="20" t="s">
+        <v>1220</v>
+      </c>
+      <c r="E54" s="20" t="s">
+        <v>1135</v>
+      </c>
+      <c r="F54" s="20" t="s">
+        <v>1221</v>
+      </c>
+      <c r="G54" s="20" t="s">
+        <v>795</v>
+      </c>
+      <c r="H54" s="21"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H54">
+    <sortCondition ref="B2:B54"/>
+  </sortState>
+  <pageMargins left="0.24" right="0.24" top="0.77" bottom="0.46" header="0.17" footer="0.3"/>
+  <pageSetup paperSize="9" scale="50" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
 </worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://singerlk-my.sharepoint.com/personal/dihank_singersl_com/Documents/Desktop/DIHAN/cr dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="575" documentId="11_5847038500C079F1E35F4C8C432471BF012A7624" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{36F1E234-B60F-4C87-B78D-8290DF743906}"/>
+  <xr:revisionPtr revIDLastSave="584" documentId="11_5847038500C079F1E35F4C8C432471BF012A7624" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5441E080-AF63-4017-A668-D5117DD7BA81}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -86,7 +86,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3107" uniqueCount="1278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3500" uniqueCount="1462">
   <si>
     <t>SHOP_CODE</t>
   </si>
@@ -3920,6 +3920,558 @@
   </si>
   <si>
     <t>YEM-H16624</t>
+  </si>
+  <si>
+    <t>YAB-H5921</t>
+  </si>
+  <si>
+    <t>Mr. HASHITHA</t>
+  </si>
+  <si>
+    <t>L1Z1LL517SA569285</t>
+  </si>
+  <si>
+    <t>YAB-H5937</t>
+  </si>
+  <si>
+    <t>Mr. P M PIYASIRI</t>
+  </si>
+  <si>
+    <t>LGMMVU1K2S0006041</t>
+  </si>
+  <si>
+    <t>YEM-H16056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ms. WARSHA RAMODI RODRIGO </t>
+  </si>
+  <si>
+    <t>No data</t>
+  </si>
+  <si>
+    <t>YEM-H16074</t>
+  </si>
+  <si>
+    <t>K.K.G.S.B.KANNANGARA</t>
+  </si>
+  <si>
+    <t>L1Z1LL51XSA569250</t>
+  </si>
+  <si>
+    <t>YEM-H16081</t>
+  </si>
+  <si>
+    <t>Mr. JEEWANTHA P</t>
+  </si>
+  <si>
+    <t>YEM-H16099</t>
+  </si>
+  <si>
+    <t>Mr. NIMESH</t>
+  </si>
+  <si>
+    <t>YEM-H16105</t>
+  </si>
+  <si>
+    <t>Mr. SAMPATH NAOTUNNA</t>
+  </si>
+  <si>
+    <t>YEM-H16106</t>
+  </si>
+  <si>
+    <t>Mr. L.M.FERDINANDO</t>
+  </si>
+  <si>
+    <t>YEM-H16108</t>
+  </si>
+  <si>
+    <t>Mr. M S M FERNANDO</t>
+  </si>
+  <si>
+    <t>L1Z1LL512SA569078</t>
+  </si>
+  <si>
+    <t>YEM-H16109</t>
+  </si>
+  <si>
+    <t>Mr. E.M.E.G.IINDIKA PRADEEP EKANAYAKE</t>
+  </si>
+  <si>
+    <t>YEM-H16114</t>
+  </si>
+  <si>
+    <t>Mr. R.M.W.KUMARA SAMPATH</t>
+  </si>
+  <si>
+    <t>YEM-H16128</t>
+  </si>
+  <si>
+    <t>Miss. C.D.COLOMBAGE</t>
+  </si>
+  <si>
+    <t>YEM-H16140</t>
+  </si>
+  <si>
+    <t>K K G R S SIRIWARDANA</t>
+  </si>
+  <si>
+    <t>LGMMVU1K0S0003543</t>
+  </si>
+  <si>
+    <t>YAB-H5965</t>
+  </si>
+  <si>
+    <t>Mr. D AMILA JAYASINGHE</t>
+  </si>
+  <si>
+    <t>LGMMVU1H7S0000689</t>
+  </si>
+  <si>
+    <t>YAB-H5966</t>
+  </si>
+  <si>
+    <t>Miss. G.D.PURNIMA NILUSHA</t>
+  </si>
+  <si>
+    <t>LGMMVU1H3S0000768</t>
+  </si>
+  <si>
+    <t>YAB-H5967</t>
+  </si>
+  <si>
+    <t>Mr. R.LALEENDRA KOTHALAWALA</t>
+  </si>
+  <si>
+    <t>LGMMVU1H9S0000810</t>
+  </si>
+  <si>
+    <t>YAB-H5968</t>
+  </si>
+  <si>
+    <t>Mr. S.S.JAGATH MAITHRIPALA</t>
+  </si>
+  <si>
+    <t>LGMMVU1H5S0000836</t>
+  </si>
+  <si>
+    <t>YAB-H5969</t>
+  </si>
+  <si>
+    <t>Mr. H G A SHANTHA</t>
+  </si>
+  <si>
+    <t>L1Z1LL511SA569654</t>
+  </si>
+  <si>
+    <t>YAB-H5971</t>
+  </si>
+  <si>
+    <t>Mr. R.A.D.R.RANASINGHA</t>
+  </si>
+  <si>
+    <t>LGMMVU1HXS0000752</t>
+  </si>
+  <si>
+    <t>YAB-H5972</t>
+  </si>
+  <si>
+    <t>Mr. A M S ERANGA</t>
+  </si>
+  <si>
+    <t>LGMMVU1K0S0006393</t>
+  </si>
+  <si>
+    <t>YAB-H5976</t>
+  </si>
+  <si>
+    <t>Mr. R V A NISHANTHA</t>
+  </si>
+  <si>
+    <t>L1Z1LL516SA569553</t>
+  </si>
+  <si>
+    <t>YAB-H5977</t>
+  </si>
+  <si>
+    <t>Mr. H.S.GAMIKA</t>
+  </si>
+  <si>
+    <t>LGMMVU1H0S0000758</t>
+  </si>
+  <si>
+    <t>YAB-H5978</t>
+  </si>
+  <si>
+    <t>Mr. R.D.DILAN PRASANA</t>
+  </si>
+  <si>
+    <t>L1Z1LL513SA569526</t>
+  </si>
+  <si>
+    <t>YAB-H5979</t>
+  </si>
+  <si>
+    <t>Mr. K A G PUSHPAKUMARA</t>
+  </si>
+  <si>
+    <t>LGMMVU1H2S0000924</t>
+  </si>
+  <si>
+    <t>YAB-H5980</t>
+  </si>
+  <si>
+    <t>Mr. W.G JEEWAN SURANGA</t>
+  </si>
+  <si>
+    <t>LGMMVU1H5S0000903</t>
+  </si>
+  <si>
+    <t>YAB-H5981</t>
+  </si>
+  <si>
+    <t>Mr. M A D H M KULARATNA</t>
+  </si>
+  <si>
+    <t>L1Z1LL515SA569382</t>
+  </si>
+  <si>
+    <t>YAB-H5982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr DILUM CHINTHAKA </t>
+  </si>
+  <si>
+    <t>L1Z1LL517SA569416</t>
+  </si>
+  <si>
+    <t>YAB-H5983</t>
+  </si>
+  <si>
+    <t>S N KODIPPILI</t>
+  </si>
+  <si>
+    <t>LGMMVU1H4S0000956</t>
+  </si>
+  <si>
+    <t>YAB-H5984</t>
+  </si>
+  <si>
+    <t>Mr. K B S JAYASEKARA</t>
+  </si>
+  <si>
+    <t>LGMMVU1H6S0000733</t>
+  </si>
+  <si>
+    <t>YAB-H5985</t>
+  </si>
+  <si>
+    <t>Mr. A A M RIYAS</t>
+  </si>
+  <si>
+    <t>L1Z1LL514SA569647</t>
+  </si>
+  <si>
+    <t>YAB-H5986</t>
+  </si>
+  <si>
+    <t>Mr. H R P LAL</t>
+  </si>
+  <si>
+    <t>L1Z1LL513SA569543</t>
+  </si>
+  <si>
+    <t>YAB-H5987</t>
+  </si>
+  <si>
+    <t>MR. UPUL CHINTHAKA</t>
+  </si>
+  <si>
+    <t>L1Z1LL514SA569731</t>
+  </si>
+  <si>
+    <t>YAB-H5988</t>
+  </si>
+  <si>
+    <t>Mr. G A GAYAN RANDIKA DARMADASA</t>
+  </si>
+  <si>
+    <t>L1Z1LL513SA569638</t>
+  </si>
+  <si>
+    <t>YAB-H5989</t>
+  </si>
+  <si>
+    <t>Mr. M.A.THUSHARA SANJEEWA KUMARA</t>
+  </si>
+  <si>
+    <t>LGMMVU1HXS0000735</t>
+  </si>
+  <si>
+    <t>YAB-H5990</t>
+  </si>
+  <si>
+    <t>R.J.R.  CHANAKA</t>
+  </si>
+  <si>
+    <t>LGMMVU1H4S0000942</t>
+  </si>
+  <si>
+    <t>YAB-H5991</t>
+  </si>
+  <si>
+    <t>Mr. H PRIYATHILAKA</t>
+  </si>
+  <si>
+    <t>L1Z1LL51XSA569555</t>
+  </si>
+  <si>
+    <t>CR COLLECT BY ASITHA</t>
+  </si>
+  <si>
+    <t>YAB-H5997</t>
+  </si>
+  <si>
+    <t>Mr. S LA DE SILVA</t>
+  </si>
+  <si>
+    <t>LGMMVU1H1S0000901</t>
+  </si>
+  <si>
+    <t>YAB-H5998</t>
+  </si>
+  <si>
+    <t>Mr. D M N DISANAYAKE</t>
+  </si>
+  <si>
+    <t>L1Z1LL511SA569587</t>
+  </si>
+  <si>
+    <t>YAB-H5944</t>
+  </si>
+  <si>
+    <t>Mr. S K B V K FERNANDO</t>
+  </si>
+  <si>
+    <t>L1Z1LL514SA569583</t>
+  </si>
+  <si>
+    <t>YAB-H5952</t>
+  </si>
+  <si>
+    <t>Mr. K.G. AYESH</t>
+  </si>
+  <si>
+    <t>LGMMVU1H3S0000916</t>
+  </si>
+  <si>
+    <t>YAB-H5955</t>
+  </si>
+  <si>
+    <t>Mr. CHAMINDA</t>
+  </si>
+  <si>
+    <t>LGMMVU1H7S0000773</t>
+  </si>
+  <si>
+    <t>YAB-H5957</t>
+  </si>
+  <si>
+    <t>Mr. A A M KI PERERA</t>
+  </si>
+  <si>
+    <t>LGMMVU1K3S0006050</t>
+  </si>
+  <si>
+    <t>YAB-H5959</t>
+  </si>
+  <si>
+    <t>Mr. A G R A RAJAPAKSA</t>
+  </si>
+  <si>
+    <t>LGMMVU1H2S0000907</t>
+  </si>
+  <si>
+    <t>YAB-H5960</t>
+  </si>
+  <si>
+    <t>Mr. S A C P KUMARA</t>
+  </si>
+  <si>
+    <t>LGMMVU1H4S0000794</t>
+  </si>
+  <si>
+    <t>YAB-H5963</t>
+  </si>
+  <si>
+    <t>Mr. M.K.C.MALKANTHA 0112622613 060 2381845</t>
+  </si>
+  <si>
+    <t>LGMMVU1H4S0000830</t>
+  </si>
+  <si>
+    <t>YAB-H5964</t>
+  </si>
+  <si>
+    <t>Mr. K C P PEIRIS</t>
+  </si>
+  <si>
+    <t>L1Z1LL517SA569528</t>
+  </si>
+  <si>
+    <t>YEM-H16127</t>
+  </si>
+  <si>
+    <t>S K WITHARANA</t>
+  </si>
+  <si>
+    <t>YEM-H16148</t>
+  </si>
+  <si>
+    <t>Mr. B N PATHIRANA</t>
+  </si>
+  <si>
+    <t>LGMMVU1H9S0000757</t>
+  </si>
+  <si>
+    <t>YEM-H16152</t>
+  </si>
+  <si>
+    <t>MR.SAMUDU SHAMMIKA</t>
+  </si>
+  <si>
+    <t>YEM-H16157</t>
+  </si>
+  <si>
+    <t>Mr. WEERASEKARA ARACHCHIGE PIYUMANTHA NADEESHAN</t>
+  </si>
+  <si>
+    <t>LGMMVU1K7S0006343</t>
+  </si>
+  <si>
+    <t>YEM-H16171</t>
+  </si>
+  <si>
+    <t>Ms. D.K.GANGA KUMUDUNIE</t>
+  </si>
+  <si>
+    <t>L1Z1LL517SA569559</t>
+  </si>
+  <si>
+    <t>YEM-H16182</t>
+  </si>
+  <si>
+    <t>Mr. A M  JANAKA SENARATH</t>
+  </si>
+  <si>
+    <t>LGMMVU1K7S0006049</t>
+  </si>
+  <si>
+    <t>YEM-H16192</t>
+  </si>
+  <si>
+    <t>Mr. S D DAMMIKA</t>
+  </si>
+  <si>
+    <t>LGMMVU1K6S0006351</t>
+  </si>
+  <si>
+    <t>YEM-H16217</t>
+  </si>
+  <si>
+    <t>MR P G RASIKA PRABATH</t>
+  </si>
+  <si>
+    <t>LGMMVU1K2S0006315</t>
+  </si>
+  <si>
+    <t>YEM-H16218</t>
+  </si>
+  <si>
+    <t>MR HIRAN MADURANGA WEERAKOON</t>
+  </si>
+  <si>
+    <t>LGMMVU1K1S0006306</t>
+  </si>
+  <si>
+    <t>YEM-H16249</t>
+  </si>
+  <si>
+    <t>Mr. N W A ROSHAN KUMARA</t>
+  </si>
+  <si>
+    <t>LGMMVU1K6S0005989</t>
+  </si>
+  <si>
+    <t>YEM-H16241</t>
+  </si>
+  <si>
+    <t>MR.E.S.ASELA</t>
+  </si>
+  <si>
+    <t>LGMMVU1K4S0005960</t>
+  </si>
+  <si>
+    <t>YEM-H16203</t>
+  </si>
+  <si>
+    <t>Mr. P.M. SAMPATH BANDARA</t>
+  </si>
+  <si>
+    <t>L1Z1LL518SA569182</t>
+  </si>
+  <si>
+    <t>YEM-H16351</t>
+  </si>
+  <si>
+    <t>Miss. B. V. T MADURANGI AMARASINGHA</t>
+  </si>
+  <si>
+    <t>YEM-H16298</t>
+  </si>
+  <si>
+    <t>Ms. THUSHARI WARNASOORIYA</t>
+  </si>
+  <si>
+    <t>L1Z1LL515SA569351</t>
+  </si>
+  <si>
+    <t>YEM-H16564</t>
+  </si>
+  <si>
+    <t>Mr. W.M.A.P WEERASINGHE</t>
+  </si>
+  <si>
+    <t>LGMMVU1K3T0001951</t>
+  </si>
+  <si>
+    <t>YEM-H16617</t>
+  </si>
+  <si>
+    <t>Mr. A S THUSHARA SADARATHNA</t>
+  </si>
+  <si>
+    <t>Mr. W.M.CHAMARA MADHUSHAN WANNINAYAKE</t>
+  </si>
+  <si>
+    <t>LGMMVU1K8T0002979</t>
+  </si>
+  <si>
+    <t>YEM-H16596</t>
+  </si>
+  <si>
+    <t>Mr. H K RUWAN PRADEEP KARUNARATHNA</t>
+  </si>
+  <si>
+    <t>LGMMVU1K1T0002046</t>
+  </si>
+  <si>
+    <t>CR NOT RECEIVED FROM RMV</t>
+  </si>
+  <si>
+    <t>YEM-H16578</t>
+  </si>
+  <si>
+    <t>Mr. H M A M HERATH</t>
   </si>
 </sst>
 </file>
@@ -3946,14 +4498,14 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -4082,9 +4634,11 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -16967,7 +17521,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H54"/>
+  <dimension ref="A1:H119"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="19.453125" customWidth="1"/>
@@ -17016,19 +17570,19 @@
       <c r="C2" s="19" t="s">
         <v>1250</v>
       </c>
-      <c r="D2" s="20" t="s">
+      <c r="D2" s="19" t="s">
         <v>1180</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="E2" s="19" t="s">
         <v>1115</v>
       </c>
-      <c r="F2" s="20" t="s">
+      <c r="F2" s="19" t="s">
         <v>1181</v>
       </c>
-      <c r="G2" s="20" t="s">
+      <c r="G2" s="19" t="s">
         <v>795</v>
       </c>
-      <c r="H2" s="21" t="s">
+      <c r="H2" s="20" t="s">
         <v>1268</v>
       </c>
     </row>
@@ -17054,7 +17608,7 @@
       <c r="G3" s="19" t="s">
         <v>795</v>
       </c>
-      <c r="H3" s="21" t="s">
+      <c r="H3" s="20" t="s">
         <v>36</v>
       </c>
     </row>
@@ -17080,7 +17634,7 @@
       <c r="G4" s="19" t="s">
         <v>795</v>
       </c>
-      <c r="H4" s="21" t="s">
+      <c r="H4" s="20" t="s">
         <v>36</v>
       </c>
     </row>
@@ -17106,7 +17660,7 @@
       <c r="G5" s="19" t="s">
         <v>795</v>
       </c>
-      <c r="H5" s="21" t="s">
+      <c r="H5" s="20" t="s">
         <v>36</v>
       </c>
     </row>
@@ -17132,7 +17686,7 @@
       <c r="G6" s="19" t="s">
         <v>795</v>
       </c>
-      <c r="H6" s="21" t="s">
+      <c r="H6" s="20" t="s">
         <v>36</v>
       </c>
     </row>
@@ -17146,19 +17700,19 @@
       <c r="C7" s="19" t="s">
         <v>1243</v>
       </c>
-      <c r="D7" s="20" t="s">
+      <c r="D7" s="19" t="s">
         <v>1165</v>
       </c>
-      <c r="E7" s="20" t="s">
+      <c r="E7" s="19" t="s">
         <v>1135</v>
       </c>
-      <c r="F7" s="20" t="s">
+      <c r="F7" s="19" t="s">
         <v>1166</v>
       </c>
-      <c r="G7" s="20" t="s">
+      <c r="G7" s="19" t="s">
         <v>795</v>
       </c>
-      <c r="H7" s="21" t="s">
+      <c r="H7" s="20" t="s">
         <v>1268</v>
       </c>
     </row>
@@ -17172,19 +17726,19 @@
       <c r="C8" s="19" t="s">
         <v>1248</v>
       </c>
-      <c r="D8" s="20" t="s">
+      <c r="D8" s="19" t="s">
         <v>1176</v>
       </c>
-      <c r="E8" s="20" t="s">
+      <c r="E8" s="19" t="s">
         <v>1115</v>
       </c>
-      <c r="F8" s="20" t="s">
+      <c r="F8" s="19" t="s">
         <v>1177</v>
       </c>
-      <c r="G8" s="20" t="s">
+      <c r="G8" s="19" t="s">
         <v>795</v>
       </c>
-      <c r="H8" s="21" t="s">
+      <c r="H8" s="20" t="s">
         <v>36</v>
       </c>
     </row>
@@ -17198,19 +17752,19 @@
       <c r="C9" s="19" t="s">
         <v>1251</v>
       </c>
-      <c r="D9" s="20" t="s">
+      <c r="D9" s="19" t="s">
         <v>1182</v>
       </c>
-      <c r="E9" s="20" t="s">
+      <c r="E9" s="19" t="s">
         <v>1135</v>
       </c>
-      <c r="F9" s="20" t="s">
+      <c r="F9" s="19" t="s">
         <v>1183</v>
       </c>
-      <c r="G9" s="20" t="s">
+      <c r="G9" s="19" t="s">
         <v>795</v>
       </c>
-      <c r="H9" s="21" t="s">
+      <c r="H9" s="20" t="s">
         <v>36</v>
       </c>
     </row>
@@ -17224,19 +17778,19 @@
       <c r="C10" s="19" t="s">
         <v>1253</v>
       </c>
-      <c r="D10" s="20" t="s">
+      <c r="D10" s="19" t="s">
         <v>1186</v>
       </c>
-      <c r="E10" s="20" t="s">
+      <c r="E10" s="19" t="s">
         <v>1135</v>
       </c>
-      <c r="F10" s="20" t="s">
+      <c r="F10" s="19" t="s">
         <v>1187</v>
       </c>
-      <c r="G10" s="20" t="s">
+      <c r="G10" s="19" t="s">
         <v>795</v>
       </c>
-      <c r="H10" s="21" t="s">
+      <c r="H10" s="20" t="s">
         <v>36</v>
       </c>
     </row>
@@ -17250,19 +17804,19 @@
       <c r="C11" s="19" t="s">
         <v>1254</v>
       </c>
-      <c r="D11" s="20" t="s">
+      <c r="D11" s="19" t="s">
         <v>1188</v>
       </c>
-      <c r="E11" s="20" t="s">
+      <c r="E11" s="19" t="s">
         <v>1135</v>
       </c>
-      <c r="F11" s="20" t="s">
+      <c r="F11" s="19" t="s">
         <v>1189</v>
       </c>
-      <c r="G11" s="20" t="s">
+      <c r="G11" s="19" t="s">
         <v>795</v>
       </c>
-      <c r="H11" s="21" t="s">
+      <c r="H11" s="20" t="s">
         <v>36</v>
       </c>
     </row>
@@ -17276,19 +17830,19 @@
       <c r="C12" s="19" t="s">
         <v>1255</v>
       </c>
-      <c r="D12" s="20" t="s">
+      <c r="D12" s="19" t="s">
         <v>1190</v>
       </c>
-      <c r="E12" s="20" t="s">
+      <c r="E12" s="19" t="s">
         <v>1135</v>
       </c>
-      <c r="F12" s="20" t="s">
+      <c r="F12" s="19" t="s">
         <v>1191</v>
       </c>
-      <c r="G12" s="20" t="s">
+      <c r="G12" s="19" t="s">
         <v>795</v>
       </c>
-      <c r="H12" s="21" t="s">
+      <c r="H12" s="20" t="s">
         <v>36</v>
       </c>
     </row>
@@ -17302,19 +17856,19 @@
       <c r="C13" s="19" t="s">
         <v>1257</v>
       </c>
-      <c r="D13" s="20" t="s">
+      <c r="D13" s="19" t="s">
         <v>1194</v>
       </c>
-      <c r="E13" s="20" t="s">
+      <c r="E13" s="19" t="s">
         <v>1135</v>
       </c>
-      <c r="F13" s="20" t="s">
+      <c r="F13" s="19" t="s">
         <v>1195</v>
       </c>
-      <c r="G13" s="20" t="s">
+      <c r="G13" s="19" t="s">
         <v>795</v>
       </c>
-      <c r="H13" s="21" t="s">
+      <c r="H13" s="20" t="s">
         <v>36</v>
       </c>
     </row>
@@ -17328,19 +17882,19 @@
       <c r="C14" s="19" t="s">
         <v>1264</v>
       </c>
-      <c r="D14" s="20" t="s">
+      <c r="D14" s="19" t="s">
         <v>1206</v>
       </c>
-      <c r="E14" s="20" t="s">
+      <c r="E14" s="19" t="s">
         <v>1135</v>
       </c>
-      <c r="F14" s="20" t="s">
+      <c r="F14" s="19" t="s">
         <v>1207</v>
       </c>
-      <c r="G14" s="20" t="s">
+      <c r="G14" s="19" t="s">
         <v>795</v>
       </c>
-      <c r="H14" s="21" t="s">
+      <c r="H14" s="20" t="s">
         <v>36</v>
       </c>
     </row>
@@ -17574,7 +18128,7 @@
       <c r="G23" s="19" t="s">
         <v>795</v>
       </c>
-      <c r="H23" s="21" t="s">
+      <c r="H23" s="20" t="s">
         <v>36</v>
       </c>
     </row>
@@ -17600,7 +18154,7 @@
       <c r="G24" s="19" t="s">
         <v>795</v>
       </c>
-      <c r="H24" s="21" t="s">
+      <c r="H24" s="20" t="s">
         <v>36</v>
       </c>
     </row>
@@ -17614,19 +18168,19 @@
       <c r="C25" s="19" t="s">
         <v>1238</v>
       </c>
-      <c r="D25" s="20" t="s">
+      <c r="D25" s="19" t="s">
         <v>1158</v>
       </c>
-      <c r="E25" s="20" t="s">
+      <c r="E25" s="19" t="s">
         <v>1135</v>
       </c>
-      <c r="F25" s="20" t="s">
+      <c r="F25" s="19" t="s">
         <v>1159</v>
       </c>
-      <c r="G25" s="20" t="s">
+      <c r="G25" s="19" t="s">
         <v>795</v>
       </c>
-      <c r="H25" s="21" t="s">
+      <c r="H25" s="20" t="s">
         <v>1268</v>
       </c>
     </row>
@@ -17640,19 +18194,19 @@
       <c r="C26" s="19" t="s">
         <v>1247</v>
       </c>
-      <c r="D26" s="20" t="s">
+      <c r="D26" s="19" t="s">
         <v>1173</v>
       </c>
-      <c r="E26" s="20" t="s">
+      <c r="E26" s="19" t="s">
         <v>1174</v>
       </c>
-      <c r="F26" s="20" t="s">
+      <c r="F26" s="19" t="s">
         <v>1175</v>
       </c>
-      <c r="G26" s="20" t="s">
+      <c r="G26" s="19" t="s">
         <v>795</v>
       </c>
-      <c r="H26" s="21" t="s">
+      <c r="H26" s="20" t="s">
         <v>36</v>
       </c>
     </row>
@@ -17666,19 +18220,19 @@
       <c r="C27" s="19" t="s">
         <v>1249</v>
       </c>
-      <c r="D27" s="20" t="s">
+      <c r="D27" s="19" t="s">
         <v>1178</v>
       </c>
-      <c r="E27" s="20" t="s">
+      <c r="E27" s="19" t="s">
         <v>1115</v>
       </c>
-      <c r="F27" s="20" t="s">
+      <c r="F27" s="19" t="s">
         <v>1179</v>
       </c>
-      <c r="G27" s="20" t="s">
+      <c r="G27" s="19" t="s">
         <v>795</v>
       </c>
-      <c r="H27" s="21" t="s">
+      <c r="H27" s="20" t="s">
         <v>36</v>
       </c>
     </row>
@@ -17692,19 +18246,19 @@
       <c r="C28" s="19" t="s">
         <v>1252</v>
       </c>
-      <c r="D28" s="20" t="s">
+      <c r="D28" s="19" t="s">
         <v>1184</v>
       </c>
-      <c r="E28" s="20" t="s">
+      <c r="E28" s="19" t="s">
         <v>1115</v>
       </c>
-      <c r="F28" s="20" t="s">
+      <c r="F28" s="19" t="s">
         <v>1185</v>
       </c>
-      <c r="G28" s="20" t="s">
+      <c r="G28" s="19" t="s">
         <v>795</v>
       </c>
-      <c r="H28" s="21" t="s">
+      <c r="H28" s="20" t="s">
         <v>36</v>
       </c>
     </row>
@@ -17718,19 +18272,19 @@
       <c r="C29" s="19" t="s">
         <v>1256</v>
       </c>
-      <c r="D29" s="20" t="s">
+      <c r="D29" s="19" t="s">
         <v>1192</v>
       </c>
-      <c r="E29" s="20" t="s">
+      <c r="E29" s="19" t="s">
         <v>1135</v>
       </c>
-      <c r="F29" s="20" t="s">
+      <c r="F29" s="19" t="s">
         <v>1193</v>
       </c>
-      <c r="G29" s="20" t="s">
+      <c r="G29" s="19" t="s">
         <v>795</v>
       </c>
-      <c r="H29" s="21" t="s">
+      <c r="H29" s="20" t="s">
         <v>36</v>
       </c>
     </row>
@@ -17744,19 +18298,19 @@
       <c r="C30" s="19" t="s">
         <v>1263</v>
       </c>
-      <c r="D30" s="20" t="s">
+      <c r="D30" s="19" t="s">
         <v>1204</v>
       </c>
-      <c r="E30" s="20" t="s">
+      <c r="E30" s="19" t="s">
         <v>1135</v>
       </c>
-      <c r="F30" s="20" t="s">
+      <c r="F30" s="19" t="s">
         <v>1205</v>
       </c>
-      <c r="G30" s="20" t="s">
+      <c r="G30" s="19" t="s">
         <v>795</v>
       </c>
-      <c r="H30" s="21" t="s">
+      <c r="H30" s="20" t="s">
         <v>36</v>
       </c>
     </row>
@@ -17770,19 +18324,19 @@
       <c r="C31" s="19" t="s">
         <v>1265</v>
       </c>
-      <c r="D31" s="20" t="s">
+      <c r="D31" s="19" t="s">
         <v>1208</v>
       </c>
-      <c r="E31" s="20" t="s">
+      <c r="E31" s="19" t="s">
         <v>1135</v>
       </c>
-      <c r="F31" s="20" t="s">
+      <c r="F31" s="19" t="s">
         <v>1209</v>
       </c>
-      <c r="G31" s="20" t="s">
+      <c r="G31" s="19" t="s">
         <v>795</v>
       </c>
-      <c r="H31" s="21" t="s">
+      <c r="H31" s="20" t="s">
         <v>36</v>
       </c>
     </row>
@@ -17796,19 +18350,19 @@
       <c r="C32" s="19" t="s">
         <v>1266</v>
       </c>
-      <c r="D32" s="20" t="s">
+      <c r="D32" s="19" t="s">
         <v>1212</v>
       </c>
-      <c r="E32" s="20" t="s">
+      <c r="E32" s="19" t="s">
         <v>1135</v>
       </c>
-      <c r="F32" s="20" t="s">
+      <c r="F32" s="19" t="s">
         <v>1213</v>
       </c>
-      <c r="G32" s="20" t="s">
+      <c r="G32" s="19" t="s">
         <v>795</v>
       </c>
-      <c r="H32" s="21" t="s">
+      <c r="H32" s="20" t="s">
         <v>36</v>
       </c>
     </row>
@@ -17822,19 +18376,19 @@
       <c r="C33" s="19" t="s">
         <v>1267</v>
       </c>
-      <c r="D33" s="20" t="s">
+      <c r="D33" s="19" t="s">
         <v>1222</v>
       </c>
-      <c r="E33" s="20" t="s">
+      <c r="E33" s="19" t="s">
         <v>1135</v>
       </c>
-      <c r="F33" s="20" t="s">
+      <c r="F33" s="19" t="s">
         <v>1223</v>
       </c>
-      <c r="G33" s="20" t="s">
+      <c r="G33" s="19" t="s">
         <v>795</v>
       </c>
-      <c r="H33" s="21" t="s">
+      <c r="H33" s="20" t="s">
         <v>1268</v>
       </c>
     </row>
@@ -17848,19 +18402,19 @@
       <c r="C34" s="19" t="s">
         <v>1275</v>
       </c>
-      <c r="D34" s="21" t="s">
+      <c r="D34" s="20" t="s">
         <v>1269</v>
       </c>
-      <c r="E34" s="21" t="s">
+      <c r="E34" s="20" t="s">
         <v>1115</v>
       </c>
-      <c r="F34" s="21" t="s">
+      <c r="F34" s="20" t="s">
         <v>1270</v>
       </c>
-      <c r="G34" s="21" t="s">
+      <c r="G34" s="20" t="s">
         <v>795</v>
       </c>
-      <c r="H34" s="21" t="s">
+      <c r="H34" s="20" t="s">
         <v>36</v>
       </c>
     </row>
@@ -17874,19 +18428,19 @@
       <c r="C35" s="19" t="s">
         <v>1276</v>
       </c>
-      <c r="D35" s="21" t="s">
+      <c r="D35" s="20" t="s">
         <v>1271</v>
       </c>
-      <c r="E35" s="21" t="s">
+      <c r="E35" s="20" t="s">
         <v>1115</v>
       </c>
-      <c r="F35" s="21" t="s">
+      <c r="F35" s="20" t="s">
         <v>1272</v>
       </c>
-      <c r="G35" s="21" t="s">
+      <c r="G35" s="20" t="s">
         <v>795</v>
       </c>
-      <c r="H35" s="21" t="s">
+      <c r="H35" s="20" t="s">
         <v>36</v>
       </c>
     </row>
@@ -17900,19 +18454,19 @@
       <c r="C36" s="19" t="s">
         <v>1277</v>
       </c>
-      <c r="D36" s="21" t="s">
+      <c r="D36" s="20" t="s">
         <v>1273</v>
       </c>
-      <c r="E36" s="21" t="s">
+      <c r="E36" s="20" t="s">
         <v>1115</v>
       </c>
-      <c r="F36" s="21" t="s">
+      <c r="F36" s="20" t="s">
         <v>1274</v>
       </c>
-      <c r="G36" s="21" t="s">
+      <c r="G36" s="20" t="s">
         <v>795</v>
       </c>
-      <c r="H36" s="21" t="s">
+      <c r="H36" s="20" t="s">
         <v>1268</v>
       </c>
     </row>
@@ -17926,19 +18480,19 @@
       <c r="C37" s="19" t="s">
         <v>1240</v>
       </c>
-      <c r="D37" s="20" t="s">
+      <c r="D37" s="19" t="s">
         <v>1160</v>
       </c>
-      <c r="E37" s="20" t="s">
+      <c r="E37" s="19" t="s">
         <v>1115</v>
       </c>
-      <c r="F37" s="20" t="s">
+      <c r="F37" s="19" t="s">
         <v>1161</v>
       </c>
-      <c r="G37" s="20" t="s">
+      <c r="G37" s="19" t="s">
         <v>795</v>
       </c>
-      <c r="H37" s="21" t="s">
+      <c r="H37" s="20" t="s">
         <v>1268</v>
       </c>
     </row>
@@ -17952,19 +18506,19 @@
       <c r="C38" s="19" t="s">
         <v>1260</v>
       </c>
-      <c r="D38" s="20" t="s">
+      <c r="D38" s="19" t="s">
         <v>1196</v>
       </c>
-      <c r="E38" s="20" t="s">
+      <c r="E38" s="19" t="s">
         <v>1135</v>
       </c>
-      <c r="F38" s="20" t="s">
+      <c r="F38" s="19" t="s">
         <v>1197</v>
       </c>
-      <c r="G38" s="20" t="s">
+      <c r="G38" s="19" t="s">
         <v>795</v>
       </c>
-      <c r="H38" s="21" t="s">
+      <c r="H38" s="20" t="s">
         <v>1268</v>
       </c>
     </row>
@@ -17990,7 +18544,7 @@
       <c r="G39" s="19" t="s">
         <v>795</v>
       </c>
-      <c r="H39" s="21" t="s">
+      <c r="H39" s="20" t="s">
         <v>1268</v>
       </c>
     </row>
@@ -18004,19 +18558,19 @@
       <c r="C40" s="19" t="s">
         <v>1242</v>
       </c>
-      <c r="D40" s="20" t="s">
+      <c r="D40" s="19" t="s">
         <v>1162</v>
       </c>
-      <c r="E40" s="20" t="s">
+      <c r="E40" s="19" t="s">
         <v>1163</v>
       </c>
-      <c r="F40" s="20" t="s">
+      <c r="F40" s="19" t="s">
         <v>1164</v>
       </c>
-      <c r="G40" s="20" t="s">
+      <c r="G40" s="19" t="s">
         <v>795</v>
       </c>
-      <c r="H40" s="21" t="s">
+      <c r="H40" s="20" t="s">
         <v>1268</v>
       </c>
     </row>
@@ -18030,19 +18584,19 @@
       <c r="C41" s="19" t="s">
         <v>1245</v>
       </c>
-      <c r="D41" s="20" t="s">
+      <c r="D41" s="19" t="s">
         <v>1171</v>
       </c>
-      <c r="E41" s="20" t="s">
+      <c r="E41" s="19" t="s">
         <v>1135</v>
       </c>
-      <c r="F41" s="20" t="s">
+      <c r="F41" s="19" t="s">
         <v>1172</v>
       </c>
-      <c r="G41" s="20" t="s">
+      <c r="G41" s="19" t="s">
         <v>795</v>
       </c>
-      <c r="H41" s="21" t="s">
+      <c r="H41" s="20" t="s">
         <v>1268</v>
       </c>
     </row>
@@ -18056,19 +18610,19 @@
       <c r="C42" s="19" t="s">
         <v>1261</v>
       </c>
-      <c r="D42" s="20" t="s">
+      <c r="D42" s="19" t="s">
         <v>1198</v>
       </c>
-      <c r="E42" s="20" t="s">
+      <c r="E42" s="19" t="s">
         <v>1135</v>
       </c>
-      <c r="F42" s="20" t="s">
+      <c r="F42" s="19" t="s">
         <v>1199</v>
       </c>
-      <c r="G42" s="20" t="s">
+      <c r="G42" s="19" t="s">
         <v>795</v>
       </c>
-      <c r="H42" s="21" t="s">
+      <c r="H42" s="20" t="s">
         <v>1268</v>
       </c>
     </row>
@@ -18082,19 +18636,19 @@
       <c r="C43" s="19" t="s">
         <v>1262</v>
       </c>
-      <c r="D43" s="20" t="s">
+      <c r="D43" s="19" t="s">
         <v>1202</v>
       </c>
-      <c r="E43" s="20" t="s">
+      <c r="E43" s="19" t="s">
         <v>1135</v>
       </c>
-      <c r="F43" s="20" t="s">
+      <c r="F43" s="19" t="s">
         <v>1203</v>
       </c>
-      <c r="G43" s="20" t="s">
+      <c r="G43" s="19" t="s">
         <v>795</v>
       </c>
-      <c r="H43" s="21" t="s">
+      <c r="H43" s="20" t="s">
         <v>1268</v>
       </c>
     </row>
@@ -18146,7 +18700,7 @@
       <c r="G45" s="19" t="s">
         <v>795</v>
       </c>
-      <c r="H45" s="21" t="s">
+      <c r="H45" s="20" t="s">
         <v>1268</v>
       </c>
     </row>
@@ -18166,151 +18720,1587 @@
       <c r="G46" s="19" t="s">
         <v>795</v>
       </c>
-      <c r="H46" s="21"/>
+      <c r="H46" s="20"/>
     </row>
     <row r="47" spans="1:8" ht="21">
       <c r="A47" s="19"/>
       <c r="B47" s="19"/>
       <c r="C47" s="19"/>
-      <c r="D47" s="20" t="s">
+      <c r="D47" s="19" t="s">
         <v>1167</v>
       </c>
-      <c r="E47" s="20" t="s">
+      <c r="E47" s="19" t="s">
         <v>1135</v>
       </c>
-      <c r="F47" s="20" t="s">
+      <c r="F47" s="19" t="s">
         <v>1168</v>
       </c>
-      <c r="G47" s="20" t="s">
+      <c r="G47" s="19" t="s">
         <v>795</v>
       </c>
-      <c r="H47" s="21"/>
+      <c r="H47" s="20"/>
     </row>
     <row r="48" spans="1:8" ht="21">
       <c r="A48" s="19"/>
       <c r="B48" s="19"/>
       <c r="C48" s="19"/>
-      <c r="D48" s="20" t="s">
+      <c r="D48" s="19" t="s">
         <v>1169</v>
       </c>
-      <c r="E48" s="20" t="s">
+      <c r="E48" s="19" t="s">
         <v>1135</v>
       </c>
-      <c r="F48" s="20" t="s">
+      <c r="F48" s="19" t="s">
         <v>1170</v>
       </c>
-      <c r="G48" s="20" t="s">
+      <c r="G48" s="19" t="s">
         <v>795</v>
       </c>
-      <c r="H48" s="21"/>
+      <c r="H48" s="20"/>
     </row>
     <row r="49" spans="1:8" ht="21">
       <c r="A49" s="19"/>
       <c r="B49" s="19"/>
       <c r="C49" s="19"/>
-      <c r="D49" s="20" t="s">
+      <c r="D49" s="19" t="s">
         <v>1200</v>
       </c>
-      <c r="E49" s="20" t="s">
+      <c r="E49" s="19" t="s">
         <v>1135</v>
       </c>
-      <c r="F49" s="20" t="s">
+      <c r="F49" s="19" t="s">
         <v>1201</v>
       </c>
-      <c r="G49" s="20" t="s">
+      <c r="G49" s="19" t="s">
         <v>795</v>
       </c>
-      <c r="H49" s="21"/>
+      <c r="H49" s="20"/>
     </row>
     <row r="50" spans="1:8" ht="21">
       <c r="A50" s="19"/>
       <c r="B50" s="19"/>
       <c r="C50" s="19"/>
-      <c r="D50" s="20" t="s">
+      <c r="D50" s="19" t="s">
         <v>1210</v>
       </c>
-      <c r="E50" s="20" t="s">
+      <c r="E50" s="19" t="s">
         <v>1135</v>
       </c>
-      <c r="F50" s="20" t="s">
+      <c r="F50" s="19" t="s">
         <v>1211</v>
       </c>
-      <c r="G50" s="20" t="s">
+      <c r="G50" s="19" t="s">
         <v>795</v>
       </c>
-      <c r="H50" s="21"/>
+      <c r="H50" s="20"/>
     </row>
     <row r="51" spans="1:8" ht="21">
       <c r="A51" s="19"/>
       <c r="B51" s="19"/>
       <c r="C51" s="19"/>
-      <c r="D51" s="20" t="s">
+      <c r="D51" s="19" t="s">
         <v>1214</v>
       </c>
-      <c r="E51" s="20" t="s">
+      <c r="E51" s="19" t="s">
         <v>1135</v>
       </c>
-      <c r="F51" s="20" t="s">
+      <c r="F51" s="19" t="s">
         <v>1215</v>
       </c>
-      <c r="G51" s="20" t="s">
+      <c r="G51" s="19" t="s">
         <v>795</v>
       </c>
-      <c r="H51" s="21"/>
+      <c r="H51" s="20"/>
     </row>
     <row r="52" spans="1:8" ht="21">
       <c r="A52" s="19"/>
       <c r="B52" s="19"/>
       <c r="C52" s="19"/>
-      <c r="D52" s="20" t="s">
+      <c r="D52" s="19" t="s">
         <v>1216</v>
       </c>
-      <c r="E52" s="20" t="s">
+      <c r="E52" s="19" t="s">
         <v>1135</v>
       </c>
-      <c r="F52" s="20" t="s">
+      <c r="F52" s="19" t="s">
         <v>1217</v>
       </c>
-      <c r="G52" s="20" t="s">
+      <c r="G52" s="19" t="s">
         <v>795</v>
       </c>
-      <c r="H52" s="21"/>
+      <c r="H52" s="20"/>
     </row>
     <row r="53" spans="1:8" ht="21">
       <c r="A53" s="19"/>
       <c r="B53" s="19"/>
       <c r="C53" s="19"/>
-      <c r="D53" s="20" t="s">
+      <c r="D53" s="19" t="s">
         <v>1218</v>
       </c>
-      <c r="E53" s="20" t="s">
+      <c r="E53" s="19" t="s">
         <v>1135</v>
       </c>
-      <c r="F53" s="20" t="s">
+      <c r="F53" s="19" t="s">
         <v>1219</v>
       </c>
-      <c r="G53" s="20" t="s">
+      <c r="G53" s="19" t="s">
         <v>795</v>
       </c>
-      <c r="H53" s="21"/>
+      <c r="H53" s="20"/>
     </row>
     <row r="54" spans="1:8" ht="21">
       <c r="A54" s="19"/>
       <c r="B54" s="19"/>
       <c r="C54" s="19"/>
-      <c r="D54" s="20" t="s">
+      <c r="D54" s="19" t="s">
         <v>1220</v>
       </c>
-      <c r="E54" s="20" t="s">
+      <c r="E54" s="19" t="s">
         <v>1135</v>
       </c>
-      <c r="F54" s="20" t="s">
+      <c r="F54" s="19" t="s">
         <v>1221</v>
       </c>
-      <c r="G54" s="20" t="s">
+      <c r="G54" s="19" t="s">
         <v>795</v>
       </c>
-      <c r="H54" s="21"/>
+      <c r="H54" s="20"/>
+    </row>
+    <row r="55" spans="1:8">
+      <c r="A55" s="21" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B55" s="21" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C55" s="21" t="s">
+        <v>1278</v>
+      </c>
+      <c r="D55" s="21" t="s">
+        <v>1279</v>
+      </c>
+      <c r="E55" s="9"/>
+      <c r="F55" s="3" t="s">
+        <v>1280</v>
+      </c>
+      <c r="G55" s="3"/>
+      <c r="H55" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8">
+      <c r="A56" s="21" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B56" s="21" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C56" s="21" t="s">
+        <v>1281</v>
+      </c>
+      <c r="D56" s="21" t="s">
+        <v>1282</v>
+      </c>
+      <c r="E56" s="9"/>
+      <c r="F56" s="3" t="s">
+        <v>1283</v>
+      </c>
+      <c r="G56" s="3"/>
+      <c r="H56" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="A57" s="21" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B57" s="21" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C57" s="21" t="s">
+        <v>1284</v>
+      </c>
+      <c r="D57" s="21" t="s">
+        <v>1285</v>
+      </c>
+      <c r="E57" s="9"/>
+      <c r="F57" s="3" t="s">
+        <v>1286</v>
+      </c>
+      <c r="G57" s="3"/>
+      <c r="H57" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8">
+      <c r="A58" s="21" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B58" s="21" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C58" s="21" t="s">
+        <v>1287</v>
+      </c>
+      <c r="D58" s="21" t="s">
+        <v>1288</v>
+      </c>
+      <c r="E58" s="9"/>
+      <c r="F58" s="3" t="s">
+        <v>1289</v>
+      </c>
+      <c r="G58" s="3"/>
+      <c r="H58" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8">
+      <c r="A59" s="21" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B59" s="21" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C59" s="21" t="s">
+        <v>1290</v>
+      </c>
+      <c r="D59" s="21" t="s">
+        <v>1291</v>
+      </c>
+      <c r="E59" s="9"/>
+      <c r="F59" s="3" t="s">
+        <v>1286</v>
+      </c>
+      <c r="G59" s="3"/>
+      <c r="H59" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="A60" s="21" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B60" s="21" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C60" s="21" t="s">
+        <v>1292</v>
+      </c>
+      <c r="D60" s="21" t="s">
+        <v>1293</v>
+      </c>
+      <c r="E60" s="9"/>
+      <c r="F60" s="3" t="s">
+        <v>1286</v>
+      </c>
+      <c r="G60" s="3"/>
+      <c r="H60" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8">
+      <c r="A61" s="21" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B61" s="21" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C61" s="21" t="s">
+        <v>1294</v>
+      </c>
+      <c r="D61" s="21" t="s">
+        <v>1295</v>
+      </c>
+      <c r="E61" s="9"/>
+      <c r="F61" s="3" t="s">
+        <v>1286</v>
+      </c>
+      <c r="G61" s="3"/>
+      <c r="H61" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
+      <c r="A62" s="21" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B62" s="21" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C62" s="21" t="s">
+        <v>1296</v>
+      </c>
+      <c r="D62" s="21" t="s">
+        <v>1297</v>
+      </c>
+      <c r="E62" s="9"/>
+      <c r="F62" s="3" t="s">
+        <v>1286</v>
+      </c>
+      <c r="G62" s="3"/>
+      <c r="H62" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8">
+      <c r="A63" s="21" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B63" s="21" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C63" s="21" t="s">
+        <v>1298</v>
+      </c>
+      <c r="D63" s="21" t="s">
+        <v>1299</v>
+      </c>
+      <c r="E63" s="9"/>
+      <c r="F63" s="3" t="s">
+        <v>1300</v>
+      </c>
+      <c r="G63" s="3"/>
+      <c r="H63" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8">
+      <c r="A64" s="21" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B64" s="21" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C64" s="21" t="s">
+        <v>1301</v>
+      </c>
+      <c r="D64" s="21" t="s">
+        <v>1302</v>
+      </c>
+      <c r="E64" s="9"/>
+      <c r="F64" s="3" t="s">
+        <v>1286</v>
+      </c>
+      <c r="G64" s="3"/>
+      <c r="H64" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8">
+      <c r="A65" s="21" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B65" s="21" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C65" s="21" t="s">
+        <v>1303</v>
+      </c>
+      <c r="D65" s="21" t="s">
+        <v>1304</v>
+      </c>
+      <c r="E65" s="9"/>
+      <c r="F65" s="3" t="s">
+        <v>1286</v>
+      </c>
+      <c r="G65" s="3"/>
+      <c r="H65" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8">
+      <c r="A66" s="21" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B66" s="21" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C66" s="21" t="s">
+        <v>1305</v>
+      </c>
+      <c r="D66" s="21" t="s">
+        <v>1306</v>
+      </c>
+      <c r="E66" s="9"/>
+      <c r="F66" s="3" t="s">
+        <v>1286</v>
+      </c>
+      <c r="G66" s="3"/>
+      <c r="H66" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8">
+      <c r="A67" s="21" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B67" s="21" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C67" s="21" t="s">
+        <v>1307</v>
+      </c>
+      <c r="D67" s="21" t="s">
+        <v>1308</v>
+      </c>
+      <c r="E67" s="9"/>
+      <c r="F67" s="3" t="s">
+        <v>1309</v>
+      </c>
+      <c r="G67" s="3"/>
+      <c r="H67" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8">
+      <c r="A68" s="21" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B68" s="21" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C68" s="21" t="s">
+        <v>1310</v>
+      </c>
+      <c r="D68" s="21" t="s">
+        <v>1311</v>
+      </c>
+      <c r="E68" s="9"/>
+      <c r="F68" s="3" t="s">
+        <v>1312</v>
+      </c>
+      <c r="G68" s="3"/>
+      <c r="H68" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
+      <c r="A69" s="21" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B69" s="21" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C69" s="21" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D69" s="21" t="s">
+        <v>1314</v>
+      </c>
+      <c r="E69" s="9"/>
+      <c r="F69" s="3" t="s">
+        <v>1315</v>
+      </c>
+      <c r="G69" s="3"/>
+      <c r="H69" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
+      <c r="A70" s="21" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B70" s="21" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C70" s="21" t="s">
+        <v>1316</v>
+      </c>
+      <c r="D70" s="21" t="s">
+        <v>1317</v>
+      </c>
+      <c r="E70" s="9"/>
+      <c r="F70" s="3" t="s">
+        <v>1318</v>
+      </c>
+      <c r="G70" s="3"/>
+      <c r="H70" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8">
+      <c r="A71" s="21" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B71" s="21" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C71" s="21" t="s">
+        <v>1319</v>
+      </c>
+      <c r="D71" s="21" t="s">
+        <v>1320</v>
+      </c>
+      <c r="E71" s="9"/>
+      <c r="F71" s="3" t="s">
+        <v>1321</v>
+      </c>
+      <c r="G71" s="3"/>
+      <c r="H71" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8">
+      <c r="A72" s="21" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B72" s="21" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C72" s="21" t="s">
+        <v>1322</v>
+      </c>
+      <c r="D72" s="21" t="s">
+        <v>1323</v>
+      </c>
+      <c r="E72" s="9"/>
+      <c r="F72" s="3" t="s">
+        <v>1324</v>
+      </c>
+      <c r="G72" s="3"/>
+      <c r="H72" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8">
+      <c r="A73" s="21" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B73" s="21" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C73" s="21" t="s">
+        <v>1325</v>
+      </c>
+      <c r="D73" s="21" t="s">
+        <v>1326</v>
+      </c>
+      <c r="E73" s="9"/>
+      <c r="F73" s="3" t="s">
+        <v>1327</v>
+      </c>
+      <c r="G73" s="3"/>
+      <c r="H73" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
+      <c r="A74" s="21" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B74" s="21" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C74" s="21" t="s">
+        <v>1328</v>
+      </c>
+      <c r="D74" s="21" t="s">
+        <v>1329</v>
+      </c>
+      <c r="E74" s="9"/>
+      <c r="F74" s="3" t="s">
+        <v>1330</v>
+      </c>
+      <c r="G74" s="3"/>
+      <c r="H74" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8">
+      <c r="A75" s="21" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B75" s="21" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C75" s="21" t="s">
+        <v>1331</v>
+      </c>
+      <c r="D75" s="21" t="s">
+        <v>1332</v>
+      </c>
+      <c r="E75" s="9"/>
+      <c r="F75" s="3" t="s">
+        <v>1333</v>
+      </c>
+      <c r="G75" s="3"/>
+      <c r="H75" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="A76" s="21" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B76" s="21" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C76" s="21" t="s">
+        <v>1334</v>
+      </c>
+      <c r="D76" s="21" t="s">
+        <v>1335</v>
+      </c>
+      <c r="E76" s="9"/>
+      <c r="F76" s="3" t="s">
+        <v>1336</v>
+      </c>
+      <c r="G76" s="3"/>
+      <c r="H76" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
+      <c r="A77" s="21" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B77" s="21" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C77" s="21" t="s">
+        <v>1337</v>
+      </c>
+      <c r="D77" s="21" t="s">
+        <v>1338</v>
+      </c>
+      <c r="E77" s="9"/>
+      <c r="F77" s="3" t="s">
+        <v>1339</v>
+      </c>
+      <c r="G77" s="3"/>
+      <c r="H77" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8">
+      <c r="A78" s="21" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B78" s="21" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C78" s="21" t="s">
+        <v>1340</v>
+      </c>
+      <c r="D78" s="21" t="s">
+        <v>1341</v>
+      </c>
+      <c r="E78" s="9"/>
+      <c r="F78" s="3" t="s">
+        <v>1342</v>
+      </c>
+      <c r="G78" s="3"/>
+      <c r="H78" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8">
+      <c r="A79" s="21" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B79" s="21" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C79" s="21" t="s">
+        <v>1343</v>
+      </c>
+      <c r="D79" s="21" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E79" s="9"/>
+      <c r="F79" s="3" t="s">
+        <v>1345</v>
+      </c>
+      <c r="G79" s="3"/>
+      <c r="H79" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8">
+      <c r="A80" s="21" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B80" s="21" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C80" s="21" t="s">
+        <v>1346</v>
+      </c>
+      <c r="D80" s="21" t="s">
+        <v>1347</v>
+      </c>
+      <c r="E80" s="9"/>
+      <c r="F80" s="3" t="s">
+        <v>1348</v>
+      </c>
+      <c r="G80" s="3"/>
+      <c r="H80" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8">
+      <c r="A81" s="21" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B81" s="21" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C81" s="21" t="s">
+        <v>1349</v>
+      </c>
+      <c r="D81" s="21" t="s">
+        <v>1350</v>
+      </c>
+      <c r="E81" s="9"/>
+      <c r="F81" s="3" t="s">
+        <v>1351</v>
+      </c>
+      <c r="G81" s="3"/>
+      <c r="H81" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8">
+      <c r="A82" s="21" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B82" s="21" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C82" s="21" t="s">
+        <v>1352</v>
+      </c>
+      <c r="D82" s="21" t="s">
+        <v>1353</v>
+      </c>
+      <c r="E82" s="9"/>
+      <c r="F82" s="3" t="s">
+        <v>1354</v>
+      </c>
+      <c r="G82" s="3"/>
+      <c r="H82" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8">
+      <c r="A83" s="21" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B83" s="21" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C83" s="21" t="s">
+        <v>1355</v>
+      </c>
+      <c r="D83" s="21" t="s">
+        <v>1356</v>
+      </c>
+      <c r="E83" s="9"/>
+      <c r="F83" s="3" t="s">
+        <v>1357</v>
+      </c>
+      <c r="G83" s="3"/>
+      <c r="H83" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8">
+      <c r="A84" s="21" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B84" s="21" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C84" s="21" t="s">
+        <v>1358</v>
+      </c>
+      <c r="D84" s="21" t="s">
+        <v>1359</v>
+      </c>
+      <c r="E84" s="9"/>
+      <c r="F84" s="3" t="s">
+        <v>1360</v>
+      </c>
+      <c r="G84" s="3"/>
+      <c r="H84" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8">
+      <c r="A85" s="21" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B85" s="21" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C85" s="21" t="s">
+        <v>1361</v>
+      </c>
+      <c r="D85" s="21" t="s">
+        <v>1362</v>
+      </c>
+      <c r="E85" s="9"/>
+      <c r="F85" s="3" t="s">
+        <v>1363</v>
+      </c>
+      <c r="G85" s="3"/>
+      <c r="H85" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8">
+      <c r="A86" s="21" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B86" s="21" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C86" s="21" t="s">
+        <v>1364</v>
+      </c>
+      <c r="D86" s="21" t="s">
+        <v>1365</v>
+      </c>
+      <c r="E86" s="9"/>
+      <c r="F86" s="3" t="s">
+        <v>1366</v>
+      </c>
+      <c r="G86" s="3"/>
+      <c r="H86" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8">
+      <c r="A87" s="21" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B87" s="21" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C87" s="21" t="s">
+        <v>1367</v>
+      </c>
+      <c r="D87" s="21" t="s">
+        <v>1368</v>
+      </c>
+      <c r="E87" s="9"/>
+      <c r="F87" s="3" t="s">
+        <v>1369</v>
+      </c>
+      <c r="G87" s="3"/>
+      <c r="H87" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8">
+      <c r="A88" s="21" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B88" s="21" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C88" s="21" t="s">
+        <v>1370</v>
+      </c>
+      <c r="D88" s="21" t="s">
+        <v>1371</v>
+      </c>
+      <c r="E88" s="9"/>
+      <c r="F88" s="3" t="s">
+        <v>1372</v>
+      </c>
+      <c r="G88" s="3"/>
+      <c r="H88" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8">
+      <c r="A89" s="21" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B89" s="21" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C89" s="21" t="s">
+        <v>1373</v>
+      </c>
+      <c r="D89" s="21" t="s">
+        <v>1374</v>
+      </c>
+      <c r="E89" s="9"/>
+      <c r="F89" s="3" t="s">
+        <v>1375</v>
+      </c>
+      <c r="G89" s="3"/>
+      <c r="H89" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8">
+      <c r="A90" s="21" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B90" s="21" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C90" s="21" t="s">
+        <v>1376</v>
+      </c>
+      <c r="D90" s="21" t="s">
+        <v>1377</v>
+      </c>
+      <c r="E90" s="9"/>
+      <c r="F90" s="3" t="s">
+        <v>1378</v>
+      </c>
+      <c r="G90" s="3" t="s">
+        <v>1379</v>
+      </c>
+      <c r="H90" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8">
+      <c r="A91" s="21" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B91" s="21" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C91" s="21" t="s">
+        <v>1380</v>
+      </c>
+      <c r="D91" s="21" t="s">
+        <v>1381</v>
+      </c>
+      <c r="E91" s="9"/>
+      <c r="F91" s="3" t="s">
+        <v>1382</v>
+      </c>
+      <c r="G91" s="3"/>
+      <c r="H91" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8">
+      <c r="A92" s="21" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B92" s="21" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C92" s="21" t="s">
+        <v>1383</v>
+      </c>
+      <c r="D92" s="21" t="s">
+        <v>1384</v>
+      </c>
+      <c r="E92" s="9"/>
+      <c r="F92" s="3" t="s">
+        <v>1385</v>
+      </c>
+      <c r="G92" s="3"/>
+      <c r="H92" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8">
+      <c r="A93" s="21" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B93" s="21" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C93" s="21" t="s">
+        <v>1386</v>
+      </c>
+      <c r="D93" s="21" t="s">
+        <v>1387</v>
+      </c>
+      <c r="E93" s="9"/>
+      <c r="F93" s="3" t="s">
+        <v>1388</v>
+      </c>
+      <c r="G93" s="3"/>
+      <c r="H93" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8">
+      <c r="A94" s="21" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B94" s="21" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C94" s="21" t="s">
+        <v>1389</v>
+      </c>
+      <c r="D94" s="21" t="s">
+        <v>1390</v>
+      </c>
+      <c r="E94" s="9"/>
+      <c r="F94" s="3" t="s">
+        <v>1391</v>
+      </c>
+      <c r="G94" s="3"/>
+      <c r="H94" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8">
+      <c r="A95" s="21" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B95" s="21" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C95" s="21" t="s">
+        <v>1392</v>
+      </c>
+      <c r="D95" s="21" t="s">
+        <v>1393</v>
+      </c>
+      <c r="E95" s="9"/>
+      <c r="F95" s="3" t="s">
+        <v>1394</v>
+      </c>
+      <c r="G95" s="3"/>
+      <c r="H95" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8">
+      <c r="A96" s="21" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B96" s="21" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C96" s="21" t="s">
+        <v>1395</v>
+      </c>
+      <c r="D96" s="21" t="s">
+        <v>1396</v>
+      </c>
+      <c r="E96" s="9"/>
+      <c r="F96" s="3" t="s">
+        <v>1397</v>
+      </c>
+      <c r="G96" s="3"/>
+      <c r="H96" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8">
+      <c r="A97" s="21" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B97" s="21" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C97" s="21" t="s">
+        <v>1398</v>
+      </c>
+      <c r="D97" s="21" t="s">
+        <v>1399</v>
+      </c>
+      <c r="E97" s="9"/>
+      <c r="F97" s="3" t="s">
+        <v>1400</v>
+      </c>
+      <c r="G97" s="3"/>
+      <c r="H97" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8">
+      <c r="A98" s="21" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B98" s="21" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C98" s="21" t="s">
+        <v>1401</v>
+      </c>
+      <c r="D98" s="21" t="s">
+        <v>1402</v>
+      </c>
+      <c r="E98" s="9"/>
+      <c r="F98" s="3" t="s">
+        <v>1403</v>
+      </c>
+      <c r="G98" s="3"/>
+      <c r="H98" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8">
+      <c r="A99" s="21" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B99" s="21" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C99" s="21" t="s">
+        <v>1404</v>
+      </c>
+      <c r="D99" s="21" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E99" s="9"/>
+      <c r="F99" s="3" t="s">
+        <v>1406</v>
+      </c>
+      <c r="G99" s="3"/>
+      <c r="H99" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8">
+      <c r="A100" s="21" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B100" s="21" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C100" s="21" t="s">
+        <v>1407</v>
+      </c>
+      <c r="D100" s="21" t="s">
+        <v>1408</v>
+      </c>
+      <c r="E100" s="9"/>
+      <c r="F100" s="3" t="s">
+        <v>1409</v>
+      </c>
+      <c r="G100" s="3"/>
+      <c r="H100" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8">
+      <c r="A101" s="21" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B101" s="21" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C101" s="21" t="s">
+        <v>1410</v>
+      </c>
+      <c r="D101" s="21" t="s">
+        <v>1411</v>
+      </c>
+      <c r="E101" s="9"/>
+      <c r="F101" s="3" t="s">
+        <v>1286</v>
+      </c>
+      <c r="G101" s="3"/>
+      <c r="H101" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8">
+      <c r="A102" s="21" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B102" s="21" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C102" s="21" t="s">
+        <v>1412</v>
+      </c>
+      <c r="D102" s="21" t="s">
+        <v>1413</v>
+      </c>
+      <c r="E102" s="9"/>
+      <c r="F102" s="3" t="s">
+        <v>1414</v>
+      </c>
+      <c r="G102" s="3"/>
+      <c r="H102" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8">
+      <c r="A103" s="21" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B103" s="21" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C103" s="21" t="s">
+        <v>1415</v>
+      </c>
+      <c r="D103" s="21" t="s">
+        <v>1416</v>
+      </c>
+      <c r="E103" s="9"/>
+      <c r="F103" s="3" t="s">
+        <v>1286</v>
+      </c>
+      <c r="G103" s="3"/>
+      <c r="H103" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8">
+      <c r="A104" s="21" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B104" s="21" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C104" s="21" t="s">
+        <v>1417</v>
+      </c>
+      <c r="D104" s="21" t="s">
+        <v>1418</v>
+      </c>
+      <c r="E104" s="9"/>
+      <c r="F104" s="3" t="s">
+        <v>1419</v>
+      </c>
+      <c r="G104" s="3"/>
+      <c r="H104" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8">
+      <c r="A105" s="21" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B105" s="21" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C105" s="21" t="s">
+        <v>1420</v>
+      </c>
+      <c r="D105" s="21" t="s">
+        <v>1421</v>
+      </c>
+      <c r="E105" s="9"/>
+      <c r="F105" s="3" t="s">
+        <v>1422</v>
+      </c>
+      <c r="G105" s="3"/>
+      <c r="H105" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8">
+      <c r="A106" s="21" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B106" s="21" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C106" s="21" t="s">
+        <v>1423</v>
+      </c>
+      <c r="D106" s="21" t="s">
+        <v>1424</v>
+      </c>
+      <c r="E106" s="9"/>
+      <c r="F106" s="3" t="s">
+        <v>1425</v>
+      </c>
+      <c r="G106" s="3"/>
+      <c r="H106" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8">
+      <c r="A107" s="21" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B107" s="21" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C107" s="21" t="s">
+        <v>1426</v>
+      </c>
+      <c r="D107" s="21" t="s">
+        <v>1427</v>
+      </c>
+      <c r="E107" s="9"/>
+      <c r="F107" s="3" t="s">
+        <v>1428</v>
+      </c>
+      <c r="G107" s="3"/>
+      <c r="H107" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8">
+      <c r="A108" s="21" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B108" s="21" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C108" s="21" t="s">
+        <v>1429</v>
+      </c>
+      <c r="D108" s="21" t="s">
+        <v>1430</v>
+      </c>
+      <c r="E108" s="9"/>
+      <c r="F108" s="3" t="s">
+        <v>1431</v>
+      </c>
+      <c r="G108" s="3"/>
+      <c r="H108" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8">
+      <c r="A109" s="21" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B109" s="21" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C109" s="21" t="s">
+        <v>1432</v>
+      </c>
+      <c r="D109" s="21" t="s">
+        <v>1433</v>
+      </c>
+      <c r="E109" s="9"/>
+      <c r="F109" s="3" t="s">
+        <v>1434</v>
+      </c>
+      <c r="G109" s="3"/>
+      <c r="H109" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8">
+      <c r="A110" s="21" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B110" s="21" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C110" s="21" t="s">
+        <v>1435</v>
+      </c>
+      <c r="D110" s="21" t="s">
+        <v>1436</v>
+      </c>
+      <c r="E110" s="9"/>
+      <c r="F110" s="3" t="s">
+        <v>1437</v>
+      </c>
+      <c r="G110" s="3"/>
+      <c r="H110" s="3" t="s">
+        <v>1268</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8">
+      <c r="A111" s="21" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B111" s="21" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C111" s="21" t="s">
+        <v>1438</v>
+      </c>
+      <c r="D111" s="21" t="s">
+        <v>1439</v>
+      </c>
+      <c r="E111" s="9"/>
+      <c r="F111" s="3" t="s">
+        <v>1440</v>
+      </c>
+      <c r="G111" s="3"/>
+      <c r="H111" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8">
+      <c r="A112" s="21" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B112" s="21" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C112" s="21" t="s">
+        <v>1441</v>
+      </c>
+      <c r="D112" s="21" t="s">
+        <v>1442</v>
+      </c>
+      <c r="E112" s="9"/>
+      <c r="F112" s="3" t="s">
+        <v>1443</v>
+      </c>
+      <c r="G112" s="3"/>
+      <c r="H112" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8">
+      <c r="A113" s="21" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B113" s="21" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C113" s="21" t="s">
+        <v>1444</v>
+      </c>
+      <c r="D113" s="21" t="s">
+        <v>1445</v>
+      </c>
+      <c r="E113" s="9"/>
+      <c r="F113" s="3" t="s">
+        <v>1286</v>
+      </c>
+      <c r="G113" s="3"/>
+      <c r="H113" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8">
+      <c r="A114" s="21" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B114" s="21" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C114" s="21" t="s">
+        <v>1446</v>
+      </c>
+      <c r="D114" s="21" t="s">
+        <v>1447</v>
+      </c>
+      <c r="E114" s="9"/>
+      <c r="F114" s="3" t="s">
+        <v>1448</v>
+      </c>
+      <c r="G114" s="3"/>
+      <c r="H114" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8">
+      <c r="A115" s="21" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B115" s="21" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C115" s="21" t="s">
+        <v>1449</v>
+      </c>
+      <c r="D115" s="21" t="s">
+        <v>1450</v>
+      </c>
+      <c r="E115" s="9"/>
+      <c r="F115" s="3" t="s">
+        <v>1451</v>
+      </c>
+      <c r="G115" s="3"/>
+      <c r="H115" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8">
+      <c r="A116" s="21" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B116" s="21" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C116" s="21" t="s">
+        <v>1452</v>
+      </c>
+      <c r="D116" s="21" t="s">
+        <v>1453</v>
+      </c>
+      <c r="E116" s="9"/>
+      <c r="F116" s="3" t="s">
+        <v>1286</v>
+      </c>
+      <c r="G116" s="3"/>
+      <c r="H116" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8">
+      <c r="A117" s="21" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B117" s="21" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C117" s="21" t="s">
+        <v>1276</v>
+      </c>
+      <c r="D117" s="21" t="s">
+        <v>1454</v>
+      </c>
+      <c r="E117" s="9"/>
+      <c r="F117" s="3" t="s">
+        <v>1455</v>
+      </c>
+      <c r="G117" s="3" t="s">
+        <v>795</v>
+      </c>
+      <c r="H117" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8">
+      <c r="A118" s="21" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B118" s="21" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C118" s="21" t="s">
+        <v>1456</v>
+      </c>
+      <c r="D118" s="21" t="s">
+        <v>1457</v>
+      </c>
+      <c r="E118" s="9"/>
+      <c r="F118" s="3" t="s">
+        <v>1458</v>
+      </c>
+      <c r="G118" s="3" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H118" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8">
+      <c r="A119" s="21" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B119" s="21" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C119" s="21" t="s">
+        <v>1460</v>
+      </c>
+      <c r="D119" s="21" t="s">
+        <v>1461</v>
+      </c>
+      <c r="E119" s="9"/>
+      <c r="F119" s="3" t="s">
+        <v>1286</v>
+      </c>
+      <c r="G119" s="3"/>
+      <c r="H119" s="3" t="s">
+        <v>36</v>
+      </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H54">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://singerlk-my.sharepoint.com/personal/dihank_singersl_com/Documents/Desktop/DIHAN/cr dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="626" documentId="11_5847038500C079F1E35F4C8C432471BF012A7624" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7D7D7AC3-C0F2-4585-ABF3-8D680AECE85C}"/>
+  <xr:revisionPtr revIDLastSave="648" documentId="11_5847038500C079F1E35F4C8C432471BF012A7624" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1A32CB5A-02BA-4DC4-AD8C-20BACA411EE6}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -86,7 +86,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3501" uniqueCount="1463">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3501" uniqueCount="1464">
   <si>
     <t>SHOP_CODE</t>
   </si>
@@ -4475,18 +4475,28 @@
   </si>
   <si>
     <t>CR SENT TO SFL</t>
+  </si>
+  <si>
+    <t>CR SENT FOR CORRECTIONS</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4605,8 +4615,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
@@ -4630,27 +4640,27 @@
     <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="14" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -4714,7 +4724,7 @@
         <color rgb="FF9C0006"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
@@ -4734,7 +4744,7 @@
         <color rgb="FF9C0006"/>
       </font>
       <fill>
-        <patternFill>
+        <patternFill patternType="solid">
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
@@ -5652,7 +5662,7 @@
       <c r="X2" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="Y2" s="22" t="s">
+      <c r="Y2" s="21" t="s">
         <v>46</v>
       </c>
       <c r="Z2" s="9"/>
@@ -10681,7 +10691,7 @@
         <v>36</v>
       </c>
       <c r="Y91" s="3" t="s">
-        <v>211</v>
+        <v>46</v>
       </c>
       <c r="Z91" s="9"/>
     </row>
@@ -11237,7 +11247,7 @@
         <v>36</v>
       </c>
       <c r="Y101" s="9" t="s">
-        <v>242</v>
+        <v>211</v>
       </c>
       <c r="Z101" s="9"/>
     </row>
@@ -11600,10 +11610,10 @@
       <c r="X108" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="Y108" s="23" t="s">
+      <c r="Y108" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="Z108" s="23" t="s">
+      <c r="Z108" s="22" t="s">
         <v>72</v>
       </c>
     </row>
@@ -11758,7 +11768,7 @@
       <c r="X111" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="Y111" s="23" t="s">
+      <c r="Y111" s="22" t="s">
         <v>211</v>
       </c>
       <c r="Z111" s="9"/>
@@ -12386,7 +12396,7 @@
       <c r="X123" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="Y123" s="23" t="s">
+      <c r="Y123" s="22" t="s">
         <v>46</v>
       </c>
       <c r="Z123" s="9"/>
@@ -12701,7 +12711,7 @@
         <v>36</v>
       </c>
       <c r="Y129" s="9" t="s">
-        <v>242</v>
+        <v>46</v>
       </c>
       <c r="Z129" s="9"/>
     </row>
@@ -14158,7 +14168,7 @@
       <c r="X157" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="Y157" s="23" t="s">
+      <c r="Y157" s="22" t="s">
         <v>98</v>
       </c>
       <c r="Z157" s="9"/>
@@ -14210,8 +14220,8 @@
       <c r="X158" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="Y158" s="16" t="s">
-        <v>242</v>
+      <c r="Y158" s="23" t="s">
+        <v>211</v>
       </c>
       <c r="Z158" s="9"/>
     </row>
@@ -14730,7 +14740,7 @@
       <c r="X168" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="Y168" s="23" t="s">
+      <c r="Y168" s="22" t="s">
         <v>46</v>
       </c>
       <c r="Z168" s="9"/>
@@ -14988,10 +14998,10 @@
       <c r="V173" s="9"/>
       <c r="W173" s="9"/>
       <c r="X173" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y173" s="16" t="s">
-        <v>242</v>
+        <v>70</v>
+      </c>
+      <c r="Y173" s="23" t="s">
+        <v>794</v>
       </c>
       <c r="Z173" s="9"/>
     </row>
@@ -15251,7 +15261,7 @@
         <v>36</v>
       </c>
       <c r="Y178" s="9" t="s">
-        <v>211</v>
+        <v>794</v>
       </c>
       <c r="Z178" s="9"/>
     </row>
@@ -15302,8 +15312,8 @@
       <c r="X179" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="Y179" s="16" t="s">
-        <v>242</v>
+      <c r="Y179" s="23" t="s">
+        <v>211</v>
       </c>
       <c r="Z179" s="9"/>
     </row>
@@ -15355,7 +15365,7 @@
         <v>36</v>
       </c>
       <c r="Y180" s="9" t="s">
-        <v>242</v>
+        <v>211</v>
       </c>
       <c r="Z180" s="9"/>
     </row>
@@ -15614,8 +15624,8 @@
       <c r="X185" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="Y185" s="16" t="s">
-        <v>242</v>
+      <c r="Y185" s="23" t="s">
+        <v>211</v>
       </c>
       <c r="Z185" s="9"/>
     </row>
@@ -15718,7 +15728,7 @@
       <c r="X187" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="Y187" s="23" t="s">
+      <c r="Y187" s="22" t="s">
         <v>1462</v>
       </c>
       <c r="Z187" s="9"/>
@@ -15978,8 +15988,8 @@
       <c r="X192" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="Y192" s="16" t="s">
-        <v>242</v>
+      <c r="Y192" s="23" t="s">
+        <v>211</v>
       </c>
       <c r="Z192" s="9"/>
     </row>
@@ -16187,7 +16197,7 @@
         <v>36</v>
       </c>
       <c r="Y196" s="23" t="s">
-        <v>211</v>
+        <v>46</v>
       </c>
       <c r="Z196" s="9"/>
     </row>
@@ -16499,7 +16509,7 @@
         <v>36</v>
       </c>
       <c r="Y202" s="9" t="s">
-        <v>211</v>
+        <v>1463</v>
       </c>
       <c r="Z202" s="9"/>
     </row>
@@ -16550,7 +16560,7 @@
       <c r="X203" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="Y203" s="23" t="s">
+      <c r="Y203" s="22" t="s">
         <v>211</v>
       </c>
       <c r="Z203" s="9"/>
@@ -16707,7 +16717,7 @@
         <v>36</v>
       </c>
       <c r="Y206" s="23" t="s">
-        <v>211</v>
+        <v>1463</v>
       </c>
       <c r="Z206" s="9"/>
     </row>
@@ -16862,8 +16872,8 @@
       <c r="X209" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="Y209" s="16" t="s">
-        <v>242</v>
+      <c r="Y209" s="23" t="s">
+        <v>794</v>
       </c>
       <c r="Z209" s="9"/>
     </row>
@@ -17018,8 +17028,8 @@
       <c r="X212" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="Y212" s="16" t="s">
-        <v>242</v>
+      <c r="Y212" s="23" t="s">
+        <v>211</v>
       </c>
       <c r="Z212" s="9"/>
     </row>
@@ -17434,7 +17444,7 @@
       <c r="X220" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="Y220" s="23" t="s">
+      <c r="Y220" s="22" t="s">
         <v>211</v>
       </c>
       <c r="Z220" s="9"/>
@@ -17498,17 +17508,17 @@
   <conditionalFormatting sqref="J2:J60">
     <cfRule type="duplicateValues" dxfId="8" priority="9"/>
   </conditionalFormatting>
+  <conditionalFormatting sqref="J61:J100 N2:N60">
+    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="J130:J157">
-    <cfRule type="duplicateValues" dxfId="7" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K130:K153">
-    <cfRule type="duplicateValues" dxfId="6" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:M60">
-    <cfRule type="duplicateValues" dxfId="5" priority="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J61:J100 N2:N60">
-    <cfRule type="duplicateValues" dxfId="4" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N2:N100">
     <cfRule type="duplicateValues" dxfId="3" priority="11"/>
@@ -18877,1439 +18887,1439 @@
       </c>
       <c r="H54" s="20"/>
     </row>
-    <row r="55" spans="1:8">
-      <c r="A55" s="21" t="s">
+    <row r="55" spans="1:8" ht="21">
+      <c r="A55" s="19" t="s">
         <v>1226</v>
       </c>
-      <c r="B55" s="21" t="s">
+      <c r="B55" s="19" t="s">
         <v>1227</v>
       </c>
-      <c r="C55" s="21" t="s">
+      <c r="C55" s="19" t="s">
         <v>1277</v>
       </c>
-      <c r="D55" s="21" t="s">
+      <c r="D55" s="19" t="s">
         <v>1278</v>
       </c>
-      <c r="E55" s="9"/>
-      <c r="F55" s="3" t="s">
+      <c r="E55" s="19"/>
+      <c r="F55" s="19" t="s">
         <v>1279</v>
       </c>
-      <c r="G55" s="3"/>
-      <c r="H55" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8">
-      <c r="A56" s="21" t="s">
+      <c r="G55" s="19"/>
+      <c r="H55" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" ht="21">
+      <c r="A56" s="19" t="s">
         <v>1226</v>
       </c>
-      <c r="B56" s="21" t="s">
+      <c r="B56" s="19" t="s">
         <v>1227</v>
       </c>
-      <c r="C56" s="21" t="s">
+      <c r="C56" s="19" t="s">
         <v>1280</v>
       </c>
-      <c r="D56" s="21" t="s">
+      <c r="D56" s="19" t="s">
         <v>1281</v>
       </c>
-      <c r="E56" s="9"/>
-      <c r="F56" s="3" t="s">
+      <c r="E56" s="19"/>
+      <c r="F56" s="19" t="s">
         <v>1282</v>
       </c>
-      <c r="G56" s="3"/>
-      <c r="H56" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8">
-      <c r="A57" s="21" t="s">
+      <c r="G56" s="19"/>
+      <c r="H56" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" ht="21">
+      <c r="A57" s="19" t="s">
         <v>1110</v>
       </c>
-      <c r="B57" s="21" t="s">
+      <c r="B57" s="19" t="s">
         <v>1111</v>
       </c>
-      <c r="C57" s="21" t="s">
+      <c r="C57" s="19" t="s">
         <v>1283</v>
       </c>
-      <c r="D57" s="21" t="s">
+      <c r="D57" s="19" t="s">
         <v>1284</v>
       </c>
-      <c r="E57" s="9"/>
-      <c r="F57" s="3" t="s">
+      <c r="E57" s="19"/>
+      <c r="F57" s="19" t="s">
         <v>1285</v>
       </c>
-      <c r="G57" s="3"/>
-      <c r="H57" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8">
-      <c r="A58" s="21" t="s">
+      <c r="G57" s="19"/>
+      <c r="H57" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" ht="21">
+      <c r="A58" s="19" t="s">
         <v>1110</v>
       </c>
-      <c r="B58" s="21" t="s">
+      <c r="B58" s="19" t="s">
         <v>1111</v>
       </c>
-      <c r="C58" s="21" t="s">
+      <c r="C58" s="19" t="s">
         <v>1286</v>
       </c>
-      <c r="D58" s="21" t="s">
+      <c r="D58" s="19" t="s">
         <v>1287</v>
       </c>
-      <c r="E58" s="9"/>
-      <c r="F58" s="3" t="s">
+      <c r="E58" s="19"/>
+      <c r="F58" s="19" t="s">
         <v>1288</v>
       </c>
-      <c r="G58" s="3"/>
-      <c r="H58" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8">
-      <c r="A59" s="21" t="s">
+      <c r="G58" s="19"/>
+      <c r="H58" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" ht="21">
+      <c r="A59" s="19" t="s">
         <v>1110</v>
       </c>
-      <c r="B59" s="21" t="s">
+      <c r="B59" s="19" t="s">
         <v>1111</v>
       </c>
-      <c r="C59" s="21" t="s">
+      <c r="C59" s="19" t="s">
         <v>1289</v>
       </c>
-      <c r="D59" s="21" t="s">
+      <c r="D59" s="19" t="s">
         <v>1290</v>
       </c>
-      <c r="E59" s="9"/>
-      <c r="F59" s="3" t="s">
+      <c r="E59" s="19"/>
+      <c r="F59" s="19" t="s">
         <v>1285</v>
       </c>
-      <c r="G59" s="3"/>
-      <c r="H59" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8">
-      <c r="A60" s="21" t="s">
+      <c r="G59" s="19"/>
+      <c r="H59" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" ht="21">
+      <c r="A60" s="19" t="s">
         <v>1110</v>
       </c>
-      <c r="B60" s="21" t="s">
+      <c r="B60" s="19" t="s">
         <v>1111</v>
       </c>
-      <c r="C60" s="21" t="s">
+      <c r="C60" s="19" t="s">
         <v>1291</v>
       </c>
-      <c r="D60" s="21" t="s">
+      <c r="D60" s="19" t="s">
         <v>1292</v>
       </c>
-      <c r="E60" s="9"/>
-      <c r="F60" s="3" t="s">
+      <c r="E60" s="19"/>
+      <c r="F60" s="19" t="s">
         <v>1285</v>
       </c>
-      <c r="G60" s="3"/>
-      <c r="H60" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8">
-      <c r="A61" s="21" t="s">
+      <c r="G60" s="19"/>
+      <c r="H60" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" ht="21">
+      <c r="A61" s="19" t="s">
         <v>1110</v>
       </c>
-      <c r="B61" s="21" t="s">
+      <c r="B61" s="19" t="s">
         <v>1111</v>
       </c>
-      <c r="C61" s="21" t="s">
+      <c r="C61" s="19" t="s">
         <v>1293</v>
       </c>
-      <c r="D61" s="21" t="s">
+      <c r="D61" s="19" t="s">
         <v>1294</v>
       </c>
-      <c r="E61" s="9"/>
-      <c r="F61" s="3" t="s">
+      <c r="E61" s="19"/>
+      <c r="F61" s="19" t="s">
         <v>1285</v>
       </c>
-      <c r="G61" s="3"/>
-      <c r="H61" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8">
-      <c r="A62" s="21" t="s">
+      <c r="G61" s="19"/>
+      <c r="H61" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" ht="21">
+      <c r="A62" s="19" t="s">
         <v>1110</v>
       </c>
-      <c r="B62" s="21" t="s">
+      <c r="B62" s="19" t="s">
         <v>1111</v>
       </c>
-      <c r="C62" s="21" t="s">
+      <c r="C62" s="19" t="s">
         <v>1295</v>
       </c>
-      <c r="D62" s="21" t="s">
+      <c r="D62" s="19" t="s">
         <v>1296</v>
       </c>
-      <c r="E62" s="9"/>
-      <c r="F62" s="3" t="s">
+      <c r="E62" s="19"/>
+      <c r="F62" s="19" t="s">
         <v>1285</v>
       </c>
-      <c r="G62" s="3"/>
-      <c r="H62" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8">
-      <c r="A63" s="21" t="s">
+      <c r="G62" s="19"/>
+      <c r="H62" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" ht="21">
+      <c r="A63" s="19" t="s">
         <v>1110</v>
       </c>
-      <c r="B63" s="21" t="s">
+      <c r="B63" s="19" t="s">
         <v>1111</v>
       </c>
-      <c r="C63" s="21" t="s">
+      <c r="C63" s="19" t="s">
         <v>1297</v>
       </c>
-      <c r="D63" s="21" t="s">
+      <c r="D63" s="19" t="s">
         <v>1298</v>
       </c>
-      <c r="E63" s="9"/>
-      <c r="F63" s="3" t="s">
+      <c r="E63" s="19"/>
+      <c r="F63" s="19" t="s">
         <v>1299</v>
       </c>
-      <c r="G63" s="3"/>
-      <c r="H63" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8">
-      <c r="A64" s="21" t="s">
+      <c r="G63" s="19"/>
+      <c r="H63" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" ht="21">
+      <c r="A64" s="19" t="s">
         <v>1110</v>
       </c>
-      <c r="B64" s="21" t="s">
+      <c r="B64" s="19" t="s">
         <v>1111</v>
       </c>
-      <c r="C64" s="21" t="s">
+      <c r="C64" s="19" t="s">
         <v>1300</v>
       </c>
-      <c r="D64" s="21" t="s">
+      <c r="D64" s="19" t="s">
         <v>1301</v>
       </c>
-      <c r="E64" s="9"/>
-      <c r="F64" s="3" t="s">
+      <c r="E64" s="19"/>
+      <c r="F64" s="19" t="s">
         <v>1285</v>
       </c>
-      <c r="G64" s="3"/>
-      <c r="H64" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8">
-      <c r="A65" s="21" t="s">
+      <c r="G64" s="19"/>
+      <c r="H64" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" ht="21">
+      <c r="A65" s="19" t="s">
         <v>1110</v>
       </c>
-      <c r="B65" s="21" t="s">
+      <c r="B65" s="19" t="s">
         <v>1111</v>
       </c>
-      <c r="C65" s="21" t="s">
+      <c r="C65" s="19" t="s">
         <v>1302</v>
       </c>
-      <c r="D65" s="21" t="s">
+      <c r="D65" s="19" t="s">
         <v>1303</v>
       </c>
-      <c r="E65" s="9"/>
-      <c r="F65" s="3" t="s">
+      <c r="E65" s="19"/>
+      <c r="F65" s="19" t="s">
         <v>1285</v>
       </c>
-      <c r="G65" s="3"/>
-      <c r="H65" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8">
-      <c r="A66" s="21" t="s">
+      <c r="G65" s="19"/>
+      <c r="H65" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="21">
+      <c r="A66" s="19" t="s">
         <v>1110</v>
       </c>
-      <c r="B66" s="21" t="s">
+      <c r="B66" s="19" t="s">
         <v>1111</v>
       </c>
-      <c r="C66" s="21" t="s">
+      <c r="C66" s="19" t="s">
         <v>1304</v>
       </c>
-      <c r="D66" s="21" t="s">
+      <c r="D66" s="19" t="s">
         <v>1305</v>
       </c>
-      <c r="E66" s="9"/>
-      <c r="F66" s="3" t="s">
+      <c r="E66" s="19"/>
+      <c r="F66" s="19" t="s">
         <v>1285</v>
       </c>
-      <c r="G66" s="3"/>
-      <c r="H66" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8">
-      <c r="A67" s="21" t="s">
+      <c r="G66" s="19"/>
+      <c r="H66" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" ht="21">
+      <c r="A67" s="19" t="s">
         <v>1110</v>
       </c>
-      <c r="B67" s="21" t="s">
+      <c r="B67" s="19" t="s">
         <v>1111</v>
       </c>
-      <c r="C67" s="21" t="s">
+      <c r="C67" s="19" t="s">
         <v>1306</v>
       </c>
-      <c r="D67" s="21" t="s">
+      <c r="D67" s="19" t="s">
         <v>1307</v>
       </c>
-      <c r="E67" s="9"/>
-      <c r="F67" s="3" t="s">
+      <c r="E67" s="19"/>
+      <c r="F67" s="19" t="s">
         <v>1308</v>
       </c>
-      <c r="G67" s="3"/>
-      <c r="H67" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8">
-      <c r="A68" s="21" t="s">
+      <c r="G67" s="19"/>
+      <c r="H67" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="21">
+      <c r="A68" s="19" t="s">
         <v>1226</v>
       </c>
-      <c r="B68" s="21" t="s">
+      <c r="B68" s="19" t="s">
         <v>1227</v>
       </c>
-      <c r="C68" s="21" t="s">
+      <c r="C68" s="19" t="s">
         <v>1309</v>
       </c>
-      <c r="D68" s="21" t="s">
+      <c r="D68" s="19" t="s">
         <v>1310</v>
       </c>
-      <c r="E68" s="9"/>
-      <c r="F68" s="3" t="s">
+      <c r="E68" s="19"/>
+      <c r="F68" s="19" t="s">
         <v>1311</v>
       </c>
-      <c r="G68" s="3"/>
-      <c r="H68" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8">
-      <c r="A69" s="21" t="s">
+      <c r="G68" s="19"/>
+      <c r="H68" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" ht="21">
+      <c r="A69" s="19" t="s">
         <v>1226</v>
       </c>
-      <c r="B69" s="21" t="s">
+      <c r="B69" s="19" t="s">
         <v>1227</v>
       </c>
-      <c r="C69" s="21" t="s">
+      <c r="C69" s="19" t="s">
         <v>1312</v>
       </c>
-      <c r="D69" s="21" t="s">
+      <c r="D69" s="19" t="s">
         <v>1313</v>
       </c>
-      <c r="E69" s="9"/>
-      <c r="F69" s="3" t="s">
+      <c r="E69" s="19"/>
+      <c r="F69" s="19" t="s">
         <v>1314</v>
       </c>
-      <c r="G69" s="3"/>
-      <c r="H69" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8">
-      <c r="A70" s="21" t="s">
+      <c r="G69" s="19"/>
+      <c r="H69" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" ht="21">
+      <c r="A70" s="19" t="s">
         <v>1226</v>
       </c>
-      <c r="B70" s="21" t="s">
+      <c r="B70" s="19" t="s">
         <v>1227</v>
       </c>
-      <c r="C70" s="21" t="s">
+      <c r="C70" s="19" t="s">
         <v>1315</v>
       </c>
-      <c r="D70" s="21" t="s">
+      <c r="D70" s="19" t="s">
         <v>1316</v>
       </c>
-      <c r="E70" s="9"/>
-      <c r="F70" s="3" t="s">
+      <c r="E70" s="19"/>
+      <c r="F70" s="19" t="s">
         <v>1317</v>
       </c>
-      <c r="G70" s="3"/>
-      <c r="H70" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8">
-      <c r="A71" s="21" t="s">
+      <c r="G70" s="19"/>
+      <c r="H70" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" ht="21">
+      <c r="A71" s="19" t="s">
         <v>1226</v>
       </c>
-      <c r="B71" s="21" t="s">
+      <c r="B71" s="19" t="s">
         <v>1227</v>
       </c>
-      <c r="C71" s="21" t="s">
+      <c r="C71" s="19" t="s">
         <v>1318</v>
       </c>
-      <c r="D71" s="21" t="s">
+      <c r="D71" s="19" t="s">
         <v>1319</v>
       </c>
-      <c r="E71" s="9"/>
-      <c r="F71" s="3" t="s">
+      <c r="E71" s="19"/>
+      <c r="F71" s="19" t="s">
         <v>1320</v>
       </c>
-      <c r="G71" s="3"/>
-      <c r="H71" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8">
-      <c r="A72" s="21" t="s">
+      <c r="G71" s="19"/>
+      <c r="H71" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" ht="21">
+      <c r="A72" s="19" t="s">
         <v>1226</v>
       </c>
-      <c r="B72" s="21" t="s">
+      <c r="B72" s="19" t="s">
         <v>1227</v>
       </c>
-      <c r="C72" s="21" t="s">
+      <c r="C72" s="19" t="s">
         <v>1321</v>
       </c>
-      <c r="D72" s="21" t="s">
+      <c r="D72" s="19" t="s">
         <v>1322</v>
       </c>
-      <c r="E72" s="9"/>
-      <c r="F72" s="3" t="s">
+      <c r="E72" s="19"/>
+      <c r="F72" s="19" t="s">
         <v>1323</v>
       </c>
-      <c r="G72" s="3"/>
-      <c r="H72" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8">
-      <c r="A73" s="21" t="s">
+      <c r="G72" s="19"/>
+      <c r="H72" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" ht="21">
+      <c r="A73" s="19" t="s">
         <v>1226</v>
       </c>
-      <c r="B73" s="21" t="s">
+      <c r="B73" s="19" t="s">
         <v>1227</v>
       </c>
-      <c r="C73" s="21" t="s">
+      <c r="C73" s="19" t="s">
         <v>1324</v>
       </c>
-      <c r="D73" s="21" t="s">
+      <c r="D73" s="19" t="s">
         <v>1325</v>
       </c>
-      <c r="E73" s="9"/>
-      <c r="F73" s="3" t="s">
+      <c r="E73" s="19"/>
+      <c r="F73" s="19" t="s">
         <v>1326</v>
       </c>
-      <c r="G73" s="3"/>
-      <c r="H73" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8">
-      <c r="A74" s="21" t="s">
+      <c r="G73" s="19"/>
+      <c r="H73" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" ht="21">
+      <c r="A74" s="19" t="s">
         <v>1226</v>
       </c>
-      <c r="B74" s="21" t="s">
+      <c r="B74" s="19" t="s">
         <v>1227</v>
       </c>
-      <c r="C74" s="21" t="s">
+      <c r="C74" s="19" t="s">
         <v>1327</v>
       </c>
-      <c r="D74" s="21" t="s">
+      <c r="D74" s="19" t="s">
         <v>1328</v>
       </c>
-      <c r="E74" s="9"/>
-      <c r="F74" s="3" t="s">
+      <c r="E74" s="19"/>
+      <c r="F74" s="19" t="s">
         <v>1329</v>
       </c>
-      <c r="G74" s="3"/>
-      <c r="H74" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8">
-      <c r="A75" s="21" t="s">
+      <c r="G74" s="19"/>
+      <c r="H74" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" ht="21">
+      <c r="A75" s="19" t="s">
         <v>1226</v>
       </c>
-      <c r="B75" s="21" t="s">
+      <c r="B75" s="19" t="s">
         <v>1227</v>
       </c>
-      <c r="C75" s="21" t="s">
+      <c r="C75" s="19" t="s">
         <v>1330</v>
       </c>
-      <c r="D75" s="21" t="s">
+      <c r="D75" s="19" t="s">
         <v>1331</v>
       </c>
-      <c r="E75" s="9"/>
-      <c r="F75" s="3" t="s">
+      <c r="E75" s="19"/>
+      <c r="F75" s="19" t="s">
         <v>1332</v>
       </c>
-      <c r="G75" s="3"/>
-      <c r="H75" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8">
-      <c r="A76" s="21" t="s">
+      <c r="G75" s="19"/>
+      <c r="H75" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" ht="21">
+      <c r="A76" s="19" t="s">
         <v>1226</v>
       </c>
-      <c r="B76" s="21" t="s">
+      <c r="B76" s="19" t="s">
         <v>1227</v>
       </c>
-      <c r="C76" s="21" t="s">
+      <c r="C76" s="19" t="s">
         <v>1333</v>
       </c>
-      <c r="D76" s="21" t="s">
+      <c r="D76" s="19" t="s">
         <v>1334</v>
       </c>
-      <c r="E76" s="9"/>
-      <c r="F76" s="3" t="s">
+      <c r="E76" s="19"/>
+      <c r="F76" s="19" t="s">
         <v>1335</v>
       </c>
-      <c r="G76" s="3"/>
-      <c r="H76" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8">
-      <c r="A77" s="21" t="s">
+      <c r="G76" s="19"/>
+      <c r="H76" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" ht="21">
+      <c r="A77" s="19" t="s">
         <v>1226</v>
       </c>
-      <c r="B77" s="21" t="s">
+      <c r="B77" s="19" t="s">
         <v>1227</v>
       </c>
-      <c r="C77" s="21" t="s">
+      <c r="C77" s="19" t="s">
         <v>1336</v>
       </c>
-      <c r="D77" s="21" t="s">
+      <c r="D77" s="19" t="s">
         <v>1337</v>
       </c>
-      <c r="E77" s="9"/>
-      <c r="F77" s="3" t="s">
+      <c r="E77" s="19"/>
+      <c r="F77" s="19" t="s">
         <v>1338</v>
       </c>
-      <c r="G77" s="3"/>
-      <c r="H77" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8">
-      <c r="A78" s="21" t="s">
+      <c r="G77" s="19"/>
+      <c r="H77" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" ht="21">
+      <c r="A78" s="19" t="s">
         <v>1226</v>
       </c>
-      <c r="B78" s="21" t="s">
+      <c r="B78" s="19" t="s">
         <v>1227</v>
       </c>
-      <c r="C78" s="21" t="s">
+      <c r="C78" s="19" t="s">
         <v>1339</v>
       </c>
-      <c r="D78" s="21" t="s">
+      <c r="D78" s="19" t="s">
         <v>1340</v>
       </c>
-      <c r="E78" s="9"/>
-      <c r="F78" s="3" t="s">
+      <c r="E78" s="19"/>
+      <c r="F78" s="19" t="s">
         <v>1341</v>
       </c>
-      <c r="G78" s="3"/>
-      <c r="H78" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8">
-      <c r="A79" s="21" t="s">
+      <c r="G78" s="19"/>
+      <c r="H78" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" ht="21">
+      <c r="A79" s="19" t="s">
         <v>1226</v>
       </c>
-      <c r="B79" s="21" t="s">
+      <c r="B79" s="19" t="s">
         <v>1227</v>
       </c>
-      <c r="C79" s="21" t="s">
+      <c r="C79" s="19" t="s">
         <v>1342</v>
       </c>
-      <c r="D79" s="21" t="s">
+      <c r="D79" s="19" t="s">
         <v>1343</v>
       </c>
-      <c r="E79" s="9"/>
-      <c r="F79" s="3" t="s">
+      <c r="E79" s="19"/>
+      <c r="F79" s="19" t="s">
         <v>1344</v>
       </c>
-      <c r="G79" s="3"/>
-      <c r="H79" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8">
-      <c r="A80" s="21" t="s">
+      <c r="G79" s="19"/>
+      <c r="H79" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" ht="21">
+      <c r="A80" s="19" t="s">
         <v>1226</v>
       </c>
-      <c r="B80" s="21" t="s">
+      <c r="B80" s="19" t="s">
         <v>1227</v>
       </c>
-      <c r="C80" s="21" t="s">
+      <c r="C80" s="19" t="s">
         <v>1345</v>
       </c>
-      <c r="D80" s="21" t="s">
+      <c r="D80" s="19" t="s">
         <v>1346</v>
       </c>
-      <c r="E80" s="9"/>
-      <c r="F80" s="3" t="s">
+      <c r="E80" s="19"/>
+      <c r="F80" s="19" t="s">
         <v>1347</v>
       </c>
-      <c r="G80" s="3"/>
-      <c r="H80" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8">
-      <c r="A81" s="21" t="s">
+      <c r="G80" s="19"/>
+      <c r="H80" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" ht="21">
+      <c r="A81" s="19" t="s">
         <v>1226</v>
       </c>
-      <c r="B81" s="21" t="s">
+      <c r="B81" s="19" t="s">
         <v>1227</v>
       </c>
-      <c r="C81" s="21" t="s">
+      <c r="C81" s="19" t="s">
         <v>1348</v>
       </c>
-      <c r="D81" s="21" t="s">
+      <c r="D81" s="19" t="s">
         <v>1349</v>
       </c>
-      <c r="E81" s="9"/>
-      <c r="F81" s="3" t="s">
+      <c r="E81" s="19"/>
+      <c r="F81" s="19" t="s">
         <v>1350</v>
       </c>
-      <c r="G81" s="3"/>
-      <c r="H81" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8">
-      <c r="A82" s="21" t="s">
+      <c r="G81" s="19"/>
+      <c r="H81" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" ht="21">
+      <c r="A82" s="19" t="s">
         <v>1226</v>
       </c>
-      <c r="B82" s="21" t="s">
+      <c r="B82" s="19" t="s">
         <v>1227</v>
       </c>
-      <c r="C82" s="21" t="s">
+      <c r="C82" s="19" t="s">
         <v>1351</v>
       </c>
-      <c r="D82" s="21" t="s">
+      <c r="D82" s="19" t="s">
         <v>1352</v>
       </c>
-      <c r="E82" s="9"/>
-      <c r="F82" s="3" t="s">
+      <c r="E82" s="19"/>
+      <c r="F82" s="19" t="s">
         <v>1353</v>
       </c>
-      <c r="G82" s="3"/>
-      <c r="H82" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8">
-      <c r="A83" s="21" t="s">
+      <c r="G82" s="19"/>
+      <c r="H82" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" ht="21">
+      <c r="A83" s="19" t="s">
         <v>1226</v>
       </c>
-      <c r="B83" s="21" t="s">
+      <c r="B83" s="19" t="s">
         <v>1227</v>
       </c>
-      <c r="C83" s="21" t="s">
+      <c r="C83" s="19" t="s">
         <v>1354</v>
       </c>
-      <c r="D83" s="21" t="s">
+      <c r="D83" s="19" t="s">
         <v>1355</v>
       </c>
-      <c r="E83" s="9"/>
-      <c r="F83" s="3" t="s">
+      <c r="E83" s="19"/>
+      <c r="F83" s="19" t="s">
         <v>1356</v>
       </c>
-      <c r="G83" s="3"/>
-      <c r="H83" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8">
-      <c r="A84" s="21" t="s">
+      <c r="G83" s="19"/>
+      <c r="H83" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" ht="21">
+      <c r="A84" s="19" t="s">
         <v>1226</v>
       </c>
-      <c r="B84" s="21" t="s">
+      <c r="B84" s="19" t="s">
         <v>1227</v>
       </c>
-      <c r="C84" s="21" t="s">
+      <c r="C84" s="19" t="s">
         <v>1357</v>
       </c>
-      <c r="D84" s="21" t="s">
+      <c r="D84" s="19" t="s">
         <v>1358</v>
       </c>
-      <c r="E84" s="9"/>
-      <c r="F84" s="3" t="s">
+      <c r="E84" s="19"/>
+      <c r="F84" s="19" t="s">
         <v>1359</v>
       </c>
-      <c r="G84" s="3"/>
-      <c r="H84" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8">
-      <c r="A85" s="21" t="s">
+      <c r="G84" s="19"/>
+      <c r="H84" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" ht="21">
+      <c r="A85" s="19" t="s">
         <v>1226</v>
       </c>
-      <c r="B85" s="21" t="s">
+      <c r="B85" s="19" t="s">
         <v>1227</v>
       </c>
-      <c r="C85" s="21" t="s">
+      <c r="C85" s="19" t="s">
         <v>1360</v>
       </c>
-      <c r="D85" s="21" t="s">
+      <c r="D85" s="19" t="s">
         <v>1361</v>
       </c>
-      <c r="E85" s="9"/>
-      <c r="F85" s="3" t="s">
+      <c r="E85" s="19"/>
+      <c r="F85" s="19" t="s">
         <v>1362</v>
       </c>
-      <c r="G85" s="3"/>
-      <c r="H85" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8">
-      <c r="A86" s="21" t="s">
+      <c r="G85" s="19"/>
+      <c r="H85" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" ht="21">
+      <c r="A86" s="19" t="s">
         <v>1226</v>
       </c>
-      <c r="B86" s="21" t="s">
+      <c r="B86" s="19" t="s">
         <v>1227</v>
       </c>
-      <c r="C86" s="21" t="s">
+      <c r="C86" s="19" t="s">
         <v>1363</v>
       </c>
-      <c r="D86" s="21" t="s">
+      <c r="D86" s="19" t="s">
         <v>1364</v>
       </c>
-      <c r="E86" s="9"/>
-      <c r="F86" s="3" t="s">
+      <c r="E86" s="19"/>
+      <c r="F86" s="19" t="s">
         <v>1365</v>
       </c>
-      <c r="G86" s="3"/>
-      <c r="H86" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8">
-      <c r="A87" s="21" t="s">
+      <c r="G86" s="19"/>
+      <c r="H86" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" ht="21">
+      <c r="A87" s="19" t="s">
         <v>1226</v>
       </c>
-      <c r="B87" s="21" t="s">
+      <c r="B87" s="19" t="s">
         <v>1227</v>
       </c>
-      <c r="C87" s="21" t="s">
+      <c r="C87" s="19" t="s">
         <v>1366</v>
       </c>
-      <c r="D87" s="21" t="s">
+      <c r="D87" s="19" t="s">
         <v>1367</v>
       </c>
-      <c r="E87" s="9"/>
-      <c r="F87" s="3" t="s">
+      <c r="E87" s="19"/>
+      <c r="F87" s="19" t="s">
         <v>1368</v>
       </c>
-      <c r="G87" s="3"/>
-      <c r="H87" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8">
-      <c r="A88" s="21" t="s">
+      <c r="G87" s="19"/>
+      <c r="H87" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" ht="21">
+      <c r="A88" s="19" t="s">
         <v>1226</v>
       </c>
-      <c r="B88" s="21" t="s">
+      <c r="B88" s="19" t="s">
         <v>1227</v>
       </c>
-      <c r="C88" s="21" t="s">
+      <c r="C88" s="19" t="s">
         <v>1369</v>
       </c>
-      <c r="D88" s="21" t="s">
+      <c r="D88" s="19" t="s">
         <v>1370</v>
       </c>
-      <c r="E88" s="9"/>
-      <c r="F88" s="3" t="s">
+      <c r="E88" s="19"/>
+      <c r="F88" s="19" t="s">
         <v>1371</v>
       </c>
-      <c r="G88" s="3"/>
-      <c r="H88" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8">
-      <c r="A89" s="21" t="s">
+      <c r="G88" s="19"/>
+      <c r="H88" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" ht="21">
+      <c r="A89" s="19" t="s">
         <v>1226</v>
       </c>
-      <c r="B89" s="21" t="s">
+      <c r="B89" s="19" t="s">
         <v>1227</v>
       </c>
-      <c r="C89" s="21" t="s">
+      <c r="C89" s="19" t="s">
         <v>1372</v>
       </c>
-      <c r="D89" s="21" t="s">
+      <c r="D89" s="19" t="s">
         <v>1373</v>
       </c>
-      <c r="E89" s="9"/>
-      <c r="F89" s="3" t="s">
+      <c r="E89" s="19"/>
+      <c r="F89" s="19" t="s">
         <v>1374</v>
       </c>
-      <c r="G89" s="3"/>
-      <c r="H89" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8">
-      <c r="A90" s="21" t="s">
+      <c r="G89" s="19"/>
+      <c r="H89" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" ht="21">
+      <c r="A90" s="19" t="s">
         <v>1226</v>
       </c>
-      <c r="B90" s="21" t="s">
+      <c r="B90" s="19" t="s">
         <v>1227</v>
       </c>
-      <c r="C90" s="21" t="s">
+      <c r="C90" s="19" t="s">
         <v>1375</v>
       </c>
-      <c r="D90" s="21" t="s">
+      <c r="D90" s="19" t="s">
         <v>1376</v>
       </c>
-      <c r="E90" s="9"/>
-      <c r="F90" s="3" t="s">
+      <c r="E90" s="19"/>
+      <c r="F90" s="19" t="s">
         <v>1377</v>
       </c>
-      <c r="G90" s="3" t="s">
+      <c r="G90" s="19" t="s">
         <v>1378</v>
       </c>
-      <c r="H90" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8">
-      <c r="A91" s="21" t="s">
+      <c r="H90" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" ht="21">
+      <c r="A91" s="19" t="s">
         <v>1226</v>
       </c>
-      <c r="B91" s="21" t="s">
+      <c r="B91" s="19" t="s">
         <v>1227</v>
       </c>
-      <c r="C91" s="21" t="s">
+      <c r="C91" s="19" t="s">
         <v>1379</v>
       </c>
-      <c r="D91" s="21" t="s">
+      <c r="D91" s="19" t="s">
         <v>1380</v>
       </c>
-      <c r="E91" s="9"/>
-      <c r="F91" s="3" t="s">
+      <c r="E91" s="19"/>
+      <c r="F91" s="19" t="s">
         <v>1381</v>
       </c>
-      <c r="G91" s="3"/>
-      <c r="H91" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8">
-      <c r="A92" s="21" t="s">
+      <c r="G91" s="19"/>
+      <c r="H91" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" ht="21">
+      <c r="A92" s="19" t="s">
         <v>1226</v>
       </c>
-      <c r="B92" s="21" t="s">
+      <c r="B92" s="19" t="s">
         <v>1227</v>
       </c>
-      <c r="C92" s="21" t="s">
+      <c r="C92" s="19" t="s">
         <v>1382</v>
       </c>
-      <c r="D92" s="21" t="s">
+      <c r="D92" s="19" t="s">
         <v>1383</v>
       </c>
-      <c r="E92" s="9"/>
-      <c r="F92" s="3" t="s">
+      <c r="E92" s="19"/>
+      <c r="F92" s="19" t="s">
         <v>1384</v>
       </c>
-      <c r="G92" s="3"/>
-      <c r="H92" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8">
-      <c r="A93" s="21" t="s">
+      <c r="G92" s="19"/>
+      <c r="H92" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" ht="21">
+      <c r="A93" s="19" t="s">
         <v>1226</v>
       </c>
-      <c r="B93" s="21" t="s">
+      <c r="B93" s="19" t="s">
         <v>1227</v>
       </c>
-      <c r="C93" s="21" t="s">
+      <c r="C93" s="19" t="s">
         <v>1385</v>
       </c>
-      <c r="D93" s="21" t="s">
+      <c r="D93" s="19" t="s">
         <v>1386</v>
       </c>
-      <c r="E93" s="9"/>
-      <c r="F93" s="3" t="s">
+      <c r="E93" s="19"/>
+      <c r="F93" s="19" t="s">
         <v>1387</v>
       </c>
-      <c r="G93" s="3"/>
-      <c r="H93" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8">
-      <c r="A94" s="21" t="s">
+      <c r="G93" s="19"/>
+      <c r="H93" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" ht="21">
+      <c r="A94" s="19" t="s">
         <v>1226</v>
       </c>
-      <c r="B94" s="21" t="s">
+      <c r="B94" s="19" t="s">
         <v>1227</v>
       </c>
-      <c r="C94" s="21" t="s">
+      <c r="C94" s="19" t="s">
         <v>1388</v>
       </c>
-      <c r="D94" s="21" t="s">
+      <c r="D94" s="19" t="s">
         <v>1389</v>
       </c>
-      <c r="E94" s="9"/>
-      <c r="F94" s="3" t="s">
+      <c r="E94" s="19"/>
+      <c r="F94" s="19" t="s">
         <v>1390</v>
       </c>
-      <c r="G94" s="3"/>
-      <c r="H94" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8">
-      <c r="A95" s="21" t="s">
+      <c r="G94" s="19"/>
+      <c r="H94" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" ht="21">
+      <c r="A95" s="19" t="s">
         <v>1226</v>
       </c>
-      <c r="B95" s="21" t="s">
+      <c r="B95" s="19" t="s">
         <v>1227</v>
       </c>
-      <c r="C95" s="21" t="s">
+      <c r="C95" s="19" t="s">
         <v>1391</v>
       </c>
-      <c r="D95" s="21" t="s">
+      <c r="D95" s="19" t="s">
         <v>1392</v>
       </c>
-      <c r="E95" s="9"/>
-      <c r="F95" s="3" t="s">
+      <c r="E95" s="19"/>
+      <c r="F95" s="19" t="s">
         <v>1393</v>
       </c>
-      <c r="G95" s="3"/>
-      <c r="H95" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="96" spans="1:8">
-      <c r="A96" s="21" t="s">
+      <c r="G95" s="19"/>
+      <c r="H95" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" ht="21">
+      <c r="A96" s="19" t="s">
         <v>1226</v>
       </c>
-      <c r="B96" s="21" t="s">
+      <c r="B96" s="19" t="s">
         <v>1227</v>
       </c>
-      <c r="C96" s="21" t="s">
+      <c r="C96" s="19" t="s">
         <v>1394</v>
       </c>
-      <c r="D96" s="21" t="s">
+      <c r="D96" s="19" t="s">
         <v>1395</v>
       </c>
-      <c r="E96" s="9"/>
-      <c r="F96" s="3" t="s">
+      <c r="E96" s="19"/>
+      <c r="F96" s="19" t="s">
         <v>1396</v>
       </c>
-      <c r="G96" s="3"/>
-      <c r="H96" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8">
-      <c r="A97" s="21" t="s">
+      <c r="G96" s="19"/>
+      <c r="H96" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" ht="21">
+      <c r="A97" s="19" t="s">
         <v>1226</v>
       </c>
-      <c r="B97" s="21" t="s">
+      <c r="B97" s="19" t="s">
         <v>1227</v>
       </c>
-      <c r="C97" s="21" t="s">
+      <c r="C97" s="19" t="s">
         <v>1397</v>
       </c>
-      <c r="D97" s="21" t="s">
+      <c r="D97" s="19" t="s">
         <v>1398</v>
       </c>
-      <c r="E97" s="9"/>
-      <c r="F97" s="3" t="s">
+      <c r="E97" s="19"/>
+      <c r="F97" s="19" t="s">
         <v>1399</v>
       </c>
-      <c r="G97" s="3"/>
-      <c r="H97" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8">
-      <c r="A98" s="21" t="s">
+      <c r="G97" s="19"/>
+      <c r="H97" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" ht="21">
+      <c r="A98" s="19" t="s">
         <v>1226</v>
       </c>
-      <c r="B98" s="21" t="s">
+      <c r="B98" s="19" t="s">
         <v>1227</v>
       </c>
-      <c r="C98" s="21" t="s">
+      <c r="C98" s="19" t="s">
         <v>1400</v>
       </c>
-      <c r="D98" s="21" t="s">
+      <c r="D98" s="19" t="s">
         <v>1401</v>
       </c>
-      <c r="E98" s="9"/>
-      <c r="F98" s="3" t="s">
+      <c r="E98" s="19"/>
+      <c r="F98" s="19" t="s">
         <v>1402</v>
       </c>
-      <c r="G98" s="3"/>
-      <c r="H98" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8">
-      <c r="A99" s="21" t="s">
+      <c r="G98" s="19"/>
+      <c r="H98" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" ht="21">
+      <c r="A99" s="19" t="s">
         <v>1226</v>
       </c>
-      <c r="B99" s="21" t="s">
+      <c r="B99" s="19" t="s">
         <v>1227</v>
       </c>
-      <c r="C99" s="21" t="s">
+      <c r="C99" s="19" t="s">
         <v>1403</v>
       </c>
-      <c r="D99" s="21" t="s">
+      <c r="D99" s="19" t="s">
         <v>1404</v>
       </c>
-      <c r="E99" s="9"/>
-      <c r="F99" s="3" t="s">
+      <c r="E99" s="19"/>
+      <c r="F99" s="19" t="s">
         <v>1405</v>
       </c>
-      <c r="G99" s="3"/>
-      <c r="H99" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8">
-      <c r="A100" s="21" t="s">
+      <c r="G99" s="19"/>
+      <c r="H99" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" ht="21">
+      <c r="A100" s="19" t="s">
         <v>1226</v>
       </c>
-      <c r="B100" s="21" t="s">
+      <c r="B100" s="19" t="s">
         <v>1227</v>
       </c>
-      <c r="C100" s="21" t="s">
+      <c r="C100" s="19" t="s">
         <v>1406</v>
       </c>
-      <c r="D100" s="21" t="s">
+      <c r="D100" s="19" t="s">
         <v>1407</v>
       </c>
-      <c r="E100" s="9"/>
-      <c r="F100" s="3" t="s">
+      <c r="E100" s="19"/>
+      <c r="F100" s="19" t="s">
         <v>1408</v>
       </c>
-      <c r="G100" s="3"/>
-      <c r="H100" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8">
-      <c r="A101" s="21" t="s">
+      <c r="G100" s="19"/>
+      <c r="H100" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" ht="21">
+      <c r="A101" s="19" t="s">
         <v>1110</v>
       </c>
-      <c r="B101" s="21" t="s">
+      <c r="B101" s="19" t="s">
         <v>1111</v>
       </c>
-      <c r="C101" s="21" t="s">
+      <c r="C101" s="19" t="s">
         <v>1409</v>
       </c>
-      <c r="D101" s="21" t="s">
+      <c r="D101" s="19" t="s">
         <v>1410</v>
       </c>
-      <c r="E101" s="9"/>
-      <c r="F101" s="3" t="s">
+      <c r="E101" s="19"/>
+      <c r="F101" s="19" t="s">
         <v>1285</v>
       </c>
-      <c r="G101" s="3"/>
-      <c r="H101" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="102" spans="1:8">
-      <c r="A102" s="21" t="s">
+      <c r="G101" s="19"/>
+      <c r="H101" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" ht="21">
+      <c r="A102" s="19" t="s">
         <v>1110</v>
       </c>
-      <c r="B102" s="21" t="s">
+      <c r="B102" s="19" t="s">
         <v>1111</v>
       </c>
-      <c r="C102" s="21" t="s">
+      <c r="C102" s="19" t="s">
         <v>1411</v>
       </c>
-      <c r="D102" s="21" t="s">
+      <c r="D102" s="19" t="s">
         <v>1412</v>
       </c>
-      <c r="E102" s="9"/>
-      <c r="F102" s="3" t="s">
+      <c r="E102" s="19"/>
+      <c r="F102" s="19" t="s">
         <v>1413</v>
       </c>
-      <c r="G102" s="3"/>
-      <c r="H102" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="103" spans="1:8">
-      <c r="A103" s="21" t="s">
+      <c r="G102" s="19"/>
+      <c r="H102" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" ht="21">
+      <c r="A103" s="19" t="s">
         <v>1110</v>
       </c>
-      <c r="B103" s="21" t="s">
+      <c r="B103" s="19" t="s">
         <v>1111</v>
       </c>
-      <c r="C103" s="21" t="s">
+      <c r="C103" s="19" t="s">
         <v>1414</v>
       </c>
-      <c r="D103" s="21" t="s">
+      <c r="D103" s="19" t="s">
         <v>1415</v>
       </c>
-      <c r="E103" s="9"/>
-      <c r="F103" s="3" t="s">
+      <c r="E103" s="19"/>
+      <c r="F103" s="19" t="s">
         <v>1285</v>
       </c>
-      <c r="G103" s="3"/>
-      <c r="H103" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="104" spans="1:8">
-      <c r="A104" s="21" t="s">
+      <c r="G103" s="19"/>
+      <c r="H103" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" ht="21">
+      <c r="A104" s="19" t="s">
         <v>1110</v>
       </c>
-      <c r="B104" s="21" t="s">
+      <c r="B104" s="19" t="s">
         <v>1111</v>
       </c>
-      <c r="C104" s="21" t="s">
+      <c r="C104" s="19" t="s">
         <v>1416</v>
       </c>
-      <c r="D104" s="21" t="s">
+      <c r="D104" s="19" t="s">
         <v>1417</v>
       </c>
-      <c r="E104" s="9"/>
-      <c r="F104" s="3" t="s">
+      <c r="E104" s="19"/>
+      <c r="F104" s="19" t="s">
         <v>1418</v>
       </c>
-      <c r="G104" s="3"/>
-      <c r="H104" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="105" spans="1:8">
-      <c r="A105" s="21" t="s">
+      <c r="G104" s="19"/>
+      <c r="H104" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" ht="21">
+      <c r="A105" s="19" t="s">
         <v>1110</v>
       </c>
-      <c r="B105" s="21" t="s">
+      <c r="B105" s="19" t="s">
         <v>1111</v>
       </c>
-      <c r="C105" s="21" t="s">
+      <c r="C105" s="19" t="s">
         <v>1419</v>
       </c>
-      <c r="D105" s="21" t="s">
+      <c r="D105" s="19" t="s">
         <v>1420</v>
       </c>
-      <c r="E105" s="9"/>
-      <c r="F105" s="3" t="s">
+      <c r="E105" s="19"/>
+      <c r="F105" s="19" t="s">
         <v>1421</v>
       </c>
-      <c r="G105" s="3"/>
-      <c r="H105" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="106" spans="1:8">
-      <c r="A106" s="21" t="s">
+      <c r="G105" s="19"/>
+      <c r="H105" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" ht="21">
+      <c r="A106" s="19" t="s">
         <v>1110</v>
       </c>
-      <c r="B106" s="21" t="s">
+      <c r="B106" s="19" t="s">
         <v>1111</v>
       </c>
-      <c r="C106" s="21" t="s">
+      <c r="C106" s="19" t="s">
         <v>1422</v>
       </c>
-      <c r="D106" s="21" t="s">
+      <c r="D106" s="19" t="s">
         <v>1423</v>
       </c>
-      <c r="E106" s="9"/>
-      <c r="F106" s="3" t="s">
+      <c r="E106" s="19"/>
+      <c r="F106" s="19" t="s">
         <v>1424</v>
       </c>
-      <c r="G106" s="3"/>
-      <c r="H106" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="107" spans="1:8">
-      <c r="A107" s="21" t="s">
+      <c r="G106" s="19"/>
+      <c r="H106" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" ht="21">
+      <c r="A107" s="19" t="s">
         <v>1110</v>
       </c>
-      <c r="B107" s="21" t="s">
+      <c r="B107" s="19" t="s">
         <v>1111</v>
       </c>
-      <c r="C107" s="21" t="s">
+      <c r="C107" s="19" t="s">
         <v>1425</v>
       </c>
-      <c r="D107" s="21" t="s">
+      <c r="D107" s="19" t="s">
         <v>1426</v>
       </c>
-      <c r="E107" s="9"/>
-      <c r="F107" s="3" t="s">
+      <c r="E107" s="19"/>
+      <c r="F107" s="19" t="s">
         <v>1427</v>
       </c>
-      <c r="G107" s="3"/>
-      <c r="H107" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="108" spans="1:8">
-      <c r="A108" s="21" t="s">
+      <c r="G107" s="19"/>
+      <c r="H107" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" ht="21">
+      <c r="A108" s="19" t="s">
         <v>1110</v>
       </c>
-      <c r="B108" s="21" t="s">
+      <c r="B108" s="19" t="s">
         <v>1111</v>
       </c>
-      <c r="C108" s="21" t="s">
+      <c r="C108" s="19" t="s">
         <v>1428</v>
       </c>
-      <c r="D108" s="21" t="s">
+      <c r="D108" s="19" t="s">
         <v>1429</v>
       </c>
-      <c r="E108" s="9"/>
-      <c r="F108" s="3" t="s">
+      <c r="E108" s="19"/>
+      <c r="F108" s="19" t="s">
         <v>1430</v>
       </c>
-      <c r="G108" s="3"/>
-      <c r="H108" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="109" spans="1:8">
-      <c r="A109" s="21" t="s">
+      <c r="G108" s="19"/>
+      <c r="H108" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" ht="21">
+      <c r="A109" s="19" t="s">
         <v>1110</v>
       </c>
-      <c r="B109" s="21" t="s">
+      <c r="B109" s="19" t="s">
         <v>1111</v>
       </c>
-      <c r="C109" s="21" t="s">
+      <c r="C109" s="19" t="s">
         <v>1431</v>
       </c>
-      <c r="D109" s="21" t="s">
+      <c r="D109" s="19" t="s">
         <v>1432</v>
       </c>
-      <c r="E109" s="9"/>
-      <c r="F109" s="3" t="s">
+      <c r="E109" s="19"/>
+      <c r="F109" s="19" t="s">
         <v>1433</v>
       </c>
-      <c r="G109" s="3"/>
-      <c r="H109" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="110" spans="1:8">
-      <c r="A110" s="21" t="s">
+      <c r="G109" s="19"/>
+      <c r="H109" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" ht="21">
+      <c r="A110" s="19" t="s">
         <v>1110</v>
       </c>
-      <c r="B110" s="21" t="s">
+      <c r="B110" s="19" t="s">
         <v>1111</v>
       </c>
-      <c r="C110" s="21" t="s">
+      <c r="C110" s="19" t="s">
         <v>1434</v>
       </c>
-      <c r="D110" s="21" t="s">
+      <c r="D110" s="19" t="s">
         <v>1435</v>
       </c>
-      <c r="E110" s="9"/>
-      <c r="F110" s="3" t="s">
+      <c r="E110" s="19"/>
+      <c r="F110" s="19" t="s">
         <v>1436</v>
       </c>
-      <c r="G110" s="3"/>
-      <c r="H110" s="3" t="s">
+      <c r="G110" s="19"/>
+      <c r="H110" s="19" t="s">
         <v>1267</v>
       </c>
     </row>
-    <row r="111" spans="1:8">
-      <c r="A111" s="21" t="s">
+    <row r="111" spans="1:8" ht="21">
+      <c r="A111" s="19" t="s">
         <v>1110</v>
       </c>
-      <c r="B111" s="21" t="s">
+      <c r="B111" s="19" t="s">
         <v>1111</v>
       </c>
-      <c r="C111" s="21" t="s">
+      <c r="C111" s="19" t="s">
         <v>1437</v>
       </c>
-      <c r="D111" s="21" t="s">
+      <c r="D111" s="19" t="s">
         <v>1438</v>
       </c>
-      <c r="E111" s="9"/>
-      <c r="F111" s="3" t="s">
+      <c r="E111" s="19"/>
+      <c r="F111" s="19" t="s">
         <v>1439</v>
       </c>
-      <c r="G111" s="3"/>
-      <c r="H111" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="112" spans="1:8">
-      <c r="A112" s="21" t="s">
+      <c r="G111" s="19"/>
+      <c r="H111" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" ht="21">
+      <c r="A112" s="19" t="s">
         <v>1110</v>
       </c>
-      <c r="B112" s="21" t="s">
+      <c r="B112" s="19" t="s">
         <v>1111</v>
       </c>
-      <c r="C112" s="21" t="s">
+      <c r="C112" s="19" t="s">
         <v>1440</v>
       </c>
-      <c r="D112" s="21" t="s">
+      <c r="D112" s="19" t="s">
         <v>1441</v>
       </c>
-      <c r="E112" s="9"/>
-      <c r="F112" s="3" t="s">
+      <c r="E112" s="19"/>
+      <c r="F112" s="19" t="s">
         <v>1442</v>
       </c>
-      <c r="G112" s="3"/>
-      <c r="H112" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="113" spans="1:8">
-      <c r="A113" s="21" t="s">
+      <c r="G112" s="19"/>
+      <c r="H112" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" ht="21">
+      <c r="A113" s="19" t="s">
         <v>1110</v>
       </c>
-      <c r="B113" s="21" t="s">
+      <c r="B113" s="19" t="s">
         <v>1111</v>
       </c>
-      <c r="C113" s="21" t="s">
+      <c r="C113" s="19" t="s">
         <v>1443</v>
       </c>
-      <c r="D113" s="21" t="s">
+      <c r="D113" s="19" t="s">
         <v>1444</v>
       </c>
-      <c r="E113" s="9"/>
-      <c r="F113" s="3" t="s">
+      <c r="E113" s="19"/>
+      <c r="F113" s="19" t="s">
         <v>1285</v>
       </c>
-      <c r="G113" s="3"/>
-      <c r="H113" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="114" spans="1:8">
-      <c r="A114" s="21" t="s">
+      <c r="G113" s="19"/>
+      <c r="H113" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" ht="21">
+      <c r="A114" s="19" t="s">
         <v>1110</v>
       </c>
-      <c r="B114" s="21" t="s">
+      <c r="B114" s="19" t="s">
         <v>1111</v>
       </c>
-      <c r="C114" s="21" t="s">
+      <c r="C114" s="19" t="s">
         <v>1445</v>
       </c>
-      <c r="D114" s="21" t="s">
+      <c r="D114" s="19" t="s">
         <v>1446</v>
       </c>
-      <c r="E114" s="9"/>
-      <c r="F114" s="3" t="s">
+      <c r="E114" s="19"/>
+      <c r="F114" s="19" t="s">
         <v>1447</v>
       </c>
-      <c r="G114" s="3"/>
-      <c r="H114" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="115" spans="1:8">
-      <c r="A115" s="21" t="s">
+      <c r="G114" s="19"/>
+      <c r="H114" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" ht="21">
+      <c r="A115" s="19" t="s">
         <v>1110</v>
       </c>
-      <c r="B115" s="21" t="s">
+      <c r="B115" s="19" t="s">
         <v>1111</v>
       </c>
-      <c r="C115" s="21" t="s">
+      <c r="C115" s="19" t="s">
         <v>1448</v>
       </c>
-      <c r="D115" s="21" t="s">
+      <c r="D115" s="19" t="s">
         <v>1449</v>
       </c>
-      <c r="E115" s="9"/>
-      <c r="F115" s="3" t="s">
+      <c r="E115" s="19"/>
+      <c r="F115" s="19" t="s">
         <v>1450</v>
       </c>
-      <c r="G115" s="3"/>
-      <c r="H115" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="116" spans="1:8">
-      <c r="A116" s="21" t="s">
+      <c r="G115" s="19"/>
+      <c r="H115" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" ht="21">
+      <c r="A116" s="19" t="s">
         <v>1110</v>
       </c>
-      <c r="B116" s="21" t="s">
+      <c r="B116" s="19" t="s">
         <v>1111</v>
       </c>
-      <c r="C116" s="21" t="s">
+      <c r="C116" s="19" t="s">
         <v>1451</v>
       </c>
-      <c r="D116" s="21" t="s">
+      <c r="D116" s="19" t="s">
         <v>1452</v>
       </c>
-      <c r="E116" s="9"/>
-      <c r="F116" s="3" t="s">
+      <c r="E116" s="19"/>
+      <c r="F116" s="19" t="s">
         <v>1285</v>
       </c>
-      <c r="G116" s="3"/>
-      <c r="H116" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="117" spans="1:8">
-      <c r="A117" s="21" t="s">
+      <c r="G116" s="19"/>
+      <c r="H116" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" ht="21">
+      <c r="A117" s="19" t="s">
         <v>1110</v>
       </c>
-      <c r="B117" s="21" t="s">
+      <c r="B117" s="19" t="s">
         <v>1111</v>
       </c>
-      <c r="C117" s="21" t="s">
+      <c r="C117" s="19" t="s">
         <v>1275</v>
       </c>
-      <c r="D117" s="21" t="s">
+      <c r="D117" s="19" t="s">
         <v>1453</v>
       </c>
-      <c r="E117" s="9"/>
-      <c r="F117" s="3" t="s">
+      <c r="E117" s="19"/>
+      <c r="F117" s="19" t="s">
         <v>1454</v>
       </c>
-      <c r="G117" s="3" t="s">
+      <c r="G117" s="19" t="s">
         <v>794</v>
       </c>
-      <c r="H117" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="118" spans="1:8">
-      <c r="A118" s="21" t="s">
+      <c r="H117" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" ht="21">
+      <c r="A118" s="19" t="s">
         <v>1110</v>
       </c>
-      <c r="B118" s="21" t="s">
+      <c r="B118" s="19" t="s">
         <v>1111</v>
       </c>
-      <c r="C118" s="21" t="s">
+      <c r="C118" s="19" t="s">
         <v>1455</v>
       </c>
-      <c r="D118" s="21" t="s">
+      <c r="D118" s="19" t="s">
         <v>1456</v>
       </c>
-      <c r="E118" s="9"/>
-      <c r="F118" s="3" t="s">
+      <c r="E118" s="19"/>
+      <c r="F118" s="19" t="s">
         <v>1457</v>
       </c>
-      <c r="G118" s="3" t="s">
+      <c r="G118" s="19" t="s">
         <v>1458</v>
       </c>
-      <c r="H118" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="119" spans="1:8">
-      <c r="A119" s="21" t="s">
+      <c r="H118" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" ht="21">
+      <c r="A119" s="19" t="s">
         <v>1110</v>
       </c>
-      <c r="B119" s="21" t="s">
+      <c r="B119" s="19" t="s">
         <v>1111</v>
       </c>
-      <c r="C119" s="21" t="s">
+      <c r="C119" s="19" t="s">
         <v>1459</v>
       </c>
-      <c r="D119" s="21" t="s">
+      <c r="D119" s="19" t="s">
         <v>1460</v>
       </c>
-      <c r="E119" s="9"/>
-      <c r="F119" s="3" t="s">
+      <c r="E119" s="19"/>
+      <c r="F119" s="19" t="s">
         <v>1285</v>
       </c>
-      <c r="G119" s="3"/>
-      <c r="H119" s="3" t="s">
+      <c r="G119" s="19"/>
+      <c r="H119" s="19" t="s">
         <v>36</v>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30527"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://singerlk-my.sharepoint.com/personal/dihank_singersl_com/Documents/Desktop/DIHAN/cr dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="648" documentId="11_5847038500C079F1E35F4C8C432471BF012A7624" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1A32CB5A-02BA-4DC4-AD8C-20BACA411EE6}"/>
+  <xr:revisionPtr revIDLastSave="677" documentId="11_5847038500C079F1E35F4C8C432471BF012A7624" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7BF559D9-7E3F-4343-B036-6447644B8FDF}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4484,12 +4484,19 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4611,12 +4618,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
@@ -4640,24 +4647,27 @@
     <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="14" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -8586,7 +8596,7 @@
         <v>409</v>
       </c>
       <c r="X54" s="3" t="s">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="Y54" s="3" t="s">
         <v>46</v>
@@ -10032,7 +10042,7 @@
         <v>556</v>
       </c>
       <c r="X79" s="3" t="s">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="Y79" s="3" t="s">
         <v>46</v>
@@ -11507,7 +11517,7 @@
         <v>36</v>
       </c>
       <c r="Y106" s="9" t="s">
-        <v>242</v>
+        <v>211</v>
       </c>
       <c r="Z106" s="9"/>
     </row>
@@ -11818,7 +11828,7 @@
       <c r="V112" s="3"/>
       <c r="W112" s="9"/>
       <c r="X112" s="3" t="s">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="Y112" s="9" t="s">
         <v>242</v>
@@ -12916,7 +12926,7 @@
       <c r="V133" s="9"/>
       <c r="W133" s="9"/>
       <c r="X133" s="10" t="s">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="Y133" s="9" t="s">
         <v>242</v>
@@ -13072,7 +13082,7 @@
       <c r="V136" s="9"/>
       <c r="W136" s="9"/>
       <c r="X136" s="10" t="s">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="Y136" s="9" t="s">
         <v>242</v>
@@ -14480,8 +14490,8 @@
       <c r="X163" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="Y163" s="16" t="s">
-        <v>242</v>
+      <c r="Y163" s="24" t="s">
+        <v>211</v>
       </c>
       <c r="Z163" s="9"/>
     </row>
@@ -14634,7 +14644,7 @@
       <c r="V166" s="9"/>
       <c r="W166" s="9"/>
       <c r="X166" s="10" t="s">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="Y166" s="16" t="s">
         <v>242</v>
@@ -15000,8 +15010,8 @@
       <c r="X173" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="Y173" s="23" t="s">
-        <v>794</v>
+      <c r="Y173" s="24" t="s">
+        <v>98</v>
       </c>
       <c r="Z173" s="9"/>
     </row>
@@ -15157,7 +15167,7 @@
         <v>36</v>
       </c>
       <c r="Y176" s="9" t="s">
-        <v>211</v>
+        <v>46</v>
       </c>
       <c r="Z176" s="9"/>
     </row>
@@ -15261,7 +15271,7 @@
         <v>36</v>
       </c>
       <c r="Y178" s="9" t="s">
-        <v>794</v>
+        <v>1463</v>
       </c>
       <c r="Z178" s="9"/>
     </row>
@@ -15624,8 +15634,8 @@
       <c r="X185" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="Y185" s="23" t="s">
-        <v>211</v>
+      <c r="Y185" s="24" t="s">
+        <v>46</v>
       </c>
       <c r="Z185" s="9"/>
     </row>
@@ -15832,8 +15842,8 @@
       <c r="X189" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="Y189" s="16" t="s">
-        <v>242</v>
+      <c r="Y189" s="24" t="s">
+        <v>211</v>
       </c>
       <c r="Z189" s="9"/>
     </row>
@@ -16090,10 +16100,10 @@
       <c r="V194" s="9"/>
       <c r="W194" s="9"/>
       <c r="X194" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y194" s="16" t="s">
-        <v>242</v>
+        <v>70</v>
+      </c>
+      <c r="Y194" s="24" t="s">
+        <v>211</v>
       </c>
       <c r="Z194" s="9"/>
     </row>
@@ -16558,7 +16568,7 @@
       <c r="V203" s="9"/>
       <c r="W203" s="9"/>
       <c r="X203" s="10" t="s">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="Y203" s="22" t="s">
         <v>211</v>
@@ -16872,8 +16882,8 @@
       <c r="X209" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="Y209" s="23" t="s">
-        <v>794</v>
+      <c r="Y209" s="24" t="s">
+        <v>46</v>
       </c>
       <c r="Z209" s="9"/>
     </row>
@@ -17080,8 +17090,8 @@
       <c r="X213" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="Y213" s="16" t="s">
-        <v>242</v>
+      <c r="Y213" s="24" t="s">
+        <v>211</v>
       </c>
       <c r="Z213" s="9"/>
     </row>
@@ -17444,8 +17454,8 @@
       <c r="X220" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="Y220" s="22" t="s">
-        <v>211</v>
+      <c r="Y220" s="24" t="s">
+        <v>1463</v>
       </c>
       <c r="Z220" s="9"/>
     </row>
